--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46079.01041666666</v>
+        <v>46094.01041666666</v>
       </c>
       <c r="B2">
-        <v>920.524</v>
+        <v>182.436</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46079.02083333334</v>
+        <v>46094.02083333334</v>
       </c>
       <c r="B3">
-        <v>931.064</v>
+        <v>186.989</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46079.03125</v>
+        <v>46094.03125</v>
       </c>
       <c r="B4">
-        <v>945.496</v>
+        <v>190.398</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46079.04166666666</v>
+        <v>46094.04166666666</v>
       </c>
       <c r="B5">
-        <v>949.593</v>
+        <v>193.212</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46079.05208333334</v>
+        <v>46094.05208333334</v>
       </c>
       <c r="B6">
-        <v>970.5359999999999</v>
+        <v>204.769</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46079.0625</v>
+        <v>46094.0625</v>
       </c>
       <c r="B7">
-        <v>997.542</v>
+        <v>209.053</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46079.07291666666</v>
+        <v>46094.07291666666</v>
       </c>
       <c r="B8">
-        <v>1021.302</v>
+        <v>213.468</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46079.08333333334</v>
+        <v>46094.08333333334</v>
       </c>
       <c r="B9">
-        <v>1046.905</v>
+        <v>218.152</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46079.09375</v>
+        <v>46094.09375</v>
       </c>
       <c r="B10">
-        <v>1077.073</v>
+        <v>220.481</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46079.10416666666</v>
+        <v>46094.10416666666</v>
       </c>
       <c r="B11">
-        <v>1101.532</v>
+        <v>245.32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46079.11458333334</v>
+        <v>46094.11458333334</v>
       </c>
       <c r="B12">
-        <v>1132.267</v>
+        <v>252.074</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46079.125</v>
+        <v>46094.125</v>
       </c>
       <c r="B13">
-        <v>1156.886</v>
+        <v>259.715</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46079.13541666666</v>
+        <v>46094.13541666666</v>
       </c>
       <c r="B14">
-        <v>1217.117</v>
+        <v>281.152</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46079.14583333334</v>
+        <v>46094.14583333334</v>
       </c>
       <c r="B15">
-        <v>1240.529</v>
+        <v>292.399</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46079.15625</v>
+        <v>46094.15625</v>
       </c>
       <c r="B16">
-        <v>1264.845</v>
+        <v>299.506</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46079.16666666666</v>
+        <v>46094.16666666666</v>
       </c>
       <c r="B17">
-        <v>1285.573</v>
+        <v>303.727</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46079.17708333334</v>
+        <v>46094.17708333334</v>
       </c>
       <c r="B18">
-        <v>1354.253</v>
+        <v>332.798</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46079.1875</v>
+        <v>46094.1875</v>
       </c>
       <c r="B19">
-        <v>1377.423</v>
+        <v>335.128</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46079.19791666666</v>
+        <v>46094.19791666666</v>
       </c>
       <c r="B20">
-        <v>1400.985</v>
+        <v>337.679</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46079.20833333334</v>
+        <v>46094.20833333334</v>
       </c>
       <c r="B21">
-        <v>1432.609</v>
+        <v>336.01</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46079.21875</v>
+        <v>46094.21875</v>
       </c>
       <c r="B22">
-        <v>1502.359</v>
+        <v>353.783</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46079.22916666666</v>
+        <v>46094.22916666666</v>
       </c>
       <c r="B23">
-        <v>1541.065</v>
+        <v>365.636</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46079.23958333334</v>
+        <v>46094.23958333334</v>
       </c>
       <c r="B24">
-        <v>1588.608</v>
+        <v>367.822</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46079.25</v>
+        <v>46094.25</v>
       </c>
       <c r="B25">
-        <v>1623.904</v>
+        <v>372.627</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46079.26041666666</v>
+        <v>46094.26041666666</v>
       </c>
       <c r="B26">
-        <v>1640.748</v>
+        <v>350.281</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46079.27083333334</v>
+        <v>46094.27083333334</v>
       </c>
       <c r="B27">
-        <v>1661.487</v>
+        <v>353.634</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46079.28125</v>
+        <v>46094.28125</v>
       </c>
       <c r="B28">
-        <v>1686.489</v>
+        <v>352.326</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46079.29166666666</v>
+        <v>46094.29166666666</v>
       </c>
       <c r="B29">
-        <v>1707.676</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46079.30208333334</v>
+        <v>46094.30208333334</v>
       </c>
       <c r="B30">
-        <v>1714.817</v>
+        <v>333.488</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46079.3125</v>
+        <v>46094.3125</v>
       </c>
       <c r="B31">
-        <v>1709.694</v>
+        <v>315.239</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46079.32291666666</v>
+        <v>46094.32291666666</v>
       </c>
       <c r="B32">
-        <v>1720.588</v>
+        <v>311.112</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46079.33333333334</v>
+        <v>46094.33333333334</v>
       </c>
       <c r="B33">
-        <v>1715.12</v>
+        <v>296.144</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46079.34375</v>
+        <v>46094.34375</v>
       </c>
       <c r="B34">
-        <v>1668.335</v>
+        <v>352.736</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46079.35416666666</v>
+        <v>46094.35416666666</v>
       </c>
       <c r="B35">
-        <v>1668.126</v>
+        <v>334.458</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46079.36458333334</v>
+        <v>46094.36458333334</v>
       </c>
       <c r="B36">
-        <v>1652.964</v>
+        <v>312.659</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46079.375</v>
+        <v>46094.375</v>
       </c>
       <c r="B37">
-        <v>1649.883</v>
+        <v>293.556</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46079.38541666666</v>
+        <v>46094.38541666666</v>
       </c>
       <c r="B38">
-        <v>1832.228</v>
+        <v>267.896</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46079.39583333334</v>
+        <v>46094.39583333334</v>
       </c>
       <c r="B39">
-        <v>1812.022</v>
+        <v>267.081</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46079.40625</v>
+        <v>46094.40625</v>
       </c>
       <c r="B40">
-        <v>1787.707</v>
+        <v>265.93</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46079.41666666666</v>
+        <v>46094.41666666666</v>
       </c>
       <c r="B41">
-        <v>1765.237</v>
+        <v>265.037</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46079.42708333334</v>
+        <v>46094.42708333334</v>
       </c>
       <c r="B42">
-        <v>1755.211</v>
+        <v>267.003</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46079.4375</v>
+        <v>46094.4375</v>
       </c>
       <c r="B43">
-        <v>1722.595</v>
+        <v>273.659</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46079.44791666666</v>
+        <v>46094.44791666666</v>
       </c>
       <c r="B44">
-        <v>1689.932</v>
+        <v>283.963</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46079.45833333334</v>
+        <v>46094.45833333334</v>
       </c>
       <c r="B45">
-        <v>1656.253</v>
+        <v>290.565</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46079.46875</v>
+        <v>46094.46875</v>
       </c>
       <c r="B46">
-        <v>1625.553</v>
+        <v>300.388</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46079.47916666666</v>
+        <v>46094.47916666666</v>
       </c>
       <c r="B47">
-        <v>1618.561</v>
+        <v>307.036</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46079.48958333334</v>
+        <v>46094.48958333334</v>
       </c>
       <c r="B48">
-        <v>1611.877</v>
+        <v>314.525</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46079.5</v>
+        <v>46094.5</v>
       </c>
       <c r="B49">
-        <v>1605.209</v>
+        <v>322.696</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46079.51041666666</v>
+        <v>46094.51041666666</v>
       </c>
       <c r="B50">
-        <v>1617.489</v>
+        <v>331.373</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46079.52083333334</v>
+        <v>46094.52083333334</v>
       </c>
       <c r="B51">
-        <v>1624.588</v>
+        <v>342.06</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46079.53125</v>
+        <v>46094.53125</v>
       </c>
       <c r="B52">
-        <v>1631.367</v>
+        <v>350.969</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46079.54166666666</v>
+        <v>46094.54166666666</v>
       </c>
       <c r="B53">
-        <v>1638.768</v>
+        <v>357.787</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46079.55208333334</v>
+        <v>46094.55208333334</v>
       </c>
       <c r="B54">
-        <v>1651.801</v>
+        <v>367.339</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46079.5625</v>
+        <v>46094.5625</v>
       </c>
       <c r="B55">
-        <v>1659.213</v>
+        <v>374.498</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46079.57291666666</v>
+        <v>46094.57291666666</v>
       </c>
       <c r="B56">
-        <v>1666.19</v>
+        <v>384.824</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46079.58333333334</v>
+        <v>46094.58333333334</v>
       </c>
       <c r="B57">
-        <v>1673.011</v>
+        <v>395.169</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46079.59375</v>
+        <v>46094.59375</v>
       </c>
       <c r="B58">
-        <v>1709.548</v>
+        <v>411.268</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46079.60416666666</v>
+        <v>46094.60416666666</v>
       </c>
       <c r="B59">
-        <v>1708.725</v>
+        <v>419.463</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46079.61458333334</v>
+        <v>46094.61458333334</v>
       </c>
       <c r="B60">
-        <v>1706.367</v>
+        <v>427.417</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46079.625</v>
+        <v>46094.625</v>
       </c>
       <c r="B61">
-        <v>1703.002</v>
+        <v>436.416</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46079.63541666666</v>
+        <v>46094.63541666666</v>
       </c>
       <c r="B62">
-        <v>1680.72</v>
+        <v>406.384</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46079.64583333334</v>
+        <v>46094.64583333334</v>
       </c>
       <c r="B63">
-        <v>1645.357</v>
+        <v>419.494</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46079.65625</v>
+        <v>46094.65625</v>
       </c>
       <c r="B64">
-        <v>1609.523</v>
+        <v>434.199</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46079.66666666666</v>
+        <v>46094.66666666666</v>
       </c>
       <c r="B65">
-        <v>1581.221</v>
+        <v>449.864</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46079.67708333334</v>
+        <v>46094.67708333334</v>
       </c>
       <c r="B66">
-        <v>1366.736</v>
+        <v>479.821</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46079.6875</v>
+        <v>46094.6875</v>
       </c>
       <c r="B67">
-        <v>1310.14</v>
+        <v>504.967</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46079.69791666666</v>
+        <v>46094.69791666666</v>
       </c>
       <c r="B68">
-        <v>1249.842</v>
+        <v>529.746</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46079.70833333334</v>
+        <v>46094.70833333334</v>
       </c>
       <c r="B69">
-        <v>1193.69</v>
+        <v>557.847</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46079.71875</v>
+        <v>46094.71875</v>
       </c>
       <c r="B70">
-        <v>1120.788</v>
+        <v>527.186</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46079.72916666666</v>
+        <v>46094.72916666666</v>
       </c>
       <c r="B71">
-        <v>1093.164</v>
+        <v>560.638</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46079.73958333334</v>
+        <v>46094.73958333334</v>
       </c>
       <c r="B72">
-        <v>1064.168</v>
+        <v>594.8390000000001</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46079.75</v>
+        <v>46094.75</v>
       </c>
       <c r="B73">
-        <v>1038.52</v>
+        <v>626.718</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46079.76041666666</v>
+        <v>46094.76041666666</v>
       </c>
       <c r="B74">
-        <v>1004.053</v>
+        <v>657.622</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46079.77083333334</v>
+        <v>46094.77083333334</v>
       </c>
       <c r="B75">
-        <v>989.991</v>
+        <v>671.7910000000001</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46079.78125</v>
+        <v>46094.78125</v>
       </c>
       <c r="B76">
-        <v>977.901</v>
+        <v>686.817</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46079.79166666666</v>
+        <v>46094.79166666666</v>
       </c>
       <c r="B77">
-        <v>964.999</v>
+        <v>700.268</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46079.80208333334</v>
+        <v>46094.80208333334</v>
       </c>
       <c r="B78">
-        <v>976.068</v>
+        <v>705.28</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46079.8125</v>
+        <v>46094.8125</v>
       </c>
       <c r="B79">
-        <v>962.5700000000001</v>
+        <v>691.26</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46079.82291666666</v>
+        <v>46094.82291666666</v>
       </c>
       <c r="B80">
-        <v>951.317</v>
+        <v>676.254</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46079.83333333334</v>
+        <v>46094.83333333334</v>
       </c>
       <c r="B81">
-        <v>940.407</v>
+        <v>662.609</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46079.84375</v>
+        <v>46094.84375</v>
       </c>
       <c r="B82">
-        <v>915.997</v>
+        <v>632.788</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46079.85416666666</v>
+        <v>46094.85416666666</v>
       </c>
       <c r="B83">
-        <v>903.3</v>
+        <v>604.973</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46079.86458333334</v>
+        <v>46094.86458333334</v>
       </c>
       <c r="B84">
-        <v>892.0599999999999</v>
+        <v>577.023</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46079.875</v>
+        <v>46094.875</v>
       </c>
       <c r="B85">
-        <v>879.619</v>
+        <v>549.019</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46079.88541666666</v>
+        <v>46094.88541666666</v>
       </c>
       <c r="B86">
-        <v>864.264</v>
+        <v>515.9349999999999</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46079.89583333334</v>
+        <v>46094.89583333334</v>
       </c>
       <c r="B87">
-        <v>852.547</v>
+        <v>490.188</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46079.90625</v>
+        <v>46094.90625</v>
       </c>
       <c r="B88">
-        <v>841.578</v>
+        <v>465.018</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46079.91666666666</v>
+        <v>46094.91666666666</v>
       </c>
       <c r="B89">
-        <v>828.5309999999999</v>
+        <v>439.68</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46079.92708333334</v>
+        <v>46094.92708333334</v>
       </c>
       <c r="B90">
-        <v>805.571</v>
+        <v>412.635</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46079.9375</v>
+        <v>46094.9375</v>
       </c>
       <c r="B91">
-        <v>790.02</v>
+        <v>396.526</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46079.94791666666</v>
+        <v>46094.94791666666</v>
       </c>
       <c r="B92">
-        <v>774.717</v>
+        <v>380.483</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46079.95833333334</v>
+        <v>46094.95833333334</v>
       </c>
       <c r="B93">
-        <v>759.293</v>
+        <v>365.356</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46079.96875</v>
+        <v>46094.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46079.97916666666</v>
+        <v>46094.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46079.98958333334</v>
+        <v>46094.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46080</v>
+        <v>46095</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46094.01041666666</v>
+        <v>46107.01041666666</v>
       </c>
       <c r="B2">
-        <v>182.436</v>
+        <v>612.924</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46094.02083333334</v>
+        <v>46107.02083333334</v>
       </c>
       <c r="B3">
-        <v>186.989</v>
+        <v>604.886</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46094.03125</v>
+        <v>46107.03125</v>
       </c>
       <c r="B4">
-        <v>190.398</v>
+        <v>596.915</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46094.04166666666</v>
+        <v>46107.04166666666</v>
       </c>
       <c r="B5">
-        <v>193.212</v>
+        <v>588.1319999999999</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46094.05208333334</v>
+        <v>46107.05208333334</v>
       </c>
       <c r="B6">
-        <v>204.769</v>
+        <v>573.1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46094.0625</v>
+        <v>46107.0625</v>
       </c>
       <c r="B7">
-        <v>209.053</v>
+        <v>558.83</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46094.07291666666</v>
+        <v>46107.07291666666</v>
       </c>
       <c r="B8">
-        <v>213.468</v>
+        <v>515.771</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46094.08333333334</v>
+        <v>46107.08333333334</v>
       </c>
       <c r="B9">
-        <v>218.152</v>
+        <v>500.421</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46094.09375</v>
+        <v>46107.09375</v>
       </c>
       <c r="B10">
-        <v>220.481</v>
+        <v>483.99</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46094.10416666666</v>
+        <v>46107.10416666666</v>
       </c>
       <c r="B11">
-        <v>245.32</v>
+        <v>475.527</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46094.11458333334</v>
+        <v>46107.11458333334</v>
       </c>
       <c r="B12">
-        <v>252.074</v>
+        <v>467.288</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46094.125</v>
+        <v>46107.125</v>
       </c>
       <c r="B13">
-        <v>259.715</v>
+        <v>474.649</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46094.13541666666</v>
+        <v>46107.13541666666</v>
       </c>
       <c r="B14">
-        <v>281.152</v>
+        <v>475.584</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46094.14583333334</v>
+        <v>46107.14583333334</v>
       </c>
       <c r="B15">
-        <v>292.399</v>
+        <v>436.536</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46094.15625</v>
+        <v>46107.15625</v>
       </c>
       <c r="B16">
-        <v>299.506</v>
+        <v>460.419</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46094.16666666666</v>
+        <v>46107.16666666666</v>
       </c>
       <c r="B17">
-        <v>303.727</v>
+        <v>451.902</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46094.17708333334</v>
+        <v>46107.17708333334</v>
       </c>
       <c r="B18">
-        <v>332.798</v>
+        <v>468.267</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46094.1875</v>
+        <v>46107.1875</v>
       </c>
       <c r="B19">
-        <v>335.128</v>
+        <v>458.138</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46094.19791666666</v>
+        <v>46107.19791666666</v>
       </c>
       <c r="B20">
-        <v>337.679</v>
+        <v>448.863</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46094.20833333334</v>
+        <v>46107.20833333334</v>
       </c>
       <c r="B21">
-        <v>336.01</v>
+        <v>440.506</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46094.21875</v>
+        <v>46107.21875</v>
       </c>
       <c r="B22">
-        <v>353.783</v>
+        <v>427.736</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46094.22916666666</v>
+        <v>46107.22916666666</v>
       </c>
       <c r="B23">
-        <v>365.636</v>
+        <v>428.806</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46094.23958333334</v>
+        <v>46107.23958333334</v>
       </c>
       <c r="B24">
-        <v>367.822</v>
+        <v>424.886</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46094.25</v>
+        <v>46107.25</v>
       </c>
       <c r="B25">
-        <v>372.627</v>
+        <v>421.186</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46094.26041666666</v>
+        <v>46107.26041666666</v>
       </c>
       <c r="B26">
-        <v>350.281</v>
+        <v>390.986</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46094.27083333334</v>
+        <v>46107.27083333334</v>
       </c>
       <c r="B27">
-        <v>353.634</v>
+        <v>387.153</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46094.28125</v>
+        <v>46107.28125</v>
       </c>
       <c r="B28">
-        <v>352.326</v>
+        <v>385.34</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46094.29166666666</v>
+        <v>46107.29166666666</v>
       </c>
       <c r="B29">
-        <v>349</v>
+        <v>383.057</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46094.30208333334</v>
+        <v>46107.30208333334</v>
       </c>
       <c r="B30">
-        <v>333.488</v>
+        <v>396.008</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46094.3125</v>
+        <v>46107.3125</v>
       </c>
       <c r="B31">
-        <v>315.239</v>
+        <v>390.956</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46094.32291666666</v>
+        <v>46107.32291666666</v>
       </c>
       <c r="B32">
-        <v>311.112</v>
+        <v>385.578</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46094.33333333334</v>
+        <v>46107.33333333334</v>
       </c>
       <c r="B33">
-        <v>296.144</v>
+        <v>381.935</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46094.34375</v>
+        <v>46107.34375</v>
       </c>
       <c r="B34">
-        <v>352.736</v>
+        <v>398.335</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46094.35416666666</v>
+        <v>46107.35416666666</v>
       </c>
       <c r="B35">
-        <v>334.458</v>
+        <v>424.336</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46094.36458333334</v>
+        <v>46107.36458333334</v>
       </c>
       <c r="B36">
-        <v>312.659</v>
+        <v>450.86</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46094.375</v>
+        <v>46107.375</v>
       </c>
       <c r="B37">
-        <v>293.556</v>
+        <v>477.957</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46094.38541666666</v>
+        <v>46107.38541666666</v>
       </c>
       <c r="B38">
-        <v>267.896</v>
+        <v>527.635</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46094.39583333334</v>
+        <v>46107.39583333334</v>
       </c>
       <c r="B39">
-        <v>267.081</v>
+        <v>565.8099999999999</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46094.40625</v>
+        <v>46107.40625</v>
       </c>
       <c r="B40">
-        <v>265.93</v>
+        <v>605.367</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46094.41666666666</v>
+        <v>46107.41666666666</v>
       </c>
       <c r="B41">
-        <v>265.037</v>
+        <v>643.782</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46094.42708333334</v>
+        <v>46107.42708333334</v>
       </c>
       <c r="B42">
-        <v>267.003</v>
+        <v>686.043</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46094.4375</v>
+        <v>46107.4375</v>
       </c>
       <c r="B43">
-        <v>273.659</v>
+        <v>715.658</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46094.44791666666</v>
+        <v>46107.44791666666</v>
       </c>
       <c r="B44">
-        <v>283.963</v>
+        <v>746.902</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46094.45833333334</v>
+        <v>46107.45833333334</v>
       </c>
       <c r="B45">
-        <v>290.565</v>
+        <v>775.378</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46094.46875</v>
+        <v>46107.46875</v>
       </c>
       <c r="B46">
-        <v>300.388</v>
+        <v>803.016</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46094.47916666666</v>
+        <v>46107.47916666666</v>
       </c>
       <c r="B47">
-        <v>307.036</v>
+        <v>819.1849999999999</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46094.48958333334</v>
+        <v>46107.48958333334</v>
       </c>
       <c r="B48">
-        <v>314.525</v>
+        <v>836.769</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46094.5</v>
+        <v>46107.5</v>
       </c>
       <c r="B49">
-        <v>322.696</v>
+        <v>853.852</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46094.51041666666</v>
+        <v>46107.51041666666</v>
       </c>
       <c r="B50">
-        <v>331.373</v>
+        <v>846.442</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46094.52083333334</v>
+        <v>46107.52083333334</v>
       </c>
       <c r="B51">
-        <v>342.06</v>
+        <v>859.053</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46094.53125</v>
+        <v>46107.53125</v>
       </c>
       <c r="B52">
-        <v>350.969</v>
+        <v>871.553</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46094.54166666666</v>
+        <v>46107.54166666666</v>
       </c>
       <c r="B53">
-        <v>357.787</v>
+        <v>883.837</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46094.55208333334</v>
+        <v>46107.55208333334</v>
       </c>
       <c r="B54">
-        <v>367.339</v>
+        <v>915.248</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46094.5625</v>
+        <v>46107.5625</v>
       </c>
       <c r="B55">
-        <v>374.498</v>
+        <v>934.417</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46094.57291666666</v>
+        <v>46107.57291666666</v>
       </c>
       <c r="B56">
-        <v>384.824</v>
+        <v>950.341</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46094.58333333334</v>
+        <v>46107.58333333334</v>
       </c>
       <c r="B57">
-        <v>395.169</v>
+        <v>968.828</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46094.59375</v>
+        <v>46107.59375</v>
       </c>
       <c r="B58">
-        <v>411.268</v>
+        <v>974.8869999999999</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46094.60416666666</v>
+        <v>46107.60416666666</v>
       </c>
       <c r="B59">
-        <v>419.463</v>
+        <v>999.831</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46094.61458333334</v>
+        <v>46107.61458333334</v>
       </c>
       <c r="B60">
-        <v>427.417</v>
+        <v>1025.989</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46094.625</v>
+        <v>46107.625</v>
       </c>
       <c r="B61">
-        <v>436.416</v>
+        <v>1050.72</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46094.63541666666</v>
+        <v>46107.63541666666</v>
       </c>
       <c r="B62">
-        <v>406.384</v>
+        <v>1016.337</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46094.64583333334</v>
+        <v>46107.64583333334</v>
       </c>
       <c r="B63">
-        <v>419.494</v>
+        <v>1040.03</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46094.65625</v>
+        <v>46107.65625</v>
       </c>
       <c r="B64">
-        <v>434.199</v>
+        <v>1062.495</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46094.66666666666</v>
+        <v>46107.66666666666</v>
       </c>
       <c r="B65">
-        <v>449.864</v>
+        <v>1085.884</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46094.67708333334</v>
+        <v>46107.67708333334</v>
       </c>
       <c r="B66">
-        <v>479.821</v>
+        <v>1078.37</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46094.6875</v>
+        <v>46107.6875</v>
       </c>
       <c r="B67">
-        <v>504.967</v>
+        <v>1098.622</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46094.69791666666</v>
+        <v>46107.69791666666</v>
       </c>
       <c r="B68">
-        <v>529.746</v>
+        <v>1121.827</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46094.70833333334</v>
+        <v>46107.70833333334</v>
       </c>
       <c r="B69">
-        <v>557.847</v>
+        <v>1143.388</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46094.71875</v>
+        <v>46107.71875</v>
       </c>
       <c r="B70">
-        <v>527.186</v>
+        <v>1169.784</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46094.72916666666</v>
+        <v>46107.72916666666</v>
       </c>
       <c r="B71">
-        <v>560.638</v>
+        <v>1199.123</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46094.73958333334</v>
+        <v>46107.73958333334</v>
       </c>
       <c r="B72">
-        <v>594.8390000000001</v>
+        <v>1229.245</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46094.75</v>
+        <v>46107.75</v>
       </c>
       <c r="B73">
-        <v>626.718</v>
+        <v>1259.277</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46094.76041666666</v>
+        <v>46107.76041666666</v>
       </c>
       <c r="B74">
-        <v>657.622</v>
+        <v>1296.082</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46094.77083333334</v>
+        <v>46107.77083333334</v>
       </c>
       <c r="B75">
-        <v>671.7910000000001</v>
+        <v>1307.346</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46094.78125</v>
+        <v>46107.78125</v>
       </c>
       <c r="B76">
-        <v>686.817</v>
+        <v>1317.444</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46094.79166666666</v>
+        <v>46107.79166666666</v>
       </c>
       <c r="B77">
-        <v>700.268</v>
+        <v>1327.783</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46094.80208333334</v>
+        <v>46107.80208333334</v>
       </c>
       <c r="B78">
-        <v>705.28</v>
+        <v>1335.641</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46094.8125</v>
+        <v>46107.8125</v>
       </c>
       <c r="B79">
-        <v>691.26</v>
+        <v>1331.747</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46094.82291666666</v>
+        <v>46107.82291666666</v>
       </c>
       <c r="B80">
-        <v>676.254</v>
+        <v>1328.492</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46094.83333333334</v>
+        <v>46107.83333333334</v>
       </c>
       <c r="B81">
-        <v>662.609</v>
+        <v>1325.969</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46094.84375</v>
+        <v>46107.84375</v>
       </c>
       <c r="B82">
-        <v>632.788</v>
+        <v>1314.092</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46094.85416666666</v>
+        <v>46107.85416666666</v>
       </c>
       <c r="B83">
-        <v>604.973</v>
+        <v>1303.502</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46094.86458333334</v>
+        <v>46107.86458333334</v>
       </c>
       <c r="B84">
-        <v>577.023</v>
+        <v>1292.743</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46094.875</v>
+        <v>46107.875</v>
       </c>
       <c r="B85">
-        <v>549.019</v>
+        <v>1281.853</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46094.88541666666</v>
+        <v>46107.88541666666</v>
       </c>
       <c r="B86">
-        <v>515.9349999999999</v>
+        <v>1275.471</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46094.89583333334</v>
+        <v>46107.89583333334</v>
       </c>
       <c r="B87">
-        <v>490.188</v>
+        <v>1262.754</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46094.90625</v>
+        <v>46107.90625</v>
       </c>
       <c r="B88">
-        <v>465.018</v>
+        <v>1251.374</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46094.91666666666</v>
+        <v>46107.91666666666</v>
       </c>
       <c r="B89">
-        <v>439.68</v>
+        <v>1239.93</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46094.92708333334</v>
+        <v>46107.92708333334</v>
       </c>
       <c r="B90">
-        <v>412.635</v>
+        <v>1225.935</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46094.9375</v>
+        <v>46107.9375</v>
       </c>
       <c r="B91">
-        <v>396.526</v>
+        <v>1214.907</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46094.94791666666</v>
+        <v>46107.94791666666</v>
       </c>
       <c r="B92">
-        <v>380.483</v>
+        <v>1204.845</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46094.95833333334</v>
+        <v>46107.95833333334</v>
       </c>
       <c r="B93">
-        <v>365.356</v>
+        <v>1194.266</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46094.96875</v>
+        <v>46107.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46094.97916666666</v>
+        <v>46107.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46094.98958333334</v>
+        <v>46107.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46095</v>
+        <v>46108</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46107.01041666666</v>
+        <v>46108.01041666666</v>
       </c>
       <c r="B2">
-        <v>612.924</v>
+        <v>1016.396</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46107.02083333334</v>
+        <v>46108.02083333334</v>
       </c>
       <c r="B3">
-        <v>604.886</v>
+        <v>998.72</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46107.03125</v>
+        <v>46108.03125</v>
       </c>
       <c r="B4">
-        <v>596.915</v>
+        <v>980.487</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46107.04166666666</v>
+        <v>46108.04166666666</v>
       </c>
       <c r="B5">
-        <v>588.1319999999999</v>
+        <v>962.099</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46107.05208333334</v>
+        <v>46108.05208333334</v>
       </c>
       <c r="B6">
-        <v>573.1</v>
+        <v>940.331</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46107.0625</v>
+        <v>46108.0625</v>
       </c>
       <c r="B7">
-        <v>558.83</v>
+        <v>933.647</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46107.07291666666</v>
+        <v>46108.07291666666</v>
       </c>
       <c r="B8">
-        <v>515.771</v>
+        <v>928.147</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46107.08333333334</v>
+        <v>46108.08333333334</v>
       </c>
       <c r="B9">
-        <v>500.421</v>
+        <v>922.9829999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46107.09375</v>
+        <v>46108.09375</v>
       </c>
       <c r="B10">
-        <v>483.99</v>
+        <v>914.4059999999999</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46107.10416666666</v>
+        <v>46108.10416666666</v>
       </c>
       <c r="B11">
-        <v>475.527</v>
+        <v>906.4589999999999</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46107.11458333334</v>
+        <v>46108.11458333334</v>
       </c>
       <c r="B12">
-        <v>467.288</v>
+        <v>897.6</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46107.125</v>
+        <v>46108.125</v>
       </c>
       <c r="B13">
-        <v>474.649</v>
+        <v>889.276</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46107.13541666666</v>
+        <v>46108.13541666666</v>
       </c>
       <c r="B14">
-        <v>475.584</v>
+        <v>883.321</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46107.14583333334</v>
+        <v>46108.14583333334</v>
       </c>
       <c r="B15">
-        <v>436.536</v>
+        <v>883.217</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46107.15625</v>
+        <v>46108.15625</v>
       </c>
       <c r="B16">
-        <v>460.419</v>
+        <v>882.655</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46107.16666666666</v>
+        <v>46108.16666666666</v>
       </c>
       <c r="B17">
-        <v>451.902</v>
+        <v>884.51</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46107.17708333334</v>
+        <v>46108.17708333334</v>
       </c>
       <c r="B18">
-        <v>468.267</v>
+        <v>915.755</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46107.1875</v>
+        <v>46108.1875</v>
       </c>
       <c r="B19">
-        <v>458.138</v>
+        <v>925.0170000000001</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46107.19791666666</v>
+        <v>46108.19791666666</v>
       </c>
       <c r="B20">
-        <v>448.863</v>
+        <v>935.505</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46107.20833333334</v>
+        <v>46108.20833333334</v>
       </c>
       <c r="B21">
-        <v>440.506</v>
+        <v>945.02</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46107.21875</v>
+        <v>46108.21875</v>
       </c>
       <c r="B22">
-        <v>427.736</v>
+        <v>960.133</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46107.22916666666</v>
+        <v>46108.22916666666</v>
       </c>
       <c r="B23">
-        <v>428.806</v>
+        <v>973.886</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46107.23958333334</v>
+        <v>46108.23958333334</v>
       </c>
       <c r="B24">
-        <v>424.886</v>
+        <v>987.67</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46107.25</v>
+        <v>46108.25</v>
       </c>
       <c r="B25">
-        <v>421.186</v>
+        <v>1000.842</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46107.26041666666</v>
+        <v>46108.26041666666</v>
       </c>
       <c r="B26">
-        <v>390.986</v>
+        <v>1017.68</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46107.27083333334</v>
+        <v>46108.27083333334</v>
       </c>
       <c r="B27">
-        <v>387.153</v>
+        <v>1034.912</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46107.28125</v>
+        <v>46108.28125</v>
       </c>
       <c r="B28">
-        <v>385.34</v>
+        <v>1047.495</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46107.29166666666</v>
+        <v>46108.29166666666</v>
       </c>
       <c r="B29">
-        <v>383.057</v>
+        <v>1066.943</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46107.30208333334</v>
+        <v>46108.30208333334</v>
       </c>
       <c r="B30">
-        <v>396.008</v>
+        <v>1100.773</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46107.3125</v>
+        <v>46108.3125</v>
       </c>
       <c r="B31">
-        <v>390.956</v>
+        <v>1126.003</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46107.32291666666</v>
+        <v>46108.32291666666</v>
       </c>
       <c r="B32">
-        <v>385.578</v>
+        <v>1149.723</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46107.33333333334</v>
+        <v>46108.33333333334</v>
       </c>
       <c r="B33">
-        <v>381.935</v>
+        <v>1176.014</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46107.34375</v>
+        <v>46108.34375</v>
       </c>
       <c r="B34">
-        <v>398.335</v>
+        <v>1181.385</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46107.35416666666</v>
+        <v>46108.35416666666</v>
       </c>
       <c r="B35">
-        <v>424.336</v>
+        <v>1199.655</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46107.36458333334</v>
+        <v>46108.36458333334</v>
       </c>
       <c r="B36">
-        <v>450.86</v>
+        <v>1219.439</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46107.375</v>
+        <v>46108.375</v>
       </c>
       <c r="B37">
-        <v>477.957</v>
+        <v>1236.568</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46107.38541666666</v>
+        <v>46108.38541666666</v>
       </c>
       <c r="B38">
-        <v>527.635</v>
+        <v>1375.716</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46107.39583333334</v>
+        <v>46108.39583333334</v>
       </c>
       <c r="B39">
-        <v>565.8099999999999</v>
+        <v>1389.339</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46107.40625</v>
+        <v>46108.40625</v>
       </c>
       <c r="B40">
-        <v>605.367</v>
+        <v>1402.547</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46107.41666666666</v>
+        <v>46108.41666666666</v>
       </c>
       <c r="B41">
-        <v>643.782</v>
+        <v>1416.079</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46107.42708333334</v>
+        <v>46108.42708333334</v>
       </c>
       <c r="B42">
-        <v>686.043</v>
+        <v>1507.287</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46107.4375</v>
+        <v>46108.4375</v>
       </c>
       <c r="B43">
-        <v>715.658</v>
+        <v>1515.984</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46107.44791666666</v>
+        <v>46108.44791666666</v>
       </c>
       <c r="B44">
-        <v>746.902</v>
+        <v>1523.82</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46107.45833333334</v>
+        <v>46108.45833333334</v>
       </c>
       <c r="B45">
-        <v>775.378</v>
+        <v>1533.2</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46107.46875</v>
+        <v>46108.46875</v>
       </c>
       <c r="B46">
-        <v>803.016</v>
+        <v>1547.758</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46107.47916666666</v>
+        <v>46108.47916666666</v>
       </c>
       <c r="B47">
-        <v>819.1849999999999</v>
+        <v>1558.586</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46107.48958333334</v>
+        <v>46108.48958333334</v>
       </c>
       <c r="B48">
-        <v>836.769</v>
+        <v>1570.279</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46107.5</v>
+        <v>46108.5</v>
       </c>
       <c r="B49">
-        <v>853.852</v>
+        <v>1582.034</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46107.51041666666</v>
+        <v>46108.51041666666</v>
       </c>
       <c r="B50">
-        <v>846.442</v>
+        <v>1561.704</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46107.52083333334</v>
+        <v>46108.52083333334</v>
       </c>
       <c r="B51">
-        <v>859.053</v>
+        <v>1579.949</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46107.53125</v>
+        <v>46108.53125</v>
       </c>
       <c r="B52">
-        <v>871.553</v>
+        <v>1597.993</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46107.54166666666</v>
+        <v>46108.54166666666</v>
       </c>
       <c r="B53">
-        <v>883.837</v>
+        <v>1617.352</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46107.55208333334</v>
+        <v>46108.55208333334</v>
       </c>
       <c r="B54">
-        <v>915.248</v>
+        <v>1579.449</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46107.5625</v>
+        <v>46108.5625</v>
       </c>
       <c r="B55">
-        <v>934.417</v>
+        <v>1604.255</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46107.57291666666</v>
+        <v>46108.57291666666</v>
       </c>
       <c r="B56">
-        <v>950.341</v>
+        <v>1625.84</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46107.58333333334</v>
+        <v>46108.58333333334</v>
       </c>
       <c r="B57">
-        <v>968.828</v>
+        <v>1651.096</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46107.59375</v>
+        <v>46108.59375</v>
       </c>
       <c r="B58">
-        <v>974.8869999999999</v>
+        <v>1575.59</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46107.60416666666</v>
+        <v>46108.60416666666</v>
       </c>
       <c r="B59">
-        <v>999.831</v>
+        <v>1600.074</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46107.61458333334</v>
+        <v>46108.61458333334</v>
       </c>
       <c r="B60">
-        <v>1025.989</v>
+        <v>1622.606</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46107.625</v>
+        <v>46108.625</v>
       </c>
       <c r="B61">
-        <v>1050.72</v>
+        <v>1647.792</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46107.63541666666</v>
+        <v>46108.63541666666</v>
       </c>
       <c r="B62">
-        <v>1016.337</v>
+        <v>1691.042</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46107.64583333334</v>
+        <v>46108.64583333334</v>
       </c>
       <c r="B63">
-        <v>1040.03</v>
+        <v>1707.793</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46107.65625</v>
+        <v>46108.65625</v>
       </c>
       <c r="B64">
-        <v>1062.495</v>
+        <v>1721.416</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46107.66666666666</v>
+        <v>46108.66666666666</v>
       </c>
       <c r="B65">
-        <v>1085.884</v>
+        <v>1737.038</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46107.67708333334</v>
+        <v>46108.67708333334</v>
       </c>
       <c r="B66">
-        <v>1078.37</v>
+        <v>1702.702</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46107.6875</v>
+        <v>46108.6875</v>
       </c>
       <c r="B67">
-        <v>1098.622</v>
+        <v>1697.743</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46107.69791666666</v>
+        <v>46108.69791666666</v>
       </c>
       <c r="B68">
-        <v>1121.827</v>
+        <v>1702.46</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46107.70833333334</v>
+        <v>46108.70833333334</v>
       </c>
       <c r="B69">
-        <v>1143.388</v>
+        <v>1698.749</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46107.71875</v>
+        <v>46108.71875</v>
       </c>
       <c r="B70">
-        <v>1169.784</v>
+        <v>1692.219</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46107.72916666666</v>
+        <v>46108.72916666666</v>
       </c>
       <c r="B71">
-        <v>1199.123</v>
+        <v>1684.263</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46107.73958333334</v>
+        <v>46108.73958333334</v>
       </c>
       <c r="B72">
-        <v>1229.245</v>
+        <v>1682.341</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46107.75</v>
+        <v>46108.75</v>
       </c>
       <c r="B73">
-        <v>1259.277</v>
+        <v>1672.744</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46107.76041666666</v>
+        <v>46108.76041666666</v>
       </c>
       <c r="B74">
-        <v>1296.082</v>
+        <v>1654.802</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46107.77083333334</v>
+        <v>46108.77083333334</v>
       </c>
       <c r="B75">
-        <v>1307.346</v>
+        <v>1641.173</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46107.78125</v>
+        <v>46108.78125</v>
       </c>
       <c r="B76">
-        <v>1317.444</v>
+        <v>1627.922</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46107.79166666666</v>
+        <v>46108.79166666666</v>
       </c>
       <c r="B77">
-        <v>1327.783</v>
+        <v>1614.12</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46107.80208333334</v>
+        <v>46108.80208333334</v>
       </c>
       <c r="B78">
-        <v>1335.641</v>
+        <v>1615.434</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46107.8125</v>
+        <v>46108.8125</v>
       </c>
       <c r="B79">
-        <v>1331.747</v>
+        <v>1606.372</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46107.82291666666</v>
+        <v>46108.82291666666</v>
       </c>
       <c r="B80">
-        <v>1328.492</v>
+        <v>1599.104</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46107.83333333334</v>
+        <v>46108.83333333334</v>
       </c>
       <c r="B81">
-        <v>1325.969</v>
+        <v>1591.135</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46107.84375</v>
+        <v>46108.84375</v>
       </c>
       <c r="B82">
-        <v>1314.092</v>
+        <v>1587.419</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46107.85416666666</v>
+        <v>46108.85416666666</v>
       </c>
       <c r="B83">
-        <v>1303.502</v>
+        <v>1584.608</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46107.86458333334</v>
+        <v>46108.86458333334</v>
       </c>
       <c r="B84">
-        <v>1292.743</v>
+        <v>1581.542</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46107.875</v>
+        <v>46108.875</v>
       </c>
       <c r="B85">
-        <v>1281.853</v>
+        <v>1578.763</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46107.88541666666</v>
+        <v>46108.88541666666</v>
       </c>
       <c r="B86">
-        <v>1275.471</v>
+        <v>1563.951</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46107.89583333334</v>
+        <v>46108.89583333334</v>
       </c>
       <c r="B87">
-        <v>1262.754</v>
+        <v>1549.546</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46107.90625</v>
+        <v>46108.90625</v>
       </c>
       <c r="B88">
-        <v>1251.374</v>
+        <v>1535.407</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46107.91666666666</v>
+        <v>46108.91666666666</v>
       </c>
       <c r="B89">
-        <v>1239.93</v>
+        <v>1520.646</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46107.92708333334</v>
+        <v>46108.92708333334</v>
       </c>
       <c r="B90">
-        <v>1225.935</v>
+        <v>1503.614</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46107.9375</v>
+        <v>46108.9375</v>
       </c>
       <c r="B91">
-        <v>1214.907</v>
+        <v>1483.037</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46107.94791666666</v>
+        <v>46108.94791666666</v>
       </c>
       <c r="B92">
-        <v>1204.845</v>
+        <v>1463.039</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46107.95833333334</v>
+        <v>46108.95833333334</v>
       </c>
       <c r="B93">
-        <v>1194.266</v>
+        <v>1440.538</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46107.96875</v>
+        <v>46108.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46107.97916666666</v>
+        <v>46108.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46107.98958333334</v>
+        <v>46108.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46108.01041666666</v>
+        <v>46111.01041666666</v>
       </c>
       <c r="B2">
-        <v>1016.396</v>
+        <v>1845.754</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46108.02083333334</v>
+        <v>46111.02083333334</v>
       </c>
       <c r="B3">
-        <v>998.72</v>
+        <v>1908.073</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46108.03125</v>
+        <v>46111.03125</v>
       </c>
       <c r="B4">
-        <v>980.487</v>
+        <v>1924.24</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46108.04166666666</v>
+        <v>46111.04166666666</v>
       </c>
       <c r="B5">
-        <v>962.099</v>
+        <v>1985.245</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46108.05208333334</v>
+        <v>46111.05208333334</v>
       </c>
       <c r="B6">
-        <v>940.331</v>
+        <v>2008.704</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46108.0625</v>
+        <v>46111.0625</v>
       </c>
       <c r="B7">
-        <v>933.647</v>
+        <v>2027.438</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46108.07291666666</v>
+        <v>46111.07291666666</v>
       </c>
       <c r="B8">
-        <v>928.147</v>
+        <v>2030.167</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46108.08333333334</v>
+        <v>46111.08333333334</v>
       </c>
       <c r="B9">
-        <v>922.9829999999999</v>
+        <v>2029.884</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46108.09375</v>
+        <v>46111.09375</v>
       </c>
       <c r="B10">
-        <v>914.4059999999999</v>
+        <v>1995.274</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46108.10416666666</v>
+        <v>46111.10416666666</v>
       </c>
       <c r="B11">
-        <v>906.4589999999999</v>
+        <v>1993.968</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46108.11458333334</v>
+        <v>46111.11458333334</v>
       </c>
       <c r="B12">
-        <v>897.6</v>
+        <v>1995.45</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46108.125</v>
+        <v>46111.125</v>
       </c>
       <c r="B13">
-        <v>889.276</v>
+        <v>1993.606</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46108.13541666666</v>
+        <v>46111.13541666666</v>
       </c>
       <c r="B14">
-        <v>883.321</v>
+        <v>1972.99</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46108.14583333334</v>
+        <v>46111.14583333334</v>
       </c>
       <c r="B15">
-        <v>883.217</v>
+        <v>1991.104</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46108.15625</v>
+        <v>46111.15625</v>
       </c>
       <c r="B16">
-        <v>882.655</v>
+        <v>1999.012</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46108.16666666666</v>
+        <v>46111.16666666666</v>
       </c>
       <c r="B17">
-        <v>884.51</v>
+        <v>2002.321</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46108.17708333334</v>
+        <v>46111.17708333334</v>
       </c>
       <c r="B18">
-        <v>915.755</v>
+        <v>1998.927</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46108.1875</v>
+        <v>46111.1875</v>
       </c>
       <c r="B19">
-        <v>925.0170000000001</v>
+        <v>2012.399</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46108.19791666666</v>
+        <v>46111.19791666666</v>
       </c>
       <c r="B20">
-        <v>935.505</v>
+        <v>2002.349</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46108.20833333334</v>
+        <v>46111.20833333334</v>
       </c>
       <c r="B21">
-        <v>945.02</v>
+        <v>1998.753</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46108.21875</v>
+        <v>46111.21875</v>
       </c>
       <c r="B22">
-        <v>960.133</v>
+        <v>1995.955</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46108.22916666666</v>
+        <v>46111.22916666666</v>
       </c>
       <c r="B23">
-        <v>973.886</v>
+        <v>2003.801</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46108.23958333334</v>
+        <v>46111.23958333334</v>
       </c>
       <c r="B24">
-        <v>987.67</v>
+        <v>2005.435</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46108.25</v>
+        <v>46111.25</v>
       </c>
       <c r="B25">
-        <v>1000.842</v>
+        <v>1999.049</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46108.26041666666</v>
+        <v>46111.26041666666</v>
       </c>
       <c r="B26">
-        <v>1017.68</v>
+        <v>1979.969</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46108.27083333334</v>
+        <v>46111.27083333334</v>
       </c>
       <c r="B27">
-        <v>1034.912</v>
+        <v>1979.1</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46108.28125</v>
+        <v>46111.28125</v>
       </c>
       <c r="B28">
-        <v>1047.495</v>
+        <v>1981.219</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46108.29166666666</v>
+        <v>46111.29166666666</v>
       </c>
       <c r="B29">
-        <v>1066.943</v>
+        <v>1981.455</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46108.30208333334</v>
+        <v>46111.30208333334</v>
       </c>
       <c r="B30">
-        <v>1100.773</v>
+        <v>1908.573</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46108.3125</v>
+        <v>46111.3125</v>
       </c>
       <c r="B31">
-        <v>1126.003</v>
+        <v>1908.361</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46108.32291666666</v>
+        <v>46111.32291666666</v>
       </c>
       <c r="B32">
-        <v>1149.723</v>
+        <v>1909.387</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46108.33333333334</v>
+        <v>46111.33333333334</v>
       </c>
       <c r="B33">
-        <v>1176.014</v>
+        <v>1908.333</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46108.34375</v>
+        <v>46111.34375</v>
       </c>
       <c r="B34">
-        <v>1181.385</v>
+        <v>1870.097</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46108.35416666666</v>
+        <v>46111.35416666666</v>
       </c>
       <c r="B35">
-        <v>1199.655</v>
+        <v>1874.829</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46108.36458333334</v>
+        <v>46111.36458333334</v>
       </c>
       <c r="B36">
-        <v>1219.439</v>
+        <v>1869.744</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46108.375</v>
+        <v>46111.375</v>
       </c>
       <c r="B37">
-        <v>1236.568</v>
+        <v>1872.703</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46108.38541666666</v>
+        <v>46111.38541666666</v>
       </c>
       <c r="B38">
-        <v>1375.716</v>
+        <v>2075.338</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46108.39583333334</v>
+        <v>46111.39583333334</v>
       </c>
       <c r="B39">
-        <v>1389.339</v>
+        <v>2083.521</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46108.40625</v>
+        <v>46111.40625</v>
       </c>
       <c r="B40">
-        <v>1402.547</v>
+        <v>2090.221</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46108.41666666666</v>
+        <v>46111.41666666666</v>
       </c>
       <c r="B41">
-        <v>1416.079</v>
+        <v>2095.836</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46108.42708333334</v>
+        <v>46111.42708333334</v>
       </c>
       <c r="B42">
-        <v>1507.287</v>
+        <v>2117.898</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46108.4375</v>
+        <v>46111.4375</v>
       </c>
       <c r="B43">
-        <v>1515.984</v>
+        <v>2123.011</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46108.44791666666</v>
+        <v>46111.44791666666</v>
       </c>
       <c r="B44">
-        <v>1523.82</v>
+        <v>2127.692</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46108.45833333334</v>
+        <v>46111.45833333334</v>
       </c>
       <c r="B45">
-        <v>1533.2</v>
+        <v>2132.578</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46108.46875</v>
+        <v>46111.46875</v>
       </c>
       <c r="B46">
-        <v>1547.758</v>
+        <v>2125.707</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46108.47916666666</v>
+        <v>46111.47916666666</v>
       </c>
       <c r="B47">
-        <v>1558.586</v>
+        <v>2117.223</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46108.48958333334</v>
+        <v>46111.48958333334</v>
       </c>
       <c r="B48">
-        <v>1570.279</v>
+        <v>2109.913</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46108.5</v>
+        <v>46111.5</v>
       </c>
       <c r="B49">
-        <v>1582.034</v>
+        <v>2102.69</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46108.51041666666</v>
+        <v>46111.51041666666</v>
       </c>
       <c r="B50">
-        <v>1561.704</v>
+        <v>2091.361</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46108.52083333334</v>
+        <v>46111.52083333334</v>
       </c>
       <c r="B51">
-        <v>1579.949</v>
+        <v>2072.356</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46108.53125</v>
+        <v>46111.53125</v>
       </c>
       <c r="B52">
-        <v>1597.993</v>
+        <v>2053.609</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46108.54166666666</v>
+        <v>46111.54166666666</v>
       </c>
       <c r="B53">
-        <v>1617.352</v>
+        <v>2034.63</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46108.55208333334</v>
+        <v>46111.55208333334</v>
       </c>
       <c r="B54">
-        <v>1579.449</v>
+        <v>2007.921</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46108.5625</v>
+        <v>46111.5625</v>
       </c>
       <c r="B55">
-        <v>1604.255</v>
+        <v>1980.999</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46108.57291666666</v>
+        <v>46111.57291666666</v>
       </c>
       <c r="B56">
-        <v>1625.84</v>
+        <v>1954.174</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46108.58333333334</v>
+        <v>46111.58333333334</v>
       </c>
       <c r="B57">
-        <v>1651.096</v>
+        <v>1927.615</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46108.59375</v>
+        <v>46111.59375</v>
       </c>
       <c r="B58">
-        <v>1575.59</v>
+        <v>1834.179</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46108.60416666666</v>
+        <v>46111.60416666666</v>
       </c>
       <c r="B59">
-        <v>1600.074</v>
+        <v>1796.516</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46108.61458333334</v>
+        <v>46111.61458333334</v>
       </c>
       <c r="B60">
-        <v>1622.606</v>
+        <v>1763.156</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46108.625</v>
+        <v>46111.625</v>
       </c>
       <c r="B61">
-        <v>1647.792</v>
+        <v>1723.886</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46108.63541666666</v>
+        <v>46111.63541666666</v>
       </c>
       <c r="B62">
-        <v>1691.042</v>
+        <v>1694.981</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46108.64583333334</v>
+        <v>46111.64583333334</v>
       </c>
       <c r="B63">
-        <v>1707.793</v>
+        <v>1632.81</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46108.65625</v>
+        <v>46111.65625</v>
       </c>
       <c r="B64">
-        <v>1721.416</v>
+        <v>1571.312</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46108.66666666666</v>
+        <v>46111.66666666666</v>
       </c>
       <c r="B65">
-        <v>1737.038</v>
+        <v>1508.489</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46108.67708333334</v>
+        <v>46111.67708333334</v>
       </c>
       <c r="B66">
-        <v>1702.702</v>
+        <v>1250.28</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46108.6875</v>
+        <v>46111.6875</v>
       </c>
       <c r="B67">
-        <v>1697.743</v>
+        <v>1193.314</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46108.69791666666</v>
+        <v>46111.69791666666</v>
       </c>
       <c r="B68">
-        <v>1702.46</v>
+        <v>1135.506</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46108.70833333334</v>
+        <v>46111.70833333334</v>
       </c>
       <c r="B69">
-        <v>1698.749</v>
+        <v>1076.116</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46108.71875</v>
+        <v>46111.71875</v>
       </c>
       <c r="B70">
-        <v>1692.219</v>
+        <v>1000.485</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46108.72916666666</v>
+        <v>46111.72916666666</v>
       </c>
       <c r="B71">
-        <v>1684.263</v>
+        <v>973.441</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46108.73958333334</v>
+        <v>46111.73958333334</v>
       </c>
       <c r="B72">
-        <v>1682.341</v>
+        <v>946.793</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46108.75</v>
+        <v>46111.75</v>
       </c>
       <c r="B73">
-        <v>1672.744</v>
+        <v>920.741</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46108.76041666666</v>
+        <v>46111.76041666666</v>
       </c>
       <c r="B74">
-        <v>1654.802</v>
+        <v>894.862</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46108.77083333334</v>
+        <v>46111.77083333334</v>
       </c>
       <c r="B75">
-        <v>1641.173</v>
+        <v>892.221</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46108.78125</v>
+        <v>46111.78125</v>
       </c>
       <c r="B76">
-        <v>1627.922</v>
+        <v>890.708</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46108.79166666666</v>
+        <v>46111.79166666666</v>
       </c>
       <c r="B77">
-        <v>1614.12</v>
+        <v>889.431</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46108.80208333334</v>
+        <v>46111.80208333334</v>
       </c>
       <c r="B78">
-        <v>1615.434</v>
+        <v>888.292</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46108.8125</v>
+        <v>46111.8125</v>
       </c>
       <c r="B79">
-        <v>1606.372</v>
+        <v>896.333</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46108.82291666666</v>
+        <v>46111.82291666666</v>
       </c>
       <c r="B80">
-        <v>1599.104</v>
+        <v>904.631</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46108.83333333334</v>
+        <v>46111.83333333334</v>
       </c>
       <c r="B81">
-        <v>1591.135</v>
+        <v>914.367</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46108.84375</v>
+        <v>46111.84375</v>
       </c>
       <c r="B82">
-        <v>1587.419</v>
+        <v>922.952</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46108.85416666666</v>
+        <v>46111.85416666666</v>
       </c>
       <c r="B83">
-        <v>1584.608</v>
+        <v>932.902</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46108.86458333334</v>
+        <v>46111.86458333334</v>
       </c>
       <c r="B84">
-        <v>1581.542</v>
+        <v>942.117</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46108.875</v>
+        <v>46111.875</v>
       </c>
       <c r="B85">
-        <v>1578.763</v>
+        <v>951.893</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46108.88541666666</v>
+        <v>46111.88541666666</v>
       </c>
       <c r="B86">
-        <v>1563.951</v>
+        <v>974.816</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46108.89583333334</v>
+        <v>46111.89583333334</v>
       </c>
       <c r="B87">
-        <v>1549.546</v>
+        <v>989.085</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46108.90625</v>
+        <v>46111.90625</v>
       </c>
       <c r="B88">
-        <v>1535.407</v>
+        <v>1004.317</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46108.91666666666</v>
+        <v>46111.91666666666</v>
       </c>
       <c r="B89">
-        <v>1520.646</v>
+        <v>1019.537</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46108.92708333334</v>
+        <v>46111.92708333334</v>
       </c>
       <c r="B90">
-        <v>1503.614</v>
+        <v>1034.772</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46108.9375</v>
+        <v>46111.9375</v>
       </c>
       <c r="B91">
-        <v>1483.037</v>
+        <v>1046.253</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46108.94791666666</v>
+        <v>46111.94791666666</v>
       </c>
       <c r="B92">
-        <v>1463.039</v>
+        <v>1057.458</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46108.95833333334</v>
+        <v>46111.95833333334</v>
       </c>
       <c r="B93">
-        <v>1440.538</v>
+        <v>1068.382</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46108.96875</v>
+        <v>46111.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46108.97916666666</v>
+        <v>46111.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46108.98958333334</v>
+        <v>46111.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,769 +394,1537 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46111.01041666666</v>
+        <v>46121</v>
       </c>
       <c r="B2">
-        <v>1845.754</v>
+        <v>904.039</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46111.02083333334</v>
+        <v>46121.01041666666</v>
       </c>
       <c r="B3">
-        <v>1908.073</v>
+        <v>903.504</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46111.03125</v>
+        <v>46121.02083333334</v>
       </c>
       <c r="B4">
-        <v>1924.24</v>
+        <v>903.285</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46111.04166666666</v>
+        <v>46121.03125</v>
       </c>
       <c r="B5">
-        <v>1985.245</v>
+        <v>900.282</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46111.05208333334</v>
+        <v>46121.04166666666</v>
       </c>
       <c r="B6">
-        <v>2008.704</v>
+        <v>879.8869999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46111.0625</v>
+        <v>46121.05208333334</v>
       </c>
       <c r="B7">
-        <v>2027.438</v>
+        <v>863.421</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46111.07291666666</v>
+        <v>46121.0625</v>
       </c>
       <c r="B8">
-        <v>2030.167</v>
+        <v>850.204</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46111.08333333334</v>
+        <v>46121.07291666666</v>
       </c>
       <c r="B9">
-        <v>2029.884</v>
+        <v>847.136</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46111.09375</v>
+        <v>46121.08333333334</v>
       </c>
       <c r="B10">
-        <v>1995.274</v>
+        <v>852.676</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46111.10416666666</v>
+        <v>46121.09375</v>
       </c>
       <c r="B11">
-        <v>1993.968</v>
+        <v>854.657</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46111.11458333334</v>
+        <v>46121.10416666666</v>
       </c>
       <c r="B12">
-        <v>1995.45</v>
+        <v>847.989</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46111.125</v>
+        <v>46121.11458333334</v>
       </c>
       <c r="B13">
-        <v>1993.606</v>
+        <v>835.1</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46111.13541666666</v>
+        <v>46121.125</v>
       </c>
       <c r="B14">
-        <v>1972.99</v>
+        <v>835.202</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46111.14583333334</v>
+        <v>46121.13541666666</v>
       </c>
       <c r="B15">
-        <v>1991.104</v>
+        <v>830.59</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46111.15625</v>
+        <v>46121.14583333334</v>
       </c>
       <c r="B16">
-        <v>1999.012</v>
+        <v>817.865</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46111.16666666666</v>
+        <v>46121.15625</v>
       </c>
       <c r="B17">
-        <v>2002.321</v>
+        <v>799.353</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46111.17708333334</v>
+        <v>46121.16666666666</v>
       </c>
       <c r="B18">
-        <v>1998.927</v>
+        <v>791.196</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46111.1875</v>
+        <v>46121.17708333334</v>
       </c>
       <c r="B19">
-        <v>2012.399</v>
+        <v>777.6180000000001</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46111.19791666666</v>
+        <v>46121.1875</v>
       </c>
       <c r="B20">
-        <v>2002.349</v>
+        <v>763.972</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46111.20833333334</v>
+        <v>46121.19791666666</v>
       </c>
       <c r="B21">
-        <v>1998.753</v>
+        <v>750.107</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46111.21875</v>
+        <v>46121.20833333334</v>
       </c>
       <c r="B22">
-        <v>1995.955</v>
+        <v>734.673</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46111.22916666666</v>
+        <v>46121.21875</v>
       </c>
       <c r="B23">
-        <v>2003.801</v>
+        <v>730.487</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46111.23958333334</v>
+        <v>46121.22916666666</v>
       </c>
       <c r="B24">
-        <v>2005.435</v>
+        <v>721.407</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46111.25</v>
+        <v>46121.23958333334</v>
       </c>
       <c r="B25">
-        <v>1999.049</v>
+        <v>714.399</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46111.26041666666</v>
+        <v>46121.25</v>
       </c>
       <c r="B26">
-        <v>1979.969</v>
+        <v>704.393</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46111.27083333334</v>
+        <v>46121.26041666666</v>
       </c>
       <c r="B27">
-        <v>1979.1</v>
+        <v>699.775</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46111.28125</v>
+        <v>46121.27083333334</v>
       </c>
       <c r="B28">
-        <v>1981.219</v>
+        <v>704.554</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46111.29166666666</v>
+        <v>46121.28125</v>
       </c>
       <c r="B29">
-        <v>1981.455</v>
+        <v>747.604</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46111.30208333334</v>
+        <v>46121.29166666666</v>
       </c>
       <c r="B30">
-        <v>1908.573</v>
+        <v>746.63</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46111.3125</v>
+        <v>46121.30208333334</v>
       </c>
       <c r="B31">
-        <v>1908.361</v>
+        <v>746.7859999999999</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46111.32291666666</v>
+        <v>46121.3125</v>
       </c>
       <c r="B32">
-        <v>1909.387</v>
+        <v>743.4109999999999</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46111.33333333334</v>
+        <v>46121.32291666666</v>
       </c>
       <c r="B33">
-        <v>1908.333</v>
+        <v>742.184</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46111.34375</v>
+        <v>46121.33333333334</v>
       </c>
       <c r="B34">
-        <v>1870.097</v>
+        <v>801.313</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46111.35416666666</v>
+        <v>46121.34375</v>
       </c>
       <c r="B35">
-        <v>1874.829</v>
+        <v>825.9109999999999</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46111.36458333334</v>
+        <v>46121.35416666666</v>
       </c>
       <c r="B36">
-        <v>1869.744</v>
+        <v>854.364</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46111.375</v>
+        <v>46121.36458333334</v>
       </c>
       <c r="B37">
-        <v>1872.703</v>
+        <v>883.586</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46111.38541666666</v>
+        <v>46121.375</v>
       </c>
       <c r="B38">
-        <v>2075.338</v>
+        <v>862.452</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46111.39583333334</v>
+        <v>46121.38541666666</v>
       </c>
       <c r="B39">
-        <v>2083.521</v>
+        <v>887.158</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46111.40625</v>
+        <v>46121.39583333334</v>
       </c>
       <c r="B40">
-        <v>2090.221</v>
+        <v>909.361</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46111.41666666666</v>
+        <v>46121.40625</v>
       </c>
       <c r="B41">
-        <v>2095.836</v>
+        <v>934.838</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46111.42708333334</v>
+        <v>46121.41666666666</v>
       </c>
       <c r="B42">
-        <v>2117.898</v>
+        <v>967.367</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46111.4375</v>
+        <v>46121.42708333334</v>
       </c>
       <c r="B43">
-        <v>2123.011</v>
+        <v>963.377</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46111.44791666666</v>
+        <v>46121.4375</v>
       </c>
       <c r="B44">
-        <v>2127.692</v>
+        <v>959.202</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46111.45833333334</v>
+        <v>46121.44791666666</v>
       </c>
       <c r="B45">
-        <v>2132.578</v>
+        <v>954.076</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46111.46875</v>
+        <v>46121.45833333334</v>
       </c>
       <c r="B46">
-        <v>2125.707</v>
+        <v>938.278</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46111.47916666666</v>
+        <v>46121.46875</v>
       </c>
       <c r="B47">
-        <v>2117.223</v>
+        <v>921.982</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46111.48958333334</v>
+        <v>46121.47916666666</v>
       </c>
       <c r="B48">
-        <v>2109.913</v>
+        <v>790.853</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46111.5</v>
+        <v>46121.48958333334</v>
       </c>
       <c r="B49">
-        <v>2102.69</v>
+        <v>739.509</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46111.51041666666</v>
+        <v>46121.5</v>
       </c>
       <c r="B50">
-        <v>2091.361</v>
+        <v>757.347</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46111.52083333334</v>
+        <v>46121.51041666666</v>
       </c>
       <c r="B51">
-        <v>2072.356</v>
+        <v>744.4349999999999</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46111.53125</v>
+        <v>46121.52083333334</v>
       </c>
       <c r="B52">
-        <v>2053.609</v>
+        <v>640.794</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46111.54166666666</v>
+        <v>46121.53125</v>
       </c>
       <c r="B53">
-        <v>2034.63</v>
+        <v>632.516</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46111.55208333334</v>
+        <v>46121.54166666666</v>
       </c>
       <c r="B54">
-        <v>2007.921</v>
+        <v>666.3339999999999</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46111.5625</v>
+        <v>46121.55208333334</v>
       </c>
       <c r="B55">
-        <v>1980.999</v>
+        <v>643.196</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46111.57291666666</v>
+        <v>46121.5625</v>
       </c>
       <c r="B56">
-        <v>1954.174</v>
+        <v>677.492</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46111.58333333334</v>
+        <v>46121.57291666666</v>
       </c>
       <c r="B57">
-        <v>1927.615</v>
+        <v>665.856</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46111.59375</v>
+        <v>46121.58333333334</v>
       </c>
       <c r="B58">
-        <v>1834.179</v>
+        <v>703.524</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46111.60416666666</v>
+        <v>46121.59375</v>
       </c>
       <c r="B59">
-        <v>1796.516</v>
+        <v>689.998</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46111.61458333334</v>
+        <v>46121.60416666666</v>
       </c>
       <c r="B60">
-        <v>1763.156</v>
+        <v>686.009</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46111.625</v>
+        <v>46121.61458333334</v>
       </c>
       <c r="B61">
-        <v>1723.886</v>
+        <v>667.913</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46111.63541666666</v>
+        <v>46121.625</v>
       </c>
       <c r="B62">
-        <v>1694.981</v>
+        <v>593.9829999999999</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46111.64583333334</v>
+        <v>46121.63541666666</v>
       </c>
       <c r="B63">
-        <v>1632.81</v>
+        <v>593.0170000000001</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46111.65625</v>
+        <v>46121.64583333334</v>
       </c>
       <c r="B64">
-        <v>1571.312</v>
+        <v>593.782</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46111.66666666666</v>
+        <v>46121.65625</v>
       </c>
       <c r="B65">
-        <v>1508.489</v>
+        <v>589.175</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46111.67708333334</v>
+        <v>46121.66666666666</v>
       </c>
       <c r="B66">
-        <v>1250.28</v>
+        <v>555.545</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46111.6875</v>
+        <v>46121.67708333334</v>
       </c>
       <c r="B67">
-        <v>1193.314</v>
+        <v>534.986</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46111.69791666666</v>
+        <v>46121.6875</v>
       </c>
       <c r="B68">
-        <v>1135.506</v>
+        <v>513.468</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46111.70833333334</v>
+        <v>46121.69791666666</v>
       </c>
       <c r="B69">
-        <v>1076.116</v>
+        <v>493.734</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46111.71875</v>
+        <v>46121.70833333334</v>
       </c>
       <c r="B70">
-        <v>1000.485</v>
+        <v>462.611</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46111.72916666666</v>
+        <v>46121.71875</v>
       </c>
       <c r="B71">
-        <v>973.441</v>
+        <v>438.23</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46111.73958333334</v>
+        <v>46121.72916666666</v>
       </c>
       <c r="B72">
-        <v>946.793</v>
+        <v>414.199</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46111.75</v>
+        <v>46121.73958333334</v>
       </c>
       <c r="B73">
-        <v>920.741</v>
+        <v>391.126</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46111.76041666666</v>
+        <v>46121.75</v>
       </c>
       <c r="B74">
-        <v>894.862</v>
+        <v>370.873</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46111.77083333334</v>
+        <v>46121.76041666666</v>
       </c>
       <c r="B75">
-        <v>892.221</v>
+        <v>365.884</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46111.78125</v>
+        <v>46121.77083333334</v>
       </c>
       <c r="B76">
-        <v>890.708</v>
+        <v>361.08</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46111.79166666666</v>
+        <v>46121.78125</v>
       </c>
       <c r="B77">
-        <v>889.431</v>
+        <v>356.411</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46111.80208333334</v>
+        <v>46121.79166666666</v>
       </c>
       <c r="B78">
-        <v>888.292</v>
+        <v>352.057</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46111.8125</v>
+        <v>46121.80208333334</v>
       </c>
       <c r="B79">
-        <v>896.333</v>
+        <v>355.704</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46111.82291666666</v>
+        <v>46121.8125</v>
       </c>
       <c r="B80">
-        <v>904.631</v>
+        <v>360.467</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46111.83333333334</v>
+        <v>46121.82291666666</v>
       </c>
       <c r="B81">
-        <v>914.367</v>
+        <v>365.156</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46111.84375</v>
+        <v>46121.83333333334</v>
       </c>
       <c r="B82">
-        <v>922.952</v>
+        <v>376.996</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46111.85416666666</v>
+        <v>46121.84375</v>
       </c>
       <c r="B83">
-        <v>932.902</v>
+        <v>379.432</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46111.86458333334</v>
+        <v>46121.85416666666</v>
       </c>
       <c r="B84">
-        <v>942.117</v>
+        <v>381.469</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46111.875</v>
+        <v>46121.86458333334</v>
       </c>
       <c r="B85">
-        <v>951.893</v>
+        <v>384.292</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46111.88541666666</v>
+        <v>46121.875</v>
       </c>
       <c r="B86">
-        <v>974.816</v>
+        <v>388.708</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46111.89583333334</v>
+        <v>46121.88541666666</v>
       </c>
       <c r="B87">
-        <v>989.085</v>
+        <v>398.483</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46111.90625</v>
+        <v>46121.89583333334</v>
       </c>
       <c r="B88">
-        <v>1004.317</v>
+        <v>408.455</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46111.91666666666</v>
+        <v>46121.90625</v>
       </c>
       <c r="B89">
-        <v>1019.537</v>
+        <v>419.264</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46111.92708333334</v>
+        <v>46121.91666666666</v>
       </c>
       <c r="B90">
-        <v>1034.772</v>
+        <v>443.684</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46111.9375</v>
+        <v>46121.92708333334</v>
       </c>
       <c r="B91">
-        <v>1046.253</v>
+        <v>459.404</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46111.94791666666</v>
+        <v>46121.9375</v>
       </c>
       <c r="B92">
-        <v>1057.458</v>
+        <v>475.842</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46111.95833333334</v>
+        <v>46121.94791666666</v>
       </c>
       <c r="B93">
-        <v>1068.382</v>
+        <v>490.812</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46111.96875</v>
+        <v>46121.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>577.088</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46111.97916666666</v>
+        <v>46121.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>592.715</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46111.98958333334</v>
+        <v>46121.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>607.8440000000001</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46112</v>
+        <v>46121.98958333334</v>
       </c>
       <c r="B97">
+        <v>621.5890000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46122</v>
+      </c>
+      <c r="B98">
+        <v>610.15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46122.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>624.881</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46122.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>629.535</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46122.03125</v>
+      </c>
+      <c r="B101">
+        <v>641.432</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46122.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>644.551</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46122.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>653.672</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46122.0625</v>
+      </c>
+      <c r="B104">
+        <v>662.116</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46122.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>663.824</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46122.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>671.386</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46122.09375</v>
+      </c>
+      <c r="B107">
+        <v>682.599</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46122.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>698.974</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46122.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>711.982</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46122.125</v>
+      </c>
+      <c r="B110">
+        <v>735.777</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46122.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>739.3440000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46122.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>746.215</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46122.15625</v>
+      </c>
+      <c r="B113">
+        <v>798.527</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46122.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>819.769</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46122.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>821.691</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46122.1875</v>
+      </c>
+      <c r="B116">
+        <v>825.071</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46122.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>835.143</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46122.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>796.947</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46122.21875</v>
+      </c>
+      <c r="B119">
+        <v>823.806</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46122.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>816.269</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46122.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>807.489</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46122.25</v>
+      </c>
+      <c r="B122">
+        <v>794.961</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46122.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>784.756</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46122.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>779.461</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46122.28125</v>
+      </c>
+      <c r="B125">
+        <v>769.4450000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46122.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>748.9400000000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46122.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>723.814</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46122.3125</v>
+      </c>
+      <c r="B128">
+        <v>715.508</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46122.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>696.314</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46122.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>786.958</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46122.34375</v>
+      </c>
+      <c r="B131">
+        <v>783.22</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46122.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>774.575</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46122.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>771.88</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46122.375</v>
+      </c>
+      <c r="B134">
+        <v>818.318</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46122.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>815.2569999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46122.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>811.625</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46122.40625</v>
+      </c>
+      <c r="B137">
+        <v>806.9109999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46122.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>789.808</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46122.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>776.229</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46122.4375</v>
+      </c>
+      <c r="B140">
+        <v>762.419</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46122.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>749.939</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46122.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>734.466</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46122.46875</v>
+      </c>
+      <c r="B143">
+        <v>724.052</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46122.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>715.009</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46122.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>706.077</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46122.5</v>
+      </c>
+      <c r="B146">
+        <v>696.101</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46122.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>686.051</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46122.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>676.202</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46122.53125</v>
+      </c>
+      <c r="B149">
+        <v>667.763</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46122.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>654.615</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46122.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>642.753</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46122.5625</v>
+      </c>
+      <c r="B152">
+        <v>630.938</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46122.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>619.136</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46122.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>576.921</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46122.59375</v>
+      </c>
+      <c r="B155">
+        <v>574.298</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46122.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>571.647</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46122.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>568.478</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46122.625</v>
+      </c>
+      <c r="B158">
+        <v>541.198</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46122.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>530.201</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46122.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>518.152</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46122.65625</v>
+      </c>
+      <c r="B161">
+        <v>508.394</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46122.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>393.268</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46122.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>378.454</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46122.6875</v>
+      </c>
+      <c r="B164">
+        <v>359.609</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46122.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>344.562</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46122.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>303.006</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46122.71875</v>
+      </c>
+      <c r="B167">
+        <v>281.344</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46122.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>254.269</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46122.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>234.469</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46122.75</v>
+      </c>
+      <c r="B170">
+        <v>209.761</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46122.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>199.401</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46122.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>189.484</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46122.78125</v>
+      </c>
+      <c r="B173">
+        <v>180.056</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46122.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>172.67</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46122.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>165.115</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46122.8125</v>
+      </c>
+      <c r="B176">
+        <v>159.205</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46122.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>178.059</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46122.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>167.388</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46122.84375</v>
+      </c>
+      <c r="B179">
+        <v>162.01</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46122.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>131.837</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46122.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>126.57</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46122.875</v>
+      </c>
+      <c r="B182">
+        <v>139.718</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46122.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>109.887</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46122.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>106.752</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46122.90625</v>
+      </c>
+      <c r="B185">
+        <v>104.218</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46122.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>103.374</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46122.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>103.201</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46122.9375</v>
+      </c>
+      <c r="B188">
+        <v>103.158</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46122.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>102.906</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46122.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46122.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46122.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46122.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46129.01041666666</v>
+        <v>46132.01041666666</v>
       </c>
       <c r="B2">
-        <v>492.289</v>
+        <v>432.708</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46129.02083333334</v>
+        <v>46132.02083333334</v>
       </c>
       <c r="B3">
-        <v>470.433</v>
+        <v>441.809</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46129.03125</v>
+        <v>46132.03125</v>
       </c>
       <c r="B4">
-        <v>450.249</v>
+        <v>452.109</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46129.04166666666</v>
+        <v>46132.04166666666</v>
       </c>
       <c r="B5">
-        <v>424.939</v>
+        <v>448.302</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46129.05208333334</v>
+        <v>46132.05208333334</v>
       </c>
       <c r="B6">
-        <v>384.318</v>
+        <v>465.917</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46129.0625</v>
+        <v>46132.0625</v>
       </c>
       <c r="B7">
-        <v>366.312</v>
+        <v>472.364</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46129.07291666666</v>
+        <v>46132.07291666666</v>
       </c>
       <c r="B8">
-        <v>345.968</v>
+        <v>462.461</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46129.08333333334</v>
+        <v>46132.08333333334</v>
       </c>
       <c r="B9">
-        <v>327.101</v>
+        <v>445.559</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46129.09375</v>
+        <v>46132.09375</v>
       </c>
       <c r="B10">
-        <v>299.321</v>
+        <v>466.258</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46129.10416666666</v>
+        <v>46132.10416666666</v>
       </c>
       <c r="B11">
-        <v>283.355</v>
+        <v>450.039</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46129.11458333334</v>
+        <v>46132.11458333334</v>
       </c>
       <c r="B12">
-        <v>273.912</v>
+        <v>479.346</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46129.125</v>
+        <v>46132.125</v>
       </c>
       <c r="B13">
-        <v>265.646</v>
+        <v>478.487</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46129.13541666666</v>
+        <v>46132.13541666666</v>
       </c>
       <c r="B14">
-        <v>255.408</v>
+        <v>510.454</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46129.14583333334</v>
+        <v>46132.14583333334</v>
       </c>
       <c r="B15">
-        <v>248.314</v>
+        <v>504.502</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46129.15625</v>
+        <v>46132.15625</v>
       </c>
       <c r="B16">
-        <v>239.166</v>
+        <v>529.279</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46129.16666666666</v>
+        <v>46132.16666666666</v>
       </c>
       <c r="B17">
-        <v>232.88</v>
+        <v>533.029</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46129.17708333334</v>
+        <v>46132.17708333334</v>
       </c>
       <c r="B18">
-        <v>241.677</v>
+        <v>553.497</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46129.1875</v>
+        <v>46132.1875</v>
       </c>
       <c r="B19">
-        <v>232.256</v>
+        <v>558.114</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46129.19791666666</v>
+        <v>46132.19791666666</v>
       </c>
       <c r="B20">
-        <v>224.945</v>
+        <v>557.848</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46129.20833333334</v>
+        <v>46132.20833333334</v>
       </c>
       <c r="B21">
-        <v>218.791</v>
+        <v>559.373</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46129.21875</v>
+        <v>46132.21875</v>
       </c>
       <c r="B22">
-        <v>197.97</v>
+        <v>558.3390000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46129.22916666666</v>
+        <v>46132.22916666666</v>
       </c>
       <c r="B23">
-        <v>189.546</v>
+        <v>556.898</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46129.23958333334</v>
+        <v>46132.23958333334</v>
       </c>
       <c r="B24">
-        <v>212.254</v>
+        <v>590.338</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46129.25</v>
+        <v>46132.25</v>
       </c>
       <c r="B25">
-        <v>208.106</v>
+        <v>592.871</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46129.26041666666</v>
+        <v>46132.26041666666</v>
       </c>
       <c r="B26">
-        <v>203.017</v>
+        <v>561.0700000000001</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46129.27083333334</v>
+        <v>46132.27083333334</v>
       </c>
       <c r="B27">
-        <v>199.185</v>
+        <v>568.5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46129.28125</v>
+        <v>46132.28125</v>
       </c>
       <c r="B28">
-        <v>194.304</v>
+        <v>555.579</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46129.29166666666</v>
+        <v>46132.29166666666</v>
       </c>
       <c r="B29">
-        <v>190.044</v>
+        <v>556.778</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46129.30208333334</v>
+        <v>46132.30208333334</v>
       </c>
       <c r="B30">
-        <v>174.644</v>
+        <v>529.5700000000001</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46129.3125</v>
+        <v>46132.3125</v>
       </c>
       <c r="B31">
-        <v>168.972</v>
+        <v>524.929</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46129.32291666666</v>
+        <v>46132.32291666666</v>
       </c>
       <c r="B32">
-        <v>157.268</v>
+        <v>498.782</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46129.33333333334</v>
+        <v>46132.33333333334</v>
       </c>
       <c r="B33">
-        <v>149.267</v>
+        <v>481.623</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46129.34375</v>
+        <v>46132.34375</v>
       </c>
       <c r="B34">
-        <v>128.096</v>
+        <v>474.739</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46129.35416666666</v>
+        <v>46132.35416666666</v>
       </c>
       <c r="B35">
-        <v>119.716</v>
+        <v>469.586</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46129.36458333334</v>
+        <v>46132.36458333334</v>
       </c>
       <c r="B36">
-        <v>108.219</v>
+        <v>455.636</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46129.375</v>
+        <v>46132.375</v>
       </c>
       <c r="B37">
-        <v>101.987</v>
+        <v>449.774</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46129.38541666666</v>
+        <v>46132.38541666666</v>
       </c>
       <c r="B38">
-        <v>99.98999999999999</v>
+        <v>528.0549999999999</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46129.39583333334</v>
+        <v>46132.39583333334</v>
       </c>
       <c r="B39">
-        <v>101.639</v>
+        <v>578.211</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46129.40625</v>
+        <v>46132.40625</v>
       </c>
       <c r="B40">
-        <v>106.323</v>
+        <v>628.5700000000001</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46129.41666666666</v>
+        <v>46132.41666666666</v>
       </c>
       <c r="B41">
-        <v>111.178</v>
+        <v>680.249</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46129.42708333334</v>
+        <v>46132.42708333334</v>
       </c>
       <c r="B42">
-        <v>122.041</v>
+        <v>765.114</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46129.4375</v>
+        <v>46132.4375</v>
       </c>
       <c r="B43">
-        <v>127.32</v>
+        <v>823.2329999999999</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46129.44791666666</v>
+        <v>46132.44791666666</v>
       </c>
       <c r="B44">
-        <v>132.758</v>
+        <v>881.218</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46129.45833333334</v>
+        <v>46132.45833333334</v>
       </c>
       <c r="B45">
-        <v>137.693</v>
+        <v>926.2809999999999</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46129.46875</v>
+        <v>46132.46875</v>
       </c>
       <c r="B46">
-        <v>147.869</v>
+        <v>988.7910000000001</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46129.47916666666</v>
+        <v>46132.47916666666</v>
       </c>
       <c r="B47">
-        <v>151.088</v>
+        <v>1029.472</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46129.48958333334</v>
+        <v>46132.48958333334</v>
       </c>
       <c r="B48">
-        <v>154.678</v>
+        <v>1070.07</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46129.5</v>
+        <v>46132.5</v>
       </c>
       <c r="B49">
-        <v>159.297</v>
+        <v>1112.707</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46129.51041666666</v>
+        <v>46132.51041666666</v>
       </c>
       <c r="B50">
-        <v>149.505</v>
+        <v>1158.154</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46129.52083333334</v>
+        <v>46132.52083333334</v>
       </c>
       <c r="B51">
-        <v>152.66</v>
+        <v>1202.716</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46129.53125</v>
+        <v>46132.53125</v>
       </c>
       <c r="B52">
-        <v>156.874</v>
+        <v>1247.382</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46129.54166666666</v>
+        <v>46132.54166666666</v>
       </c>
       <c r="B53">
-        <v>159.964</v>
+        <v>1291.131</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46129.55208333334</v>
+        <v>46132.55208333334</v>
       </c>
       <c r="B54">
-        <v>163.73</v>
+        <v>1325.232</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46129.5625</v>
+        <v>46132.5625</v>
       </c>
       <c r="B55">
-        <v>168.04</v>
+        <v>1355.936</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46129.57291666666</v>
+        <v>46132.57291666666</v>
       </c>
       <c r="B56">
-        <v>171.965</v>
+        <v>1386.313</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46129.58333333334</v>
+        <v>46132.58333333334</v>
       </c>
       <c r="B57">
-        <v>175.952</v>
+        <v>1415.796</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46129.59375</v>
+        <v>46132.59375</v>
       </c>
       <c r="B58">
-        <v>172.821</v>
+        <v>1460.35</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46129.60416666666</v>
+        <v>46132.60416666666</v>
       </c>
       <c r="B59">
-        <v>177.526</v>
+        <v>1471.689</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46129.61458333334</v>
+        <v>46132.61458333334</v>
       </c>
       <c r="B60">
-        <v>182.393</v>
+        <v>1482.595</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46129.625</v>
+        <v>46132.625</v>
       </c>
       <c r="B61">
-        <v>186.972</v>
+        <v>1492.8</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46129.63541666666</v>
+        <v>46132.63541666666</v>
       </c>
       <c r="B62">
-        <v>193.94</v>
+        <v>1533.11</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46129.64583333334</v>
+        <v>46132.64583333334</v>
       </c>
       <c r="B63">
-        <v>201.676</v>
+        <v>1539.277</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46129.65625</v>
+        <v>46132.65625</v>
       </c>
       <c r="B64">
-        <v>208.28</v>
+        <v>1544.006</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46129.66666666666</v>
+        <v>46132.66666666666</v>
       </c>
       <c r="B65">
-        <v>214.292</v>
+        <v>1550.109</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46129.67708333334</v>
+        <v>46132.67708333334</v>
       </c>
       <c r="B66">
-        <v>219.51</v>
+        <v>1438.04</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46129.6875</v>
+        <v>46132.6875</v>
       </c>
       <c r="B67">
-        <v>224.067</v>
+        <v>1450.791</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46129.69791666666</v>
+        <v>46132.69791666666</v>
       </c>
       <c r="B68">
-        <v>227.76</v>
+        <v>1466.04</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46129.70833333334</v>
+        <v>46132.70833333334</v>
       </c>
       <c r="B69">
-        <v>230.483</v>
+        <v>1491.632</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46129.71875</v>
+        <v>46132.71875</v>
       </c>
       <c r="B70">
-        <v>229.954</v>
+        <v>1494.439</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46129.72916666666</v>
+        <v>46132.72916666666</v>
       </c>
       <c r="B71">
-        <v>233.124</v>
+        <v>1514.649</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46129.73958333334</v>
+        <v>46132.73958333334</v>
       </c>
       <c r="B72">
-        <v>235.809</v>
+        <v>1543.387</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46129.75</v>
+        <v>46132.75</v>
       </c>
       <c r="B73">
-        <v>239.164</v>
+        <v>1562.521</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46129.76041666666</v>
+        <v>46132.76041666666</v>
       </c>
       <c r="B74">
-        <v>248.793</v>
+        <v>1550.375</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46129.77083333334</v>
+        <v>46132.77083333334</v>
       </c>
       <c r="B75">
-        <v>250.9</v>
+        <v>1494.685</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46129.78125</v>
+        <v>46132.78125</v>
       </c>
       <c r="B76">
-        <v>252.83</v>
+        <v>1439.056</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46129.79166666666</v>
+        <v>46132.79166666666</v>
       </c>
       <c r="B77">
-        <v>255.55</v>
+        <v>1385.868</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46129.80208333334</v>
+        <v>46132.80208333334</v>
       </c>
       <c r="B78">
-        <v>250.756</v>
+        <v>1297.875</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46129.8125</v>
+        <v>46132.8125</v>
       </c>
       <c r="B79">
-        <v>247.006</v>
+        <v>1237.708</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46129.82291666666</v>
+        <v>46132.82291666666</v>
       </c>
       <c r="B80">
-        <v>242.379</v>
+        <v>1178.866</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46129.83333333334</v>
+        <v>46132.83333333334</v>
       </c>
       <c r="B81">
-        <v>236.831</v>
+        <v>1119.838</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46129.84375</v>
+        <v>46132.84375</v>
       </c>
       <c r="B82">
-        <v>227.465</v>
+        <v>1058.792</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46129.85416666666</v>
+        <v>46132.85416666666</v>
       </c>
       <c r="B83">
-        <v>221.904</v>
+        <v>1038.445</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46129.86458333334</v>
+        <v>46132.86458333334</v>
       </c>
       <c r="B84">
-        <v>215.489</v>
+        <v>1020.379</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46129.875</v>
+        <v>46132.875</v>
       </c>
       <c r="B85">
-        <v>208.289</v>
+        <v>1004.859</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46129.88541666666</v>
+        <v>46132.88541666666</v>
       </c>
       <c r="B86">
-        <v>197.694</v>
+        <v>979.351</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46129.89583333334</v>
+        <v>46132.89583333334</v>
       </c>
       <c r="B87">
-        <v>195.738</v>
+        <v>966.115</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46129.90625</v>
+        <v>46132.90625</v>
       </c>
       <c r="B88">
-        <v>193.064</v>
+        <v>955.16</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46129.91666666666</v>
+        <v>46132.91666666666</v>
       </c>
       <c r="B89">
-        <v>190.67</v>
+        <v>943.016</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46129.92708333334</v>
+        <v>46132.92708333334</v>
       </c>
       <c r="B90">
-        <v>190.547</v>
+        <v>923.506</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46129.9375</v>
+        <v>46132.9375</v>
       </c>
       <c r="B91">
-        <v>200.607</v>
+        <v>907.62</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46129.94791666666</v>
+        <v>46132.94791666666</v>
       </c>
       <c r="B92">
-        <v>211.629</v>
+        <v>892.739</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46129.95833333334</v>
+        <v>46132.95833333334</v>
       </c>
       <c r="B93">
-        <v>223.221</v>
+        <v>880.611</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46129.96875</v>
+        <v>46132.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46129.97916666666</v>
+        <v>46132.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46129.98958333334</v>
+        <v>46132.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46130</v>
+        <v>46133</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46132.01041666666</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B2">
-        <v>432.708</v>
+        <v>861.976</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46132.02083333334</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B3">
-        <v>441.809</v>
+        <v>898.958</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46132.03125</v>
+        <v>46133.03125</v>
       </c>
       <c r="B4">
-        <v>452.109</v>
+        <v>928.774</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46132.04166666666</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B5">
-        <v>448.302</v>
+        <v>948.021</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46132.05208333334</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B6">
-        <v>465.917</v>
+        <v>1077.874</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46132.0625</v>
+        <v>46133.0625</v>
       </c>
       <c r="B7">
-        <v>472.364</v>
+        <v>1133.461</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46132.07291666666</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B8">
-        <v>462.461</v>
+        <v>1182.254</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46132.08333333334</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B9">
-        <v>445.559</v>
+        <v>1216.081</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46132.09375</v>
+        <v>46133.09375</v>
       </c>
       <c r="B10">
-        <v>466.258</v>
+        <v>1274.183</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46132.10416666666</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B11">
-        <v>450.039</v>
+        <v>1324.831</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46132.11458333334</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B12">
-        <v>479.346</v>
+        <v>1348.891</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46132.125</v>
+        <v>46133.125</v>
       </c>
       <c r="B13">
-        <v>478.487</v>
+        <v>1376.946</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46132.13541666666</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B14">
-        <v>510.454</v>
+        <v>1404.427</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46132.14583333334</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B15">
-        <v>504.502</v>
+        <v>1414.548</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46132.15625</v>
+        <v>46133.15625</v>
       </c>
       <c r="B16">
-        <v>529.279</v>
+        <v>1430.951</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46132.16666666666</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B17">
-        <v>533.029</v>
+        <v>1447.523</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46132.17708333334</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B18">
-        <v>553.497</v>
+        <v>1484.44</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46132.1875</v>
+        <v>46133.1875</v>
       </c>
       <c r="B19">
-        <v>558.114</v>
+        <v>1503.468</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46132.19791666666</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B20">
-        <v>557.848</v>
+        <v>1522.836</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46132.20833333334</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B21">
-        <v>559.373</v>
+        <v>1544.936</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46132.21875</v>
+        <v>46133.21875</v>
       </c>
       <c r="B22">
-        <v>558.3390000000001</v>
+        <v>1507.048</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46132.22916666666</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B23">
-        <v>556.898</v>
+        <v>1529.185</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46132.23958333334</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B24">
-        <v>590.338</v>
+        <v>1547.264</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46132.25</v>
+        <v>46133.25</v>
       </c>
       <c r="B25">
-        <v>592.871</v>
+        <v>1567.177</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46132.26041666666</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B26">
-        <v>561.0700000000001</v>
+        <v>1548.791</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46132.27083333334</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B27">
-        <v>568.5</v>
+        <v>1528.274</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46132.28125</v>
+        <v>46133.28125</v>
       </c>
       <c r="B28">
-        <v>555.579</v>
+        <v>1514.297</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46132.29166666666</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B29">
-        <v>556.778</v>
+        <v>1508.218</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46132.30208333334</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B30">
-        <v>529.5700000000001</v>
+        <v>1450.05</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46132.3125</v>
+        <v>46133.3125</v>
       </c>
       <c r="B31">
-        <v>524.929</v>
+        <v>1428.46</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46132.32291666666</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B32">
-        <v>498.782</v>
+        <v>1402.589</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46132.33333333334</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B33">
-        <v>481.623</v>
+        <v>1371.67</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46132.34375</v>
+        <v>46133.34375</v>
       </c>
       <c r="B34">
-        <v>474.739</v>
+        <v>1398.347</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46132.35416666666</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B35">
-        <v>469.586</v>
+        <v>1360.717</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46132.36458333334</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B36">
-        <v>455.636</v>
+        <v>1335.17</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46132.375</v>
+        <v>46133.375</v>
       </c>
       <c r="B37">
-        <v>449.774</v>
+        <v>1296.393</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46132.38541666666</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B38">
-        <v>528.0549999999999</v>
+        <v>1226.429</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46132.39583333334</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B39">
-        <v>578.211</v>
+        <v>1196.936</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46132.40625</v>
+        <v>46133.40625</v>
       </c>
       <c r="B40">
-        <v>628.5700000000001</v>
+        <v>1167.024</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46132.41666666666</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B41">
-        <v>680.249</v>
+        <v>1137.75</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46132.42708333334</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B42">
-        <v>765.114</v>
+        <v>1080.848</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46132.4375</v>
+        <v>46133.4375</v>
       </c>
       <c r="B43">
-        <v>823.2329999999999</v>
+        <v>1055.565</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46132.44791666666</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B44">
-        <v>881.218</v>
+        <v>1028.35</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46132.45833333334</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B45">
-        <v>926.2809999999999</v>
+        <v>992.583</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46132.46875</v>
+        <v>46133.46875</v>
       </c>
       <c r="B46">
-        <v>988.7910000000001</v>
+        <v>962.218</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46132.47916666666</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B47">
-        <v>1029.472</v>
+        <v>926.774</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46132.48958333334</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B48">
-        <v>1070.07</v>
+        <v>903.449</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46132.5</v>
+        <v>46133.5</v>
       </c>
       <c r="B49">
-        <v>1112.707</v>
+        <v>879.111</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46132.51041666666</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B50">
-        <v>1158.154</v>
+        <v>854.42</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46132.52083333334</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B51">
-        <v>1202.716</v>
+        <v>826.579</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46132.53125</v>
+        <v>46133.53125</v>
       </c>
       <c r="B52">
-        <v>1247.382</v>
+        <v>795.973</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46132.54166666666</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B53">
-        <v>1291.131</v>
+        <v>768.671</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46132.55208333334</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B54">
-        <v>1325.232</v>
+        <v>737.912</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46132.5625</v>
+        <v>46133.5625</v>
       </c>
       <c r="B55">
-        <v>1355.936</v>
+        <v>716.249</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46132.57291666666</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B56">
-        <v>1386.313</v>
+        <v>694.509</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46132.58333333334</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B57">
-        <v>1415.796</v>
+        <v>673.726</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46132.59375</v>
+        <v>46133.59375</v>
       </c>
       <c r="B58">
-        <v>1460.35</v>
+        <v>652.4400000000001</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46132.60416666666</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B59">
-        <v>1471.689</v>
+        <v>628.48</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46132.61458333334</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B60">
-        <v>1482.595</v>
+        <v>603.484</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46132.625</v>
+        <v>46133.625</v>
       </c>
       <c r="B61">
-        <v>1492.8</v>
+        <v>577.245</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46132.63541666666</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B62">
-        <v>1533.11</v>
+        <v>479.83</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46132.64583333334</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B63">
-        <v>1539.277</v>
+        <v>465.959</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46132.65625</v>
+        <v>46133.65625</v>
       </c>
       <c r="B64">
-        <v>1544.006</v>
+        <v>447.618</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46132.66666666666</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B65">
-        <v>1550.109</v>
+        <v>438.696</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46132.67708333334</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B66">
-        <v>1438.04</v>
+        <v>384.676</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46132.6875</v>
+        <v>46133.6875</v>
       </c>
       <c r="B67">
-        <v>1450.791</v>
+        <v>380.195</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46132.69791666666</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B68">
-        <v>1466.04</v>
+        <v>372.484</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46132.70833333334</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B69">
-        <v>1491.632</v>
+        <v>368.806</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46132.71875</v>
+        <v>46133.71875</v>
       </c>
       <c r="B70">
-        <v>1494.439</v>
+        <v>359.26</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46132.72916666666</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B71">
-        <v>1514.649</v>
+        <v>344.714</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46132.73958333334</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B72">
-        <v>1543.387</v>
+        <v>330.445</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46132.75</v>
+        <v>46133.75</v>
       </c>
       <c r="B73">
-        <v>1562.521</v>
+        <v>316.297</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46132.76041666666</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B74">
-        <v>1550.375</v>
+        <v>289.643</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46132.77083333334</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B75">
-        <v>1494.685</v>
+        <v>280.347</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46132.78125</v>
+        <v>46133.78125</v>
       </c>
       <c r="B76">
-        <v>1439.056</v>
+        <v>272.872</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46132.79166666666</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B77">
-        <v>1385.868</v>
+        <v>266.022</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46132.80208333334</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B78">
-        <v>1297.875</v>
+        <v>257.366</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46132.8125</v>
+        <v>46133.8125</v>
       </c>
       <c r="B79">
-        <v>1237.708</v>
+        <v>257.522</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46132.82291666666</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B80">
-        <v>1178.866</v>
+        <v>257.86</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46132.83333333334</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B81">
-        <v>1119.838</v>
+        <v>282.689</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46132.84375</v>
+        <v>46133.84375</v>
       </c>
       <c r="B82">
-        <v>1058.792</v>
+        <v>253.54</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46132.85416666666</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B83">
-        <v>1038.445</v>
+        <v>250.577</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46132.86458333334</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B84">
-        <v>1020.379</v>
+        <v>248.198</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46132.875</v>
+        <v>46133.875</v>
       </c>
       <c r="B85">
-        <v>1004.859</v>
+        <v>245.698</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46132.88541666666</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B86">
-        <v>979.351</v>
+        <v>241.75</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46132.89583333334</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B87">
-        <v>966.115</v>
+        <v>241.722</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46132.90625</v>
+        <v>46133.90625</v>
       </c>
       <c r="B88">
-        <v>955.16</v>
+        <v>242.544</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46132.91666666666</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B89">
-        <v>943.016</v>
+        <v>242.781</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46132.92708333334</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B90">
-        <v>923.506</v>
+        <v>244.823</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46132.9375</v>
+        <v>46133.9375</v>
       </c>
       <c r="B91">
-        <v>907.62</v>
+        <v>244.969</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46132.94791666666</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B92">
-        <v>892.739</v>
+        <v>245.517</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46132.95833333334</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B93">
-        <v>880.611</v>
+        <v>246.372</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46132.96875</v>
+        <v>46133.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46132.97916666666</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46132.98958333334</v>
+        <v>46133.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46133.01041666666</v>
+        <v>46133</v>
       </c>
       <c r="B2">
         <v>861.976</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46133.02083333334</v>
+        <v>46133.01041666666</v>
       </c>
       <c r="B3">
         <v>898.958</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46133.03125</v>
+        <v>46133.02083333334</v>
       </c>
       <c r="B4">
         <v>928.774</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46133.04166666666</v>
+        <v>46133.03125</v>
       </c>
       <c r="B5">
         <v>948.021</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46133.05208333334</v>
+        <v>46133.04166666666</v>
       </c>
       <c r="B6">
         <v>1077.874</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46133.0625</v>
+        <v>46133.05208333334</v>
       </c>
       <c r="B7">
         <v>1133.461</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46133.07291666666</v>
+        <v>46133.0625</v>
       </c>
       <c r="B8">
         <v>1182.254</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46133.08333333334</v>
+        <v>46133.07291666666</v>
       </c>
       <c r="B9">
         <v>1216.081</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46133.09375</v>
+        <v>46133.08333333334</v>
       </c>
       <c r="B10">
         <v>1274.183</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46133.10416666666</v>
+        <v>46133.09375</v>
       </c>
       <c r="B11">
         <v>1324.831</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46133.11458333334</v>
+        <v>46133.10416666666</v>
       </c>
       <c r="B12">
         <v>1348.891</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46133.125</v>
+        <v>46133.11458333334</v>
       </c>
       <c r="B13">
         <v>1376.946</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46133.13541666666</v>
+        <v>46133.125</v>
       </c>
       <c r="B14">
         <v>1404.427</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46133.14583333334</v>
+        <v>46133.13541666666</v>
       </c>
       <c r="B15">
         <v>1414.548</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46133.15625</v>
+        <v>46133.14583333334</v>
       </c>
       <c r="B16">
         <v>1430.951</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46133.16666666666</v>
+        <v>46133.15625</v>
       </c>
       <c r="B17">
         <v>1447.523</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46133.17708333334</v>
+        <v>46133.16666666666</v>
       </c>
       <c r="B18">
         <v>1484.44</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46133.1875</v>
+        <v>46133.17708333334</v>
       </c>
       <c r="B19">
         <v>1503.468</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46133.19791666666</v>
+        <v>46133.1875</v>
       </c>
       <c r="B20">
         <v>1522.836</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46133.20833333334</v>
+        <v>46133.19791666666</v>
       </c>
       <c r="B21">
         <v>1544.936</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46133.21875</v>
+        <v>46133.20833333334</v>
       </c>
       <c r="B22">
         <v>1507.048</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46133.22916666666</v>
+        <v>46133.21875</v>
       </c>
       <c r="B23">
         <v>1529.185</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46133.23958333334</v>
+        <v>46133.22916666666</v>
       </c>
       <c r="B24">
         <v>1547.264</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46133.25</v>
+        <v>46133.23958333334</v>
       </c>
       <c r="B25">
         <v>1567.177</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46133.26041666666</v>
+        <v>46133.25</v>
       </c>
       <c r="B26">
         <v>1548.791</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46133.27083333334</v>
+        <v>46133.26041666666</v>
       </c>
       <c r="B27">
         <v>1528.274</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46133.28125</v>
+        <v>46133.27083333334</v>
       </c>
       <c r="B28">
         <v>1514.297</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46133.29166666666</v>
+        <v>46133.28125</v>
       </c>
       <c r="B29">
         <v>1508.218</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46133.30208333334</v>
+        <v>46133.29166666666</v>
       </c>
       <c r="B30">
         <v>1450.05</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46133.3125</v>
+        <v>46133.30208333334</v>
       </c>
       <c r="B31">
         <v>1428.46</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46133.32291666666</v>
+        <v>46133.3125</v>
       </c>
       <c r="B32">
         <v>1402.589</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46133.33333333334</v>
+        <v>46133.32291666666</v>
       </c>
       <c r="B33">
         <v>1371.67</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46133.34375</v>
+        <v>46133.33333333334</v>
       </c>
       <c r="B34">
         <v>1398.347</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46133.35416666666</v>
+        <v>46133.34375</v>
       </c>
       <c r="B35">
         <v>1360.717</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46133.36458333334</v>
+        <v>46133.35416666666</v>
       </c>
       <c r="B36">
         <v>1335.17</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46133.375</v>
+        <v>46133.36458333334</v>
       </c>
       <c r="B37">
         <v>1296.393</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46133.38541666666</v>
+        <v>46133.375</v>
       </c>
       <c r="B38">
         <v>1226.429</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46133.39583333334</v>
+        <v>46133.38541666666</v>
       </c>
       <c r="B39">
         <v>1196.936</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46133.40625</v>
+        <v>46133.39583333334</v>
       </c>
       <c r="B40">
         <v>1167.024</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46133.41666666666</v>
+        <v>46133.40625</v>
       </c>
       <c r="B41">
         <v>1137.75</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46133.42708333334</v>
+        <v>46133.41666666666</v>
       </c>
       <c r="B42">
         <v>1080.848</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46133.4375</v>
+        <v>46133.42708333334</v>
       </c>
       <c r="B43">
         <v>1055.565</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46133.44791666666</v>
+        <v>46133.4375</v>
       </c>
       <c r="B44">
         <v>1028.35</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46133.45833333334</v>
+        <v>46133.44791666666</v>
       </c>
       <c r="B45">
         <v>992.583</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46133.46875</v>
+        <v>46133.45833333334</v>
       </c>
       <c r="B46">
         <v>962.218</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46133.47916666666</v>
+        <v>46133.46875</v>
       </c>
       <c r="B47">
         <v>926.774</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46133.48958333334</v>
+        <v>46133.47916666666</v>
       </c>
       <c r="B48">
         <v>903.449</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46133.5</v>
+        <v>46133.48958333334</v>
       </c>
       <c r="B49">
         <v>879.111</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46133.51041666666</v>
+        <v>46133.5</v>
       </c>
       <c r="B50">
         <v>854.42</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46133.52083333334</v>
+        <v>46133.51041666666</v>
       </c>
       <c r="B51">
         <v>826.579</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46133.53125</v>
+        <v>46133.52083333334</v>
       </c>
       <c r="B52">
         <v>795.973</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46133.54166666666</v>
+        <v>46133.53125</v>
       </c>
       <c r="B53">
         <v>768.671</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46133.55208333334</v>
+        <v>46133.54166666666</v>
       </c>
       <c r="B54">
         <v>737.912</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46133.5625</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="B55">
         <v>716.249</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46133.57291666666</v>
+        <v>46133.5625</v>
       </c>
       <c r="B56">
         <v>694.509</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46133.58333333334</v>
+        <v>46133.57291666666</v>
       </c>
       <c r="B57">
         <v>673.726</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46133.59375</v>
+        <v>46133.58333333334</v>
       </c>
       <c r="B58">
         <v>652.4400000000001</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46133.60416666666</v>
+        <v>46133.59375</v>
       </c>
       <c r="B59">
         <v>628.48</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46133.61458333334</v>
+        <v>46133.60416666666</v>
       </c>
       <c r="B60">
         <v>603.484</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46133.625</v>
+        <v>46133.61458333334</v>
       </c>
       <c r="B61">
         <v>577.245</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46133.63541666666</v>
+        <v>46133.625</v>
       </c>
       <c r="B62">
         <v>479.83</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46133.64583333334</v>
+        <v>46133.63541666666</v>
       </c>
       <c r="B63">
         <v>465.959</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46133.65625</v>
+        <v>46133.64583333334</v>
       </c>
       <c r="B64">
         <v>447.618</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46133.66666666666</v>
+        <v>46133.65625</v>
       </c>
       <c r="B65">
         <v>438.696</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46133.67708333334</v>
+        <v>46133.66666666666</v>
       </c>
       <c r="B66">
         <v>384.676</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46133.6875</v>
+        <v>46133.67708333334</v>
       </c>
       <c r="B67">
         <v>380.195</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46133.69791666666</v>
+        <v>46133.6875</v>
       </c>
       <c r="B68">
         <v>372.484</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46133.70833333334</v>
+        <v>46133.69791666666</v>
       </c>
       <c r="B69">
         <v>368.806</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46133.71875</v>
+        <v>46133.70833333334</v>
       </c>
       <c r="B70">
         <v>359.26</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46133.72916666666</v>
+        <v>46133.71875</v>
       </c>
       <c r="B71">
         <v>344.714</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46133.73958333334</v>
+        <v>46133.72916666666</v>
       </c>
       <c r="B72">
         <v>330.445</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46133.75</v>
+        <v>46133.73958333334</v>
       </c>
       <c r="B73">
         <v>316.297</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46133.76041666666</v>
+        <v>46133.75</v>
       </c>
       <c r="B74">
         <v>289.643</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46133.77083333334</v>
+        <v>46133.76041666666</v>
       </c>
       <c r="B75">
         <v>280.347</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46133.78125</v>
+        <v>46133.77083333334</v>
       </c>
       <c r="B76">
         <v>272.872</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46133.79166666666</v>
+        <v>46133.78125</v>
       </c>
       <c r="B77">
         <v>266.022</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46133.80208333334</v>
+        <v>46133.79166666666</v>
       </c>
       <c r="B78">
         <v>257.366</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46133.8125</v>
+        <v>46133.80208333334</v>
       </c>
       <c r="B79">
         <v>257.522</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46133.82291666666</v>
+        <v>46133.8125</v>
       </c>
       <c r="B80">
         <v>257.86</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46133.83333333334</v>
+        <v>46133.82291666666</v>
       </c>
       <c r="B81">
         <v>282.689</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46133.84375</v>
+        <v>46133.83333333334</v>
       </c>
       <c r="B82">
         <v>253.54</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46133.85416666666</v>
+        <v>46133.84375</v>
       </c>
       <c r="B83">
         <v>250.577</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46133.86458333334</v>
+        <v>46133.85416666666</v>
       </c>
       <c r="B84">
         <v>248.198</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46133.875</v>
+        <v>46133.86458333334</v>
       </c>
       <c r="B85">
         <v>245.698</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46133.88541666666</v>
+        <v>46133.875</v>
       </c>
       <c r="B86">
         <v>241.75</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46133.89583333334</v>
+        <v>46133.88541666666</v>
       </c>
       <c r="B87">
         <v>241.722</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46133.90625</v>
+        <v>46133.89583333334</v>
       </c>
       <c r="B88">
         <v>242.544</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46133.91666666666</v>
+        <v>46133.90625</v>
       </c>
       <c r="B89">
         <v>242.781</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46133.92708333334</v>
+        <v>46133.91666666666</v>
       </c>
       <c r="B90">
         <v>244.823</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46133.9375</v>
+        <v>46133.92708333334</v>
       </c>
       <c r="B91">
         <v>244.969</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46133.94791666666</v>
+        <v>46133.9375</v>
       </c>
       <c r="B92">
         <v>245.517</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46133.95833333334</v>
+        <v>46133.94791666666</v>
       </c>
       <c r="B93">
         <v>246.372</v>
@@ -1130,33 +1130,801 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46133.96875</v>
+        <v>46133.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>191.294</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46133.97916666666</v>
+        <v>46133.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>187.847</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46133.98958333334</v>
+        <v>46133.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>191.819</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
+        <v>46133.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>191.992</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>46134</v>
       </c>
-      <c r="B97">
+      <c r="B98">
+        <v>158.174</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46134.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>155.872</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46134.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>153.695</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46134.03125</v>
+      </c>
+      <c r="B101">
+        <v>151.473</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46134.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>160.64</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46134.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>160.307</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46134.0625</v>
+      </c>
+      <c r="B104">
+        <v>159.694</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46134.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>164.316</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46134.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>151.49</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46134.09375</v>
+      </c>
+      <c r="B107">
+        <v>148.96</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46134.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>146.664</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46134.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>144.892</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46134.125</v>
+      </c>
+      <c r="B110">
+        <v>138.836</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46134.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>139.182</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46134.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>134.931</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46134.15625</v>
+      </c>
+      <c r="B113">
+        <v>133.371</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46134.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>130.362</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46134.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>129.74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46134.1875</v>
+      </c>
+      <c r="B116">
+        <v>128.585</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46134.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>128.406</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46134.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>126.483</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46134.21875</v>
+      </c>
+      <c r="B119">
+        <v>130.537</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46134.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>127.264</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46134.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>126.524</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46134.25</v>
+      </c>
+      <c r="B122">
+        <v>126.459</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46134.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>124.088</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46134.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>122.142</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46134.28125</v>
+      </c>
+      <c r="B125">
+        <v>122.967</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46134.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>114.014</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46134.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>104.521</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46134.3125</v>
+      </c>
+      <c r="B128">
+        <v>105.309</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46134.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>102.014</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46134.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>101.664</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46134.34375</v>
+      </c>
+      <c r="B131">
+        <v>103.078</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46134.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>106.413</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46134.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>107.525</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46134.375</v>
+      </c>
+      <c r="B134">
+        <v>117.023</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46134.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>117.767</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46134.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>120.02</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46134.40625</v>
+      </c>
+      <c r="B137">
+        <v>122.091</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46134.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>132.836</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46134.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>136.99</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46134.4375</v>
+      </c>
+      <c r="B140">
+        <v>142.054</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46134.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>146.909</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46134.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>157.659</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46134.46875</v>
+      </c>
+      <c r="B143">
+        <v>161.587</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46134.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>166.04</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46134.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>171.034</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46134.5</v>
+      </c>
+      <c r="B146">
+        <v>177.005</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46134.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>183.822</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46134.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>190.732</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46134.53125</v>
+      </c>
+      <c r="B149">
+        <v>198.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46134.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>207.101</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46134.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>211.85</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46134.5625</v>
+      </c>
+      <c r="B152">
+        <v>215.998</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46134.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>220.702</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46134.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>209.954</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46134.59375</v>
+      </c>
+      <c r="B155">
+        <v>212.789</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46134.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>215.351</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46134.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>218.587</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46134.625</v>
+      </c>
+      <c r="B158">
+        <v>216.018</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46134.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>217.418</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46134.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>218.832</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46134.65625</v>
+      </c>
+      <c r="B161">
+        <v>220.038</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46134.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>202.203</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46134.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>202.076</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46134.6875</v>
+      </c>
+      <c r="B164">
+        <v>202.339</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46134.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>202.629</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46134.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>204.068</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46134.71875</v>
+      </c>
+      <c r="B167">
+        <v>201.438</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46134.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>197.952</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46134.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>194.897</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46134.75</v>
+      </c>
+      <c r="B170">
+        <v>186.38</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46134.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>183.014</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46134.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>182.938</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46134.78125</v>
+      </c>
+      <c r="B173">
+        <v>180.603</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46134.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>179.394</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46134.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>178.479</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46134.8125</v>
+      </c>
+      <c r="B176">
+        <v>177.533</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46134.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>204.031</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46134.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>204.143</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46134.84375</v>
+      </c>
+      <c r="B179">
+        <v>183.175</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46134.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>174.296</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46134.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>172.46</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46134.875</v>
+      </c>
+      <c r="B182">
+        <v>203.364</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46134.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>181.195</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46134.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>186.171</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46134.90625</v>
+      </c>
+      <c r="B185">
+        <v>191.384</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46134.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>193.589</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46134.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>201.694</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46134.9375</v>
+      </c>
+      <c r="B188">
+        <v>209.729</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46134.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>218.427</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46134.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46134.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46134.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46134.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46139.01041666666</v>
+        <v>46142.01041666666</v>
       </c>
       <c r="B2">
-        <v>1098.587</v>
+        <v>648.849</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46139.02083333334</v>
+        <v>46142.02083333334</v>
       </c>
       <c r="B3">
-        <v>1049.537</v>
+        <v>652.102</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46139.03125</v>
+        <v>46142.03125</v>
       </c>
       <c r="B4">
-        <v>996.675</v>
+        <v>652.4349999999999</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46139.04166666666</v>
+        <v>46142.04166666666</v>
       </c>
       <c r="B5">
-        <v>995.662</v>
+        <v>657.736</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46139.05208333334</v>
+        <v>46142.05208333334</v>
       </c>
       <c r="B6">
-        <v>924.468</v>
+        <v>634.076</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46139.0625</v>
+        <v>46142.0625</v>
       </c>
       <c r="B7">
-        <v>913.903</v>
+        <v>645.49</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46139.07291666666</v>
+        <v>46142.07291666666</v>
       </c>
       <c r="B8">
-        <v>902.963</v>
+        <v>659.099</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46139.08333333334</v>
+        <v>46142.08333333334</v>
       </c>
       <c r="B9">
-        <v>874.16</v>
+        <v>675.169</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46139.09375</v>
+        <v>46142.09375</v>
       </c>
       <c r="B10">
-        <v>838.809</v>
+        <v>684.753</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46139.10416666666</v>
+        <v>46142.10416666666</v>
       </c>
       <c r="B11">
-        <v>826.361</v>
+        <v>698.7910000000001</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46139.11458333334</v>
+        <v>46142.11458333334</v>
       </c>
       <c r="B12">
-        <v>812.409</v>
+        <v>712.357</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46139.125</v>
+        <v>46142.125</v>
       </c>
       <c r="B13">
-        <v>790.47</v>
+        <v>729.8819999999999</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46139.13541666666</v>
+        <v>46142.13541666666</v>
       </c>
       <c r="B14">
-        <v>760.476</v>
+        <v>753.501</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46139.14583333334</v>
+        <v>46142.14583333334</v>
       </c>
       <c r="B15">
-        <v>769.836</v>
+        <v>774.6660000000001</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46139.15625</v>
+        <v>46142.15625</v>
       </c>
       <c r="B16">
-        <v>759.821</v>
+        <v>790.66</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46139.16666666666</v>
+        <v>46142.16666666666</v>
       </c>
       <c r="B17">
-        <v>725.421</v>
+        <v>815.938</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46139.17708333334</v>
+        <v>46142.17708333334</v>
       </c>
       <c r="B18">
-        <v>670.1420000000001</v>
+        <v>848.564</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46139.1875</v>
+        <v>46142.1875</v>
       </c>
       <c r="B19">
-        <v>649.968</v>
+        <v>868.607</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46139.19791666666</v>
+        <v>46142.19791666666</v>
       </c>
       <c r="B20">
-        <v>624.922</v>
+        <v>891.778</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46139.20833333334</v>
+        <v>46142.20833333334</v>
       </c>
       <c r="B21">
-        <v>611.199</v>
+        <v>910.2329999999999</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46139.21875</v>
+        <v>46142.21875</v>
       </c>
       <c r="B22">
-        <v>560.783</v>
+        <v>971.033</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46139.22916666666</v>
+        <v>46142.22916666666</v>
       </c>
       <c r="B23">
-        <v>528.7569999999999</v>
+        <v>996.926</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46139.23958333334</v>
+        <v>46142.23958333334</v>
       </c>
       <c r="B24">
-        <v>500.799</v>
+        <v>1022.417</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46139.25</v>
+        <v>46142.25</v>
       </c>
       <c r="B25">
-        <v>466.528</v>
+        <v>1045.328</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46139.26041666666</v>
+        <v>46142.26041666666</v>
       </c>
       <c r="B26">
-        <v>385.067</v>
+        <v>1119.208</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46139.27083333334</v>
+        <v>46142.27083333334</v>
       </c>
       <c r="B27">
-        <v>364.182</v>
+        <v>1142.173</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46139.28125</v>
+        <v>46142.28125</v>
       </c>
       <c r="B28">
-        <v>351.931</v>
+        <v>1160.553</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46139.29166666666</v>
+        <v>46142.29166666666</v>
       </c>
       <c r="B29">
-        <v>333.269</v>
+        <v>1164.352</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46139.30208333334</v>
+        <v>46142.30208333334</v>
       </c>
       <c r="B30">
-        <v>306.711</v>
+        <v>1215.261</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46139.3125</v>
+        <v>46142.3125</v>
       </c>
       <c r="B31">
-        <v>314.599</v>
+        <v>1213.192</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46139.32291666666</v>
+        <v>46142.32291666666</v>
       </c>
       <c r="B32">
-        <v>312.717</v>
+        <v>1210.118</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46139.33333333334</v>
+        <v>46142.33333333334</v>
       </c>
       <c r="B33">
-        <v>302.537</v>
+        <v>1220.582</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46139.34375</v>
+        <v>46142.34375</v>
       </c>
       <c r="B34">
-        <v>329.192</v>
+        <v>1116.184</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46139.35416666666</v>
+        <v>46142.35416666666</v>
       </c>
       <c r="B35">
-        <v>322.348</v>
+        <v>1119.482</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46139.36458333334</v>
+        <v>46142.36458333334</v>
       </c>
       <c r="B36">
-        <v>321.427</v>
+        <v>1134.834</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46139.375</v>
+        <v>46142.375</v>
       </c>
       <c r="B37">
-        <v>316.179</v>
+        <v>1142.694</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46139.38541666666</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="B38">
-        <v>322.345</v>
+        <v>1318.648</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46139.39583333334</v>
+        <v>46142.39583333334</v>
       </c>
       <c r="B39">
-        <v>306.786</v>
+        <v>1331.289</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46139.40625</v>
+        <v>46142.40625</v>
       </c>
       <c r="B40">
-        <v>290.984</v>
+        <v>1343.271</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46139.41666666666</v>
+        <v>46142.41666666666</v>
       </c>
       <c r="B41">
-        <v>275.459</v>
+        <v>1318.529</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46139.42708333334</v>
+        <v>46142.42708333334</v>
       </c>
       <c r="B42">
-        <v>277.774</v>
+        <v>1369.836</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46139.4375</v>
+        <v>46142.4375</v>
       </c>
       <c r="B43">
-        <v>266.334</v>
+        <v>1345.14</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46139.44791666666</v>
+        <v>46142.44791666666</v>
       </c>
       <c r="B44">
-        <v>255.004</v>
+        <v>1387.805</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46139.45833333334</v>
+        <v>46142.45833333334</v>
       </c>
       <c r="B45">
-        <v>244.57</v>
+        <v>1416.536</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46139.46875</v>
+        <v>46142.46875</v>
       </c>
       <c r="B46">
-        <v>199.082</v>
+        <v>1494.563</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46139.47916666666</v>
+        <v>46142.47916666666</v>
       </c>
       <c r="B47">
-        <v>181.206</v>
+        <v>1513.067</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46139.48958333334</v>
+        <v>46142.48958333334</v>
       </c>
       <c r="B48">
-        <v>169.225</v>
+        <v>1535.332</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46139.5</v>
+        <v>46142.5</v>
       </c>
       <c r="B49">
-        <v>164.601</v>
+        <v>1553.759</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46139.51041666666</v>
+        <v>46142.51041666666</v>
       </c>
       <c r="B50">
-        <v>171.219</v>
+        <v>1585.976</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46139.52083333334</v>
+        <v>46142.52083333334</v>
       </c>
       <c r="B51">
-        <v>173</v>
+        <v>1610.747</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46139.53125</v>
+        <v>46142.53125</v>
       </c>
       <c r="B52">
-        <v>174.979</v>
+        <v>1587.508</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46139.54166666666</v>
+        <v>46142.54166666666</v>
       </c>
       <c r="B53">
-        <v>176.989</v>
+        <v>1609.954</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46139.55208333334</v>
+        <v>46142.55208333334</v>
       </c>
       <c r="B54">
-        <v>183.538</v>
+        <v>1615.319</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46139.5625</v>
+        <v>46142.5625</v>
       </c>
       <c r="B55">
-        <v>189.984</v>
+        <v>1623.051</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46139.57291666666</v>
+        <v>46142.57291666666</v>
       </c>
       <c r="B56">
-        <v>195.538</v>
+        <v>1629.591</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46139.58333333334</v>
+        <v>46142.58333333334</v>
       </c>
       <c r="B57">
-        <v>202.743</v>
+        <v>1690.212</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46139.59375</v>
+        <v>46142.59375</v>
       </c>
       <c r="B58">
-        <v>218.684</v>
+        <v>1691.257</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46139.60416666666</v>
+        <v>46142.60416666666</v>
       </c>
       <c r="B59">
-        <v>245.462</v>
+        <v>1684.456</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46139.61458333334</v>
+        <v>46142.61458333334</v>
       </c>
       <c r="B60">
-        <v>271.293</v>
+        <v>1730.248</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46139.625</v>
+        <v>46142.625</v>
       </c>
       <c r="B61">
-        <v>297.991</v>
+        <v>1667.491</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46139.63541666666</v>
+        <v>46142.63541666666</v>
       </c>
       <c r="B62">
-        <v>294.546</v>
+        <v>1651.491</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46139.64583333334</v>
+        <v>46142.64583333334</v>
       </c>
       <c r="B63">
-        <v>324.271</v>
+        <v>1639.549</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46139.65625</v>
+        <v>46142.65625</v>
       </c>
       <c r="B64">
-        <v>355.158</v>
+        <v>1678.808</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46139.66666666666</v>
+        <v>46142.66666666666</v>
       </c>
       <c r="B65">
-        <v>408.287</v>
+        <v>1664.533</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46139.67708333334</v>
+        <v>46142.67708333334</v>
       </c>
       <c r="B66">
-        <v>435.06</v>
+        <v>1596.839</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46139.6875</v>
+        <v>46142.6875</v>
       </c>
       <c r="B67">
-        <v>473.326</v>
+        <v>1561.902</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46139.69791666666</v>
+        <v>46142.69791666666</v>
       </c>
       <c r="B68">
-        <v>509.229</v>
+        <v>1523.067</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46139.70833333334</v>
+        <v>46142.70833333334</v>
       </c>
       <c r="B69">
-        <v>544.872</v>
+        <v>1481.622</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46139.71875</v>
+        <v>46142.71875</v>
       </c>
       <c r="B70">
-        <v>549.2140000000001</v>
+        <v>1202.378</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46139.72916666666</v>
+        <v>46142.72916666666</v>
       </c>
       <c r="B71">
-        <v>590.837</v>
+        <v>1140.683</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46139.73958333334</v>
+        <v>46142.73958333334</v>
       </c>
       <c r="B72">
-        <v>634.539</v>
+        <v>1082.644</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46139.75</v>
+        <v>46142.75</v>
       </c>
       <c r="B73">
-        <v>678.954</v>
+        <v>1026.684</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46139.76041666666</v>
+        <v>46142.76041666666</v>
       </c>
       <c r="B74">
-        <v>751.826</v>
+        <v>934.331</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46139.77083333334</v>
+        <v>46142.77083333334</v>
       </c>
       <c r="B75">
-        <v>810.625</v>
+        <v>873.372</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46139.78125</v>
+        <v>46142.78125</v>
       </c>
       <c r="B76">
-        <v>871.121</v>
+        <v>814.657</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46139.79166666666</v>
+        <v>46142.79166666666</v>
       </c>
       <c r="B77">
-        <v>931.152</v>
+        <v>755.008</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46139.80208333334</v>
+        <v>46142.80208333334</v>
       </c>
       <c r="B78">
-        <v>1014.763</v>
+        <v>684.558</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46139.8125</v>
+        <v>46142.8125</v>
       </c>
       <c r="B79">
-        <v>1076.04</v>
+        <v>645.986</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46139.82291666666</v>
+        <v>46142.82291666666</v>
       </c>
       <c r="B80">
-        <v>1140.012</v>
+        <v>608.806</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46139.83333333334</v>
+        <v>46142.83333333334</v>
       </c>
       <c r="B81">
-        <v>1200.132</v>
+        <v>571.515</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46139.84375</v>
+        <v>46142.84375</v>
       </c>
       <c r="B82">
-        <v>1271.342</v>
+        <v>515.564</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46139.85416666666</v>
+        <v>46142.85416666666</v>
       </c>
       <c r="B83">
-        <v>1292.747</v>
+        <v>494.889</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46139.86458333334</v>
+        <v>46142.86458333334</v>
       </c>
       <c r="B84">
-        <v>1311.048</v>
+        <v>474.77</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46139.875</v>
+        <v>46142.875</v>
       </c>
       <c r="B85">
-        <v>1331.301</v>
+        <v>454.56</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46139.88541666666</v>
+        <v>46142.88541666666</v>
       </c>
       <c r="B86">
-        <v>1345.363</v>
+        <v>448.509</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46139.89583333334</v>
+        <v>46142.89583333334</v>
       </c>
       <c r="B87">
-        <v>1340.855</v>
+        <v>445.173</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46139.90625</v>
+        <v>46142.90625</v>
       </c>
       <c r="B88">
-        <v>1338.817</v>
+        <v>442.81</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46139.91666666666</v>
+        <v>46142.91666666666</v>
       </c>
       <c r="B89">
-        <v>1336.875</v>
+        <v>429.088</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46139.92708333334</v>
+        <v>46142.92708333334</v>
       </c>
       <c r="B90">
-        <v>1321.734</v>
+        <v>448.858</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46139.9375</v>
+        <v>46142.9375</v>
       </c>
       <c r="B91">
-        <v>1307.586</v>
+        <v>469.044</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46139.94791666666</v>
+        <v>46142.94791666666</v>
       </c>
       <c r="B92">
-        <v>1294</v>
+        <v>489.697</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46139.95833333334</v>
+        <v>46142.95833333334</v>
       </c>
       <c r="B93">
-        <v>1278.48</v>
+        <v>509.745</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46139.96875</v>
+        <v>46142.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46139.97916666666</v>
+        <v>46142.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46139.98958333334</v>
+        <v>46142.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46140</v>
+        <v>46143</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46142.01041666666</v>
+        <v>46146.01041666666</v>
       </c>
       <c r="B2">
-        <v>648.849</v>
+        <v>321.179</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46142.02083333334</v>
+        <v>46146.02083333334</v>
       </c>
       <c r="B3">
-        <v>652.102</v>
+        <v>358.975</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46142.03125</v>
+        <v>46146.03125</v>
       </c>
       <c r="B4">
-        <v>652.4349999999999</v>
+        <v>400.4</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46142.04166666666</v>
+        <v>46146.04166666666</v>
       </c>
       <c r="B5">
-        <v>657.736</v>
+        <v>435.715</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46142.05208333334</v>
+        <v>46146.05208333334</v>
       </c>
       <c r="B6">
-        <v>634.076</v>
+        <v>523.473</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46142.0625</v>
+        <v>46146.0625</v>
       </c>
       <c r="B7">
-        <v>645.49</v>
+        <v>576.629</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46142.07291666666</v>
+        <v>46146.07291666666</v>
       </c>
       <c r="B8">
-        <v>659.099</v>
+        <v>633.7809999999999</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46142.08333333334</v>
+        <v>46146.08333333334</v>
       </c>
       <c r="B9">
-        <v>675.169</v>
+        <v>686.773</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46142.09375</v>
+        <v>46146.09375</v>
       </c>
       <c r="B10">
-        <v>684.753</v>
+        <v>765.367</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46142.10416666666</v>
+        <v>46146.10416666666</v>
       </c>
       <c r="B11">
-        <v>698.7910000000001</v>
+        <v>809.1420000000001</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46142.11458333334</v>
+        <v>46146.11458333334</v>
       </c>
       <c r="B12">
-        <v>712.357</v>
+        <v>854.982</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46142.125</v>
+        <v>46146.125</v>
       </c>
       <c r="B13">
-        <v>729.8819999999999</v>
+        <v>901.0700000000001</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46142.13541666666</v>
+        <v>46146.13541666666</v>
       </c>
       <c r="B14">
-        <v>753.501</v>
+        <v>933.098</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46142.14583333334</v>
+        <v>46146.14583333334</v>
       </c>
       <c r="B15">
-        <v>774.6660000000001</v>
+        <v>940.434</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46142.15625</v>
+        <v>46146.15625</v>
       </c>
       <c r="B16">
-        <v>790.66</v>
+        <v>950.9829999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46142.16666666666</v>
+        <v>46146.16666666666</v>
       </c>
       <c r="B17">
-        <v>815.938</v>
+        <v>960.503</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46142.17708333334</v>
+        <v>46146.17708333334</v>
       </c>
       <c r="B18">
-        <v>848.564</v>
+        <v>987.227</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46142.1875</v>
+        <v>46146.1875</v>
       </c>
       <c r="B19">
-        <v>868.607</v>
+        <v>975.657</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46142.19791666666</v>
+        <v>46146.19791666666</v>
       </c>
       <c r="B20">
-        <v>891.778</v>
+        <v>973.208</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46142.20833333334</v>
+        <v>46146.20833333334</v>
       </c>
       <c r="B21">
-        <v>910.2329999999999</v>
+        <v>970.766</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46142.21875</v>
+        <v>46146.21875</v>
       </c>
       <c r="B22">
-        <v>971.033</v>
+        <v>983.554</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46142.22916666666</v>
+        <v>46146.22916666666</v>
       </c>
       <c r="B23">
-        <v>996.926</v>
+        <v>966.086</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46142.23958333334</v>
+        <v>46146.23958333334</v>
       </c>
       <c r="B24">
-        <v>1022.417</v>
+        <v>949.351</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46142.25</v>
+        <v>46146.25</v>
       </c>
       <c r="B25">
-        <v>1045.328</v>
+        <v>936.811</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46142.26041666666</v>
+        <v>46146.26041666666</v>
       </c>
       <c r="B26">
-        <v>1119.208</v>
+        <v>874.3579999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46142.27083333334</v>
+        <v>46146.27083333334</v>
       </c>
       <c r="B27">
-        <v>1142.173</v>
+        <v>829.378</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46142.28125</v>
+        <v>46146.28125</v>
       </c>
       <c r="B28">
-        <v>1160.553</v>
+        <v>790.652</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46142.29166666666</v>
+        <v>46146.29166666666</v>
       </c>
       <c r="B29">
-        <v>1164.352</v>
+        <v>761.8579999999999</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46142.30208333334</v>
+        <v>46146.30208333334</v>
       </c>
       <c r="B30">
-        <v>1215.261</v>
+        <v>710.475</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46142.3125</v>
+        <v>46146.3125</v>
       </c>
       <c r="B31">
-        <v>1213.192</v>
+        <v>648.1319999999999</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46142.32291666666</v>
+        <v>46146.32291666666</v>
       </c>
       <c r="B32">
-        <v>1210.118</v>
+        <v>594.109</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46142.33333333334</v>
+        <v>46146.33333333334</v>
       </c>
       <c r="B33">
-        <v>1220.582</v>
+        <v>538.867</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46142.34375</v>
+        <v>46146.34375</v>
       </c>
       <c r="B34">
-        <v>1116.184</v>
+        <v>526.653</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46142.35416666666</v>
+        <v>46146.35416666666</v>
       </c>
       <c r="B35">
-        <v>1119.482</v>
+        <v>511.289</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46142.36458333334</v>
+        <v>46146.36458333334</v>
       </c>
       <c r="B36">
-        <v>1134.834</v>
+        <v>492.434</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46142.375</v>
+        <v>46146.375</v>
       </c>
       <c r="B37">
-        <v>1142.694</v>
+        <v>484.004</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46142.38541666666</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="B38">
-        <v>1318.648</v>
+        <v>581.164</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46142.39583333334</v>
+        <v>46146.39583333334</v>
       </c>
       <c r="B39">
-        <v>1331.289</v>
+        <v>624.288</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46142.40625</v>
+        <v>46146.40625</v>
       </c>
       <c r="B40">
-        <v>1343.271</v>
+        <v>668.321</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46142.41666666666</v>
+        <v>46146.41666666666</v>
       </c>
       <c r="B41">
-        <v>1318.529</v>
+        <v>711.7430000000001</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46142.42708333334</v>
+        <v>46146.42708333334</v>
       </c>
       <c r="B42">
-        <v>1369.836</v>
+        <v>741.652</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46142.4375</v>
+        <v>46146.4375</v>
       </c>
       <c r="B43">
-        <v>1345.14</v>
+        <v>766.6849999999999</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46142.44791666666</v>
+        <v>46146.44791666666</v>
       </c>
       <c r="B44">
-        <v>1387.805</v>
+        <v>790.359</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46142.45833333334</v>
+        <v>46146.45833333334</v>
       </c>
       <c r="B45">
-        <v>1416.536</v>
+        <v>813.653</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46142.46875</v>
+        <v>46146.46875</v>
       </c>
       <c r="B46">
-        <v>1494.563</v>
+        <v>833.396</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46142.47916666666</v>
+        <v>46146.47916666666</v>
       </c>
       <c r="B47">
-        <v>1513.067</v>
+        <v>852.876</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46142.48958333334</v>
+        <v>46146.48958333334</v>
       </c>
       <c r="B48">
-        <v>1535.332</v>
+        <v>870.932</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46142.5</v>
+        <v>46146.5</v>
       </c>
       <c r="B49">
-        <v>1553.759</v>
+        <v>889.84</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46142.51041666666</v>
+        <v>46146.51041666666</v>
       </c>
       <c r="B50">
-        <v>1585.976</v>
+        <v>888.986</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46142.52083333334</v>
+        <v>46146.52083333334</v>
       </c>
       <c r="B51">
-        <v>1610.747</v>
+        <v>897.708</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46142.53125</v>
+        <v>46146.53125</v>
       </c>
       <c r="B52">
-        <v>1587.508</v>
+        <v>906.01</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46142.54166666666</v>
+        <v>46146.54166666666</v>
       </c>
       <c r="B53">
-        <v>1609.954</v>
+        <v>914.174</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46142.55208333334</v>
+        <v>46146.55208333334</v>
       </c>
       <c r="B54">
-        <v>1615.319</v>
+        <v>933.086</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46142.5625</v>
+        <v>46146.5625</v>
       </c>
       <c r="B55">
-        <v>1623.051</v>
+        <v>932.346</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46142.57291666666</v>
+        <v>46146.57291666666</v>
       </c>
       <c r="B56">
-        <v>1629.591</v>
+        <v>930.4109999999999</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46142.58333333334</v>
+        <v>46146.58333333334</v>
       </c>
       <c r="B57">
-        <v>1690.212</v>
+        <v>928.7190000000001</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46142.59375</v>
+        <v>46146.59375</v>
       </c>
       <c r="B58">
-        <v>1691.257</v>
+        <v>935.6559999999999</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46142.60416666666</v>
+        <v>46146.60416666666</v>
       </c>
       <c r="B59">
-        <v>1684.456</v>
+        <v>922.064</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46142.61458333334</v>
+        <v>46146.61458333334</v>
       </c>
       <c r="B60">
-        <v>1730.248</v>
+        <v>909.5700000000001</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46142.625</v>
+        <v>46146.625</v>
       </c>
       <c r="B61">
-        <v>1667.491</v>
+        <v>896.622</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46142.63541666666</v>
+        <v>46146.63541666666</v>
       </c>
       <c r="B62">
-        <v>1651.491</v>
+        <v>861.654</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46142.64583333334</v>
+        <v>46146.64583333334</v>
       </c>
       <c r="B63">
-        <v>1639.549</v>
+        <v>838.954</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46142.65625</v>
+        <v>46146.65625</v>
       </c>
       <c r="B64">
-        <v>1678.808</v>
+        <v>816.558</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46142.66666666666</v>
+        <v>46146.66666666666</v>
       </c>
       <c r="B65">
-        <v>1664.533</v>
+        <v>793.851</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46142.67708333334</v>
+        <v>46146.67708333334</v>
       </c>
       <c r="B66">
-        <v>1596.839</v>
+        <v>670.649</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46142.6875</v>
+        <v>46146.6875</v>
       </c>
       <c r="B67">
-        <v>1561.902</v>
+        <v>637.075</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46142.69791666666</v>
+        <v>46146.69791666666</v>
       </c>
       <c r="B68">
-        <v>1523.067</v>
+        <v>602.746</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46142.70833333334</v>
+        <v>46146.70833333334</v>
       </c>
       <c r="B69">
-        <v>1481.622</v>
+        <v>568.256</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46142.71875</v>
+        <v>46146.71875</v>
       </c>
       <c r="B70">
-        <v>1202.378</v>
+        <v>521.7329999999999</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46142.72916666666</v>
+        <v>46146.72916666666</v>
       </c>
       <c r="B71">
-        <v>1140.683</v>
+        <v>486.272</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46142.73958333334</v>
+        <v>46146.73958333334</v>
       </c>
       <c r="B72">
-        <v>1082.644</v>
+        <v>452.48</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46142.75</v>
+        <v>46146.75</v>
       </c>
       <c r="B73">
-        <v>1026.684</v>
+        <v>419.509</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46142.76041666666</v>
+        <v>46146.76041666666</v>
       </c>
       <c r="B74">
-        <v>934.331</v>
+        <v>384.43</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46142.77083333334</v>
+        <v>46146.77083333334</v>
       </c>
       <c r="B75">
-        <v>873.372</v>
+        <v>367.768</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46142.78125</v>
+        <v>46146.78125</v>
       </c>
       <c r="B76">
-        <v>814.657</v>
+        <v>352.286</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46142.79166666666</v>
+        <v>46146.79166666666</v>
       </c>
       <c r="B77">
-        <v>755.008</v>
+        <v>336.974</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46142.80208333334</v>
+        <v>46146.80208333334</v>
       </c>
       <c r="B78">
-        <v>684.558</v>
+        <v>288.111</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46142.8125</v>
+        <v>46146.8125</v>
       </c>
       <c r="B79">
-        <v>645.986</v>
+        <v>283.442</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46142.82291666666</v>
+        <v>46146.82291666666</v>
       </c>
       <c r="B80">
-        <v>608.806</v>
+        <v>279.81</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46142.83333333334</v>
+        <v>46146.83333333334</v>
       </c>
       <c r="B81">
-        <v>571.515</v>
+        <v>297.538</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46142.84375</v>
+        <v>46146.84375</v>
       </c>
       <c r="B82">
-        <v>515.564</v>
+        <v>278.591</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46142.85416666666</v>
+        <v>46146.85416666666</v>
       </c>
       <c r="B83">
-        <v>494.889</v>
+        <v>268.529</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46142.86458333334</v>
+        <v>46146.86458333334</v>
       </c>
       <c r="B84">
-        <v>474.77</v>
+        <v>258.671</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46142.875</v>
+        <v>46146.875</v>
       </c>
       <c r="B85">
-        <v>454.56</v>
+        <v>227.964</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46142.88541666666</v>
+        <v>46146.88541666666</v>
       </c>
       <c r="B86">
-        <v>448.509</v>
+        <v>236.234</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46142.89583333334</v>
+        <v>46146.89583333334</v>
       </c>
       <c r="B87">
-        <v>445.173</v>
+        <v>230.014</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46142.90625</v>
+        <v>46146.90625</v>
       </c>
       <c r="B88">
-        <v>442.81</v>
+        <v>222.607</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46142.91666666666</v>
+        <v>46146.91666666666</v>
       </c>
       <c r="B89">
-        <v>429.088</v>
+        <v>194.154</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46142.92708333334</v>
+        <v>46146.92708333334</v>
       </c>
       <c r="B90">
-        <v>448.858</v>
+        <v>200.394</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46142.9375</v>
+        <v>46146.9375</v>
       </c>
       <c r="B91">
-        <v>469.044</v>
+        <v>196.854</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46142.94791666666</v>
+        <v>46146.94791666666</v>
       </c>
       <c r="B92">
-        <v>489.697</v>
+        <v>193.225</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46142.95833333334</v>
+        <v>46146.95833333334</v>
       </c>
       <c r="B93">
-        <v>509.745</v>
+        <v>190.135</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46142.96875</v>
+        <v>46146.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46142.97916666666</v>
+        <v>46146.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46142.98958333334</v>
+        <v>46146.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46146.01041666666</v>
+        <v>46148.01041666666</v>
       </c>
       <c r="B2">
-        <v>321.179</v>
+        <v>782.6</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46146.02083333334</v>
+        <v>46148.02083333334</v>
       </c>
       <c r="B3">
-        <v>358.975</v>
+        <v>750.5599999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46146.03125</v>
+        <v>46148.03125</v>
       </c>
       <c r="B4">
-        <v>400.4</v>
+        <v>731.287</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46146.04166666666</v>
+        <v>46148.04166666666</v>
       </c>
       <c r="B5">
-        <v>435.715</v>
+        <v>706.922</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46146.05208333334</v>
+        <v>46148.05208333334</v>
       </c>
       <c r="B6">
-        <v>523.473</v>
+        <v>637.643</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46146.0625</v>
+        <v>46148.0625</v>
       </c>
       <c r="B7">
-        <v>576.629</v>
+        <v>603.902</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46146.07291666666</v>
+        <v>46148.07291666666</v>
       </c>
       <c r="B8">
-        <v>633.7809999999999</v>
+        <v>580.249</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46146.08333333334</v>
+        <v>46148.08333333334</v>
       </c>
       <c r="B9">
-        <v>686.773</v>
+        <v>558.985</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46146.09375</v>
+        <v>46148.09375</v>
       </c>
       <c r="B10">
-        <v>765.367</v>
+        <v>519.23</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46146.10416666666</v>
+        <v>46148.10416666666</v>
       </c>
       <c r="B11">
-        <v>809.1420000000001</v>
+        <v>487.589</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46146.11458333334</v>
+        <v>46148.11458333334</v>
       </c>
       <c r="B12">
-        <v>854.982</v>
+        <v>468.55</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46146.125</v>
+        <v>46148.125</v>
       </c>
       <c r="B13">
-        <v>901.0700000000001</v>
+        <v>444.037</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46146.13541666666</v>
+        <v>46148.13541666666</v>
       </c>
       <c r="B14">
-        <v>933.098</v>
+        <v>443.371</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46146.14583333334</v>
+        <v>46148.14583333334</v>
       </c>
       <c r="B15">
-        <v>940.434</v>
+        <v>425.783</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46146.15625</v>
+        <v>46148.15625</v>
       </c>
       <c r="B16">
-        <v>950.9829999999999</v>
+        <v>413.582</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46146.16666666666</v>
+        <v>46148.16666666666</v>
       </c>
       <c r="B17">
-        <v>960.503</v>
+        <v>395.002</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46146.17708333334</v>
+        <v>46148.17708333334</v>
       </c>
       <c r="B18">
-        <v>987.227</v>
+        <v>334.312</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46146.1875</v>
+        <v>46148.1875</v>
       </c>
       <c r="B19">
-        <v>975.657</v>
+        <v>320.263</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46146.19791666666</v>
+        <v>46148.19791666666</v>
       </c>
       <c r="B20">
-        <v>973.208</v>
+        <v>307.128</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46146.20833333334</v>
+        <v>46148.20833333334</v>
       </c>
       <c r="B21">
-        <v>970.766</v>
+        <v>294.25</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46146.21875</v>
+        <v>46148.21875</v>
       </c>
       <c r="B22">
-        <v>983.554</v>
+        <v>274.426</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46146.22916666666</v>
+        <v>46148.22916666666</v>
       </c>
       <c r="B23">
-        <v>966.086</v>
+        <v>263.078</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46146.23958333334</v>
+        <v>46148.23958333334</v>
       </c>
       <c r="B24">
-        <v>949.351</v>
+        <v>256.936</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46146.25</v>
+        <v>46148.25</v>
       </c>
       <c r="B25">
-        <v>936.811</v>
+        <v>249.909</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46146.26041666666</v>
+        <v>46148.26041666666</v>
       </c>
       <c r="B26">
-        <v>874.3579999999999</v>
+        <v>238.905</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46146.27083333334</v>
+        <v>46148.27083333334</v>
       </c>
       <c r="B27">
-        <v>829.378</v>
+        <v>237.743</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46146.28125</v>
+        <v>46148.28125</v>
       </c>
       <c r="B28">
-        <v>790.652</v>
+        <v>233.729</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46146.29166666666</v>
+        <v>46148.29166666666</v>
       </c>
       <c r="B29">
-        <v>761.8579999999999</v>
+        <v>232.179</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46146.30208333334</v>
+        <v>46148.30208333334</v>
       </c>
       <c r="B30">
-        <v>710.475</v>
+        <v>236.659</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46146.3125</v>
+        <v>46148.3125</v>
       </c>
       <c r="B31">
-        <v>648.1319999999999</v>
+        <v>234.812</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46146.32291666666</v>
+        <v>46148.32291666666</v>
       </c>
       <c r="B32">
-        <v>594.109</v>
+        <v>233.834</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46146.33333333334</v>
+        <v>46148.33333333334</v>
       </c>
       <c r="B33">
-        <v>538.867</v>
+        <v>239.047</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46146.34375</v>
+        <v>46148.34375</v>
       </c>
       <c r="B34">
-        <v>526.653</v>
+        <v>300.224</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46146.35416666666</v>
+        <v>46148.35416666666</v>
       </c>
       <c r="B35">
-        <v>511.289</v>
+        <v>303.863</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46146.36458333334</v>
+        <v>46148.36458333334</v>
       </c>
       <c r="B36">
-        <v>492.434</v>
+        <v>318.007</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46146.375</v>
+        <v>46148.375</v>
       </c>
       <c r="B37">
-        <v>484.004</v>
+        <v>313.134</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46146.38541666666</v>
+        <v>46148.38541666666</v>
       </c>
       <c r="B38">
-        <v>581.164</v>
+        <v>345.72</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46146.39583333334</v>
+        <v>46148.39583333334</v>
       </c>
       <c r="B39">
-        <v>624.288</v>
+        <v>372.873</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46146.40625</v>
+        <v>46148.40625</v>
       </c>
       <c r="B40">
-        <v>668.321</v>
+        <v>399.491</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46146.41666666666</v>
+        <v>46148.41666666666</v>
       </c>
       <c r="B41">
-        <v>711.7430000000001</v>
+        <v>426.29</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46146.42708333334</v>
+        <v>46148.42708333334</v>
       </c>
       <c r="B42">
-        <v>741.652</v>
+        <v>434.392</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46146.4375</v>
+        <v>46148.4375</v>
       </c>
       <c r="B43">
-        <v>766.6849999999999</v>
+        <v>458.299</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46146.44791666666</v>
+        <v>46148.44791666666</v>
       </c>
       <c r="B44">
-        <v>790.359</v>
+        <v>481.282</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46146.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="B45">
-        <v>813.653</v>
+        <v>503.735</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46146.46875</v>
+        <v>46148.46875</v>
       </c>
       <c r="B46">
-        <v>833.396</v>
+        <v>544.563</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46146.47916666666</v>
+        <v>46148.47916666666</v>
       </c>
       <c r="B47">
-        <v>852.876</v>
+        <v>560.078</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46146.48958333334</v>
+        <v>46148.48958333334</v>
       </c>
       <c r="B48">
-        <v>870.932</v>
+        <v>575.821</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46146.5</v>
+        <v>46148.5</v>
       </c>
       <c r="B49">
-        <v>889.84</v>
+        <v>592.349</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46146.51041666666</v>
+        <v>46148.51041666666</v>
       </c>
       <c r="B50">
-        <v>888.986</v>
+        <v>594.5309999999999</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46146.52083333334</v>
+        <v>46148.52083333334</v>
       </c>
       <c r="B51">
-        <v>897.708</v>
+        <v>602.684</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46146.53125</v>
+        <v>46148.53125</v>
       </c>
       <c r="B52">
-        <v>906.01</v>
+        <v>610.708</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46146.54166666666</v>
+        <v>46148.54166666666</v>
       </c>
       <c r="B53">
-        <v>914.174</v>
+        <v>618.492</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46146.55208333334</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="B54">
-        <v>933.086</v>
+        <v>622.478</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46146.5625</v>
+        <v>46148.5625</v>
       </c>
       <c r="B55">
-        <v>932.346</v>
+        <v>624.4930000000001</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46146.57291666666</v>
+        <v>46148.57291666666</v>
       </c>
       <c r="B56">
-        <v>930.4109999999999</v>
+        <v>626.129</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46146.58333333334</v>
+        <v>46148.58333333334</v>
       </c>
       <c r="B57">
-        <v>928.7190000000001</v>
+        <v>628.698</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46146.59375</v>
+        <v>46148.59375</v>
       </c>
       <c r="B58">
-        <v>935.6559999999999</v>
+        <v>649.298</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46146.60416666666</v>
+        <v>46148.60416666666</v>
       </c>
       <c r="B59">
-        <v>922.064</v>
+        <v>653.508</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46146.61458333334</v>
+        <v>46148.61458333334</v>
       </c>
       <c r="B60">
-        <v>909.5700000000001</v>
+        <v>657.486</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46146.625</v>
+        <v>46148.625</v>
       </c>
       <c r="B61">
-        <v>896.622</v>
+        <v>661.277</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46146.63541666666</v>
+        <v>46148.63541666666</v>
       </c>
       <c r="B62">
-        <v>861.654</v>
+        <v>668.0170000000001</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46146.64583333334</v>
+        <v>46148.64583333334</v>
       </c>
       <c r="B63">
-        <v>838.954</v>
+        <v>675.697</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46146.65625</v>
+        <v>46148.65625</v>
       </c>
       <c r="B64">
-        <v>816.558</v>
+        <v>683.78</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46146.66666666666</v>
+        <v>46148.66666666666</v>
       </c>
       <c r="B65">
-        <v>793.851</v>
+        <v>691.801</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46146.67708333334</v>
+        <v>46148.67708333334</v>
       </c>
       <c r="B66">
-        <v>670.649</v>
+        <v>750.998</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46146.6875</v>
+        <v>46148.6875</v>
       </c>
       <c r="B67">
-        <v>637.075</v>
+        <v>760.914</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46146.69791666666</v>
+        <v>46148.69791666666</v>
       </c>
       <c r="B68">
-        <v>602.746</v>
+        <v>770.251</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46146.70833333334</v>
+        <v>46148.70833333334</v>
       </c>
       <c r="B69">
-        <v>568.256</v>
+        <v>778.332</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46146.71875</v>
+        <v>46148.71875</v>
       </c>
       <c r="B70">
-        <v>521.7329999999999</v>
+        <v>762.087</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46146.72916666666</v>
+        <v>46148.72916666666</v>
       </c>
       <c r="B71">
-        <v>486.272</v>
+        <v>776.933</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46146.73958333334</v>
+        <v>46148.73958333334</v>
       </c>
       <c r="B72">
-        <v>452.48</v>
+        <v>792.0890000000001</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46146.75</v>
+        <v>46148.75</v>
       </c>
       <c r="B73">
-        <v>419.509</v>
+        <v>805.84</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46146.76041666666</v>
+        <v>46148.76041666666</v>
       </c>
       <c r="B74">
-        <v>384.43</v>
+        <v>834.356</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46146.77083333334</v>
+        <v>46148.77083333334</v>
       </c>
       <c r="B75">
-        <v>367.768</v>
+        <v>863.265</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46146.78125</v>
+        <v>46148.78125</v>
       </c>
       <c r="B76">
-        <v>352.286</v>
+        <v>893.154</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46146.79166666666</v>
+        <v>46148.79166666666</v>
       </c>
       <c r="B77">
-        <v>336.974</v>
+        <v>923.309</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46146.80208333334</v>
+        <v>46148.80208333334</v>
       </c>
       <c r="B78">
-        <v>288.111</v>
+        <v>951.201</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46146.8125</v>
+        <v>46148.8125</v>
       </c>
       <c r="B79">
-        <v>283.442</v>
+        <v>974.909</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46146.82291666666</v>
+        <v>46148.82291666666</v>
       </c>
       <c r="B80">
-        <v>279.81</v>
+        <v>1001.251</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46146.83333333334</v>
+        <v>46148.83333333334</v>
       </c>
       <c r="B81">
-        <v>297.538</v>
+        <v>1024.676</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46146.84375</v>
+        <v>46148.84375</v>
       </c>
       <c r="B82">
-        <v>278.591</v>
+        <v>1059.86</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46146.85416666666</v>
+        <v>46148.85416666666</v>
       </c>
       <c r="B83">
-        <v>268.529</v>
+        <v>1069.276</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46146.86458333334</v>
+        <v>46148.86458333334</v>
       </c>
       <c r="B84">
-        <v>258.671</v>
+        <v>1077.697</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46146.875</v>
+        <v>46148.875</v>
       </c>
       <c r="B85">
-        <v>227.964</v>
+        <v>1085.675</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46146.88541666666</v>
+        <v>46148.88541666666</v>
       </c>
       <c r="B86">
-        <v>236.234</v>
+        <v>1093.885</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46146.89583333334</v>
+        <v>46148.89583333334</v>
       </c>
       <c r="B87">
-        <v>230.014</v>
+        <v>1094.099</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46146.90625</v>
+        <v>46148.90625</v>
       </c>
       <c r="B88">
-        <v>222.607</v>
+        <v>1093.667</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46146.91666666666</v>
+        <v>46148.91666666666</v>
       </c>
       <c r="B89">
-        <v>194.154</v>
+        <v>1094.016</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46146.92708333334</v>
+        <v>46148.92708333334</v>
       </c>
       <c r="B90">
-        <v>200.394</v>
+        <v>1066.746</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46146.9375</v>
+        <v>46148.9375</v>
       </c>
       <c r="B91">
-        <v>196.854</v>
+        <v>1063.407</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46146.94791666666</v>
+        <v>46148.94791666666</v>
       </c>
       <c r="B92">
-        <v>193.225</v>
+        <v>1062.067</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46146.95833333334</v>
+        <v>46148.95833333334</v>
       </c>
       <c r="B93">
-        <v>190.135</v>
+        <v>1060.107</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46146.96875</v>
+        <v>46148.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46146.97916666666</v>
+        <v>46148.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46146.98958333334</v>
+        <v>46148.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46148.01041666666</v>
+        <v>46150.01041666666</v>
       </c>
       <c r="B2">
-        <v>782.6</v>
+        <v>1128.219</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46148.02083333334</v>
+        <v>46150.02083333334</v>
       </c>
       <c r="B3">
-        <v>750.5599999999999</v>
+        <v>1103.223</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46148.03125</v>
+        <v>46150.03125</v>
       </c>
       <c r="B4">
-        <v>731.287</v>
+        <v>1076.002</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46148.04166666666</v>
+        <v>46150.04166666666</v>
       </c>
       <c r="B5">
-        <v>706.922</v>
+        <v>1055.529</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46148.05208333334</v>
+        <v>46150.05208333334</v>
       </c>
       <c r="B6">
-        <v>637.643</v>
+        <v>1035.284</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46148.0625</v>
+        <v>46150.0625</v>
       </c>
       <c r="B7">
-        <v>603.902</v>
+        <v>1025.564</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46148.07291666666</v>
+        <v>46150.07291666666</v>
       </c>
       <c r="B8">
-        <v>580.249</v>
+        <v>1005.742</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46148.08333333334</v>
+        <v>46150.08333333334</v>
       </c>
       <c r="B9">
-        <v>558.985</v>
+        <v>991.107</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46148.09375</v>
+        <v>46150.09375</v>
       </c>
       <c r="B10">
-        <v>519.23</v>
+        <v>963.066</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46148.10416666666</v>
+        <v>46150.10416666666</v>
       </c>
       <c r="B11">
-        <v>487.589</v>
+        <v>953.102</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46148.11458333334</v>
+        <v>46150.11458333334</v>
       </c>
       <c r="B12">
-        <v>468.55</v>
+        <v>957.638</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46148.125</v>
+        <v>46150.125</v>
       </c>
       <c r="B13">
-        <v>444.037</v>
+        <v>938.829</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46148.13541666666</v>
+        <v>46150.13541666666</v>
       </c>
       <c r="B14">
-        <v>443.371</v>
+        <v>898.919</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46148.14583333334</v>
+        <v>46150.14583333334</v>
       </c>
       <c r="B15">
-        <v>425.783</v>
+        <v>874.433</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46148.15625</v>
+        <v>46150.15625</v>
       </c>
       <c r="B16">
-        <v>413.582</v>
+        <v>853.569</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46148.16666666666</v>
+        <v>46150.16666666666</v>
       </c>
       <c r="B17">
-        <v>395.002</v>
+        <v>828.7190000000001</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46148.17708333334</v>
+        <v>46150.17708333334</v>
       </c>
       <c r="B18">
-        <v>334.312</v>
+        <v>725.808</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46148.1875</v>
+        <v>46150.1875</v>
       </c>
       <c r="B19">
-        <v>320.263</v>
+        <v>705.97</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46148.19791666666</v>
+        <v>46150.19791666666</v>
       </c>
       <c r="B20">
-        <v>307.128</v>
+        <v>683.84</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46148.20833333334</v>
+        <v>46150.20833333334</v>
       </c>
       <c r="B21">
-        <v>294.25</v>
+        <v>658.9829999999999</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46148.21875</v>
+        <v>46150.21875</v>
       </c>
       <c r="B22">
-        <v>274.426</v>
+        <v>610.22</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46148.22916666666</v>
+        <v>46150.22916666666</v>
       </c>
       <c r="B23">
-        <v>263.078</v>
+        <v>603.42</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46148.23958333334</v>
+        <v>46150.23958333334</v>
       </c>
       <c r="B24">
-        <v>256.936</v>
+        <v>588.58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46148.25</v>
+        <v>46150.25</v>
       </c>
       <c r="B25">
-        <v>249.909</v>
+        <v>576.699</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46148.26041666666</v>
+        <v>46150.26041666666</v>
       </c>
       <c r="B26">
-        <v>238.905</v>
+        <v>512.752</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46148.27083333334</v>
+        <v>46150.27083333334</v>
       </c>
       <c r="B27">
-        <v>237.743</v>
+        <v>510.174</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46148.28125</v>
+        <v>46150.28125</v>
       </c>
       <c r="B28">
-        <v>233.729</v>
+        <v>524.353</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46148.29166666666</v>
+        <v>46150.29166666666</v>
       </c>
       <c r="B29">
-        <v>232.179</v>
+        <v>518.778</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46148.30208333334</v>
+        <v>46150.30208333334</v>
       </c>
       <c r="B30">
-        <v>236.659</v>
+        <v>446.075</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46148.3125</v>
+        <v>46150.3125</v>
       </c>
       <c r="B31">
-        <v>234.812</v>
+        <v>430.238</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46148.32291666666</v>
+        <v>46150.32291666666</v>
       </c>
       <c r="B32">
-        <v>233.834</v>
+        <v>409.691</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46148.33333333334</v>
+        <v>46150.33333333334</v>
       </c>
       <c r="B33">
-        <v>239.047</v>
+        <v>396.414</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46148.34375</v>
+        <v>46150.34375</v>
       </c>
       <c r="B34">
-        <v>300.224</v>
+        <v>405.968</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46148.35416666666</v>
+        <v>46150.35416666666</v>
       </c>
       <c r="B35">
-        <v>303.863</v>
+        <v>392.106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46148.36458333334</v>
+        <v>46150.36458333334</v>
       </c>
       <c r="B36">
-        <v>318.007</v>
+        <v>384.164</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46148.375</v>
+        <v>46150.375</v>
       </c>
       <c r="B37">
-        <v>313.134</v>
+        <v>375.771</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46148.38541666666</v>
+        <v>46150.38541666666</v>
       </c>
       <c r="B38">
-        <v>345.72</v>
+        <v>379.921</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46148.39583333334</v>
+        <v>46150.39583333334</v>
       </c>
       <c r="B39">
-        <v>372.873</v>
+        <v>379.085</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46148.40625</v>
+        <v>46150.40625</v>
       </c>
       <c r="B40">
-        <v>399.491</v>
+        <v>378.58</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46148.41666666666</v>
+        <v>46150.41666666666</v>
       </c>
       <c r="B41">
-        <v>426.29</v>
+        <v>377.693</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46148.42708333334</v>
+        <v>46150.42708333334</v>
       </c>
       <c r="B42">
-        <v>434.392</v>
+        <v>384.565</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46148.4375</v>
+        <v>46150.4375</v>
       </c>
       <c r="B43">
-        <v>458.299</v>
+        <v>396.72</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46148.44791666666</v>
+        <v>46150.44791666666</v>
       </c>
       <c r="B44">
-        <v>481.282</v>
+        <v>408.144</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46148.45833333334</v>
+        <v>46150.45833333334</v>
       </c>
       <c r="B45">
-        <v>503.735</v>
+        <v>419.41</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46148.46875</v>
+        <v>46150.46875</v>
       </c>
       <c r="B46">
-        <v>544.563</v>
+        <v>432.76</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46148.47916666666</v>
+        <v>46150.47916666666</v>
       </c>
       <c r="B47">
-        <v>560.078</v>
+        <v>441.251</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46148.48958333334</v>
+        <v>46150.48958333334</v>
       </c>
       <c r="B48">
-        <v>575.821</v>
+        <v>450.268</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46148.5</v>
+        <v>46150.5</v>
       </c>
       <c r="B49">
-        <v>592.349</v>
+        <v>459.733</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46148.51041666666</v>
+        <v>46150.51041666666</v>
       </c>
       <c r="B50">
-        <v>594.5309999999999</v>
+        <v>478.332</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46148.52083333334</v>
+        <v>46150.52083333334</v>
       </c>
       <c r="B51">
-        <v>602.684</v>
+        <v>485.135</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46148.53125</v>
+        <v>46150.53125</v>
       </c>
       <c r="B52">
-        <v>610.708</v>
+        <v>491.605</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46148.54166666666</v>
+        <v>46150.54166666666</v>
       </c>
       <c r="B53">
-        <v>618.492</v>
+        <v>498.903</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46148.55208333334</v>
+        <v>46150.55208333334</v>
       </c>
       <c r="B54">
-        <v>622.478</v>
+        <v>511.014</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46148.5625</v>
+        <v>46150.5625</v>
       </c>
       <c r="B55">
-        <v>624.4930000000001</v>
+        <v>517.292</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46148.57291666666</v>
+        <v>46150.57291666666</v>
       </c>
       <c r="B56">
-        <v>626.129</v>
+        <v>521.86</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46148.58333333334</v>
+        <v>46150.58333333334</v>
       </c>
       <c r="B57">
-        <v>628.698</v>
+        <v>526.9930000000001</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46148.59375</v>
+        <v>46150.59375</v>
       </c>
       <c r="B58">
-        <v>649.298</v>
+        <v>524.653</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46148.60416666666</v>
+        <v>46150.60416666666</v>
       </c>
       <c r="B59">
-        <v>653.508</v>
+        <v>532.766</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46148.61458333334</v>
+        <v>46150.61458333334</v>
       </c>
       <c r="B60">
-        <v>657.486</v>
+        <v>540.204</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46148.625</v>
+        <v>46150.625</v>
       </c>
       <c r="B61">
-        <v>661.277</v>
+        <v>549.728</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46148.63541666666</v>
+        <v>46150.63541666666</v>
       </c>
       <c r="B62">
-        <v>668.0170000000001</v>
+        <v>554.545</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46148.64583333334</v>
+        <v>46150.64583333334</v>
       </c>
       <c r="B63">
-        <v>675.697</v>
+        <v>559.178</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46148.65625</v>
+        <v>46150.65625</v>
       </c>
       <c r="B64">
-        <v>683.78</v>
+        <v>564.417</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46148.66666666666</v>
+        <v>46150.66666666666</v>
       </c>
       <c r="B65">
-        <v>691.801</v>
+        <v>568.955</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46148.67708333334</v>
+        <v>46150.67708333334</v>
       </c>
       <c r="B66">
-        <v>750.998</v>
+        <v>509.336</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46148.6875</v>
+        <v>46150.6875</v>
       </c>
       <c r="B67">
-        <v>760.914</v>
+        <v>510.897</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46148.69791666666</v>
+        <v>46150.69791666666</v>
       </c>
       <c r="B68">
-        <v>770.251</v>
+        <v>513.307</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46148.70833333334</v>
+        <v>46150.70833333334</v>
       </c>
       <c r="B69">
-        <v>778.332</v>
+        <v>516.074</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46148.71875</v>
+        <v>46150.71875</v>
       </c>
       <c r="B70">
-        <v>762.087</v>
+        <v>515.9299999999999</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46148.72916666666</v>
+        <v>46150.72916666666</v>
       </c>
       <c r="B71">
-        <v>776.933</v>
+        <v>514.064</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46148.73958333334</v>
+        <v>46150.73958333334</v>
       </c>
       <c r="B72">
-        <v>792.0890000000001</v>
+        <v>512.515</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46148.75</v>
+        <v>46150.75</v>
       </c>
       <c r="B73">
-        <v>805.84</v>
+        <v>511.612</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46148.76041666666</v>
+        <v>46150.76041666666</v>
       </c>
       <c r="B74">
-        <v>834.356</v>
+        <v>502.257</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46148.77083333334</v>
+        <v>46150.77083333334</v>
       </c>
       <c r="B75">
-        <v>863.265</v>
+        <v>508.437</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46148.78125</v>
+        <v>46150.78125</v>
       </c>
       <c r="B76">
-        <v>893.154</v>
+        <v>516.023</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46148.79166666666</v>
+        <v>46150.79166666666</v>
       </c>
       <c r="B77">
-        <v>923.309</v>
+        <v>522.876</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46148.80208333334</v>
+        <v>46150.80208333334</v>
       </c>
       <c r="B78">
-        <v>951.201</v>
+        <v>535.347</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46148.8125</v>
+        <v>46150.8125</v>
       </c>
       <c r="B79">
-        <v>974.909</v>
+        <v>540.175</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46148.82291666666</v>
+        <v>46150.82291666666</v>
       </c>
       <c r="B80">
-        <v>1001.251</v>
+        <v>545.4829999999999</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46148.83333333334</v>
+        <v>46150.83333333334</v>
       </c>
       <c r="B81">
-        <v>1024.676</v>
+        <v>550.277</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46148.84375</v>
+        <v>46150.84375</v>
       </c>
       <c r="B82">
-        <v>1059.86</v>
+        <v>568.159</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46148.85416666666</v>
+        <v>46150.85416666666</v>
       </c>
       <c r="B83">
-        <v>1069.276</v>
+        <v>561.001</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46148.86458333334</v>
+        <v>46150.86458333334</v>
       </c>
       <c r="B84">
-        <v>1077.697</v>
+        <v>553.962</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46148.875</v>
+        <v>46150.875</v>
       </c>
       <c r="B85">
-        <v>1085.675</v>
+        <v>546.873</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46148.88541666666</v>
+        <v>46150.88541666666</v>
       </c>
       <c r="B86">
-        <v>1093.885</v>
+        <v>516.223</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46148.89583333334</v>
+        <v>46150.89583333334</v>
       </c>
       <c r="B87">
-        <v>1094.099</v>
+        <v>503.182</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46148.90625</v>
+        <v>46150.90625</v>
       </c>
       <c r="B88">
-        <v>1093.667</v>
+        <v>485.545</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46148.91666666666</v>
+        <v>46150.91666666666</v>
       </c>
       <c r="B89">
-        <v>1094.016</v>
+        <v>471.292</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46148.92708333334</v>
+        <v>46150.92708333334</v>
       </c>
       <c r="B90">
-        <v>1066.746</v>
+        <v>450.85</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46148.9375</v>
+        <v>46150.9375</v>
       </c>
       <c r="B91">
-        <v>1063.407</v>
+        <v>442.259</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46148.94791666666</v>
+        <v>46150.94791666666</v>
       </c>
       <c r="B92">
-        <v>1062.067</v>
+        <v>428.21</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46148.95833333334</v>
+        <v>46150.95833333334</v>
       </c>
       <c r="B93">
-        <v>1060.107</v>
+        <v>443.51</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46148.96875</v>
+        <v>46150.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46148.97916666666</v>
+        <v>46150.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46148.98958333334</v>
+        <v>46150.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,769 +394,1537 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46150.01041666666</v>
+        <v>46153</v>
       </c>
       <c r="B2">
-        <v>1128.219</v>
+        <v>130.332</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46150.02083333334</v>
+        <v>46153.01041666666</v>
       </c>
       <c r="B3">
-        <v>1103.223</v>
+        <v>130.352</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46150.03125</v>
+        <v>46153.02083333334</v>
       </c>
       <c r="B4">
-        <v>1076.002</v>
+        <v>130.671</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46150.04166666666</v>
+        <v>46153.03125</v>
       </c>
       <c r="B5">
-        <v>1055.529</v>
+        <v>130.81</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46150.05208333334</v>
+        <v>46153.04166666666</v>
       </c>
       <c r="B6">
-        <v>1035.284</v>
+        <v>129.903</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46150.0625</v>
+        <v>46153.05208333334</v>
       </c>
       <c r="B7">
-        <v>1025.564</v>
+        <v>128.473</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46150.07291666666</v>
+        <v>46153.0625</v>
       </c>
       <c r="B8">
-        <v>1005.742</v>
+        <v>127.035</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46150.08333333334</v>
+        <v>46153.07291666666</v>
       </c>
       <c r="B9">
-        <v>991.107</v>
+        <v>125.456</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46150.09375</v>
+        <v>46153.08333333334</v>
       </c>
       <c r="B10">
-        <v>963.066</v>
+        <v>112.252</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46150.10416666666</v>
+        <v>46153.09375</v>
       </c>
       <c r="B11">
-        <v>953.102</v>
+        <v>112.257</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46150.11458333334</v>
+        <v>46153.10416666666</v>
       </c>
       <c r="B12">
-        <v>957.638</v>
+        <v>112.884</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46150.125</v>
+        <v>46153.11458333334</v>
       </c>
       <c r="B13">
-        <v>938.829</v>
+        <v>113.472</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46150.13541666666</v>
+        <v>46153.125</v>
       </c>
       <c r="B14">
-        <v>898.919</v>
+        <v>116.366</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46150.14583333334</v>
+        <v>46153.13541666666</v>
       </c>
       <c r="B15">
-        <v>874.433</v>
+        <v>119.211</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46150.15625</v>
+        <v>46153.14583333334</v>
       </c>
       <c r="B16">
-        <v>853.569</v>
+        <v>122.09</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46150.16666666666</v>
+        <v>46153.15625</v>
       </c>
       <c r="B17">
-        <v>828.7190000000001</v>
+        <v>125.275</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46150.17708333334</v>
+        <v>46153.16666666666</v>
       </c>
       <c r="B18">
-        <v>725.808</v>
+        <v>128.958</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46150.1875</v>
+        <v>46153.17708333334</v>
       </c>
       <c r="B19">
-        <v>705.97</v>
+        <v>135.368</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46150.19791666666</v>
+        <v>46153.1875</v>
       </c>
       <c r="B20">
-        <v>683.84</v>
+        <v>139.99</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46150.20833333334</v>
+        <v>46153.19791666666</v>
       </c>
       <c r="B21">
-        <v>658.9829999999999</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46150.21875</v>
+        <v>46153.20833333334</v>
       </c>
       <c r="B22">
-        <v>610.22</v>
+        <v>161.679</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46150.22916666666</v>
+        <v>46153.21875</v>
       </c>
       <c r="B23">
-        <v>603.42</v>
+        <v>172.446</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46150.23958333334</v>
+        <v>46153.22916666666</v>
       </c>
       <c r="B24">
-        <v>588.58</v>
+        <v>184.133</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46150.25</v>
+        <v>46153.23958333334</v>
       </c>
       <c r="B25">
-        <v>576.699</v>
+        <v>195.863</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46150.26041666666</v>
+        <v>46153.25</v>
       </c>
       <c r="B26">
-        <v>512.752</v>
+        <v>184.073</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46150.27083333334</v>
+        <v>46153.26041666666</v>
       </c>
       <c r="B27">
-        <v>510.174</v>
+        <v>194.949</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46150.28125</v>
+        <v>46153.27083333334</v>
       </c>
       <c r="B28">
-        <v>524.353</v>
+        <v>207.406</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46150.29166666666</v>
+        <v>46153.28125</v>
       </c>
       <c r="B29">
-        <v>518.778</v>
+        <v>217.963</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46150.30208333334</v>
+        <v>46153.29166666666</v>
       </c>
       <c r="B30">
-        <v>446.075</v>
+        <v>223.207</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46150.3125</v>
+        <v>46153.30208333334</v>
       </c>
       <c r="B31">
-        <v>430.238</v>
+        <v>226.249</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46150.32291666666</v>
+        <v>46153.3125</v>
       </c>
       <c r="B32">
-        <v>409.691</v>
+        <v>228.391</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46150.33333333334</v>
+        <v>46153.32291666666</v>
       </c>
       <c r="B33">
-        <v>396.414</v>
+        <v>228.891</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46150.34375</v>
+        <v>46153.33333333334</v>
       </c>
       <c r="B34">
-        <v>405.968</v>
+        <v>241.616</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46150.35416666666</v>
+        <v>46153.34375</v>
       </c>
       <c r="B35">
-        <v>392.106</v>
+        <v>247.111</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46150.36458333334</v>
+        <v>46153.35416666666</v>
       </c>
       <c r="B36">
-        <v>384.164</v>
+        <v>260.222</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46150.375</v>
+        <v>46153.36458333334</v>
       </c>
       <c r="B37">
-        <v>375.771</v>
+        <v>267.281</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46150.38541666666</v>
+        <v>46153.375</v>
       </c>
       <c r="B38">
-        <v>379.921</v>
+        <v>340.494</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46150.39583333334</v>
+        <v>46153.38541666666</v>
       </c>
       <c r="B39">
-        <v>379.085</v>
+        <v>365.54</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46150.40625</v>
+        <v>46153.39583333334</v>
       </c>
       <c r="B40">
-        <v>378.58</v>
+        <v>389.794</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46150.41666666666</v>
+        <v>46153.40625</v>
       </c>
       <c r="B41">
-        <v>377.693</v>
+        <v>413.845</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46150.42708333334</v>
+        <v>46153.41666666666</v>
       </c>
       <c r="B42">
-        <v>384.565</v>
+        <v>424.131</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46150.4375</v>
+        <v>46153.42708333334</v>
       </c>
       <c r="B43">
-        <v>396.72</v>
+        <v>454.116</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46150.44791666666</v>
+        <v>46153.4375</v>
       </c>
       <c r="B44">
-        <v>408.144</v>
+        <v>483.236</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46150.45833333334</v>
+        <v>46153.44791666666</v>
       </c>
       <c r="B45">
-        <v>419.41</v>
+        <v>512.643</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46150.46875</v>
+        <v>46153.45833333334</v>
       </c>
       <c r="B46">
-        <v>432.76</v>
+        <v>540.408</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46150.47916666666</v>
+        <v>46153.46875</v>
       </c>
       <c r="B47">
-        <v>441.251</v>
+        <v>570.808</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46150.48958333334</v>
+        <v>46153.47916666666</v>
       </c>
       <c r="B48">
-        <v>450.268</v>
+        <v>600.515</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46150.5</v>
+        <v>46153.48958333334</v>
       </c>
       <c r="B49">
-        <v>459.733</v>
+        <v>630.097</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46150.51041666666</v>
+        <v>46153.5</v>
       </c>
       <c r="B50">
-        <v>478.332</v>
+        <v>698.88</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46150.52083333334</v>
+        <v>46153.51041666666</v>
       </c>
       <c r="B51">
-        <v>485.135</v>
+        <v>737.718</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46150.53125</v>
+        <v>46153.52083333334</v>
       </c>
       <c r="B52">
-        <v>491.605</v>
+        <v>777.216</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46150.54166666666</v>
+        <v>46153.53125</v>
       </c>
       <c r="B53">
-        <v>498.903</v>
+        <v>818.133</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46150.55208333334</v>
+        <v>46153.54166666666</v>
       </c>
       <c r="B54">
-        <v>511.014</v>
+        <v>883.697</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46150.5625</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="B55">
-        <v>517.292</v>
+        <v>929.708</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46150.57291666666</v>
+        <v>46153.5625</v>
       </c>
       <c r="B56">
-        <v>521.86</v>
+        <v>974.356</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46150.58333333334</v>
+        <v>46153.57291666666</v>
       </c>
       <c r="B57">
-        <v>526.9930000000001</v>
+        <v>1019.87</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46150.59375</v>
+        <v>46153.58333333334</v>
       </c>
       <c r="B58">
-        <v>524.653</v>
+        <v>1098.039</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46150.60416666666</v>
+        <v>46153.59375</v>
       </c>
       <c r="B59">
-        <v>532.766</v>
+        <v>1138.043</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46150.61458333334</v>
+        <v>46153.60416666666</v>
       </c>
       <c r="B60">
-        <v>540.204</v>
+        <v>1177.11</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46150.625</v>
+        <v>46153.61458333334</v>
       </c>
       <c r="B61">
-        <v>549.728</v>
+        <v>1218.53</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46150.63541666666</v>
+        <v>46153.625</v>
       </c>
       <c r="B62">
-        <v>554.545</v>
+        <v>1298.2</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46150.64583333334</v>
+        <v>46153.63541666666</v>
       </c>
       <c r="B63">
-        <v>559.178</v>
+        <v>1327.065</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46150.65625</v>
+        <v>46153.64583333334</v>
       </c>
       <c r="B64">
-        <v>564.417</v>
+        <v>1356.838</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46150.66666666666</v>
+        <v>46153.65625</v>
       </c>
       <c r="B65">
-        <v>568.955</v>
+        <v>1383.577</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46150.67708333334</v>
+        <v>46153.66666666666</v>
       </c>
       <c r="B66">
-        <v>509.336</v>
+        <v>1387.656</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46150.6875</v>
+        <v>46153.67708333334</v>
       </c>
       <c r="B67">
-        <v>510.897</v>
+        <v>1387.816</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46150.69791666666</v>
+        <v>46153.6875</v>
       </c>
       <c r="B68">
-        <v>513.307</v>
+        <v>1388.871</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46150.70833333334</v>
+        <v>46153.69791666666</v>
       </c>
       <c r="B69">
-        <v>516.074</v>
+        <v>1389.424</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46150.71875</v>
+        <v>46153.70833333334</v>
       </c>
       <c r="B70">
-        <v>515.9299999999999</v>
+        <v>1446.241</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46150.72916666666</v>
+        <v>46153.71875</v>
       </c>
       <c r="B71">
-        <v>514.064</v>
+        <v>1444.349</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46150.73958333334</v>
+        <v>46153.72916666666</v>
       </c>
       <c r="B72">
-        <v>512.515</v>
+        <v>1441.196</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46150.75</v>
+        <v>46153.73958333334</v>
       </c>
       <c r="B73">
-        <v>511.612</v>
+        <v>1440.542</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46150.76041666666</v>
+        <v>46153.75</v>
       </c>
       <c r="B74">
-        <v>502.257</v>
+        <v>1452.502</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46150.77083333334</v>
+        <v>46153.76041666666</v>
       </c>
       <c r="B75">
-        <v>508.437</v>
+        <v>1469.295</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46150.78125</v>
+        <v>46153.77083333334</v>
       </c>
       <c r="B76">
-        <v>516.023</v>
+        <v>1484.072</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46150.79166666666</v>
+        <v>46153.78125</v>
       </c>
       <c r="B77">
-        <v>522.876</v>
+        <v>1502.072</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46150.80208333334</v>
+        <v>46153.79166666666</v>
       </c>
       <c r="B78">
-        <v>535.347</v>
+        <v>1537.951</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46150.8125</v>
+        <v>46153.80208333334</v>
       </c>
       <c r="B79">
-        <v>540.175</v>
+        <v>1566.247</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46150.82291666666</v>
+        <v>46153.8125</v>
       </c>
       <c r="B80">
-        <v>545.4829999999999</v>
+        <v>1590.751</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46150.83333333334</v>
+        <v>46153.82291666666</v>
       </c>
       <c r="B81">
-        <v>550.277</v>
+        <v>1614.623</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46150.84375</v>
+        <v>46153.83333333334</v>
       </c>
       <c r="B82">
-        <v>568.159</v>
+        <v>1693.584</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46150.85416666666</v>
+        <v>46153.84375</v>
       </c>
       <c r="B83">
-        <v>561.001</v>
+        <v>1711.131</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46150.86458333334</v>
+        <v>46153.85416666666</v>
       </c>
       <c r="B84">
-        <v>553.962</v>
+        <v>1729.709</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46150.875</v>
+        <v>46153.86458333334</v>
       </c>
       <c r="B85">
-        <v>546.873</v>
+        <v>1748.139</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46150.88541666666</v>
+        <v>46153.875</v>
       </c>
       <c r="B86">
-        <v>516.223</v>
+        <v>1765.897</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46150.89583333334</v>
+        <v>46153.88541666666</v>
       </c>
       <c r="B87">
-        <v>503.182</v>
+        <v>1767.159</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46150.90625</v>
+        <v>46153.89583333334</v>
       </c>
       <c r="B88">
-        <v>485.545</v>
+        <v>1769.011</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46150.91666666666</v>
+        <v>46153.90625</v>
       </c>
       <c r="B89">
-        <v>471.292</v>
+        <v>1769.947</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46150.92708333334</v>
+        <v>46153.91666666666</v>
       </c>
       <c r="B90">
-        <v>450.85</v>
+        <v>1777.055</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46150.9375</v>
+        <v>46153.92708333334</v>
       </c>
       <c r="B91">
-        <v>442.259</v>
+        <v>1778.638</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46150.94791666666</v>
+        <v>46153.9375</v>
       </c>
       <c r="B92">
-        <v>428.21</v>
+        <v>1780.721</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46150.95833333334</v>
+        <v>46153.94791666666</v>
       </c>
       <c r="B93">
-        <v>443.51</v>
+        <v>1783.516</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46150.96875</v>
+        <v>46153.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>1843.986</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46150.97916666666</v>
+        <v>46153.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>1832.334</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46150.98958333334</v>
+        <v>46153.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1819.501</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46151</v>
+        <v>46153.98958333334</v>
       </c>
       <c r="B97">
+        <v>1810.982</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46154</v>
+      </c>
+      <c r="B98">
+        <v>1771.932</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46154.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>1751.182</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46154.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>1714.042</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46154.03125</v>
+      </c>
+      <c r="B101">
+        <v>1688.671</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46154.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>1622.899</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46154.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>1584.565</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46154.0625</v>
+      </c>
+      <c r="B104">
+        <v>1543.412</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46154.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>1513.14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46154.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>1444.737</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46154.09375</v>
+      </c>
+      <c r="B107">
+        <v>1408.098</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46154.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>1373.897</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46154.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>1341.622</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46154.125</v>
+      </c>
+      <c r="B110">
+        <v>1266.748</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46154.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>1229.519</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46154.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>1186.962</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46154.15625</v>
+      </c>
+      <c r="B113">
+        <v>1142.421</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46154.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>1122.598</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46154.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>1073.779</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46154.1875</v>
+      </c>
+      <c r="B116">
+        <v>1018.752</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46154.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>965.311</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46154.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>870.058</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46154.21875</v>
+      </c>
+      <c r="B119">
+        <v>813.076</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46154.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>781.1130000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46154.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>746.236</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46154.25</v>
+      </c>
+      <c r="B122">
+        <v>688.596</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46154.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>656.061</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46154.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>624.674</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46154.28125</v>
+      </c>
+      <c r="B125">
+        <v>591.022</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46154.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>530.841</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46154.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>513.6130000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46154.3125</v>
+      </c>
+      <c r="B128">
+        <v>469.495</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46154.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>460.553</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46154.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>441.822</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46154.34375</v>
+      </c>
+      <c r="B131">
+        <v>450.078</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46154.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>432.415</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46154.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>409.886</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46154.375</v>
+      </c>
+      <c r="B134">
+        <v>468.282</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46154.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>462.117</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46154.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>457.774</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46154.40625</v>
+      </c>
+      <c r="B137">
+        <v>451.082</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46154.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>439.625</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46154.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>441.053</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46154.4375</v>
+      </c>
+      <c r="B140">
+        <v>442.328</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46154.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>445.59</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46154.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>414.994</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46154.46875</v>
+      </c>
+      <c r="B143">
+        <v>425.045</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46154.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>434.314</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46154.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>442.498</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46154.5</v>
+      </c>
+      <c r="B146">
+        <v>458.33</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46154.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>469.996</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46154.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>483.167</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46154.53125</v>
+      </c>
+      <c r="B149">
+        <v>498.348</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46154.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>515.377</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46154.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>537.6420000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46154.5625</v>
+      </c>
+      <c r="B152">
+        <v>557.335</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46154.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>574.833</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46154.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>651.165</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46154.59375</v>
+      </c>
+      <c r="B155">
+        <v>663.1660000000001</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46154.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>674.6180000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46154.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>685.9690000000001</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46154.625</v>
+      </c>
+      <c r="B158">
+        <v>647.934</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46154.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>638.01</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46154.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>628.692</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46154.65625</v>
+      </c>
+      <c r="B161">
+        <v>617.827</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46154.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>594.9640000000001</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46154.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>574.833</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46154.6875</v>
+      </c>
+      <c r="B164">
+        <v>556.796</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46154.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>540.894</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46154.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>499.05</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46154.71875</v>
+      </c>
+      <c r="B167">
+        <v>494.184</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46154.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>490.37</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46154.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>484.916</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46154.75</v>
+      </c>
+      <c r="B170">
+        <v>496.24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46154.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>506.987</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46154.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>521.224</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46154.78125</v>
+      </c>
+      <c r="B173">
+        <v>537.224</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46154.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>459.371</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46154.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>469.003</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46154.8125</v>
+      </c>
+      <c r="B176">
+        <v>479.97</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46154.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>504.874</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46154.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>561.684</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46154.84375</v>
+      </c>
+      <c r="B179">
+        <v>583.133</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46154.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>599.796</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46154.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>604.559</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46154.875</v>
+      </c>
+      <c r="B182">
+        <v>655.6079999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46154.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>670.912</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46154.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>696.563</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46154.90625</v>
+      </c>
+      <c r="B185">
+        <v>728.0309999999999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46154.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>758.484</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46154.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>773.376</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46154.9375</v>
+      </c>
+      <c r="B188">
+        <v>796.628</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46154.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>818.764</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46154.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46154.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46154.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46154.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,1511 +394,1511 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B2">
-        <v>130.332</v>
+        <v>1514.13</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46153.01041666666</v>
+        <v>46155.01041666666</v>
       </c>
       <c r="B3">
-        <v>130.352</v>
+        <v>1515.061</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46153.02083333334</v>
+        <v>46155.02083333334</v>
       </c>
       <c r="B4">
-        <v>130.671</v>
+        <v>1524.795</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46153.03125</v>
+        <v>46155.03125</v>
       </c>
       <c r="B5">
-        <v>130.81</v>
+        <v>1587.942</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46153.04166666666</v>
+        <v>46155.04166666666</v>
       </c>
       <c r="B6">
-        <v>129.903</v>
+        <v>1534.096</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46153.05208333334</v>
+        <v>46155.05208333334</v>
       </c>
       <c r="B7">
-        <v>128.473</v>
+        <v>1554.276</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46153.0625</v>
+        <v>46155.0625</v>
       </c>
       <c r="B8">
-        <v>127.035</v>
+        <v>1567.674</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46153.07291666666</v>
+        <v>46155.07291666666</v>
       </c>
       <c r="B9">
-        <v>125.456</v>
+        <v>1577.159</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46153.08333333334</v>
+        <v>46155.08333333334</v>
       </c>
       <c r="B10">
-        <v>112.252</v>
+        <v>1534.106</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46153.09375</v>
+        <v>46155.09375</v>
       </c>
       <c r="B11">
-        <v>112.257</v>
+        <v>1534.661</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46153.10416666666</v>
+        <v>46155.10416666666</v>
       </c>
       <c r="B12">
-        <v>112.884</v>
+        <v>1516.831</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46153.11458333334</v>
+        <v>46155.11458333334</v>
       </c>
       <c r="B13">
-        <v>113.472</v>
+        <v>1496.469</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46153.125</v>
+        <v>46155.125</v>
       </c>
       <c r="B14">
-        <v>116.366</v>
+        <v>1492.012</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46153.13541666666</v>
+        <v>46155.13541666666</v>
       </c>
       <c r="B15">
-        <v>119.211</v>
+        <v>1498.614</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46153.14583333334</v>
+        <v>46155.14583333334</v>
       </c>
       <c r="B16">
-        <v>122.09</v>
+        <v>1518.435</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46153.15625</v>
+        <v>46155.15625</v>
       </c>
       <c r="B17">
-        <v>125.275</v>
+        <v>1489.71</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46153.16666666666</v>
+        <v>46155.16666666666</v>
       </c>
       <c r="B18">
-        <v>128.958</v>
+        <v>1458.967</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46153.17708333334</v>
+        <v>46155.17708333334</v>
       </c>
       <c r="B19">
-        <v>135.368</v>
+        <v>1471.633</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46153.1875</v>
+        <v>46155.1875</v>
       </c>
       <c r="B20">
-        <v>139.99</v>
+        <v>1496.239</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46153.19791666666</v>
+        <v>46155.19791666666</v>
       </c>
       <c r="B21">
-        <v>146.63</v>
+        <v>1499.005</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46153.20833333334</v>
+        <v>46155.20833333334</v>
       </c>
       <c r="B22">
-        <v>161.679</v>
+        <v>1510.375</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46153.21875</v>
+        <v>46155.21875</v>
       </c>
       <c r="B23">
-        <v>172.446</v>
+        <v>1539.779</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46153.22916666666</v>
+        <v>46155.22916666666</v>
       </c>
       <c r="B24">
-        <v>184.133</v>
+        <v>1567.268</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46153.23958333334</v>
+        <v>46155.23958333334</v>
       </c>
       <c r="B25">
-        <v>195.863</v>
+        <v>1585.051</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46153.25</v>
+        <v>46155.25</v>
       </c>
       <c r="B26">
-        <v>184.073</v>
+        <v>1554.619</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46153.26041666666</v>
+        <v>46155.26041666666</v>
       </c>
       <c r="B27">
-        <v>194.949</v>
+        <v>1573.037</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46153.27083333334</v>
+        <v>46155.27083333334</v>
       </c>
       <c r="B28">
-        <v>207.406</v>
+        <v>1606.125</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46153.28125</v>
+        <v>46155.28125</v>
       </c>
       <c r="B29">
-        <v>217.963</v>
+        <v>1634.351</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46153.29166666666</v>
+        <v>46155.29166666666</v>
       </c>
       <c r="B30">
-        <v>223.207</v>
+        <v>1677.919</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46153.30208333334</v>
+        <v>46155.30208333334</v>
       </c>
       <c r="B31">
-        <v>226.249</v>
+        <v>1695.033</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46153.3125</v>
+        <v>46155.3125</v>
       </c>
       <c r="B32">
-        <v>228.391</v>
+        <v>1713.155</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46153.32291666666</v>
+        <v>46155.32291666666</v>
       </c>
       <c r="B33">
-        <v>228.891</v>
+        <v>1727.28</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46153.33333333334</v>
+        <v>46155.33333333334</v>
       </c>
       <c r="B34">
-        <v>241.616</v>
+        <v>1754.489</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46153.34375</v>
+        <v>46155.34375</v>
       </c>
       <c r="B35">
-        <v>247.111</v>
+        <v>1751.634</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46153.35416666666</v>
+        <v>46155.35416666666</v>
       </c>
       <c r="B36">
-        <v>260.222</v>
+        <v>1768.254</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46153.36458333334</v>
+        <v>46155.36458333334</v>
       </c>
       <c r="B37">
-        <v>267.281</v>
+        <v>1772.681</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46153.375</v>
+        <v>46155.375</v>
       </c>
       <c r="B38">
-        <v>340.494</v>
+        <v>1755.138</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46153.38541666666</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="B39">
-        <v>365.54</v>
+        <v>1766.358</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46153.39583333334</v>
+        <v>46155.39583333334</v>
       </c>
       <c r="B40">
-        <v>389.794</v>
+        <v>1781.007</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46153.40625</v>
+        <v>46155.40625</v>
       </c>
       <c r="B41">
-        <v>413.845</v>
+        <v>1795.969</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46153.41666666666</v>
+        <v>46155.41666666666</v>
       </c>
       <c r="B42">
-        <v>424.131</v>
+        <v>1825.392</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46153.42708333334</v>
+        <v>46155.42708333334</v>
       </c>
       <c r="B43">
-        <v>454.116</v>
+        <v>1847.688</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46153.4375</v>
+        <v>46155.4375</v>
       </c>
       <c r="B44">
-        <v>483.236</v>
+        <v>1867.773</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46153.44791666666</v>
+        <v>46155.44791666666</v>
       </c>
       <c r="B45">
-        <v>512.643</v>
+        <v>1887.089</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46153.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="B46">
-        <v>540.408</v>
+        <v>1992.724</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46153.46875</v>
+        <v>46155.46875</v>
       </c>
       <c r="B47">
-        <v>570.808</v>
+        <v>1992.904</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46153.47916666666</v>
+        <v>46155.47916666666</v>
       </c>
       <c r="B48">
-        <v>600.515</v>
+        <v>1991.211</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46153.48958333334</v>
+        <v>46155.48958333334</v>
       </c>
       <c r="B49">
-        <v>630.097</v>
+        <v>1988.345</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46153.5</v>
+        <v>46155.5</v>
       </c>
       <c r="B50">
-        <v>698.88</v>
+        <v>1983.107</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46153.51041666666</v>
+        <v>46155.51041666666</v>
       </c>
       <c r="B51">
-        <v>737.718</v>
+        <v>1976.124</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46153.52083333334</v>
+        <v>46155.52083333334</v>
       </c>
       <c r="B52">
-        <v>777.216</v>
+        <v>1967.59</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46153.53125</v>
+        <v>46155.53125</v>
       </c>
       <c r="B53">
-        <v>818.133</v>
+        <v>1961.448</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46153.54166666666</v>
+        <v>46155.54166666666</v>
       </c>
       <c r="B54">
-        <v>883.697</v>
+        <v>1944.922</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46153.55208333334</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="B55">
-        <v>929.708</v>
+        <v>1940.154</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46153.5625</v>
+        <v>46155.5625</v>
       </c>
       <c r="B56">
-        <v>974.356</v>
+        <v>1936.239</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46153.57291666666</v>
+        <v>46155.57291666666</v>
       </c>
       <c r="B57">
-        <v>1019.87</v>
+        <v>1930.641</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46153.58333333334</v>
+        <v>46155.58333333334</v>
       </c>
       <c r="B58">
-        <v>1098.039</v>
+        <v>1792.393</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46153.59375</v>
+        <v>46155.59375</v>
       </c>
       <c r="B59">
-        <v>1138.043</v>
+        <v>1792.031</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46153.60416666666</v>
+        <v>46155.60416666666</v>
       </c>
       <c r="B60">
-        <v>1177.11</v>
+        <v>1792.058</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46153.61458333334</v>
+        <v>46155.61458333334</v>
       </c>
       <c r="B61">
-        <v>1218.53</v>
+        <v>1790.385</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46153.625</v>
+        <v>46155.625</v>
       </c>
       <c r="B62">
-        <v>1298.2</v>
+        <v>1748.898</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46153.63541666666</v>
+        <v>46155.63541666666</v>
       </c>
       <c r="B63">
-        <v>1327.065</v>
+        <v>1731.857</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46153.64583333334</v>
+        <v>46155.64583333334</v>
       </c>
       <c r="B64">
-        <v>1356.838</v>
+        <v>1714.094</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46153.65625</v>
+        <v>46155.65625</v>
       </c>
       <c r="B65">
-        <v>1383.577</v>
+        <v>1694.718</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46153.66666666666</v>
+        <v>46155.66666666666</v>
       </c>
       <c r="B66">
-        <v>1387.656</v>
+        <v>1660.219</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46153.67708333334</v>
+        <v>46155.67708333334</v>
       </c>
       <c r="B67">
-        <v>1387.816</v>
+        <v>1630.865</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46153.6875</v>
+        <v>46155.6875</v>
       </c>
       <c r="B68">
-        <v>1388.871</v>
+        <v>1596.048</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46153.69791666666</v>
+        <v>46155.69791666666</v>
       </c>
       <c r="B69">
-        <v>1389.424</v>
+        <v>1564.751</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46153.70833333334</v>
+        <v>46155.70833333334</v>
       </c>
       <c r="B70">
-        <v>1446.241</v>
+        <v>1512.377</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46153.71875</v>
+        <v>46155.71875</v>
       </c>
       <c r="B71">
-        <v>1444.349</v>
+        <v>1458.714</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46153.72916666666</v>
+        <v>46155.72916666666</v>
       </c>
       <c r="B72">
-        <v>1441.196</v>
+        <v>1406.566</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46153.73958333334</v>
+        <v>46155.73958333334</v>
       </c>
       <c r="B73">
-        <v>1440.542</v>
+        <v>1350.205</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46153.75</v>
+        <v>46155.75</v>
       </c>
       <c r="B74">
-        <v>1452.502</v>
+        <v>1145.099</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46153.76041666666</v>
+        <v>46155.76041666666</v>
       </c>
       <c r="B75">
-        <v>1469.295</v>
+        <v>1079.028</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46153.77083333334</v>
+        <v>46155.77083333334</v>
       </c>
       <c r="B76">
-        <v>1484.072</v>
+        <v>1014.477</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46153.78125</v>
+        <v>46155.78125</v>
       </c>
       <c r="B77">
-        <v>1502.072</v>
+        <v>947.792</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46153.79166666666</v>
+        <v>46155.79166666666</v>
       </c>
       <c r="B78">
-        <v>1537.951</v>
+        <v>851.813</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46153.80208333334</v>
+        <v>46155.80208333334</v>
       </c>
       <c r="B79">
-        <v>1566.247</v>
+        <v>824.486</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46153.8125</v>
+        <v>46155.8125</v>
       </c>
       <c r="B80">
-        <v>1590.751</v>
+        <v>796.572</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46153.82291666666</v>
+        <v>46155.82291666666</v>
       </c>
       <c r="B81">
-        <v>1614.623</v>
+        <v>771.203</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46153.83333333334</v>
+        <v>46155.83333333334</v>
       </c>
       <c r="B82">
-        <v>1693.584</v>
+        <v>748.548</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46153.84375</v>
+        <v>46155.84375</v>
       </c>
       <c r="B83">
-        <v>1711.131</v>
+        <v>744.351</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46153.85416666666</v>
+        <v>46155.85416666666</v>
       </c>
       <c r="B84">
-        <v>1729.709</v>
+        <v>737.604</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46153.86458333334</v>
+        <v>46155.86458333334</v>
       </c>
       <c r="B85">
-        <v>1748.139</v>
+        <v>730.006</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46153.875</v>
+        <v>46155.875</v>
       </c>
       <c r="B86">
-        <v>1765.897</v>
+        <v>721.509</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46153.88541666666</v>
+        <v>46155.88541666666</v>
       </c>
       <c r="B87">
-        <v>1767.159</v>
+        <v>719.472</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46153.89583333334</v>
+        <v>46155.89583333334</v>
       </c>
       <c r="B88">
-        <v>1769.011</v>
+        <v>716.616</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46153.90625</v>
+        <v>46155.90625</v>
       </c>
       <c r="B89">
-        <v>1769.947</v>
+        <v>715.165</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46153.91666666666</v>
+        <v>46155.91666666666</v>
       </c>
       <c r="B90">
-        <v>1777.055</v>
+        <v>714.871</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46153.92708333334</v>
+        <v>46155.92708333334</v>
       </c>
       <c r="B91">
-        <v>1778.638</v>
+        <v>711.456</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46153.9375</v>
+        <v>46155.9375</v>
       </c>
       <c r="B92">
-        <v>1780.721</v>
+        <v>710.492</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46153.94791666666</v>
+        <v>46155.94791666666</v>
       </c>
       <c r="B93">
-        <v>1783.516</v>
+        <v>708.744</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46153.95833333334</v>
+        <v>46155.95833333334</v>
       </c>
       <c r="B94">
-        <v>1843.986</v>
+        <v>841.873</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46153.96875</v>
+        <v>46155.96875</v>
       </c>
       <c r="B95">
-        <v>1832.334</v>
+        <v>817.362</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46153.97916666666</v>
+        <v>46155.97916666666</v>
       </c>
       <c r="B96">
-        <v>1819.501</v>
+        <v>810.7140000000001</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46153.98958333334</v>
+        <v>46155.98958333334</v>
       </c>
       <c r="B97">
-        <v>1810.982</v>
+        <v>803.0309999999999</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B98">
-        <v>1771.932</v>
+        <v>850.961</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46154.01041666666</v>
+        <v>46156.01041666666</v>
       </c>
       <c r="B99">
-        <v>1751.182</v>
+        <v>851.946</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46154.02083333334</v>
+        <v>46156.02083333334</v>
       </c>
       <c r="B100">
-        <v>1714.042</v>
+        <v>842.08</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46154.03125</v>
+        <v>46156.03125</v>
       </c>
       <c r="B101">
-        <v>1688.671</v>
+        <v>831.447</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46154.04166666666</v>
+        <v>46156.04166666666</v>
       </c>
       <c r="B102">
-        <v>1622.899</v>
+        <v>821.532</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46154.05208333334</v>
+        <v>46156.05208333334</v>
       </c>
       <c r="B103">
-        <v>1584.565</v>
+        <v>811.2809999999999</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46154.0625</v>
+        <v>46156.0625</v>
       </c>
       <c r="B104">
-        <v>1543.412</v>
+        <v>793.987</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46154.07291666666</v>
+        <v>46156.07291666666</v>
       </c>
       <c r="B105">
-        <v>1513.14</v>
+        <v>789.751</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46154.08333333334</v>
+        <v>46156.08333333334</v>
       </c>
       <c r="B106">
-        <v>1444.737</v>
+        <v>801.353</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46154.09375</v>
+        <v>46156.09375</v>
       </c>
       <c r="B107">
-        <v>1408.098</v>
+        <v>792.157</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46154.10416666666</v>
+        <v>46156.10416666666</v>
       </c>
       <c r="B108">
-        <v>1373.897</v>
+        <v>779.986</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46154.11458333334</v>
+        <v>46156.11458333334</v>
       </c>
       <c r="B109">
-        <v>1341.622</v>
+        <v>779.905</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46154.125</v>
+        <v>46156.125</v>
       </c>
       <c r="B110">
-        <v>1266.748</v>
+        <v>743.831</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46154.13541666666</v>
+        <v>46156.13541666666</v>
       </c>
       <c r="B111">
-        <v>1229.519</v>
+        <v>744.289</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46154.14583333334</v>
+        <v>46156.14583333334</v>
       </c>
       <c r="B112">
-        <v>1186.962</v>
+        <v>746.659</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46154.15625</v>
+        <v>46156.15625</v>
       </c>
       <c r="B113">
-        <v>1142.421</v>
+        <v>750.821</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46154.16666666666</v>
+        <v>46156.16666666666</v>
       </c>
       <c r="B114">
-        <v>1122.598</v>
+        <v>766.516</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46154.17708333334</v>
+        <v>46156.17708333334</v>
       </c>
       <c r="B115">
-        <v>1073.779</v>
+        <v>748.886</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46154.1875</v>
+        <v>46156.1875</v>
       </c>
       <c r="B116">
-        <v>1018.752</v>
+        <v>737.21</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46154.19791666666</v>
+        <v>46156.19791666666</v>
       </c>
       <c r="B117">
-        <v>965.311</v>
+        <v>717.085</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46154.20833333334</v>
+        <v>46156.20833333334</v>
       </c>
       <c r="B118">
-        <v>870.058</v>
+        <v>682.6559999999999</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46154.21875</v>
+        <v>46156.21875</v>
       </c>
       <c r="B119">
-        <v>813.076</v>
+        <v>659.782</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46154.22916666666</v>
+        <v>46156.22916666666</v>
       </c>
       <c r="B120">
-        <v>781.1130000000001</v>
+        <v>638.905</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46154.23958333334</v>
+        <v>46156.23958333334</v>
       </c>
       <c r="B121">
-        <v>746.236</v>
+        <v>623.833</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46154.25</v>
+        <v>46156.25</v>
       </c>
       <c r="B122">
-        <v>688.596</v>
+        <v>593.729</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46154.26041666666</v>
+        <v>46156.26041666666</v>
       </c>
       <c r="B123">
-        <v>656.061</v>
+        <v>566.782</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46154.27083333334</v>
+        <v>46156.27083333334</v>
       </c>
       <c r="B124">
-        <v>624.674</v>
+        <v>545.8680000000001</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46154.28125</v>
+        <v>46156.28125</v>
       </c>
       <c r="B125">
-        <v>591.022</v>
+        <v>526.865</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46154.29166666666</v>
+        <v>46156.29166666666</v>
       </c>
       <c r="B126">
-        <v>530.841</v>
+        <v>485.906</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46154.30208333334</v>
+        <v>46156.30208333334</v>
       </c>
       <c r="B127">
-        <v>513.6130000000001</v>
+        <v>471.932</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46154.3125</v>
+        <v>46156.3125</v>
       </c>
       <c r="B128">
-        <v>469.495</v>
+        <v>441.799</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46154.32291666666</v>
+        <v>46156.32291666666</v>
       </c>
       <c r="B129">
-        <v>460.553</v>
+        <v>421.953</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46154.33333333334</v>
+        <v>46156.33333333334</v>
       </c>
       <c r="B130">
-        <v>441.822</v>
+        <v>431.464</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46154.34375</v>
+        <v>46156.34375</v>
       </c>
       <c r="B131">
-        <v>450.078</v>
+        <v>418.926</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46154.35416666666</v>
+        <v>46156.35416666666</v>
       </c>
       <c r="B132">
-        <v>432.415</v>
+        <v>407.484</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46154.36458333334</v>
+        <v>46156.36458333334</v>
       </c>
       <c r="B133">
-        <v>409.886</v>
+        <v>397.45</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46154.375</v>
+        <v>46156.375</v>
       </c>
       <c r="B134">
-        <v>468.282</v>
+        <v>393.706</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46154.38541666666</v>
+        <v>46156.38541666666</v>
       </c>
       <c r="B135">
-        <v>462.117</v>
+        <v>384.827</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46154.39583333334</v>
+        <v>46156.39583333334</v>
       </c>
       <c r="B136">
-        <v>457.774</v>
+        <v>375.519</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46154.40625</v>
+        <v>46156.40625</v>
       </c>
       <c r="B137">
-        <v>451.082</v>
+        <v>366.706</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46154.41666666666</v>
+        <v>46156.41666666666</v>
       </c>
       <c r="B138">
-        <v>439.625</v>
+        <v>321.559</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46154.42708333334</v>
+        <v>46156.42708333334</v>
       </c>
       <c r="B139">
-        <v>441.053</v>
+        <v>314.462</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46154.4375</v>
+        <v>46156.4375</v>
       </c>
       <c r="B140">
-        <v>442.328</v>
+        <v>308.366</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46154.44791666666</v>
+        <v>46156.44791666666</v>
       </c>
       <c r="B141">
-        <v>445.59</v>
+        <v>302.297</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46154.45833333334</v>
+        <v>46156.45833333334</v>
       </c>
       <c r="B142">
-        <v>414.994</v>
+        <v>292.48</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46154.46875</v>
+        <v>46156.46875</v>
       </c>
       <c r="B143">
-        <v>425.045</v>
+        <v>290.736</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46154.47916666666</v>
+        <v>46156.47916666666</v>
       </c>
       <c r="B144">
-        <v>434.314</v>
+        <v>287.638</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46154.48958333334</v>
+        <v>46156.48958333334</v>
       </c>
       <c r="B145">
-        <v>442.498</v>
+        <v>285.027</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46154.5</v>
+        <v>46156.5</v>
       </c>
       <c r="B146">
-        <v>458.33</v>
+        <v>281.955</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46154.51041666666</v>
+        <v>46156.51041666666</v>
       </c>
       <c r="B147">
-        <v>469.996</v>
+        <v>283.506</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46154.52083333334</v>
+        <v>46156.52083333334</v>
       </c>
       <c r="B148">
-        <v>483.167</v>
+        <v>281.405</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46154.53125</v>
+        <v>46156.53125</v>
       </c>
       <c r="B149">
-        <v>498.348</v>
+        <v>279.851</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46154.54166666666</v>
+        <v>46156.54166666666</v>
       </c>
       <c r="B150">
-        <v>515.377</v>
+        <v>280.353</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46154.55208333334</v>
+        <v>46156.55208333334</v>
       </c>
       <c r="B151">
-        <v>537.6420000000001</v>
+        <v>281.242</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46154.5625</v>
+        <v>46156.5625</v>
       </c>
       <c r="B152">
-        <v>557.335</v>
+        <v>282.407</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46154.57291666666</v>
+        <v>46156.57291666666</v>
       </c>
       <c r="B153">
-        <v>574.833</v>
+        <v>283.453</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46154.58333333334</v>
+        <v>46156.58333333334</v>
       </c>
       <c r="B154">
-        <v>651.165</v>
+        <v>297.324</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46154.59375</v>
+        <v>46156.59375</v>
       </c>
       <c r="B155">
-        <v>663.1660000000001</v>
+        <v>298.037</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46154.60416666666</v>
+        <v>46156.60416666666</v>
       </c>
       <c r="B156">
-        <v>674.6180000000001</v>
+        <v>300.221</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46154.61458333334</v>
+        <v>46156.61458333334</v>
       </c>
       <c r="B157">
-        <v>685.9690000000001</v>
+        <v>301.145</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46154.625</v>
+        <v>46156.625</v>
       </c>
       <c r="B158">
-        <v>647.934</v>
+        <v>286.167</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46154.63541666666</v>
+        <v>46156.63541666666</v>
       </c>
       <c r="B159">
-        <v>638.01</v>
+        <v>284.396</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46154.64583333334</v>
+        <v>46156.64583333334</v>
       </c>
       <c r="B160">
-        <v>628.692</v>
+        <v>281.992</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46154.65625</v>
+        <v>46156.65625</v>
       </c>
       <c r="B161">
-        <v>617.827</v>
+        <v>279.394</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46154.66666666666</v>
+        <v>46156.66666666666</v>
       </c>
       <c r="B162">
-        <v>594.9640000000001</v>
+        <v>270.462</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46154.67708333334</v>
+        <v>46156.67708333334</v>
       </c>
       <c r="B163">
-        <v>574.833</v>
+        <v>260.252</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46154.6875</v>
+        <v>46156.6875</v>
       </c>
       <c r="B164">
-        <v>556.796</v>
+        <v>250.38</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46154.69791666666</v>
+        <v>46156.69791666666</v>
       </c>
       <c r="B165">
-        <v>540.894</v>
+        <v>241.314</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46154.70833333334</v>
+        <v>46156.70833333334</v>
       </c>
       <c r="B166">
-        <v>499.05</v>
+        <v>229.08</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46154.71875</v>
+        <v>46156.71875</v>
       </c>
       <c r="B167">
-        <v>494.184</v>
+        <v>219.544</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46154.72916666666</v>
+        <v>46156.72916666666</v>
       </c>
       <c r="B168">
-        <v>490.37</v>
+        <v>208.15</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46154.73958333334</v>
+        <v>46156.73958333334</v>
       </c>
       <c r="B169">
-        <v>484.916</v>
+        <v>198.242</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46154.75</v>
+        <v>46156.75</v>
       </c>
       <c r="B170">
-        <v>496.24</v>
+        <v>161.252</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46154.76041666666</v>
+        <v>46156.76041666666</v>
       </c>
       <c r="B171">
-        <v>506.987</v>
+        <v>159.013</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46154.77083333334</v>
+        <v>46156.77083333334</v>
       </c>
       <c r="B172">
-        <v>521.224</v>
+        <v>157.204</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46154.78125</v>
+        <v>46156.78125</v>
       </c>
       <c r="B173">
-        <v>537.224</v>
+        <v>156.221</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46154.79166666666</v>
+        <v>46156.79166666666</v>
       </c>
       <c r="B174">
-        <v>459.371</v>
+        <v>158.86</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46154.80208333334</v>
+        <v>46156.80208333334</v>
       </c>
       <c r="B175">
-        <v>469.003</v>
+        <v>163.381</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46154.8125</v>
+        <v>46156.8125</v>
       </c>
       <c r="B176">
-        <v>479.97</v>
+        <v>168.92</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46154.82291666666</v>
+        <v>46156.82291666666</v>
       </c>
       <c r="B177">
-        <v>504.874</v>
+        <v>192.402</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46154.83333333334</v>
+        <v>46156.83333333334</v>
       </c>
       <c r="B178">
-        <v>561.684</v>
+        <v>180.375</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46154.84375</v>
+        <v>46156.84375</v>
       </c>
       <c r="B179">
-        <v>583.133</v>
+        <v>202.573</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46154.85416666666</v>
+        <v>46156.85416666666</v>
       </c>
       <c r="B180">
-        <v>599.796</v>
+        <v>206.589</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46154.86458333334</v>
+        <v>46156.86458333334</v>
       </c>
       <c r="B181">
-        <v>604.559</v>
+        <v>211.398</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46154.875</v>
+        <v>46156.875</v>
       </c>
       <c r="B182">
-        <v>655.6079999999999</v>
+        <v>217.831</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46154.88541666666</v>
+        <v>46156.88541666666</v>
       </c>
       <c r="B183">
-        <v>670.912</v>
+        <v>223.268</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46154.89583333334</v>
+        <v>46156.89583333334</v>
       </c>
       <c r="B184">
-        <v>696.563</v>
+        <v>227.715</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46154.90625</v>
+        <v>46156.90625</v>
       </c>
       <c r="B185">
-        <v>728.0309999999999</v>
+        <v>232.507</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46154.91666666666</v>
+        <v>46156.91666666666</v>
       </c>
       <c r="B186">
-        <v>758.484</v>
+        <v>207.682</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46154.92708333334</v>
+        <v>46156.92708333334</v>
       </c>
       <c r="B187">
-        <v>773.376</v>
+        <v>211.453</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46154.9375</v>
+        <v>46156.9375</v>
       </c>
       <c r="B188">
-        <v>796.628</v>
+        <v>215.4</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46154.94791666666</v>
+        <v>46156.94791666666</v>
       </c>
       <c r="B189">
-        <v>818.764</v>
+        <v>219.97</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46154.95833333334</v>
+        <v>46156.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46154.96875</v>
+        <v>46156.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46154.97916666666</v>
+        <v>46156.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46154.98958333334</v>
+        <v>46156.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46157.01041666666</v>
+        <v>46163.01041666666</v>
       </c>
       <c r="B2">
-        <v>222.986</v>
+        <v>2011.594</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46157.02083333334</v>
+        <v>46163.02083333334</v>
       </c>
       <c r="B3">
-        <v>230.688</v>
+        <v>2014.513</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46157.03125</v>
+        <v>46163.03125</v>
       </c>
       <c r="B4">
-        <v>237.596</v>
+        <v>2021.993</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46157.04166666666</v>
+        <v>46163.04166666666</v>
       </c>
       <c r="B5">
-        <v>242.19</v>
+        <v>2038.267</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46157.05208333334</v>
+        <v>46163.05208333334</v>
       </c>
       <c r="B6">
-        <v>276.714</v>
+        <v>2082.547</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46157.0625</v>
+        <v>46163.0625</v>
       </c>
       <c r="B7">
-        <v>283.335</v>
+        <v>2102.276</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46157.07291666666</v>
+        <v>46163.07291666666</v>
       </c>
       <c r="B8">
-        <v>288.709</v>
+        <v>2116.323</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46157.08333333334</v>
+        <v>46163.08333333334</v>
       </c>
       <c r="B9">
-        <v>299.508</v>
+        <v>2125.058</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46157.09375</v>
+        <v>46163.09375</v>
       </c>
       <c r="B10">
-        <v>313.95</v>
+        <v>2100.509</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46157.10416666666</v>
+        <v>46163.10416666666</v>
       </c>
       <c r="B11">
-        <v>326.004</v>
+        <v>2114.928</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46157.11458333334</v>
+        <v>46163.11458333334</v>
       </c>
       <c r="B12">
-        <v>340.298</v>
+        <v>2121.844</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46157.125</v>
+        <v>46163.125</v>
       </c>
       <c r="B13">
-        <v>348.449</v>
+        <v>2125.094</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46157.13541666666</v>
+        <v>46163.13541666666</v>
       </c>
       <c r="B14">
-        <v>353.975</v>
+        <v>2119.449</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46157.14583333334</v>
+        <v>46163.14583333334</v>
       </c>
       <c r="B15">
-        <v>354.969</v>
+        <v>2132.258</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46157.15625</v>
+        <v>46163.15625</v>
       </c>
       <c r="B16">
-        <v>351.276</v>
+        <v>2135.947</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46157.16666666666</v>
+        <v>46163.16666666666</v>
       </c>
       <c r="B17">
-        <v>361.81</v>
+        <v>2137.335</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46157.17708333334</v>
+        <v>46163.17708333334</v>
       </c>
       <c r="B18">
-        <v>346.455</v>
+        <v>2125.63</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46157.1875</v>
+        <v>46163.1875</v>
       </c>
       <c r="B19">
-        <v>345.357</v>
+        <v>2132.514</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46157.19791666666</v>
+        <v>46163.19791666666</v>
       </c>
       <c r="B20">
-        <v>347.186</v>
+        <v>2127.748</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46157.20833333334</v>
+        <v>46163.20833333334</v>
       </c>
       <c r="B21">
-        <v>356.172</v>
+        <v>2121.565</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46157.21875</v>
+        <v>46163.21875</v>
       </c>
       <c r="B22">
-        <v>333.547</v>
+        <v>2178.735</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46157.22916666666</v>
+        <v>46163.22916666666</v>
       </c>
       <c r="B23">
-        <v>326.877</v>
+        <v>2176.146</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46157.23958333334</v>
+        <v>46163.23958333334</v>
       </c>
       <c r="B24">
-        <v>328.628</v>
+        <v>2173.474</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46157.25</v>
+        <v>46163.25</v>
       </c>
       <c r="B25">
-        <v>320.927</v>
+        <v>2167.727</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46157.26041666666</v>
+        <v>46163.26041666666</v>
       </c>
       <c r="B26">
-        <v>303.678</v>
+        <v>2164.497</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46157.27083333334</v>
+        <v>46163.27083333334</v>
       </c>
       <c r="B27">
-        <v>293.056</v>
+        <v>2177.459</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46157.28125</v>
+        <v>46163.28125</v>
       </c>
       <c r="B28">
-        <v>284.244</v>
+        <v>2195.562</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46157.29166666666</v>
+        <v>46163.29166666666</v>
       </c>
       <c r="B29">
-        <v>275.382</v>
+        <v>2220.964</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46157.30208333334</v>
+        <v>46163.30208333334</v>
       </c>
       <c r="B30">
-        <v>257.059</v>
+        <v>2213.556</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46157.3125</v>
+        <v>46163.3125</v>
       </c>
       <c r="B31">
-        <v>238.345</v>
+        <v>2208.366</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46157.32291666666</v>
+        <v>46163.32291666666</v>
       </c>
       <c r="B32">
-        <v>228.704</v>
+        <v>2205.51</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46157.33333333334</v>
+        <v>46163.33333333334</v>
       </c>
       <c r="B33">
-        <v>214.243</v>
+        <v>2207.71</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46157.34375</v>
+        <v>46163.34375</v>
       </c>
       <c r="B34">
-        <v>229.026</v>
+        <v>2166.95</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46157.35416666666</v>
+        <v>46163.35416666666</v>
       </c>
       <c r="B35">
-        <v>226.48</v>
+        <v>2151.582</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46157.36458333334</v>
+        <v>46163.36458333334</v>
       </c>
       <c r="B36">
-        <v>223.826</v>
+        <v>2122.157</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46157.375</v>
+        <v>46163.375</v>
       </c>
       <c r="B37">
-        <v>221.355</v>
+        <v>2107.632</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46157.38541666666</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="B38">
-        <v>204.523</v>
+        <v>2008.521</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46157.39583333334</v>
+        <v>46163.39583333334</v>
       </c>
       <c r="B39">
-        <v>210.767</v>
+        <v>1988.378</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46157.40625</v>
+        <v>46163.40625</v>
       </c>
       <c r="B40">
-        <v>215.808</v>
+        <v>1968.003</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46157.41666666666</v>
+        <v>46163.41666666666</v>
       </c>
       <c r="B41">
-        <v>221.519</v>
+        <v>1949.559</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46157.42708333334</v>
+        <v>46163.42708333334</v>
       </c>
       <c r="B42">
-        <v>231.147</v>
+        <v>1995.077</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46157.4375</v>
+        <v>46163.4375</v>
       </c>
       <c r="B43">
-        <v>239.129</v>
+        <v>1974.716</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46157.44791666666</v>
+        <v>46163.44791666666</v>
       </c>
       <c r="B44">
-        <v>250.918</v>
+        <v>1957.036</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46157.45833333334</v>
+        <v>46163.45833333334</v>
       </c>
       <c r="B45">
-        <v>260.606</v>
+        <v>1940.504</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46157.46875</v>
+        <v>46163.46875</v>
       </c>
       <c r="B46">
-        <v>275.241</v>
+        <v>1819.321</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46157.47916666666</v>
+        <v>46163.47916666666</v>
       </c>
       <c r="B47">
-        <v>287.181</v>
+        <v>1801.815</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46157.48958333334</v>
+        <v>46163.48958333334</v>
       </c>
       <c r="B48">
-        <v>302.018</v>
+        <v>1784.579</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46157.5</v>
+        <v>46163.5</v>
       </c>
       <c r="B49">
-        <v>317.543</v>
+        <v>1765.999</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46157.51041666666</v>
+        <v>46163.51041666666</v>
       </c>
       <c r="B50">
-        <v>348.313</v>
+        <v>1730.827</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46157.52083333334</v>
+        <v>46163.52083333334</v>
       </c>
       <c r="B51">
-        <v>375.099</v>
+        <v>1703.079</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46157.53125</v>
+        <v>46163.53125</v>
       </c>
       <c r="B52">
-        <v>403.187</v>
+        <v>1675.186</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46157.54166666666</v>
+        <v>46163.54166666666</v>
       </c>
       <c r="B53">
-        <v>430.833</v>
+        <v>1646.007</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46157.55208333334</v>
+        <v>46163.55208333334</v>
       </c>
       <c r="B54">
-        <v>482.566</v>
+        <v>1586.548</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46157.5625</v>
+        <v>46163.5625</v>
       </c>
       <c r="B55">
-        <v>526.181</v>
+        <v>1563.061</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46157.57291666666</v>
+        <v>46163.57291666666</v>
       </c>
       <c r="B56">
-        <v>568.566</v>
+        <v>1539.32</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46157.58333333334</v>
+        <v>46163.58333333334</v>
       </c>
       <c r="B57">
-        <v>611.28</v>
+        <v>1511.519</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46157.59375</v>
+        <v>46163.59375</v>
       </c>
       <c r="B58">
-        <v>682.7670000000001</v>
+        <v>1513.295</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46157.60416666666</v>
+        <v>46163.60416666666</v>
       </c>
       <c r="B59">
-        <v>733.467</v>
+        <v>1492.574</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46157.61458333334</v>
+        <v>46163.61458333334</v>
       </c>
       <c r="B60">
-        <v>782.672</v>
+        <v>1472.17</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46157.625</v>
+        <v>46163.625</v>
       </c>
       <c r="B61">
-        <v>831.625</v>
+        <v>1451.834</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46157.63541666666</v>
+        <v>46163.63541666666</v>
       </c>
       <c r="B62">
-        <v>900.1319999999999</v>
+        <v>1478.755</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46157.64583333334</v>
+        <v>46163.64583333334</v>
       </c>
       <c r="B63">
-        <v>949.564</v>
+        <v>1457.184</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46157.65625</v>
+        <v>46163.65625</v>
       </c>
       <c r="B64">
-        <v>993.9589999999999</v>
+        <v>1436.075</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46157.66666666666</v>
+        <v>46163.66666666666</v>
       </c>
       <c r="B65">
-        <v>1037.369</v>
+        <v>1416.53</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46157.67708333334</v>
+        <v>46163.67708333334</v>
       </c>
       <c r="B66">
-        <v>1093.285</v>
+        <v>1391.006</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46157.6875</v>
+        <v>46163.6875</v>
       </c>
       <c r="B67">
-        <v>1131.188</v>
+        <v>1382.72</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46157.69791666666</v>
+        <v>46163.69791666666</v>
       </c>
       <c r="B68">
-        <v>1168.437</v>
+        <v>1377.459</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46157.70833333334</v>
+        <v>46163.70833333334</v>
       </c>
       <c r="B69">
-        <v>1207.48</v>
+        <v>1371.863</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46157.71875</v>
+        <v>46163.71875</v>
       </c>
       <c r="B70">
-        <v>1256.398</v>
+        <v>1353.84</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46157.72916666666</v>
+        <v>46163.72916666666</v>
       </c>
       <c r="B71">
-        <v>1279.469</v>
+        <v>1345.745</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46157.73958333334</v>
+        <v>46163.73958333334</v>
       </c>
       <c r="B72">
-        <v>1303.068</v>
+        <v>1336.994</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46157.75</v>
+        <v>46163.75</v>
       </c>
       <c r="B73">
-        <v>1330.042</v>
+        <v>1328.238</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46157.76041666666</v>
+        <v>46163.76041666666</v>
       </c>
       <c r="B74">
-        <v>1374.92</v>
+        <v>1310.1</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46157.77083333334</v>
+        <v>46163.77083333334</v>
       </c>
       <c r="B75">
-        <v>1407.143</v>
+        <v>1296.716</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46157.78125</v>
+        <v>46163.78125</v>
       </c>
       <c r="B76">
-        <v>1444.749</v>
+        <v>1285.568</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46157.79166666666</v>
+        <v>46163.79166666666</v>
       </c>
       <c r="B77">
-        <v>1480.185</v>
+        <v>1271.845</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46157.80208333334</v>
+        <v>46163.80208333334</v>
       </c>
       <c r="B78">
-        <v>1489.991</v>
+        <v>1255.245</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46157.8125</v>
+        <v>46163.8125</v>
       </c>
       <c r="B79">
-        <v>1518.608</v>
+        <v>1240.48</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46157.82291666666</v>
+        <v>46163.82291666666</v>
       </c>
       <c r="B80">
-        <v>1547.712</v>
+        <v>1226.82</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46157.83333333334</v>
+        <v>46163.83333333334</v>
       </c>
       <c r="B81">
-        <v>1579.435</v>
+        <v>1211.221</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46157.84375</v>
+        <v>46163.84375</v>
       </c>
       <c r="B82">
-        <v>1650.331</v>
+        <v>1165.87</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46157.85416666666</v>
+        <v>46163.85416666666</v>
       </c>
       <c r="B83">
-        <v>1661.088</v>
+        <v>1150.827</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46157.86458333334</v>
+        <v>46163.86458333334</v>
       </c>
       <c r="B84">
-        <v>1668.145</v>
+        <v>1135.978</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46157.875</v>
+        <v>46163.875</v>
       </c>
       <c r="B85">
-        <v>1674.912</v>
+        <v>1120.161</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46157.88541666666</v>
+        <v>46163.88541666666</v>
       </c>
       <c r="B86">
-        <v>1680.104</v>
+        <v>1093.194</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46157.89583333334</v>
+        <v>46163.89583333334</v>
       </c>
       <c r="B87">
-        <v>1679.039</v>
+        <v>1075.387</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46157.90625</v>
+        <v>46163.90625</v>
       </c>
       <c r="B88">
-        <v>1679.32</v>
+        <v>1059.155</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46157.91666666666</v>
+        <v>46163.91666666666</v>
       </c>
       <c r="B89">
-        <v>1678.328</v>
+        <v>1042.227</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46157.92708333334</v>
+        <v>46163.92708333334</v>
       </c>
       <c r="B90">
-        <v>1671.927</v>
+        <v>1010.275</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46157.9375</v>
+        <v>46163.9375</v>
       </c>
       <c r="B91">
-        <v>1661.971</v>
+        <v>992.931</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46157.94791666666</v>
+        <v>46163.94791666666</v>
       </c>
       <c r="B92">
-        <v>1649.49</v>
+        <v>975.061</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46157.95833333334</v>
+        <v>46163.95833333334</v>
       </c>
       <c r="B93">
-        <v>1636.378</v>
+        <v>958.145</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46157.96875</v>
+        <v>46163.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46157.97916666666</v>
+        <v>46163.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46157.98958333334</v>
+        <v>46163.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46158</v>
+        <v>46164</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46163.01041666666</v>
+        <v>46164.01041666666</v>
       </c>
       <c r="B2">
-        <v>2011.594</v>
+        <v>881.374</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46163.02083333334</v>
+        <v>46164.02083333334</v>
       </c>
       <c r="B3">
-        <v>2014.513</v>
+        <v>870.271</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46163.03125</v>
+        <v>46164.03125</v>
       </c>
       <c r="B4">
-        <v>2021.993</v>
+        <v>851.846</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46163.04166666666</v>
+        <v>46164.04166666666</v>
       </c>
       <c r="B5">
-        <v>2038.267</v>
+        <v>839.737</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46163.05208333334</v>
+        <v>46164.05208333334</v>
       </c>
       <c r="B6">
-        <v>2082.547</v>
+        <v>807.894</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46163.0625</v>
+        <v>46164.0625</v>
       </c>
       <c r="B7">
-        <v>2102.276</v>
+        <v>809.749</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46163.07291666666</v>
+        <v>46164.07291666666</v>
       </c>
       <c r="B8">
-        <v>2116.323</v>
+        <v>801.558</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46163.08333333334</v>
+        <v>46164.08333333334</v>
       </c>
       <c r="B9">
-        <v>2125.058</v>
+        <v>807.412</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46163.09375</v>
+        <v>46164.09375</v>
       </c>
       <c r="B10">
-        <v>2100.509</v>
+        <v>800.36</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46163.10416666666</v>
+        <v>46164.10416666666</v>
       </c>
       <c r="B11">
-        <v>2114.928</v>
+        <v>809.723</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46163.11458333334</v>
+        <v>46164.11458333334</v>
       </c>
       <c r="B12">
-        <v>2121.844</v>
+        <v>808.6660000000001</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46163.125</v>
+        <v>46164.125</v>
       </c>
       <c r="B13">
-        <v>2125.094</v>
+        <v>812.662</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46163.13541666666</v>
+        <v>46164.13541666666</v>
       </c>
       <c r="B14">
-        <v>2119.449</v>
+        <v>817.691</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46163.14583333334</v>
+        <v>46164.14583333334</v>
       </c>
       <c r="B15">
-        <v>2132.258</v>
+        <v>823.0549999999999</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46163.15625</v>
+        <v>46164.15625</v>
       </c>
       <c r="B16">
-        <v>2135.947</v>
+        <v>825.125</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46163.16666666666</v>
+        <v>46164.16666666666</v>
       </c>
       <c r="B17">
-        <v>2137.335</v>
+        <v>834.793</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46163.17708333334</v>
+        <v>46164.17708333334</v>
       </c>
       <c r="B18">
-        <v>2125.63</v>
+        <v>804.628</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46163.1875</v>
+        <v>46164.1875</v>
       </c>
       <c r="B19">
-        <v>2132.514</v>
+        <v>811.3869999999999</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46163.19791666666</v>
+        <v>46164.19791666666</v>
       </c>
       <c r="B20">
-        <v>2127.748</v>
+        <v>817.679</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46163.20833333334</v>
+        <v>46164.20833333334</v>
       </c>
       <c r="B21">
-        <v>2121.565</v>
+        <v>830.405</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46163.21875</v>
+        <v>46164.21875</v>
       </c>
       <c r="B22">
-        <v>2178.735</v>
+        <v>831.578</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46163.22916666666</v>
+        <v>46164.22916666666</v>
       </c>
       <c r="B23">
-        <v>2176.146</v>
+        <v>833.5</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46163.23958333334</v>
+        <v>46164.23958333334</v>
       </c>
       <c r="B24">
-        <v>2173.474</v>
+        <v>836.212</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46163.25</v>
+        <v>46164.25</v>
       </c>
       <c r="B25">
-        <v>2167.727</v>
+        <v>837.139</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46163.26041666666</v>
+        <v>46164.26041666666</v>
       </c>
       <c r="B26">
-        <v>2164.497</v>
+        <v>825.7619999999999</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46163.27083333334</v>
+        <v>46164.27083333334</v>
       </c>
       <c r="B27">
-        <v>2177.459</v>
+        <v>826.002</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46163.28125</v>
+        <v>46164.28125</v>
       </c>
       <c r="B28">
-        <v>2195.562</v>
+        <v>818.394</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46163.29166666666</v>
+        <v>46164.29166666666</v>
       </c>
       <c r="B29">
-        <v>2220.964</v>
+        <v>815.753</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46163.30208333334</v>
+        <v>46164.30208333334</v>
       </c>
       <c r="B30">
-        <v>2213.556</v>
+        <v>808.288</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46163.3125</v>
+        <v>46164.3125</v>
       </c>
       <c r="B31">
-        <v>2208.366</v>
+        <v>811.279</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46163.32291666666</v>
+        <v>46164.32291666666</v>
       </c>
       <c r="B32">
-        <v>2205.51</v>
+        <v>805.973</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46163.33333333334</v>
+        <v>46164.33333333334</v>
       </c>
       <c r="B33">
-        <v>2207.71</v>
+        <v>784.494</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46163.34375</v>
+        <v>46164.34375</v>
       </c>
       <c r="B34">
-        <v>2166.95</v>
+        <v>733.323</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46163.35416666666</v>
+        <v>46164.35416666666</v>
       </c>
       <c r="B35">
-        <v>2151.582</v>
+        <v>732.0549999999999</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46163.36458333334</v>
+        <v>46164.36458333334</v>
       </c>
       <c r="B36">
-        <v>2122.157</v>
+        <v>715.103</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46163.375</v>
+        <v>46164.375</v>
       </c>
       <c r="B37">
-        <v>2107.632</v>
+        <v>713.745</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46163.38541666666</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="B38">
-        <v>2008.521</v>
+        <v>728.112</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46163.39583333334</v>
+        <v>46164.39583333334</v>
       </c>
       <c r="B39">
-        <v>1988.378</v>
+        <v>718.299</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46163.40625</v>
+        <v>46164.40625</v>
       </c>
       <c r="B40">
-        <v>1968.003</v>
+        <v>708.554</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46163.41666666666</v>
+        <v>46164.41666666666</v>
       </c>
       <c r="B41">
-        <v>1949.559</v>
+        <v>699.423</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46163.42708333334</v>
+        <v>46164.42708333334</v>
       </c>
       <c r="B42">
-        <v>1995.077</v>
+        <v>747.523</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46163.4375</v>
+        <v>46164.4375</v>
       </c>
       <c r="B43">
-        <v>1974.716</v>
+        <v>739.575</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46163.44791666666</v>
+        <v>46164.44791666666</v>
       </c>
       <c r="B44">
-        <v>1957.036</v>
+        <v>732.17</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46163.45833333334</v>
+        <v>46164.45833333334</v>
       </c>
       <c r="B45">
-        <v>1940.504</v>
+        <v>725.133</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46163.46875</v>
+        <v>46164.46875</v>
       </c>
       <c r="B46">
-        <v>1819.321</v>
+        <v>729.981</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46163.47916666666</v>
+        <v>46164.47916666666</v>
       </c>
       <c r="B47">
-        <v>1801.815</v>
+        <v>727.908</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46163.48958333334</v>
+        <v>46164.48958333334</v>
       </c>
       <c r="B48">
-        <v>1784.579</v>
+        <v>687.395</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46163.5</v>
+        <v>46164.5</v>
       </c>
       <c r="B49">
-        <v>1765.999</v>
+        <v>681.1900000000001</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46163.51041666666</v>
+        <v>46164.51041666666</v>
       </c>
       <c r="B50">
-        <v>1730.827</v>
+        <v>675.616</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46163.52083333334</v>
+        <v>46164.52083333334</v>
       </c>
       <c r="B51">
-        <v>1703.079</v>
+        <v>668.851</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46163.53125</v>
+        <v>46164.53125</v>
       </c>
       <c r="B52">
-        <v>1675.186</v>
+        <v>662.078</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46163.54166666666</v>
+        <v>46164.54166666666</v>
       </c>
       <c r="B53">
-        <v>1646.007</v>
+        <v>655.849</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46163.55208333334</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="B54">
-        <v>1586.548</v>
+        <v>647.7569999999999</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46163.5625</v>
+        <v>46164.5625</v>
       </c>
       <c r="B55">
-        <v>1563.061</v>
+        <v>636.329</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46163.57291666666</v>
+        <v>46164.57291666666</v>
       </c>
       <c r="B56">
-        <v>1539.32</v>
+        <v>613.67</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46163.58333333334</v>
+        <v>46164.58333333334</v>
       </c>
       <c r="B57">
-        <v>1511.519</v>
+        <v>590.326</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46163.59375</v>
+        <v>46164.59375</v>
       </c>
       <c r="B58">
-        <v>1513.295</v>
+        <v>609.354</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46163.60416666666</v>
+        <v>46164.60416666666</v>
       </c>
       <c r="B59">
-        <v>1492.574</v>
+        <v>598.149</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46163.61458333334</v>
+        <v>46164.61458333334</v>
       </c>
       <c r="B60">
-        <v>1472.17</v>
+        <v>584.995</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46163.625</v>
+        <v>46164.625</v>
       </c>
       <c r="B61">
-        <v>1451.834</v>
+        <v>604.95</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46163.63541666666</v>
+        <v>46164.63541666666</v>
       </c>
       <c r="B62">
-        <v>1478.755</v>
+        <v>584.232</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46163.64583333334</v>
+        <v>46164.64583333334</v>
       </c>
       <c r="B63">
-        <v>1457.184</v>
+        <v>571.936</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46163.65625</v>
+        <v>46164.65625</v>
       </c>
       <c r="B64">
-        <v>1436.075</v>
+        <v>562.206</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46163.66666666666</v>
+        <v>46164.66666666666</v>
       </c>
       <c r="B65">
-        <v>1416.53</v>
+        <v>551.4589999999999</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46163.67708333334</v>
+        <v>46164.67708333334</v>
       </c>
       <c r="B66">
-        <v>1391.006</v>
+        <v>540.091</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46163.6875</v>
+        <v>46164.6875</v>
       </c>
       <c r="B67">
-        <v>1382.72</v>
+        <v>531.514</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46163.69791666666</v>
+        <v>46164.69791666666</v>
       </c>
       <c r="B68">
-        <v>1377.459</v>
+        <v>523.713</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46163.70833333334</v>
+        <v>46164.70833333334</v>
       </c>
       <c r="B69">
-        <v>1371.863</v>
+        <v>513.831</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46163.71875</v>
+        <v>46164.71875</v>
       </c>
       <c r="B70">
-        <v>1353.84</v>
+        <v>498.973</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46163.72916666666</v>
+        <v>46164.72916666666</v>
       </c>
       <c r="B71">
-        <v>1345.745</v>
+        <v>495.552</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46163.73958333334</v>
+        <v>46164.73958333334</v>
       </c>
       <c r="B72">
-        <v>1336.994</v>
+        <v>492.963</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46163.75</v>
+        <v>46164.75</v>
       </c>
       <c r="B73">
-        <v>1328.238</v>
+        <v>487.806</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46163.76041666666</v>
+        <v>46164.76041666666</v>
       </c>
       <c r="B74">
-        <v>1310.1</v>
+        <v>472.674</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46163.77083333334</v>
+        <v>46164.77083333334</v>
       </c>
       <c r="B75">
-        <v>1296.716</v>
+        <v>475.666</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46163.78125</v>
+        <v>46164.78125</v>
       </c>
       <c r="B76">
-        <v>1285.568</v>
+        <v>477.614</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46163.79166666666</v>
+        <v>46164.79166666666</v>
       </c>
       <c r="B77">
-        <v>1271.845</v>
+        <v>479.918</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46163.80208333334</v>
+        <v>46164.80208333334</v>
       </c>
       <c r="B78">
-        <v>1255.245</v>
+        <v>454.593</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46163.8125</v>
+        <v>46164.8125</v>
       </c>
       <c r="B79">
-        <v>1240.48</v>
+        <v>464.329</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46163.82291666666</v>
+        <v>46164.82291666666</v>
       </c>
       <c r="B80">
-        <v>1226.82</v>
+        <v>475.979</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46163.83333333334</v>
+        <v>46164.83333333334</v>
       </c>
       <c r="B81">
-        <v>1211.221</v>
+        <v>507.899</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46163.84375</v>
+        <v>46164.84375</v>
       </c>
       <c r="B82">
-        <v>1165.87</v>
+        <v>544.415</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46163.85416666666</v>
+        <v>46164.85416666666</v>
       </c>
       <c r="B83">
-        <v>1150.827</v>
+        <v>553.9160000000001</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46163.86458333334</v>
+        <v>46164.86458333334</v>
       </c>
       <c r="B84">
-        <v>1135.978</v>
+        <v>563.788</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46163.875</v>
+        <v>46164.875</v>
       </c>
       <c r="B85">
-        <v>1120.161</v>
+        <v>574.63</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46163.88541666666</v>
+        <v>46164.88541666666</v>
       </c>
       <c r="B86">
-        <v>1093.194</v>
+        <v>610.204</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46163.89583333334</v>
+        <v>46164.89583333334</v>
       </c>
       <c r="B87">
-        <v>1075.387</v>
+        <v>602.856</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46163.90625</v>
+        <v>46164.90625</v>
       </c>
       <c r="B88">
-        <v>1059.155</v>
+        <v>613.211</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46163.91666666666</v>
+        <v>46164.91666666666</v>
       </c>
       <c r="B89">
-        <v>1042.227</v>
+        <v>623.426</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46163.92708333334</v>
+        <v>46164.92708333334</v>
       </c>
       <c r="B90">
-        <v>1010.275</v>
+        <v>691.136</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46163.9375</v>
+        <v>46164.9375</v>
       </c>
       <c r="B91">
-        <v>992.931</v>
+        <v>702.423</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46163.94791666666</v>
+        <v>46164.94791666666</v>
       </c>
       <c r="B92">
-        <v>975.061</v>
+        <v>716.958</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46163.95833333334</v>
+        <v>46164.95833333334</v>
       </c>
       <c r="B93">
-        <v>958.145</v>
+        <v>728.6130000000001</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46163.96875</v>
+        <v>46164.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46163.97916666666</v>
+        <v>46164.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46163.98958333334</v>
+        <v>46164.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46164.01041666666</v>
+        <v>46167.01041666666</v>
       </c>
       <c r="B2">
-        <v>881.374</v>
+        <v>972.653</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46164.02083333334</v>
+        <v>46167.02083333334</v>
       </c>
       <c r="B3">
-        <v>870.271</v>
+        <v>960.2619999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46164.03125</v>
+        <v>46167.03125</v>
       </c>
       <c r="B4">
-        <v>851.846</v>
+        <v>947.4160000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46164.04166666666</v>
+        <v>46167.04166666666</v>
       </c>
       <c r="B5">
-        <v>839.737</v>
+        <v>930.179</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46164.05208333334</v>
+        <v>46167.05208333334</v>
       </c>
       <c r="B6">
-        <v>807.894</v>
+        <v>933.896</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46164.0625</v>
+        <v>46167.0625</v>
       </c>
       <c r="B7">
-        <v>809.749</v>
+        <v>916.247</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46164.07291666666</v>
+        <v>46167.07291666666</v>
       </c>
       <c r="B8">
-        <v>801.558</v>
+        <v>896.357</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46164.08333333334</v>
+        <v>46167.08333333334</v>
       </c>
       <c r="B9">
-        <v>807.412</v>
+        <v>877.948</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46164.09375</v>
+        <v>46167.09375</v>
       </c>
       <c r="B10">
-        <v>800.36</v>
+        <v>836.875</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46164.10416666666</v>
+        <v>46167.10416666666</v>
       </c>
       <c r="B11">
-        <v>809.723</v>
+        <v>824.187</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46164.11458333334</v>
+        <v>46167.11458333334</v>
       </c>
       <c r="B12">
-        <v>808.6660000000001</v>
+        <v>816.197</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46164.125</v>
+        <v>46167.125</v>
       </c>
       <c r="B13">
-        <v>812.662</v>
+        <v>791.1660000000001</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46164.13541666666</v>
+        <v>46167.13541666666</v>
       </c>
       <c r="B14">
-        <v>817.691</v>
+        <v>788.485</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46164.14583333334</v>
+        <v>46167.14583333334</v>
       </c>
       <c r="B15">
-        <v>823.0549999999999</v>
+        <v>786.563</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46164.15625</v>
+        <v>46167.15625</v>
       </c>
       <c r="B16">
-        <v>825.125</v>
+        <v>783.505</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46164.16666666666</v>
+        <v>46167.16666666666</v>
       </c>
       <c r="B17">
-        <v>834.793</v>
+        <v>792.538</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46164.17708333334</v>
+        <v>46167.17708333334</v>
       </c>
       <c r="B18">
-        <v>804.628</v>
+        <v>864.225</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46164.1875</v>
+        <v>46167.1875</v>
       </c>
       <c r="B19">
-        <v>811.3869999999999</v>
+        <v>859.821</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46164.19791666666</v>
+        <v>46167.19791666666</v>
       </c>
       <c r="B20">
-        <v>817.679</v>
+        <v>853.453</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46164.20833333334</v>
+        <v>46167.20833333334</v>
       </c>
       <c r="B21">
-        <v>830.405</v>
+        <v>829.51</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46164.21875</v>
+        <v>46167.21875</v>
       </c>
       <c r="B22">
-        <v>831.578</v>
+        <v>812.091</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46164.22916666666</v>
+        <v>46167.22916666666</v>
       </c>
       <c r="B23">
-        <v>833.5</v>
+        <v>787.864</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46164.23958333334</v>
+        <v>46167.23958333334</v>
       </c>
       <c r="B24">
-        <v>836.212</v>
+        <v>758.96</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46164.25</v>
+        <v>46167.25</v>
       </c>
       <c r="B25">
-        <v>837.139</v>
+        <v>721.144</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46164.26041666666</v>
+        <v>46167.26041666666</v>
       </c>
       <c r="B26">
-        <v>825.7619999999999</v>
+        <v>666.047</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46164.27083333334</v>
+        <v>46167.27083333334</v>
       </c>
       <c r="B27">
-        <v>826.002</v>
+        <v>625.374</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46164.28125</v>
+        <v>46167.28125</v>
       </c>
       <c r="B28">
-        <v>818.394</v>
+        <v>594.192</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46164.29166666666</v>
+        <v>46167.29166666666</v>
       </c>
       <c r="B29">
-        <v>815.753</v>
+        <v>552.171</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46164.30208333334</v>
+        <v>46167.30208333334</v>
       </c>
       <c r="B30">
-        <v>808.288</v>
+        <v>518.33</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46164.3125</v>
+        <v>46167.3125</v>
       </c>
       <c r="B31">
-        <v>811.279</v>
+        <v>470.288</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46164.32291666666</v>
+        <v>46167.32291666666</v>
       </c>
       <c r="B32">
-        <v>805.973</v>
+        <v>420.938</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46164.33333333334</v>
+        <v>46167.33333333334</v>
       </c>
       <c r="B33">
-        <v>784.494</v>
+        <v>375.583</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46164.34375</v>
+        <v>46167.34375</v>
       </c>
       <c r="B34">
-        <v>733.323</v>
+        <v>372.912</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46164.35416666666</v>
+        <v>46167.35416666666</v>
       </c>
       <c r="B35">
-        <v>732.0549999999999</v>
+        <v>367.143</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46164.36458333334</v>
+        <v>46167.36458333334</v>
       </c>
       <c r="B36">
-        <v>715.103</v>
+        <v>358.106</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46164.375</v>
+        <v>46167.375</v>
       </c>
       <c r="B37">
-        <v>713.745</v>
+        <v>350.828</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46164.38541666666</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="B38">
-        <v>728.112</v>
+        <v>357.36</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46164.39583333334</v>
+        <v>46167.39583333334</v>
       </c>
       <c r="B39">
-        <v>718.299</v>
+        <v>368.321</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46164.40625</v>
+        <v>46167.40625</v>
       </c>
       <c r="B40">
-        <v>708.554</v>
+        <v>356.227</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46164.41666666666</v>
+        <v>46167.41666666666</v>
       </c>
       <c r="B41">
-        <v>699.423</v>
+        <v>360.337</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46164.42708333334</v>
+        <v>46167.42708333334</v>
       </c>
       <c r="B42">
-        <v>747.523</v>
+        <v>356.952</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46164.4375</v>
+        <v>46167.4375</v>
       </c>
       <c r="B43">
-        <v>739.575</v>
+        <v>365.662</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46164.44791666666</v>
+        <v>46167.44791666666</v>
       </c>
       <c r="B44">
-        <v>732.17</v>
+        <v>374.362</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46164.45833333334</v>
+        <v>46167.45833333334</v>
       </c>
       <c r="B45">
-        <v>725.133</v>
+        <v>383.482</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46164.46875</v>
+        <v>46167.46875</v>
       </c>
       <c r="B46">
-        <v>729.981</v>
+        <v>451.893</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46164.47916666666</v>
+        <v>46167.47916666666</v>
       </c>
       <c r="B47">
-        <v>727.908</v>
+        <v>462.935</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46164.48958333334</v>
+        <v>46167.48958333334</v>
       </c>
       <c r="B48">
-        <v>687.395</v>
+        <v>473.369</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46164.5</v>
+        <v>46167.5</v>
       </c>
       <c r="B49">
-        <v>681.1900000000001</v>
+        <v>485.059</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46164.51041666666</v>
+        <v>46167.51041666666</v>
       </c>
       <c r="B50">
-        <v>675.616</v>
+        <v>501.682</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46164.52083333334</v>
+        <v>46167.52083333334</v>
       </c>
       <c r="B51">
-        <v>668.851</v>
+        <v>506.619</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46164.53125</v>
+        <v>46167.53125</v>
       </c>
       <c r="B52">
-        <v>662.078</v>
+        <v>511.974</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46164.54166666666</v>
+        <v>46167.54166666666</v>
       </c>
       <c r="B53">
-        <v>655.849</v>
+        <v>516.7329999999999</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46164.55208333334</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="B54">
-        <v>647.7569999999999</v>
+        <v>482.299</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46164.5625</v>
+        <v>46167.5625</v>
       </c>
       <c r="B55">
-        <v>636.329</v>
+        <v>501.074</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46164.57291666666</v>
+        <v>46167.57291666666</v>
       </c>
       <c r="B56">
-        <v>613.67</v>
+        <v>494.035</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46164.58333333334</v>
+        <v>46167.58333333334</v>
       </c>
       <c r="B57">
-        <v>590.326</v>
+        <v>489.221</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46164.59375</v>
+        <v>46167.59375</v>
       </c>
       <c r="B58">
-        <v>609.354</v>
+        <v>504.458</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46164.60416666666</v>
+        <v>46167.60416666666</v>
       </c>
       <c r="B59">
-        <v>598.149</v>
+        <v>509.158</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46164.61458333334</v>
+        <v>46167.61458333334</v>
       </c>
       <c r="B60">
-        <v>584.995</v>
+        <v>515.256</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46164.625</v>
+        <v>46167.625</v>
       </c>
       <c r="B61">
-        <v>604.95</v>
+        <v>521.371</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46164.63541666666</v>
+        <v>46167.63541666666</v>
       </c>
       <c r="B62">
-        <v>584.232</v>
+        <v>533.936</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46164.64583333334</v>
+        <v>46167.64583333334</v>
       </c>
       <c r="B63">
-        <v>571.936</v>
+        <v>550.569</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46164.65625</v>
+        <v>46167.65625</v>
       </c>
       <c r="B64">
-        <v>562.206</v>
+        <v>567.665</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46164.66666666666</v>
+        <v>46167.66666666666</v>
       </c>
       <c r="B65">
-        <v>551.4589999999999</v>
+        <v>585.254</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46164.67708333334</v>
+        <v>46167.67708333334</v>
       </c>
       <c r="B66">
-        <v>540.091</v>
+        <v>561.723</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46164.6875</v>
+        <v>46167.6875</v>
       </c>
       <c r="B67">
-        <v>531.514</v>
+        <v>575.25</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46164.69791666666</v>
+        <v>46167.69791666666</v>
       </c>
       <c r="B68">
-        <v>523.713</v>
+        <v>589.428</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46164.70833333334</v>
+        <v>46167.70833333334</v>
       </c>
       <c r="B69">
-        <v>513.831</v>
+        <v>604.336</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46164.71875</v>
+        <v>46167.71875</v>
       </c>
       <c r="B70">
-        <v>498.973</v>
+        <v>620.523</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46164.72916666666</v>
+        <v>46167.72916666666</v>
       </c>
       <c r="B71">
-        <v>495.552</v>
+        <v>629.793</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46164.73958333334</v>
+        <v>46167.73958333334</v>
       </c>
       <c r="B72">
-        <v>492.963</v>
+        <v>638.202</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46164.75</v>
+        <v>46167.75</v>
       </c>
       <c r="B73">
-        <v>487.806</v>
+        <v>646.609</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46164.76041666666</v>
+        <v>46167.76041666666</v>
       </c>
       <c r="B74">
-        <v>472.674</v>
+        <v>673.963</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46164.77083333334</v>
+        <v>46167.77083333334</v>
       </c>
       <c r="B75">
-        <v>475.666</v>
+        <v>693.61</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46164.78125</v>
+        <v>46167.78125</v>
       </c>
       <c r="B76">
-        <v>477.614</v>
+        <v>712.08</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46164.79166666666</v>
+        <v>46167.79166666666</v>
       </c>
       <c r="B77">
-        <v>479.918</v>
+        <v>730.58</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46164.80208333334</v>
+        <v>46167.80208333334</v>
       </c>
       <c r="B78">
-        <v>454.593</v>
+        <v>753.274</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46164.8125</v>
+        <v>46167.8125</v>
       </c>
       <c r="B79">
-        <v>464.329</v>
+        <v>769.639</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46164.82291666666</v>
+        <v>46167.82291666666</v>
       </c>
       <c r="B80">
-        <v>475.979</v>
+        <v>781.79</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46164.83333333334</v>
+        <v>46167.83333333334</v>
       </c>
       <c r="B81">
-        <v>507.899</v>
+        <v>795.009</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46164.84375</v>
+        <v>46167.84375</v>
       </c>
       <c r="B82">
-        <v>544.415</v>
+        <v>820.181</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46164.85416666666</v>
+        <v>46167.85416666666</v>
       </c>
       <c r="B83">
-        <v>553.9160000000001</v>
+        <v>836.045</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46164.86458333334</v>
+        <v>46167.86458333334</v>
       </c>
       <c r="B84">
-        <v>563.788</v>
+        <v>853.657</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46164.875</v>
+        <v>46167.875</v>
       </c>
       <c r="B85">
-        <v>574.63</v>
+        <v>873.353</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46164.88541666666</v>
+        <v>46167.88541666666</v>
       </c>
       <c r="B86">
-        <v>610.204</v>
+        <v>905.3339999999999</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46164.89583333334</v>
+        <v>46167.89583333334</v>
       </c>
       <c r="B87">
-        <v>602.856</v>
+        <v>931.5700000000001</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46164.90625</v>
+        <v>46167.90625</v>
       </c>
       <c r="B88">
-        <v>613.211</v>
+        <v>956.045</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46164.91666666666</v>
+        <v>46167.91666666666</v>
       </c>
       <c r="B89">
-        <v>623.426</v>
+        <v>982.253</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46164.92708333334</v>
+        <v>46167.92708333334</v>
       </c>
       <c r="B90">
-        <v>691.136</v>
+        <v>1008.207</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46164.9375</v>
+        <v>46167.9375</v>
       </c>
       <c r="B91">
-        <v>702.423</v>
+        <v>1028.843</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46164.94791666666</v>
+        <v>46167.94791666666</v>
       </c>
       <c r="B92">
-        <v>716.958</v>
+        <v>1047.814</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46164.95833333334</v>
+        <v>46167.95833333334</v>
       </c>
       <c r="B93">
-        <v>728.6130000000001</v>
+        <v>1068.919</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46164.96875</v>
+        <v>46167.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46164.97916666666</v>
+        <v>46167.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46164.98958333334</v>
+        <v>46167.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,743 +394,743 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46167.01041666666</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B2">
-        <v>972.653</v>
+        <v>1120.118</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46167.02083333334</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B3">
-        <v>960.2619999999999</v>
+        <v>1160.955</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46167.03125</v>
+        <v>46168.03125</v>
       </c>
       <c r="B4">
-        <v>947.4160000000001</v>
+        <v>1196.695</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46167.04166666666</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B5">
-        <v>930.179</v>
+        <v>1233.087</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46167.05208333334</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B6">
-        <v>933.896</v>
+        <v>1314.219</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46167.0625</v>
+        <v>46168.0625</v>
       </c>
       <c r="B7">
-        <v>916.247</v>
+        <v>1329.801</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46167.07291666666</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B8">
-        <v>896.357</v>
+        <v>1353.694</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46167.08333333334</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B9">
-        <v>877.948</v>
+        <v>1376.095</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46167.09375</v>
+        <v>46168.09375</v>
       </c>
       <c r="B10">
-        <v>836.875</v>
+        <v>1398.617</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46167.10416666666</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B11">
-        <v>824.187</v>
+        <v>1421.584</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46167.11458333334</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B12">
-        <v>816.197</v>
+        <v>1434.341</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46167.125</v>
+        <v>46168.125</v>
       </c>
       <c r="B13">
-        <v>791.1660000000001</v>
+        <v>1462.321</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46167.13541666666</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B14">
-        <v>788.485</v>
+        <v>1502.288</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46167.14583333334</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B15">
-        <v>786.563</v>
+        <v>1524.347</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46167.15625</v>
+        <v>46168.15625</v>
       </c>
       <c r="B16">
-        <v>783.505</v>
+        <v>1536.819</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46167.16666666666</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B17">
-        <v>792.538</v>
+        <v>1558.759</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46167.17708333334</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B18">
-        <v>864.225</v>
+        <v>1554.042</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46167.1875</v>
+        <v>46168.1875</v>
       </c>
       <c r="B19">
-        <v>859.821</v>
+        <v>1569.379</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46167.19791666666</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B20">
-        <v>853.453</v>
+        <v>1582.75</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46167.20833333334</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B21">
-        <v>829.51</v>
+        <v>1602.65</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46167.21875</v>
+        <v>46168.21875</v>
       </c>
       <c r="B22">
-        <v>812.091</v>
+        <v>1584.713</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46167.22916666666</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B23">
-        <v>787.864</v>
+        <v>1557.816</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46167.23958333334</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B24">
-        <v>758.96</v>
+        <v>1532.091</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46167.25</v>
+        <v>46168.25</v>
       </c>
       <c r="B25">
-        <v>721.144</v>
+        <v>1504.972</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46167.26041666666</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B26">
-        <v>666.047</v>
+        <v>1415.558</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46167.27083333334</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B27">
-        <v>625.374</v>
+        <v>1367.098</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46167.28125</v>
+        <v>46168.28125</v>
       </c>
       <c r="B28">
-        <v>594.192</v>
+        <v>1301.627</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46167.29166666666</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B29">
-        <v>552.171</v>
+        <v>1236.599</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46167.30208333334</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B30">
-        <v>518.33</v>
+        <v>1129.476</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46167.3125</v>
+        <v>46168.3125</v>
       </c>
       <c r="B31">
-        <v>470.288</v>
+        <v>1058.591</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46167.32291666666</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B32">
-        <v>420.938</v>
+        <v>993.784</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46167.33333333334</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B33">
-        <v>375.583</v>
+        <v>937.283</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46167.34375</v>
+        <v>46168.34375</v>
       </c>
       <c r="B34">
-        <v>372.912</v>
+        <v>844.943</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46167.35416666666</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B35">
-        <v>367.143</v>
+        <v>828.136</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46167.36458333334</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B36">
-        <v>358.106</v>
+        <v>803.448</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46167.375</v>
+        <v>46168.375</v>
       </c>
       <c r="B37">
-        <v>350.828</v>
+        <v>784.869</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46167.38541666666</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B38">
-        <v>357.36</v>
+        <v>813.218</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46167.39583333334</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B39">
-        <v>368.321</v>
+        <v>812.7670000000001</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46167.40625</v>
+        <v>46168.40625</v>
       </c>
       <c r="B40">
-        <v>356.227</v>
+        <v>808.965</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46167.41666666666</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B41">
-        <v>360.337</v>
+        <v>806.551</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46167.42708333334</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B42">
-        <v>356.952</v>
+        <v>802.873</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46167.4375</v>
+        <v>46168.4375</v>
       </c>
       <c r="B43">
-        <v>365.662</v>
+        <v>800.97</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46167.44791666666</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B44">
-        <v>374.362</v>
+        <v>747.328</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46167.45833333334</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B45">
-        <v>383.482</v>
+        <v>745.619</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46167.46875</v>
+        <v>46168.46875</v>
       </c>
       <c r="B46">
-        <v>451.893</v>
+        <v>753.667</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46167.47916666666</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B47">
-        <v>462.935</v>
+        <v>754.921</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46167.48958333334</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B48">
-        <v>473.369</v>
+        <v>756.567</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46167.5</v>
+        <v>46168.5</v>
       </c>
       <c r="B49">
-        <v>485.059</v>
+        <v>758.197</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46167.51041666666</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B50">
-        <v>501.682</v>
+        <v>766.8390000000001</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46167.52083333334</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B51">
-        <v>506.619</v>
+        <v>763.717</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46167.53125</v>
+        <v>46168.53125</v>
       </c>
       <c r="B52">
-        <v>511.974</v>
+        <v>762.74</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46167.54166666666</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B53">
-        <v>516.7329999999999</v>
+        <v>760.05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46167.55208333334</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B54">
-        <v>482.299</v>
+        <v>763.246</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46167.5625</v>
+        <v>46168.5625</v>
       </c>
       <c r="B55">
-        <v>501.074</v>
+        <v>759.234</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46167.57291666666</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B56">
-        <v>494.035</v>
+        <v>801.323</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46167.58333333334</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B57">
-        <v>489.221</v>
+        <v>797.653</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46167.59375</v>
+        <v>46168.59375</v>
       </c>
       <c r="B58">
-        <v>504.458</v>
+        <v>759.356</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46167.60416666666</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B59">
-        <v>509.158</v>
+        <v>799.001</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46167.61458333334</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B60">
-        <v>515.256</v>
+        <v>790.748</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46167.625</v>
+        <v>46168.625</v>
       </c>
       <c r="B61">
-        <v>521.371</v>
+        <v>740.2910000000001</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46167.63541666666</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B62">
-        <v>533.936</v>
+        <v>719.247</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46167.64583333334</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B63">
-        <v>550.569</v>
+        <v>709.186</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46167.65625</v>
+        <v>46168.65625</v>
       </c>
       <c r="B64">
-        <v>567.665</v>
+        <v>698.943</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46167.66666666666</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B65">
-        <v>585.254</v>
+        <v>691.0119999999999</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46167.67708333334</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B66">
-        <v>561.723</v>
+        <v>667.586</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46167.6875</v>
+        <v>46168.6875</v>
       </c>
       <c r="B67">
-        <v>575.25</v>
+        <v>684.222</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46167.69791666666</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B68">
-        <v>589.428</v>
+        <v>662.734</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46167.70833333334</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B69">
-        <v>604.336</v>
+        <v>639.027</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46167.71875</v>
+        <v>46168.71875</v>
       </c>
       <c r="B70">
-        <v>620.523</v>
+        <v>570.564</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46167.72916666666</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B71">
-        <v>629.793</v>
+        <v>563.033</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46167.73958333334</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B72">
-        <v>638.202</v>
+        <v>555.946</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46167.75</v>
+        <v>46168.75</v>
       </c>
       <c r="B73">
-        <v>646.609</v>
+        <v>550.1</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46167.76041666666</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B74">
-        <v>673.963</v>
+        <v>560.678</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46167.77083333334</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B75">
-        <v>693.61</v>
+        <v>599.047</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46167.78125</v>
+        <v>46168.78125</v>
       </c>
       <c r="B76">
-        <v>712.08</v>
+        <v>639.148</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46167.79166666666</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B77">
-        <v>730.58</v>
+        <v>679.217</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46167.80208333334</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B78">
-        <v>753.274</v>
+        <v>763.313</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46167.8125</v>
+        <v>46168.8125</v>
       </c>
       <c r="B79">
-        <v>769.639</v>
+        <v>821.378</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46167.82291666666</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B80">
-        <v>781.79</v>
+        <v>883.564</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46167.83333333334</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B81">
-        <v>795.009</v>
+        <v>950.752</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46167.84375</v>
+        <v>46168.84375</v>
       </c>
       <c r="B82">
-        <v>820.181</v>
+        <v>1032.125</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46167.85416666666</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B83">
-        <v>836.045</v>
+        <v>1085.591</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46167.86458333334</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B84">
-        <v>853.657</v>
+        <v>1136.153</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46167.875</v>
+        <v>46168.875</v>
       </c>
       <c r="B85">
-        <v>873.353</v>
+        <v>1189.243</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46167.88541666666</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B86">
-        <v>905.3339999999999</v>
+        <v>1256.529</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46167.89583333334</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B87">
-        <v>931.5700000000001</v>
+        <v>1299.035</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46167.90625</v>
+        <v>46168.90625</v>
       </c>
       <c r="B88">
-        <v>956.045</v>
+        <v>1341.269</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46167.91666666666</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B89">
-        <v>982.253</v>
+        <v>1381.938</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46167.92708333334</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B90">
-        <v>1008.207</v>
+        <v>1395.934</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46167.9375</v>
+        <v>46168.9375</v>
       </c>
       <c r="B91">
-        <v>1028.843</v>
+        <v>1399.102</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46167.94791666666</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B92">
-        <v>1047.814</v>
+        <v>1397.987</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46167.95833333334</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B93">
-        <v>1068.919</v>
+        <v>1392.711</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46167.96875</v>
+        <v>46168.96875</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1138,7 +1138,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46167.97916666666</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46167.98958333334</v>
+        <v>46168.98958333334</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1154,7 +1154,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B97">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,7 +394,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168.01041666666</v>
+        <v>46168</v>
       </c>
       <c r="B2">
         <v>1120.118</v>
@@ -402,7 +402,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.02083333334</v>
+        <v>46168.01041666666</v>
       </c>
       <c r="B3">
         <v>1160.955</v>
@@ -410,7 +410,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.03125</v>
+        <v>46168.02083333334</v>
       </c>
       <c r="B4">
         <v>1196.695</v>
@@ -418,7 +418,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.04166666666</v>
+        <v>46168.03125</v>
       </c>
       <c r="B5">
         <v>1233.087</v>
@@ -426,7 +426,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.05208333334</v>
+        <v>46168.04166666666</v>
       </c>
       <c r="B6">
         <v>1314.219</v>
@@ -434,7 +434,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.0625</v>
+        <v>46168.05208333334</v>
       </c>
       <c r="B7">
         <v>1329.801</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.07291666666</v>
+        <v>46168.0625</v>
       </c>
       <c r="B8">
         <v>1353.694</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.08333333334</v>
+        <v>46168.07291666666</v>
       </c>
       <c r="B9">
         <v>1376.095</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.09375</v>
+        <v>46168.08333333334</v>
       </c>
       <c r="B10">
         <v>1398.617</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.10416666666</v>
+        <v>46168.09375</v>
       </c>
       <c r="B11">
         <v>1421.584</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.11458333334</v>
+        <v>46168.10416666666</v>
       </c>
       <c r="B12">
         <v>1434.341</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.125</v>
+        <v>46168.11458333334</v>
       </c>
       <c r="B13">
         <v>1462.321</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.13541666666</v>
+        <v>46168.125</v>
       </c>
       <c r="B14">
         <v>1502.288</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.14583333334</v>
+        <v>46168.13541666666</v>
       </c>
       <c r="B15">
         <v>1524.347</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.15625</v>
+        <v>46168.14583333334</v>
       </c>
       <c r="B16">
         <v>1536.819</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.16666666666</v>
+        <v>46168.15625</v>
       </c>
       <c r="B17">
         <v>1558.759</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.17708333334</v>
+        <v>46168.16666666666</v>
       </c>
       <c r="B18">
         <v>1554.042</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.1875</v>
+        <v>46168.17708333334</v>
       </c>
       <c r="B19">
         <v>1569.379</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.19791666666</v>
+        <v>46168.1875</v>
       </c>
       <c r="B20">
         <v>1582.75</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.20833333334</v>
+        <v>46168.19791666666</v>
       </c>
       <c r="B21">
         <v>1602.65</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.21875</v>
+        <v>46168.20833333334</v>
       </c>
       <c r="B22">
         <v>1584.713</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.22916666666</v>
+        <v>46168.21875</v>
       </c>
       <c r="B23">
         <v>1557.816</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.23958333334</v>
+        <v>46168.22916666666</v>
       </c>
       <c r="B24">
         <v>1532.091</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.25</v>
+        <v>46168.23958333334</v>
       </c>
       <c r="B25">
         <v>1504.972</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.26041666666</v>
+        <v>46168.25</v>
       </c>
       <c r="B26">
         <v>1415.558</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.27083333334</v>
+        <v>46168.26041666666</v>
       </c>
       <c r="B27">
         <v>1367.098</v>
@@ -602,7 +602,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.28125</v>
+        <v>46168.27083333334</v>
       </c>
       <c r="B28">
         <v>1301.627</v>
@@ -610,7 +610,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.29166666666</v>
+        <v>46168.28125</v>
       </c>
       <c r="B29">
         <v>1236.599</v>
@@ -618,7 +618,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.30208333334</v>
+        <v>46168.29166666666</v>
       </c>
       <c r="B30">
         <v>1129.476</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.3125</v>
+        <v>46168.30208333334</v>
       </c>
       <c r="B31">
         <v>1058.591</v>
@@ -634,7 +634,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.32291666666</v>
+        <v>46168.3125</v>
       </c>
       <c r="B32">
         <v>993.784</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.33333333334</v>
+        <v>46168.32291666666</v>
       </c>
       <c r="B33">
         <v>937.283</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.34375</v>
+        <v>46168.33333333334</v>
       </c>
       <c r="B34">
         <v>844.943</v>
@@ -658,7 +658,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.35416666666</v>
+        <v>46168.34375</v>
       </c>
       <c r="B35">
         <v>828.136</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.36458333334</v>
+        <v>46168.35416666666</v>
       </c>
       <c r="B36">
         <v>803.448</v>
@@ -674,7 +674,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.375</v>
+        <v>46168.36458333334</v>
       </c>
       <c r="B37">
         <v>784.869</v>
@@ -682,7 +682,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.38541666666</v>
+        <v>46168.375</v>
       </c>
       <c r="B38">
         <v>813.218</v>
@@ -690,7 +690,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.39583333334</v>
+        <v>46168.38541666666</v>
       </c>
       <c r="B39">
         <v>812.7670000000001</v>
@@ -698,7 +698,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.40625</v>
+        <v>46168.39583333334</v>
       </c>
       <c r="B40">
         <v>808.965</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.41666666666</v>
+        <v>46168.40625</v>
       </c>
       <c r="B41">
         <v>806.551</v>
@@ -714,7 +714,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.42708333334</v>
+        <v>46168.41666666666</v>
       </c>
       <c r="B42">
         <v>802.873</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.4375</v>
+        <v>46168.42708333334</v>
       </c>
       <c r="B43">
         <v>800.97</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.44791666666</v>
+        <v>46168.4375</v>
       </c>
       <c r="B44">
         <v>747.328</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.45833333334</v>
+        <v>46168.44791666666</v>
       </c>
       <c r="B45">
         <v>745.619</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.46875</v>
+        <v>46168.45833333334</v>
       </c>
       <c r="B46">
         <v>753.667</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.47916666666</v>
+        <v>46168.46875</v>
       </c>
       <c r="B47">
         <v>754.921</v>
@@ -762,7 +762,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.48958333334</v>
+        <v>46168.47916666666</v>
       </c>
       <c r="B48">
         <v>756.567</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.5</v>
+        <v>46168.48958333334</v>
       </c>
       <c r="B49">
         <v>758.197</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.51041666666</v>
+        <v>46168.5</v>
       </c>
       <c r="B50">
         <v>766.8390000000001</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.52083333334</v>
+        <v>46168.51041666666</v>
       </c>
       <c r="B51">
         <v>763.717</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.53125</v>
+        <v>46168.52083333334</v>
       </c>
       <c r="B52">
         <v>762.74</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.54166666666</v>
+        <v>46168.53125</v>
       </c>
       <c r="B53">
         <v>760.05</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.55208333334</v>
+        <v>46168.54166666666</v>
       </c>
       <c r="B54">
         <v>763.246</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.5625</v>
+        <v>46168.55208333334</v>
       </c>
       <c r="B55">
         <v>759.234</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.57291666666</v>
+        <v>46168.5625</v>
       </c>
       <c r="B56">
         <v>801.323</v>
@@ -834,7 +834,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.58333333334</v>
+        <v>46168.57291666666</v>
       </c>
       <c r="B57">
         <v>797.653</v>
@@ -842,7 +842,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.59375</v>
+        <v>46168.58333333334</v>
       </c>
       <c r="B58">
         <v>759.356</v>
@@ -850,7 +850,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.60416666666</v>
+        <v>46168.59375</v>
       </c>
       <c r="B59">
         <v>799.001</v>
@@ -858,7 +858,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.61458333334</v>
+        <v>46168.60416666666</v>
       </c>
       <c r="B60">
         <v>790.748</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.625</v>
+        <v>46168.61458333334</v>
       </c>
       <c r="B61">
         <v>740.2910000000001</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.63541666666</v>
+        <v>46168.625</v>
       </c>
       <c r="B62">
         <v>719.247</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.64583333334</v>
+        <v>46168.63541666666</v>
       </c>
       <c r="B63">
         <v>709.186</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.65625</v>
+        <v>46168.64583333334</v>
       </c>
       <c r="B64">
         <v>698.943</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.66666666666</v>
+        <v>46168.65625</v>
       </c>
       <c r="B65">
         <v>691.0119999999999</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.67708333334</v>
+        <v>46168.66666666666</v>
       </c>
       <c r="B66">
         <v>667.586</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.6875</v>
+        <v>46168.67708333334</v>
       </c>
       <c r="B67">
         <v>684.222</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.69791666666</v>
+        <v>46168.6875</v>
       </c>
       <c r="B68">
         <v>662.734</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.70833333334</v>
+        <v>46168.69791666666</v>
       </c>
       <c r="B69">
         <v>639.027</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.71875</v>
+        <v>46168.70833333334</v>
       </c>
       <c r="B70">
         <v>570.564</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.72916666666</v>
+        <v>46168.71875</v>
       </c>
       <c r="B71">
         <v>563.033</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.73958333334</v>
+        <v>46168.72916666666</v>
       </c>
       <c r="B72">
         <v>555.946</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.75</v>
+        <v>46168.73958333334</v>
       </c>
       <c r="B73">
         <v>550.1</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.76041666666</v>
+        <v>46168.75</v>
       </c>
       <c r="B74">
         <v>560.678</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.77083333334</v>
+        <v>46168.76041666666</v>
       </c>
       <c r="B75">
         <v>599.047</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.78125</v>
+        <v>46168.77083333334</v>
       </c>
       <c r="B76">
         <v>639.148</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.79166666666</v>
+        <v>46168.78125</v>
       </c>
       <c r="B77">
         <v>679.217</v>
@@ -1002,7 +1002,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.80208333334</v>
+        <v>46168.79166666666</v>
       </c>
       <c r="B78">
         <v>763.313</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.8125</v>
+        <v>46168.80208333334</v>
       </c>
       <c r="B79">
         <v>821.378</v>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.82291666666</v>
+        <v>46168.8125</v>
       </c>
       <c r="B80">
         <v>883.564</v>
@@ -1026,7 +1026,7 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.83333333334</v>
+        <v>46168.82291666666</v>
       </c>
       <c r="B81">
         <v>950.752</v>
@@ -1034,7 +1034,7 @@
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.84375</v>
+        <v>46168.83333333334</v>
       </c>
       <c r="B82">
         <v>1032.125</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.85416666666</v>
+        <v>46168.84375</v>
       </c>
       <c r="B83">
         <v>1085.591</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.86458333334</v>
+        <v>46168.85416666666</v>
       </c>
       <c r="B84">
         <v>1136.153</v>
@@ -1058,7 +1058,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.875</v>
+        <v>46168.86458333334</v>
       </c>
       <c r="B85">
         <v>1189.243</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.88541666666</v>
+        <v>46168.875</v>
       </c>
       <c r="B86">
         <v>1256.529</v>
@@ -1074,7 +1074,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.89583333334</v>
+        <v>46168.88541666666</v>
       </c>
       <c r="B87">
         <v>1299.035</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.90625</v>
+        <v>46168.89583333334</v>
       </c>
       <c r="B88">
         <v>1341.269</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.91666666666</v>
+        <v>46168.90625</v>
       </c>
       <c r="B89">
         <v>1381.938</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.92708333334</v>
+        <v>46168.91666666666</v>
       </c>
       <c r="B90">
         <v>1395.934</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.9375</v>
+        <v>46168.92708333334</v>
       </c>
       <c r="B91">
         <v>1399.102</v>
@@ -1114,7 +1114,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.94791666666</v>
+        <v>46168.9375</v>
       </c>
       <c r="B92">
         <v>1397.987</v>
@@ -1122,7 +1122,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.95833333334</v>
+        <v>46168.94791666666</v>
       </c>
       <c r="B93">
         <v>1392.711</v>
@@ -1130,33 +1130,801 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.96875</v>
+        <v>46168.95833333334</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>1278.774</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.97916666666</v>
+        <v>46168.96875</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>1248.323</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.98958333334</v>
+        <v>46168.97916666666</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1216.169</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
+        <v>46168.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>1182.172</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
         <v>46169</v>
       </c>
-      <c r="B97">
+      <c r="B98">
+        <v>968.177</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46169.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>925.954</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46169.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>886.772</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46169.03125</v>
+      </c>
+      <c r="B101">
+        <v>846.275</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46169.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>790.985</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46169.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>756.944</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46169.0625</v>
+      </c>
+      <c r="B104">
+        <v>732.716</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46169.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>704.546</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46169.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>669.766</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46169.09375</v>
+      </c>
+      <c r="B107">
+        <v>649.48</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46169.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>631.688</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46169.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>609.175</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46169.125</v>
+      </c>
+      <c r="B110">
+        <v>590.461</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46169.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>569.0170000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46169.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>553.9059999999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46169.15625</v>
+      </c>
+      <c r="B113">
+        <v>533.85</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46169.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>493.472</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46169.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>469.636</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46169.1875</v>
+      </c>
+      <c r="B116">
+        <v>448.506</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46169.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>429.713</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46169.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>397.968</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46169.21875</v>
+      </c>
+      <c r="B119">
+        <v>381.267</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46169.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>363.79</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46169.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>345.808</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46169.25</v>
+      </c>
+      <c r="B122">
+        <v>301.359</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46169.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>284.643</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46169.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>271.301</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46169.28125</v>
+      </c>
+      <c r="B125">
+        <v>254.307</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46169.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>234.511</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46169.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>214.131</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46169.3125</v>
+      </c>
+      <c r="B128">
+        <v>198.09</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46169.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>181.058</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46169.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>159.833</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46169.34375</v>
+      </c>
+      <c r="B131">
+        <v>160.638</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46169.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>158.173</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46169.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>154.113</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46169.375</v>
+      </c>
+      <c r="B134">
+        <v>163.42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46169.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>169.288</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46169.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>170.347</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46169.40625</v>
+      </c>
+      <c r="B137">
+        <v>166.869</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46169.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>171.866</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46169.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>179.219</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46169.4375</v>
+      </c>
+      <c r="B140">
+        <v>186.23</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46169.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>193.822</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46169.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>210.769</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46169.46875</v>
+      </c>
+      <c r="B143">
+        <v>225.097</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46169.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>241.448</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46169.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>256.327</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46169.5</v>
+      </c>
+      <c r="B146">
+        <v>283.902</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46169.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>304.168</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46169.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>325.373</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46169.53125</v>
+      </c>
+      <c r="B149">
+        <v>345.138</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46169.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>374.558</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46169.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>397.244</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46169.5625</v>
+      </c>
+      <c r="B152">
+        <v>420.209</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46169.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>442.292</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46169.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>486.002</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46169.59375</v>
+      </c>
+      <c r="B155">
+        <v>508.528</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46169.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>532.088</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46169.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>557.99</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46169.625</v>
+      </c>
+      <c r="B158">
+        <v>594.5170000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46169.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>621.851</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46169.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>646.076</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46169.65625</v>
+      </c>
+      <c r="B161">
+        <v>671.899</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46169.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>692.5839999999999</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46169.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>703.879</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46169.6875</v>
+      </c>
+      <c r="B164">
+        <v>715.573</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46169.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>727.829</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46169.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>742.475</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46169.71875</v>
+      </c>
+      <c r="B167">
+        <v>747.4450000000001</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46169.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>753.2140000000001</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46169.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>758.707</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46169.75</v>
+      </c>
+      <c r="B170">
+        <v>783.022</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46169.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>807.098</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46169.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>832.646</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46169.78125</v>
+      </c>
+      <c r="B173">
+        <v>861.077</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46169.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>881.183</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46169.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>916.026</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46169.8125</v>
+      </c>
+      <c r="B176">
+        <v>951.373</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46169.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>984.893</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46169.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>1032.365</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46169.84375</v>
+      </c>
+      <c r="B179">
+        <v>1055.294</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46169.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>1074.92</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46169.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>1098.592</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46169.875</v>
+      </c>
+      <c r="B182">
+        <v>1125.574</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46169.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>1142.988</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46169.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>1158.963</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46169.90625</v>
+      </c>
+      <c r="B185">
+        <v>1171.542</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46169.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>1173.933</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46169.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>1167.589</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46169.9375</v>
+      </c>
+      <c r="B188">
+        <v>1167.561</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46169.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>1165.584</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46169.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46169.96875</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46169.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46169.98958333334</v>
+      </c>
+      <c r="B193">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,1511 +394,1511 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B2">
-        <v>1120.118</v>
+        <v>968.177</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46168.01041666666</v>
+        <v>46169.01041666666</v>
       </c>
       <c r="B3">
-        <v>1160.955</v>
+        <v>925.954</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46168.02083333334</v>
+        <v>46169.02083333334</v>
       </c>
       <c r="B4">
-        <v>1196.695</v>
+        <v>886.772</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46168.03125</v>
+        <v>46169.03125</v>
       </c>
       <c r="B5">
-        <v>1233.087</v>
+        <v>846.275</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46168.04166666666</v>
+        <v>46169.04166666666</v>
       </c>
       <c r="B6">
-        <v>1314.219</v>
+        <v>790.985</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46168.05208333334</v>
+        <v>46169.05208333334</v>
       </c>
       <c r="B7">
-        <v>1329.801</v>
+        <v>756.944</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46168.0625</v>
+        <v>46169.0625</v>
       </c>
       <c r="B8">
-        <v>1353.694</v>
+        <v>732.716</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46168.07291666666</v>
+        <v>46169.07291666666</v>
       </c>
       <c r="B9">
-        <v>1376.095</v>
+        <v>704.546</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46168.08333333334</v>
+        <v>46169.08333333334</v>
       </c>
       <c r="B10">
-        <v>1398.617</v>
+        <v>669.766</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46168.09375</v>
+        <v>46169.09375</v>
       </c>
       <c r="B11">
-        <v>1421.584</v>
+        <v>649.48</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46168.10416666666</v>
+        <v>46169.10416666666</v>
       </c>
       <c r="B12">
-        <v>1434.341</v>
+        <v>631.688</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46168.11458333334</v>
+        <v>46169.11458333334</v>
       </c>
       <c r="B13">
-        <v>1462.321</v>
+        <v>609.175</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46168.125</v>
+        <v>46169.125</v>
       </c>
       <c r="B14">
-        <v>1502.288</v>
+        <v>590.461</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46168.13541666666</v>
+        <v>46169.13541666666</v>
       </c>
       <c r="B15">
-        <v>1524.347</v>
+        <v>569.0170000000001</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46168.14583333334</v>
+        <v>46169.14583333334</v>
       </c>
       <c r="B16">
-        <v>1536.819</v>
+        <v>553.9059999999999</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46168.15625</v>
+        <v>46169.15625</v>
       </c>
       <c r="B17">
-        <v>1558.759</v>
+        <v>533.85</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46168.16666666666</v>
+        <v>46169.16666666666</v>
       </c>
       <c r="B18">
-        <v>1554.042</v>
+        <v>493.472</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46168.17708333334</v>
+        <v>46169.17708333334</v>
       </c>
       <c r="B19">
-        <v>1569.379</v>
+        <v>469.636</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46168.1875</v>
+        <v>46169.1875</v>
       </c>
       <c r="B20">
-        <v>1582.75</v>
+        <v>448.506</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46168.19791666666</v>
+        <v>46169.19791666666</v>
       </c>
       <c r="B21">
-        <v>1602.65</v>
+        <v>429.713</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46168.20833333334</v>
+        <v>46169.20833333334</v>
       </c>
       <c r="B22">
-        <v>1584.713</v>
+        <v>397.968</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46168.21875</v>
+        <v>46169.21875</v>
       </c>
       <c r="B23">
-        <v>1557.816</v>
+        <v>381.267</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46168.22916666666</v>
+        <v>46169.22916666666</v>
       </c>
       <c r="B24">
-        <v>1532.091</v>
+        <v>363.79</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46168.23958333334</v>
+        <v>46169.23958333334</v>
       </c>
       <c r="B25">
-        <v>1504.972</v>
+        <v>345.808</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46168.25</v>
+        <v>46169.25</v>
       </c>
       <c r="B26">
-        <v>1415.558</v>
+        <v>301.359</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46168.26041666666</v>
+        <v>46169.26041666666</v>
       </c>
       <c r="B27">
-        <v>1367.098</v>
+        <v>284.643</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46168.27083333334</v>
+        <v>46169.27083333334</v>
       </c>
       <c r="B28">
-        <v>1301.627</v>
+        <v>271.301</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46168.28125</v>
+        <v>46169.28125</v>
       </c>
       <c r="B29">
-        <v>1236.599</v>
+        <v>254.307</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46168.29166666666</v>
+        <v>46169.29166666666</v>
       </c>
       <c r="B30">
-        <v>1129.476</v>
+        <v>234.511</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46168.30208333334</v>
+        <v>46169.30208333334</v>
       </c>
       <c r="B31">
-        <v>1058.591</v>
+        <v>214.131</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46168.3125</v>
+        <v>46169.3125</v>
       </c>
       <c r="B32">
-        <v>993.784</v>
+        <v>198.09</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46168.32291666666</v>
+        <v>46169.32291666666</v>
       </c>
       <c r="B33">
-        <v>937.283</v>
+        <v>181.058</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46168.33333333334</v>
+        <v>46169.33333333334</v>
       </c>
       <c r="B34">
-        <v>844.943</v>
+        <v>159.833</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46168.34375</v>
+        <v>46169.34375</v>
       </c>
       <c r="B35">
-        <v>828.136</v>
+        <v>160.638</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46168.35416666666</v>
+        <v>46169.35416666666</v>
       </c>
       <c r="B36">
-        <v>803.448</v>
+        <v>158.173</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46168.36458333334</v>
+        <v>46169.36458333334</v>
       </c>
       <c r="B37">
-        <v>784.869</v>
+        <v>154.113</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46168.375</v>
+        <v>46169.375</v>
       </c>
       <c r="B38">
-        <v>813.218</v>
+        <v>163.42</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46168.38541666666</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="B39">
-        <v>812.7670000000001</v>
+        <v>169.288</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46168.39583333334</v>
+        <v>46169.39583333334</v>
       </c>
       <c r="B40">
-        <v>808.965</v>
+        <v>170.347</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46168.40625</v>
+        <v>46169.40625</v>
       </c>
       <c r="B41">
-        <v>806.551</v>
+        <v>166.869</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46168.41666666666</v>
+        <v>46169.41666666666</v>
       </c>
       <c r="B42">
-        <v>802.873</v>
+        <v>171.866</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46168.42708333334</v>
+        <v>46169.42708333334</v>
       </c>
       <c r="B43">
-        <v>800.97</v>
+        <v>179.219</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46168.4375</v>
+        <v>46169.4375</v>
       </c>
       <c r="B44">
-        <v>747.328</v>
+        <v>186.23</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46168.44791666666</v>
+        <v>46169.44791666666</v>
       </c>
       <c r="B45">
-        <v>745.619</v>
+        <v>193.822</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46168.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="B46">
-        <v>753.667</v>
+        <v>210.769</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46168.46875</v>
+        <v>46169.46875</v>
       </c>
       <c r="B47">
-        <v>754.921</v>
+        <v>225.097</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46168.47916666666</v>
+        <v>46169.47916666666</v>
       </c>
       <c r="B48">
-        <v>756.567</v>
+        <v>241.448</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46168.48958333334</v>
+        <v>46169.48958333334</v>
       </c>
       <c r="B49">
-        <v>758.197</v>
+        <v>256.327</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46168.5</v>
+        <v>46169.5</v>
       </c>
       <c r="B50">
-        <v>766.8390000000001</v>
+        <v>283.902</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46168.51041666666</v>
+        <v>46169.51041666666</v>
       </c>
       <c r="B51">
-        <v>763.717</v>
+        <v>304.168</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46168.52083333334</v>
+        <v>46169.52083333334</v>
       </c>
       <c r="B52">
-        <v>762.74</v>
+        <v>325.373</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46168.53125</v>
+        <v>46169.53125</v>
       </c>
       <c r="B53">
-        <v>760.05</v>
+        <v>345.138</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46168.54166666666</v>
+        <v>46169.54166666666</v>
       </c>
       <c r="B54">
-        <v>763.246</v>
+        <v>374.558</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46168.55208333334</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="B55">
-        <v>759.234</v>
+        <v>397.244</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46168.5625</v>
+        <v>46169.5625</v>
       </c>
       <c r="B56">
-        <v>801.323</v>
+        <v>420.209</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46168.57291666666</v>
+        <v>46169.57291666666</v>
       </c>
       <c r="B57">
-        <v>797.653</v>
+        <v>442.292</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46168.58333333334</v>
+        <v>46169.58333333334</v>
       </c>
       <c r="B58">
-        <v>759.356</v>
+        <v>486.002</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46168.59375</v>
+        <v>46169.59375</v>
       </c>
       <c r="B59">
-        <v>799.001</v>
+        <v>508.528</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46168.60416666666</v>
+        <v>46169.60416666666</v>
       </c>
       <c r="B60">
-        <v>790.748</v>
+        <v>532.088</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46168.61458333334</v>
+        <v>46169.61458333334</v>
       </c>
       <c r="B61">
-        <v>740.2910000000001</v>
+        <v>557.99</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46168.625</v>
+        <v>46169.625</v>
       </c>
       <c r="B62">
-        <v>719.247</v>
+        <v>594.5170000000001</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46168.63541666666</v>
+        <v>46169.63541666666</v>
       </c>
       <c r="B63">
-        <v>709.186</v>
+        <v>621.851</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46168.64583333334</v>
+        <v>46169.64583333334</v>
       </c>
       <c r="B64">
-        <v>698.943</v>
+        <v>646.076</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46168.65625</v>
+        <v>46169.65625</v>
       </c>
       <c r="B65">
-        <v>691.0119999999999</v>
+        <v>671.899</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46168.66666666666</v>
+        <v>46169.66666666666</v>
       </c>
       <c r="B66">
-        <v>667.586</v>
+        <v>692.5839999999999</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46168.67708333334</v>
+        <v>46169.67708333334</v>
       </c>
       <c r="B67">
-        <v>684.222</v>
+        <v>703.879</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46168.6875</v>
+        <v>46169.6875</v>
       </c>
       <c r="B68">
-        <v>662.734</v>
+        <v>715.573</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46168.69791666666</v>
+        <v>46169.69791666666</v>
       </c>
       <c r="B69">
-        <v>639.027</v>
+        <v>727.829</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46168.70833333334</v>
+        <v>46169.70833333334</v>
       </c>
       <c r="B70">
-        <v>570.564</v>
+        <v>742.475</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46168.71875</v>
+        <v>46169.71875</v>
       </c>
       <c r="B71">
-        <v>563.033</v>
+        <v>747.4450000000001</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46168.72916666666</v>
+        <v>46169.72916666666</v>
       </c>
       <c r="B72">
-        <v>555.946</v>
+        <v>753.2140000000001</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46168.73958333334</v>
+        <v>46169.73958333334</v>
       </c>
       <c r="B73">
-        <v>550.1</v>
+        <v>758.707</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46168.75</v>
+        <v>46169.75</v>
       </c>
       <c r="B74">
-        <v>560.678</v>
+        <v>783.022</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46168.76041666666</v>
+        <v>46169.76041666666</v>
       </c>
       <c r="B75">
-        <v>599.047</v>
+        <v>807.098</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46168.77083333334</v>
+        <v>46169.77083333334</v>
       </c>
       <c r="B76">
-        <v>639.148</v>
+        <v>832.646</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46168.78125</v>
+        <v>46169.78125</v>
       </c>
       <c r="B77">
-        <v>679.217</v>
+        <v>861.077</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46168.79166666666</v>
+        <v>46169.79166666666</v>
       </c>
       <c r="B78">
-        <v>763.313</v>
+        <v>881.183</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46168.80208333334</v>
+        <v>46169.80208333334</v>
       </c>
       <c r="B79">
-        <v>821.378</v>
+        <v>916.026</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46168.8125</v>
+        <v>46169.8125</v>
       </c>
       <c r="B80">
-        <v>883.564</v>
+        <v>951.373</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46168.82291666666</v>
+        <v>46169.82291666666</v>
       </c>
       <c r="B81">
-        <v>950.752</v>
+        <v>984.893</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46168.83333333334</v>
+        <v>46169.83333333334</v>
       </c>
       <c r="B82">
-        <v>1032.125</v>
+        <v>1032.365</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46168.84375</v>
+        <v>46169.84375</v>
       </c>
       <c r="B83">
-        <v>1085.591</v>
+        <v>1055.294</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46168.85416666666</v>
+        <v>46169.85416666666</v>
       </c>
       <c r="B84">
-        <v>1136.153</v>
+        <v>1074.92</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46168.86458333334</v>
+        <v>46169.86458333334</v>
       </c>
       <c r="B85">
-        <v>1189.243</v>
+        <v>1098.592</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46168.875</v>
+        <v>46169.875</v>
       </c>
       <c r="B86">
-        <v>1256.529</v>
+        <v>1125.574</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46168.88541666666</v>
+        <v>46169.88541666666</v>
       </c>
       <c r="B87">
-        <v>1299.035</v>
+        <v>1142.988</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46168.89583333334</v>
+        <v>46169.89583333334</v>
       </c>
       <c r="B88">
-        <v>1341.269</v>
+        <v>1158.963</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46168.90625</v>
+        <v>46169.90625</v>
       </c>
       <c r="B89">
-        <v>1381.938</v>
+        <v>1171.542</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46168.91666666666</v>
+        <v>46169.91666666666</v>
       </c>
       <c r="B90">
-        <v>1395.934</v>
+        <v>1173.933</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46168.92708333334</v>
+        <v>46169.92708333334</v>
       </c>
       <c r="B91">
-        <v>1399.102</v>
+        <v>1167.589</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46168.9375</v>
+        <v>46169.9375</v>
       </c>
       <c r="B92">
-        <v>1397.987</v>
+        <v>1167.561</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46168.94791666666</v>
+        <v>46169.94791666666</v>
       </c>
       <c r="B93">
-        <v>1392.711</v>
+        <v>1165.584</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46168.95833333334</v>
+        <v>46169.95833333334</v>
       </c>
       <c r="B94">
-        <v>1278.774</v>
+        <v>1102.103</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46168.96875</v>
+        <v>46169.96875</v>
       </c>
       <c r="B95">
-        <v>1248.323</v>
+        <v>1107.912</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46168.97916666666</v>
+        <v>46169.97916666666</v>
       </c>
       <c r="B96">
-        <v>1216.169</v>
+        <v>1104.848</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46168.98958333334</v>
+        <v>46169.98958333334</v>
       </c>
       <c r="B97">
-        <v>1182.172</v>
+        <v>1091.355</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B98">
-        <v>968.177</v>
+        <v>1145.311</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B99">
-        <v>925.954</v>
+        <v>1123.122</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B100">
-        <v>886.772</v>
+        <v>1116.171</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B101">
-        <v>846.275</v>
+        <v>1108.729</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B102">
-        <v>790.985</v>
+        <v>1124.744</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B103">
-        <v>756.944</v>
+        <v>1136.86</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B104">
-        <v>732.716</v>
+        <v>1153.913</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B105">
-        <v>704.546</v>
+        <v>1155.775</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B106">
-        <v>669.766</v>
+        <v>1132.338</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B107">
-        <v>649.48</v>
+        <v>1122.575</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B108">
-        <v>631.688</v>
+        <v>1127.766</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B109">
-        <v>609.175</v>
+        <v>1133.853</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B110">
-        <v>590.461</v>
+        <v>1117.217</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B111">
-        <v>569.0170000000001</v>
+        <v>1111.369</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B112">
-        <v>553.9059999999999</v>
+        <v>1099.843</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B113">
-        <v>533.85</v>
+        <v>1085.726</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B114">
-        <v>493.472</v>
+        <v>1111.567</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B115">
-        <v>469.636</v>
+        <v>1093.644</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B116">
-        <v>448.506</v>
+        <v>1075.779</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B117">
-        <v>429.713</v>
+        <v>1058.034</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B118">
-        <v>397.968</v>
+        <v>1097.86</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B119">
-        <v>381.267</v>
+        <v>1084.866</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B120">
-        <v>363.79</v>
+        <v>1067.601</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B121">
-        <v>345.808</v>
+        <v>1060.729</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B122">
-        <v>301.359</v>
+        <v>1042.536</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B123">
-        <v>284.643</v>
+        <v>1001.511</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B124">
-        <v>271.301</v>
+        <v>979.593</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B125">
-        <v>254.307</v>
+        <v>952.644</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B126">
-        <v>234.511</v>
+        <v>918.862</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B127">
-        <v>214.131</v>
+        <v>915.29</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B128">
-        <v>198.09</v>
+        <v>918.626</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B129">
-        <v>181.058</v>
+        <v>922.864</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B130">
-        <v>159.833</v>
+        <v>870.261</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B131">
-        <v>160.638</v>
+        <v>864.173</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B132">
-        <v>158.173</v>
+        <v>890.585</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B133">
-        <v>154.113</v>
+        <v>883.152</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B134">
-        <v>163.42</v>
+        <v>1044.111</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B135">
-        <v>169.288</v>
+        <v>1051.657</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B136">
-        <v>170.347</v>
+        <v>1054.17</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B137">
-        <v>166.869</v>
+        <v>1055.901</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B138">
-        <v>171.866</v>
+        <v>976.917</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B139">
-        <v>179.219</v>
+        <v>973.501</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B140">
-        <v>186.23</v>
+        <v>969.021</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B141">
-        <v>193.822</v>
+        <v>962.736</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B142">
-        <v>210.769</v>
+        <v>974.122</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B143">
-        <v>225.097</v>
+        <v>954.162</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B144">
-        <v>241.448</v>
+        <v>876.26</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B145">
-        <v>256.327</v>
+        <v>857.999</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B146">
-        <v>283.902</v>
+        <v>868.049</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B147">
-        <v>304.168</v>
+        <v>860.923</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B148">
-        <v>325.373</v>
+        <v>856.353</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B149">
-        <v>345.138</v>
+        <v>852.186</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B150">
-        <v>374.558</v>
+        <v>878.2190000000001</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B151">
-        <v>397.244</v>
+        <v>882.754</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B152">
-        <v>420.209</v>
+        <v>888.447</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B153">
-        <v>442.292</v>
+        <v>894.586</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B154">
-        <v>486.002</v>
+        <v>912.5700000000001</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B155">
-        <v>508.528</v>
+        <v>913.051</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B156">
-        <v>532.088</v>
+        <v>915.259</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B157">
-        <v>557.99</v>
+        <v>915.321</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B158">
-        <v>594.5170000000001</v>
+        <v>956.386</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B159">
-        <v>621.851</v>
+        <v>953.712</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B160">
-        <v>646.076</v>
+        <v>1003.502</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B161">
-        <v>671.899</v>
+        <v>999.491</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B162">
-        <v>692.5839999999999</v>
+        <v>927.549</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B163">
-        <v>703.879</v>
+        <v>934.987</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B164">
-        <v>715.573</v>
+        <v>944.985</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B165">
-        <v>727.829</v>
+        <v>953.644</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B166">
-        <v>742.475</v>
+        <v>915.097</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B167">
-        <v>747.4450000000001</v>
+        <v>927.851</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B168">
-        <v>753.2140000000001</v>
+        <v>940.785</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B169">
-        <v>758.707</v>
+        <v>953.522</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B170">
-        <v>783.022</v>
+        <v>964.107</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B171">
-        <v>807.098</v>
+        <v>968.4299999999999</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B172">
-        <v>832.646</v>
+        <v>971.021</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B173">
-        <v>861.077</v>
+        <v>972.691</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B174">
-        <v>881.183</v>
+        <v>1013.818</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B175">
-        <v>916.026</v>
+        <v>1006.628</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B176">
-        <v>951.373</v>
+        <v>998.481</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B177">
-        <v>984.893</v>
+        <v>987.854</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B178">
-        <v>1032.365</v>
+        <v>970.533</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B179">
-        <v>1055.294</v>
+        <v>952.837</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B180">
-        <v>1074.92</v>
+        <v>931.707</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B181">
-        <v>1098.592</v>
+        <v>910.35</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B182">
-        <v>1125.574</v>
+        <v>848.825</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B183">
-        <v>1142.988</v>
+        <v>848.266</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B184">
-        <v>1158.963</v>
+        <v>845.915</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B185">
-        <v>1171.542</v>
+        <v>845.731</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B186">
-        <v>1173.933</v>
+        <v>842.111</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B187">
-        <v>1167.589</v>
+        <v>843.746</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B188">
-        <v>1167.561</v>
+        <v>845.639</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B189">
-        <v>1165.584</v>
+        <v>852.399</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,1511 +394,1511 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B2">
-        <v>968.177</v>
+        <v>1145.311</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46169.01041666666</v>
+        <v>46170.01041666666</v>
       </c>
       <c r="B3">
-        <v>925.954</v>
+        <v>1123.122</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46169.02083333334</v>
+        <v>46170.02083333334</v>
       </c>
       <c r="B4">
-        <v>886.772</v>
+        <v>1116.171</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46169.03125</v>
+        <v>46170.03125</v>
       </c>
       <c r="B5">
-        <v>846.275</v>
+        <v>1108.729</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46169.04166666666</v>
+        <v>46170.04166666666</v>
       </c>
       <c r="B6">
-        <v>790.985</v>
+        <v>1124.744</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46169.05208333334</v>
+        <v>46170.05208333334</v>
       </c>
       <c r="B7">
-        <v>756.944</v>
+        <v>1136.86</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46169.0625</v>
+        <v>46170.0625</v>
       </c>
       <c r="B8">
-        <v>732.716</v>
+        <v>1153.913</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46169.07291666666</v>
+        <v>46170.07291666666</v>
       </c>
       <c r="B9">
-        <v>704.546</v>
+        <v>1155.775</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46169.08333333334</v>
+        <v>46170.08333333334</v>
       </c>
       <c r="B10">
-        <v>669.766</v>
+        <v>1132.338</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46169.09375</v>
+        <v>46170.09375</v>
       </c>
       <c r="B11">
-        <v>649.48</v>
+        <v>1122.575</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46169.10416666666</v>
+        <v>46170.10416666666</v>
       </c>
       <c r="B12">
-        <v>631.688</v>
+        <v>1127.766</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46169.11458333334</v>
+        <v>46170.11458333334</v>
       </c>
       <c r="B13">
-        <v>609.175</v>
+        <v>1133.853</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46169.125</v>
+        <v>46170.125</v>
       </c>
       <c r="B14">
-        <v>590.461</v>
+        <v>1117.217</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46169.13541666666</v>
+        <v>46170.13541666666</v>
       </c>
       <c r="B15">
-        <v>569.0170000000001</v>
+        <v>1111.369</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46169.14583333334</v>
+        <v>46170.14583333334</v>
       </c>
       <c r="B16">
-        <v>553.9059999999999</v>
+        <v>1099.843</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46169.15625</v>
+        <v>46170.15625</v>
       </c>
       <c r="B17">
-        <v>533.85</v>
+        <v>1085.726</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46169.16666666666</v>
+        <v>46170.16666666666</v>
       </c>
       <c r="B18">
-        <v>493.472</v>
+        <v>1111.567</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46169.17708333334</v>
+        <v>46170.17708333334</v>
       </c>
       <c r="B19">
-        <v>469.636</v>
+        <v>1093.644</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46169.1875</v>
+        <v>46170.1875</v>
       </c>
       <c r="B20">
-        <v>448.506</v>
+        <v>1075.779</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46169.19791666666</v>
+        <v>46170.19791666666</v>
       </c>
       <c r="B21">
-        <v>429.713</v>
+        <v>1058.034</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46169.20833333334</v>
+        <v>46170.20833333334</v>
       </c>
       <c r="B22">
-        <v>397.968</v>
+        <v>1097.86</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46169.21875</v>
+        <v>46170.21875</v>
       </c>
       <c r="B23">
-        <v>381.267</v>
+        <v>1084.866</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46169.22916666666</v>
+        <v>46170.22916666666</v>
       </c>
       <c r="B24">
-        <v>363.79</v>
+        <v>1067.601</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46169.23958333334</v>
+        <v>46170.23958333334</v>
       </c>
       <c r="B25">
-        <v>345.808</v>
+        <v>1060.729</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46169.25</v>
+        <v>46170.25</v>
       </c>
       <c r="B26">
-        <v>301.359</v>
+        <v>1042.536</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46169.26041666666</v>
+        <v>46170.26041666666</v>
       </c>
       <c r="B27">
-        <v>284.643</v>
+        <v>1001.511</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46169.27083333334</v>
+        <v>46170.27083333334</v>
       </c>
       <c r="B28">
-        <v>271.301</v>
+        <v>979.593</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46169.28125</v>
+        <v>46170.28125</v>
       </c>
       <c r="B29">
-        <v>254.307</v>
+        <v>952.644</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46169.29166666666</v>
+        <v>46170.29166666666</v>
       </c>
       <c r="B30">
-        <v>234.511</v>
+        <v>918.862</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46169.30208333334</v>
+        <v>46170.30208333334</v>
       </c>
       <c r="B31">
-        <v>214.131</v>
+        <v>915.29</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46169.3125</v>
+        <v>46170.3125</v>
       </c>
       <c r="B32">
-        <v>198.09</v>
+        <v>918.626</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46169.32291666666</v>
+        <v>46170.32291666666</v>
       </c>
       <c r="B33">
-        <v>181.058</v>
+        <v>922.864</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46169.33333333334</v>
+        <v>46170.33333333334</v>
       </c>
       <c r="B34">
-        <v>159.833</v>
+        <v>870.261</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46169.34375</v>
+        <v>46170.34375</v>
       </c>
       <c r="B35">
-        <v>160.638</v>
+        <v>864.173</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46169.35416666666</v>
+        <v>46170.35416666666</v>
       </c>
       <c r="B36">
-        <v>158.173</v>
+        <v>890.585</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46169.36458333334</v>
+        <v>46170.36458333334</v>
       </c>
       <c r="B37">
-        <v>154.113</v>
+        <v>883.152</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46169.375</v>
+        <v>46170.375</v>
       </c>
       <c r="B38">
-        <v>163.42</v>
+        <v>1044.111</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46169.38541666666</v>
+        <v>46170.38541666666</v>
       </c>
       <c r="B39">
-        <v>169.288</v>
+        <v>1051.657</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46169.39583333334</v>
+        <v>46170.39583333334</v>
       </c>
       <c r="B40">
-        <v>170.347</v>
+        <v>1054.17</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46169.40625</v>
+        <v>46170.40625</v>
       </c>
       <c r="B41">
-        <v>166.869</v>
+        <v>1055.901</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46169.41666666666</v>
+        <v>46170.41666666666</v>
       </c>
       <c r="B42">
-        <v>171.866</v>
+        <v>976.917</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46169.42708333334</v>
+        <v>46170.42708333334</v>
       </c>
       <c r="B43">
-        <v>179.219</v>
+        <v>973.501</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46169.4375</v>
+        <v>46170.4375</v>
       </c>
       <c r="B44">
-        <v>186.23</v>
+        <v>969.021</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46169.44791666666</v>
+        <v>46170.44791666666</v>
       </c>
       <c r="B45">
-        <v>193.822</v>
+        <v>962.736</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46169.45833333334</v>
+        <v>46170.45833333334</v>
       </c>
       <c r="B46">
-        <v>210.769</v>
+        <v>974.122</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46169.46875</v>
+        <v>46170.46875</v>
       </c>
       <c r="B47">
-        <v>225.097</v>
+        <v>954.162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46169.47916666666</v>
+        <v>46170.47916666666</v>
       </c>
       <c r="B48">
-        <v>241.448</v>
+        <v>876.26</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46169.48958333334</v>
+        <v>46170.48958333334</v>
       </c>
       <c r="B49">
-        <v>256.327</v>
+        <v>857.999</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46169.5</v>
+        <v>46170.5</v>
       </c>
       <c r="B50">
-        <v>283.902</v>
+        <v>868.049</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46169.51041666666</v>
+        <v>46170.51041666666</v>
       </c>
       <c r="B51">
-        <v>304.168</v>
+        <v>860.923</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46169.52083333334</v>
+        <v>46170.52083333334</v>
       </c>
       <c r="B52">
-        <v>325.373</v>
+        <v>856.353</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46169.53125</v>
+        <v>46170.53125</v>
       </c>
       <c r="B53">
-        <v>345.138</v>
+        <v>852.186</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46169.54166666666</v>
+        <v>46170.54166666666</v>
       </c>
       <c r="B54">
-        <v>374.558</v>
+        <v>878.2190000000001</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46169.55208333334</v>
+        <v>46170.55208333334</v>
       </c>
       <c r="B55">
-        <v>397.244</v>
+        <v>882.754</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46169.5625</v>
+        <v>46170.5625</v>
       </c>
       <c r="B56">
-        <v>420.209</v>
+        <v>888.447</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46169.57291666666</v>
+        <v>46170.57291666666</v>
       </c>
       <c r="B57">
-        <v>442.292</v>
+        <v>894.586</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46169.58333333334</v>
+        <v>46170.58333333334</v>
       </c>
       <c r="B58">
-        <v>486.002</v>
+        <v>912.5700000000001</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46169.59375</v>
+        <v>46170.59375</v>
       </c>
       <c r="B59">
-        <v>508.528</v>
+        <v>913.051</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46169.60416666666</v>
+        <v>46170.60416666666</v>
       </c>
       <c r="B60">
-        <v>532.088</v>
+        <v>915.259</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46169.61458333334</v>
+        <v>46170.61458333334</v>
       </c>
       <c r="B61">
-        <v>557.99</v>
+        <v>915.321</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46169.625</v>
+        <v>46170.625</v>
       </c>
       <c r="B62">
-        <v>594.5170000000001</v>
+        <v>956.386</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46169.63541666666</v>
+        <v>46170.63541666666</v>
       </c>
       <c r="B63">
-        <v>621.851</v>
+        <v>953.712</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46169.64583333334</v>
+        <v>46170.64583333334</v>
       </c>
       <c r="B64">
-        <v>646.076</v>
+        <v>1003.502</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46169.65625</v>
+        <v>46170.65625</v>
       </c>
       <c r="B65">
-        <v>671.899</v>
+        <v>999.491</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46169.66666666666</v>
+        <v>46170.66666666666</v>
       </c>
       <c r="B66">
-        <v>692.5839999999999</v>
+        <v>927.549</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46169.67708333334</v>
+        <v>46170.67708333334</v>
       </c>
       <c r="B67">
-        <v>703.879</v>
+        <v>934.987</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46169.6875</v>
+        <v>46170.6875</v>
       </c>
       <c r="B68">
-        <v>715.573</v>
+        <v>944.985</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46169.69791666666</v>
+        <v>46170.69791666666</v>
       </c>
       <c r="B69">
-        <v>727.829</v>
+        <v>953.644</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46169.70833333334</v>
+        <v>46170.70833333334</v>
       </c>
       <c r="B70">
-        <v>742.475</v>
+        <v>915.097</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46169.71875</v>
+        <v>46170.71875</v>
       </c>
       <c r="B71">
-        <v>747.4450000000001</v>
+        <v>927.851</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46169.72916666666</v>
+        <v>46170.72916666666</v>
       </c>
       <c r="B72">
-        <v>753.2140000000001</v>
+        <v>940.785</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46169.73958333334</v>
+        <v>46170.73958333334</v>
       </c>
       <c r="B73">
-        <v>758.707</v>
+        <v>953.522</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46169.75</v>
+        <v>46170.75</v>
       </c>
       <c r="B74">
-        <v>783.022</v>
+        <v>964.107</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46169.76041666666</v>
+        <v>46170.76041666666</v>
       </c>
       <c r="B75">
-        <v>807.098</v>
+        <v>968.4299999999999</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46169.77083333334</v>
+        <v>46170.77083333334</v>
       </c>
       <c r="B76">
-        <v>832.646</v>
+        <v>971.021</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46169.78125</v>
+        <v>46170.78125</v>
       </c>
       <c r="B77">
-        <v>861.077</v>
+        <v>972.691</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46169.79166666666</v>
+        <v>46170.79166666666</v>
       </c>
       <c r="B78">
-        <v>881.183</v>
+        <v>1013.818</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46169.80208333334</v>
+        <v>46170.80208333334</v>
       </c>
       <c r="B79">
-        <v>916.026</v>
+        <v>1006.628</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46169.8125</v>
+        <v>46170.8125</v>
       </c>
       <c r="B80">
-        <v>951.373</v>
+        <v>998.481</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46169.82291666666</v>
+        <v>46170.82291666666</v>
       </c>
       <c r="B81">
-        <v>984.893</v>
+        <v>987.854</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46169.83333333334</v>
+        <v>46170.83333333334</v>
       </c>
       <c r="B82">
-        <v>1032.365</v>
+        <v>970.533</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46169.84375</v>
+        <v>46170.84375</v>
       </c>
       <c r="B83">
-        <v>1055.294</v>
+        <v>952.837</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46169.85416666666</v>
+        <v>46170.85416666666</v>
       </c>
       <c r="B84">
-        <v>1074.92</v>
+        <v>931.707</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46169.86458333334</v>
+        <v>46170.86458333334</v>
       </c>
       <c r="B85">
-        <v>1098.592</v>
+        <v>910.35</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46169.875</v>
+        <v>46170.875</v>
       </c>
       <c r="B86">
-        <v>1125.574</v>
+        <v>848.825</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46169.88541666666</v>
+        <v>46170.88541666666</v>
       </c>
       <c r="B87">
-        <v>1142.988</v>
+        <v>848.266</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46169.89583333334</v>
+        <v>46170.89583333334</v>
       </c>
       <c r="B88">
-        <v>1158.963</v>
+        <v>845.915</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46169.90625</v>
+        <v>46170.90625</v>
       </c>
       <c r="B89">
-        <v>1171.542</v>
+        <v>845.731</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46169.91666666666</v>
+        <v>46170.91666666666</v>
       </c>
       <c r="B90">
-        <v>1173.933</v>
+        <v>842.111</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46169.92708333334</v>
+        <v>46170.92708333334</v>
       </c>
       <c r="B91">
-        <v>1167.589</v>
+        <v>843.746</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46169.9375</v>
+        <v>46170.9375</v>
       </c>
       <c r="B92">
-        <v>1167.561</v>
+        <v>845.639</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46169.94791666666</v>
+        <v>46170.94791666666</v>
       </c>
       <c r="B93">
-        <v>1165.584</v>
+        <v>852.399</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46169.95833333334</v>
+        <v>46170.95833333334</v>
       </c>
       <c r="B94">
-        <v>1102.103</v>
+        <v>951.077</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46169.96875</v>
+        <v>46170.96875</v>
       </c>
       <c r="B95">
-        <v>1107.912</v>
+        <v>956.926</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46169.97916666666</v>
+        <v>46170.97916666666</v>
       </c>
       <c r="B96">
-        <v>1104.848</v>
+        <v>942.524</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46169.98958333334</v>
+        <v>46170.98958333334</v>
       </c>
       <c r="B97">
-        <v>1091.355</v>
+        <v>942.952</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B98">
-        <v>1145.311</v>
+        <v>940.735</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B99">
-        <v>1123.122</v>
+        <v>922.115</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B100">
-        <v>1116.171</v>
+        <v>896.678</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B101">
-        <v>1108.729</v>
+        <v>880.107</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B102">
-        <v>1124.744</v>
+        <v>850.032</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B103">
-        <v>1136.86</v>
+        <v>851.812</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B104">
-        <v>1153.913</v>
+        <v>848.515</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B105">
-        <v>1155.775</v>
+        <v>847.87</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B106">
-        <v>1132.338</v>
+        <v>847.55</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B107">
-        <v>1122.575</v>
+        <v>861.245</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B108">
-        <v>1127.766</v>
+        <v>875.669</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B109">
-        <v>1133.853</v>
+        <v>905.244</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B110">
-        <v>1117.217</v>
+        <v>941.001</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B111">
-        <v>1111.369</v>
+        <v>970.492</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B112">
-        <v>1099.843</v>
+        <v>987.1130000000001</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B113">
-        <v>1085.726</v>
+        <v>1004.18</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B114">
-        <v>1111.567</v>
+        <v>1048.057</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B115">
-        <v>1093.644</v>
+        <v>1063.948</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B116">
-        <v>1075.779</v>
+        <v>1075.113</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B117">
-        <v>1058.034</v>
+        <v>1082.456</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B118">
-        <v>1097.86</v>
+        <v>1085.848</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B119">
-        <v>1084.866</v>
+        <v>1073.242</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B120">
-        <v>1067.601</v>
+        <v>1062.672</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B121">
-        <v>1060.729</v>
+        <v>1053.064</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B122">
-        <v>1042.536</v>
+        <v>1029.939</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B123">
-        <v>1001.511</v>
+        <v>979.907</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B124">
-        <v>979.593</v>
+        <v>935.568</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B125">
-        <v>952.644</v>
+        <v>895.271</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B126">
-        <v>918.862</v>
+        <v>881.612</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B127">
-        <v>915.29</v>
+        <v>885.614</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B128">
-        <v>918.626</v>
+        <v>890.519</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B129">
-        <v>922.864</v>
+        <v>899.0650000000001</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B130">
-        <v>870.261</v>
+        <v>916.687</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B131">
-        <v>864.173</v>
+        <v>943.788</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B132">
-        <v>890.585</v>
+        <v>971.8200000000001</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B133">
-        <v>883.152</v>
+        <v>1004.072</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B134">
-        <v>1044.111</v>
+        <v>1125.688</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B135">
-        <v>1051.657</v>
+        <v>1161.654</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B136">
-        <v>1054.17</v>
+        <v>1197.062</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B137">
-        <v>1055.901</v>
+        <v>1232.957</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B138">
-        <v>976.917</v>
+        <v>1352.951</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B139">
-        <v>973.501</v>
+        <v>1394.104</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B140">
-        <v>969.021</v>
+        <v>1436.909</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B141">
-        <v>962.736</v>
+        <v>1477.779</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B142">
-        <v>974.122</v>
+        <v>1528.587</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B143">
-        <v>954.162</v>
+        <v>1554.609</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B144">
-        <v>876.26</v>
+        <v>1577.678</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B145">
-        <v>857.999</v>
+        <v>1598.411</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B146">
-        <v>868.049</v>
+        <v>1580.333</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B147">
-        <v>860.923</v>
+        <v>1599.826</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B148">
-        <v>856.353</v>
+        <v>1619.63</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B149">
-        <v>852.186</v>
+        <v>1638.402</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B150">
-        <v>878.2190000000001</v>
+        <v>1606.43</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B151">
-        <v>882.754</v>
+        <v>1597.345</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B152">
-        <v>888.447</v>
+        <v>1588.115</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B153">
-        <v>894.586</v>
+        <v>1577.401</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B154">
-        <v>912.5700000000001</v>
+        <v>1573.094</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B155">
-        <v>913.051</v>
+        <v>1544.475</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B156">
-        <v>915.259</v>
+        <v>1515.642</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B157">
-        <v>915.321</v>
+        <v>1486.99</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B158">
-        <v>956.386</v>
+        <v>1473.462</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B159">
-        <v>953.712</v>
+        <v>1437.031</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B160">
-        <v>1003.502</v>
+        <v>1401.151</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B161">
-        <v>999.491</v>
+        <v>1361.086</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B162">
-        <v>927.549</v>
+        <v>1230.863</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B163">
-        <v>934.987</v>
+        <v>1202.179</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B164">
-        <v>944.985</v>
+        <v>1174.575</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B165">
-        <v>953.644</v>
+        <v>1149.54</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B166">
-        <v>915.097</v>
+        <v>1094.509</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B167">
-        <v>927.851</v>
+        <v>1043.154</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B168">
-        <v>940.785</v>
+        <v>994.076</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B169">
-        <v>953.522</v>
+        <v>947.4880000000001</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B170">
-        <v>964.107</v>
+        <v>887.542</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B171">
-        <v>968.4299999999999</v>
+        <v>864.98</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B172">
-        <v>971.021</v>
+        <v>844.538</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B173">
-        <v>972.691</v>
+        <v>825.651</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B174">
-        <v>1013.818</v>
+        <v>796.273</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B175">
-        <v>1006.628</v>
+        <v>793.112</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B176">
-        <v>998.481</v>
+        <v>786.64</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B177">
-        <v>987.854</v>
+        <v>780.309</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B178">
-        <v>970.533</v>
+        <v>764.907</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B179">
-        <v>952.837</v>
+        <v>747.316</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B180">
-        <v>931.707</v>
+        <v>732.135</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B181">
-        <v>910.35</v>
+        <v>712.827</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B182">
-        <v>848.825</v>
+        <v>678.509</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B183">
-        <v>848.266</v>
+        <v>660.641</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B184">
-        <v>845.915</v>
+        <v>645.8440000000001</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B185">
-        <v>845.731</v>
+        <v>627.514</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B186">
-        <v>842.111</v>
+        <v>608.4640000000001</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B187">
-        <v>843.746</v>
+        <v>585.35</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B188">
-        <v>845.639</v>
+        <v>563.232</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B189">
-        <v>852.399</v>
+        <v>542.976</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B190">
         <v>0</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1922,7 +1922,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B193">
         <v>0</v>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1537 +394,4609 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B2">
-        <v>1145.311</v>
+        <v>940.735</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46170.01041666666</v>
+        <v>46171.01041666666</v>
       </c>
       <c r="B3">
-        <v>1123.122</v>
+        <v>922.115</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46170.02083333334</v>
+        <v>46171.02083333334</v>
       </c>
       <c r="B4">
-        <v>1116.171</v>
+        <v>896.678</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46170.03125</v>
+        <v>46171.03125</v>
       </c>
       <c r="B5">
-        <v>1108.729</v>
+        <v>880.107</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46170.04166666666</v>
+        <v>46171.04166666666</v>
       </c>
       <c r="B6">
-        <v>1124.744</v>
+        <v>850.032</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46170.05208333334</v>
+        <v>46171.05208333334</v>
       </c>
       <c r="B7">
-        <v>1136.86</v>
+        <v>851.812</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46170.0625</v>
+        <v>46171.0625</v>
       </c>
       <c r="B8">
-        <v>1153.913</v>
+        <v>848.515</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46170.07291666666</v>
+        <v>46171.07291666666</v>
       </c>
       <c r="B9">
-        <v>1155.775</v>
+        <v>847.87</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46170.08333333334</v>
+        <v>46171.08333333334</v>
       </c>
       <c r="B10">
-        <v>1132.338</v>
+        <v>847.55</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46170.09375</v>
+        <v>46171.09375</v>
       </c>
       <c r="B11">
-        <v>1122.575</v>
+        <v>861.245</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46170.10416666666</v>
+        <v>46171.10416666666</v>
       </c>
       <c r="B12">
-        <v>1127.766</v>
+        <v>875.669</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46170.11458333334</v>
+        <v>46171.11458333334</v>
       </c>
       <c r="B13">
-        <v>1133.853</v>
+        <v>905.244</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46170.125</v>
+        <v>46171.125</v>
       </c>
       <c r="B14">
-        <v>1117.217</v>
+        <v>941.001</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46170.13541666666</v>
+        <v>46171.13541666666</v>
       </c>
       <c r="B15">
-        <v>1111.369</v>
+        <v>970.492</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46170.14583333334</v>
+        <v>46171.14583333334</v>
       </c>
       <c r="B16">
-        <v>1099.843</v>
+        <v>987.1130000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46170.15625</v>
+        <v>46171.15625</v>
       </c>
       <c r="B17">
-        <v>1085.726</v>
+        <v>1004.18</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46170.16666666666</v>
+        <v>46171.16666666666</v>
       </c>
       <c r="B18">
-        <v>1111.567</v>
+        <v>1048.057</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46170.17708333334</v>
+        <v>46171.17708333334</v>
       </c>
       <c r="B19">
-        <v>1093.644</v>
+        <v>1063.948</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46170.1875</v>
+        <v>46171.1875</v>
       </c>
       <c r="B20">
-        <v>1075.779</v>
+        <v>1075.113</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46170.19791666666</v>
+        <v>46171.19791666666</v>
       </c>
       <c r="B21">
-        <v>1058.034</v>
+        <v>1082.456</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46170.20833333334</v>
+        <v>46171.20833333334</v>
       </c>
       <c r="B22">
-        <v>1097.86</v>
+        <v>1085.848</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46170.21875</v>
+        <v>46171.21875</v>
       </c>
       <c r="B23">
-        <v>1084.866</v>
+        <v>1073.242</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46170.22916666666</v>
+        <v>46171.22916666666</v>
       </c>
       <c r="B24">
-        <v>1067.601</v>
+        <v>1062.672</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46170.23958333334</v>
+        <v>46171.23958333334</v>
       </c>
       <c r="B25">
-        <v>1060.729</v>
+        <v>1053.064</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46170.25</v>
+        <v>46171.25</v>
       </c>
       <c r="B26">
-        <v>1042.536</v>
+        <v>1029.939</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46170.26041666666</v>
+        <v>46171.26041666666</v>
       </c>
       <c r="B27">
-        <v>1001.511</v>
+        <v>979.907</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46170.27083333334</v>
+        <v>46171.27083333334</v>
       </c>
       <c r="B28">
-        <v>979.593</v>
+        <v>935.568</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46170.28125</v>
+        <v>46171.28125</v>
       </c>
       <c r="B29">
-        <v>952.644</v>
+        <v>895.271</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46170.29166666666</v>
+        <v>46171.29166666666</v>
       </c>
       <c r="B30">
-        <v>918.862</v>
+        <v>881.612</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46170.30208333334</v>
+        <v>46171.30208333334</v>
       </c>
       <c r="B31">
-        <v>915.29</v>
+        <v>885.614</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46170.3125</v>
+        <v>46171.3125</v>
       </c>
       <c r="B32">
-        <v>918.626</v>
+        <v>890.519</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46170.32291666666</v>
+        <v>46171.32291666666</v>
       </c>
       <c r="B33">
-        <v>922.864</v>
+        <v>899.0650000000001</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46170.33333333334</v>
+        <v>46171.33333333334</v>
       </c>
       <c r="B34">
-        <v>870.261</v>
+        <v>916.687</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46170.34375</v>
+        <v>46171.34375</v>
       </c>
       <c r="B35">
-        <v>864.173</v>
+        <v>943.788</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46170.35416666666</v>
+        <v>46171.35416666666</v>
       </c>
       <c r="B36">
-        <v>890.585</v>
+        <v>971.8200000000001</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46170.36458333334</v>
+        <v>46171.36458333334</v>
       </c>
       <c r="B37">
-        <v>883.152</v>
+        <v>1004.072</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46170.375</v>
+        <v>46171.375</v>
       </c>
       <c r="B38">
-        <v>1044.111</v>
+        <v>1125.688</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46170.38541666666</v>
+        <v>46171.38541666666</v>
       </c>
       <c r="B39">
-        <v>1051.657</v>
+        <v>1161.654</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46170.39583333334</v>
+        <v>46171.39583333334</v>
       </c>
       <c r="B40">
-        <v>1054.17</v>
+        <v>1197.062</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46170.40625</v>
+        <v>46171.40625</v>
       </c>
       <c r="B41">
-        <v>1055.901</v>
+        <v>1232.957</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46170.41666666666</v>
+        <v>46171.41666666666</v>
       </c>
       <c r="B42">
-        <v>976.917</v>
+        <v>1352.951</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46170.42708333334</v>
+        <v>46171.42708333334</v>
       </c>
       <c r="B43">
-        <v>973.501</v>
+        <v>1394.104</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46170.4375</v>
+        <v>46171.4375</v>
       </c>
       <c r="B44">
-        <v>969.021</v>
+        <v>1436.909</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46170.44791666666</v>
+        <v>46171.44791666666</v>
       </c>
       <c r="B45">
-        <v>962.736</v>
+        <v>1477.779</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46170.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="B46">
-        <v>974.122</v>
+        <v>1528.587</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46170.46875</v>
+        <v>46171.46875</v>
       </c>
       <c r="B47">
-        <v>954.162</v>
+        <v>1554.609</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46170.47916666666</v>
+        <v>46171.47916666666</v>
       </c>
       <c r="B48">
-        <v>876.26</v>
+        <v>1577.678</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46170.48958333334</v>
+        <v>46171.48958333334</v>
       </c>
       <c r="B49">
-        <v>857.999</v>
+        <v>1598.411</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46170.5</v>
+        <v>46171.5</v>
       </c>
       <c r="B50">
-        <v>868.049</v>
+        <v>1580.333</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46170.51041666666</v>
+        <v>46171.51041666666</v>
       </c>
       <c r="B51">
-        <v>860.923</v>
+        <v>1599.826</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46170.52083333334</v>
+        <v>46171.52083333334</v>
       </c>
       <c r="B52">
-        <v>856.353</v>
+        <v>1619.63</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46170.53125</v>
+        <v>46171.53125</v>
       </c>
       <c r="B53">
-        <v>852.186</v>
+        <v>1638.402</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46170.54166666666</v>
+        <v>46171.54166666666</v>
       </c>
       <c r="B54">
-        <v>878.2190000000001</v>
+        <v>1606.43</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46170.55208333334</v>
+        <v>46171.55208333334</v>
       </c>
       <c r="B55">
-        <v>882.754</v>
+        <v>1597.345</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46170.5625</v>
+        <v>46171.5625</v>
       </c>
       <c r="B56">
-        <v>888.447</v>
+        <v>1588.115</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46170.57291666666</v>
+        <v>46171.57291666666</v>
       </c>
       <c r="B57">
-        <v>894.586</v>
+        <v>1577.401</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46170.58333333334</v>
+        <v>46171.58333333334</v>
       </c>
       <c r="B58">
-        <v>912.5700000000001</v>
+        <v>1573.094</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46170.59375</v>
+        <v>46171.59375</v>
       </c>
       <c r="B59">
-        <v>913.051</v>
+        <v>1544.475</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46170.60416666666</v>
+        <v>46171.60416666666</v>
       </c>
       <c r="B60">
-        <v>915.259</v>
+        <v>1515.642</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46170.61458333334</v>
+        <v>46171.61458333334</v>
       </c>
       <c r="B61">
-        <v>915.321</v>
+        <v>1486.99</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46170.625</v>
+        <v>46171.625</v>
       </c>
       <c r="B62">
-        <v>956.386</v>
+        <v>1473.462</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46170.63541666666</v>
+        <v>46171.63541666666</v>
       </c>
       <c r="B63">
-        <v>953.712</v>
+        <v>1437.031</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46170.64583333334</v>
+        <v>46171.64583333334</v>
       </c>
       <c r="B64">
-        <v>1003.502</v>
+        <v>1401.151</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46170.65625</v>
+        <v>46171.65625</v>
       </c>
       <c r="B65">
-        <v>999.491</v>
+        <v>1361.086</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46170.66666666666</v>
+        <v>46171.66666666666</v>
       </c>
       <c r="B66">
-        <v>927.549</v>
+        <v>1230.863</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46170.67708333334</v>
+        <v>46171.67708333334</v>
       </c>
       <c r="B67">
-        <v>934.987</v>
+        <v>1202.179</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46170.6875</v>
+        <v>46171.6875</v>
       </c>
       <c r="B68">
-        <v>944.985</v>
+        <v>1174.575</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46170.69791666666</v>
+        <v>46171.69791666666</v>
       </c>
       <c r="B69">
-        <v>953.644</v>
+        <v>1149.54</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46170.70833333334</v>
+        <v>46171.70833333334</v>
       </c>
       <c r="B70">
-        <v>915.097</v>
+        <v>1094.509</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46170.71875</v>
+        <v>46171.71875</v>
       </c>
       <c r="B71">
-        <v>927.851</v>
+        <v>1043.154</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46170.72916666666</v>
+        <v>46171.72916666666</v>
       </c>
       <c r="B72">
-        <v>940.785</v>
+        <v>994.076</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46170.73958333334</v>
+        <v>46171.73958333334</v>
       </c>
       <c r="B73">
-        <v>953.522</v>
+        <v>947.4880000000001</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46170.75</v>
+        <v>46171.75</v>
       </c>
       <c r="B74">
-        <v>964.107</v>
+        <v>887.542</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46170.76041666666</v>
+        <v>46171.76041666666</v>
       </c>
       <c r="B75">
-        <v>968.4299999999999</v>
+        <v>864.98</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46170.77083333334</v>
+        <v>46171.77083333334</v>
       </c>
       <c r="B76">
-        <v>971.021</v>
+        <v>844.538</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46170.78125</v>
+        <v>46171.78125</v>
       </c>
       <c r="B77">
-        <v>972.691</v>
+        <v>825.651</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46170.79166666666</v>
+        <v>46171.79166666666</v>
       </c>
       <c r="B78">
-        <v>1013.818</v>
+        <v>796.273</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46170.80208333334</v>
+        <v>46171.80208333334</v>
       </c>
       <c r="B79">
-        <v>1006.628</v>
+        <v>793.112</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46170.8125</v>
+        <v>46171.8125</v>
       </c>
       <c r="B80">
-        <v>998.481</v>
+        <v>786.64</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46170.82291666666</v>
+        <v>46171.82291666666</v>
       </c>
       <c r="B81">
-        <v>987.854</v>
+        <v>780.309</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46170.83333333334</v>
+        <v>46171.83333333334</v>
       </c>
       <c r="B82">
-        <v>970.533</v>
+        <v>764.907</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46170.84375</v>
+        <v>46171.84375</v>
       </c>
       <c r="B83">
-        <v>952.837</v>
+        <v>747.316</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46170.85416666666</v>
+        <v>46171.85416666666</v>
       </c>
       <c r="B84">
-        <v>931.707</v>
+        <v>732.135</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46170.86458333334</v>
+        <v>46171.86458333334</v>
       </c>
       <c r="B85">
-        <v>910.35</v>
+        <v>712.827</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46170.875</v>
+        <v>46171.875</v>
       </c>
       <c r="B86">
-        <v>848.825</v>
+        <v>678.509</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46170.88541666666</v>
+        <v>46171.88541666666</v>
       </c>
       <c r="B87">
-        <v>848.266</v>
+        <v>660.641</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46170.89583333334</v>
+        <v>46171.89583333334</v>
       </c>
       <c r="B88">
-        <v>845.915</v>
+        <v>645.8440000000001</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46170.90625</v>
+        <v>46171.90625</v>
       </c>
       <c r="B89">
-        <v>845.731</v>
+        <v>627.514</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46170.91666666666</v>
+        <v>46171.91666666666</v>
       </c>
       <c r="B90">
-        <v>842.111</v>
+        <v>608.4640000000001</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46170.92708333334</v>
+        <v>46171.92708333334</v>
       </c>
       <c r="B91">
-        <v>843.746</v>
+        <v>585.35</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46170.9375</v>
+        <v>46171.9375</v>
       </c>
       <c r="B92">
-        <v>845.639</v>
+        <v>563.232</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46170.94791666666</v>
+        <v>46171.94791666666</v>
       </c>
       <c r="B93">
-        <v>852.399</v>
+        <v>542.976</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46170.95833333334</v>
+        <v>46171.95833333334</v>
       </c>
       <c r="B94">
-        <v>951.077</v>
+        <v>595.973</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46170.96875</v>
+        <v>46171.96875</v>
       </c>
       <c r="B95">
-        <v>956.926</v>
+        <v>583.239</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46170.97916666666</v>
+        <v>46171.97916666666</v>
       </c>
       <c r="B96">
-        <v>942.524</v>
+        <v>555.032</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46170.98958333334</v>
+        <v>46171.98958333334</v>
       </c>
       <c r="B97">
-        <v>942.952</v>
+        <v>535.742</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B98">
-        <v>940.735</v>
+        <v>522.897</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46171.01041666666</v>
+        <v>46172.01041666666</v>
       </c>
       <c r="B99">
-        <v>922.115</v>
+        <v>494.887</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46171.02083333334</v>
+        <v>46172.02083333334</v>
       </c>
       <c r="B100">
-        <v>896.678</v>
+        <v>475.893</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46171.03125</v>
+        <v>46172.03125</v>
       </c>
       <c r="B101">
-        <v>880.107</v>
+        <v>434.786</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46171.04166666666</v>
+        <v>46172.04166666666</v>
       </c>
       <c r="B102">
-        <v>850.032</v>
+        <v>382.509</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46171.05208333334</v>
+        <v>46172.05208333334</v>
       </c>
       <c r="B103">
-        <v>851.812</v>
+        <v>367.373</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46171.0625</v>
+        <v>46172.0625</v>
       </c>
       <c r="B104">
-        <v>848.515</v>
+        <v>353.453</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46171.07291666666</v>
+        <v>46172.07291666666</v>
       </c>
       <c r="B105">
-        <v>847.87</v>
+        <v>340.457</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46171.08333333334</v>
+        <v>46172.08333333334</v>
       </c>
       <c r="B106">
-        <v>847.55</v>
+        <v>309.952</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46171.09375</v>
+        <v>46172.09375</v>
       </c>
       <c r="B107">
-        <v>861.245</v>
+        <v>317.088</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46171.10416666666</v>
+        <v>46172.10416666666</v>
       </c>
       <c r="B108">
-        <v>875.669</v>
+        <v>320.86</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46171.11458333334</v>
+        <v>46172.11458333334</v>
       </c>
       <c r="B109">
-        <v>905.244</v>
+        <v>324.639</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46171.125</v>
+        <v>46172.125</v>
       </c>
       <c r="B110">
-        <v>941.001</v>
+        <v>327.93</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46171.13541666666</v>
+        <v>46172.13541666666</v>
       </c>
       <c r="B111">
-        <v>970.492</v>
+        <v>345.637</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46171.14583333334</v>
+        <v>46172.14583333334</v>
       </c>
       <c r="B112">
-        <v>987.1130000000001</v>
+        <v>350.645</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46171.15625</v>
+        <v>46172.15625</v>
       </c>
       <c r="B113">
-        <v>1004.18</v>
+        <v>364.309</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46171.16666666666</v>
+        <v>46172.16666666666</v>
       </c>
       <c r="B114">
-        <v>1048.057</v>
+        <v>377.007</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46171.17708333334</v>
+        <v>46172.17708333334</v>
       </c>
       <c r="B115">
-        <v>1063.948</v>
+        <v>410.04</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46171.1875</v>
+        <v>46172.1875</v>
       </c>
       <c r="B116">
-        <v>1075.113</v>
+        <v>437.216</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46171.19791666666</v>
+        <v>46172.19791666666</v>
       </c>
       <c r="B117">
-        <v>1082.456</v>
+        <v>459.725</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46171.20833333334</v>
+        <v>46172.20833333334</v>
       </c>
       <c r="B118">
-        <v>1085.848</v>
+        <v>511.701</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46171.21875</v>
+        <v>46172.21875</v>
       </c>
       <c r="B119">
-        <v>1073.242</v>
+        <v>533.605</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46171.22916666666</v>
+        <v>46172.22916666666</v>
       </c>
       <c r="B120">
-        <v>1062.672</v>
+        <v>550.852</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46171.23958333334</v>
+        <v>46172.23958333334</v>
       </c>
       <c r="B121">
-        <v>1053.064</v>
+        <v>573.443</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46171.25</v>
+        <v>46172.25</v>
       </c>
       <c r="B122">
-        <v>1029.939</v>
+        <v>620.451</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46171.26041666666</v>
+        <v>46172.26041666666</v>
       </c>
       <c r="B123">
-        <v>979.907</v>
+        <v>649.534</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46171.27083333334</v>
+        <v>46172.27083333334</v>
       </c>
       <c r="B124">
-        <v>935.568</v>
+        <v>680.958</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46171.28125</v>
+        <v>46172.28125</v>
       </c>
       <c r="B125">
-        <v>895.271</v>
+        <v>713.196</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46171.29166666666</v>
+        <v>46172.29166666666</v>
       </c>
       <c r="B126">
-        <v>881.612</v>
+        <v>795.454</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46171.30208333334</v>
+        <v>46172.30208333334</v>
       </c>
       <c r="B127">
-        <v>885.614</v>
+        <v>839.46</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46171.3125</v>
+        <v>46172.3125</v>
       </c>
       <c r="B128">
-        <v>890.519</v>
+        <v>880.891</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46171.32291666666</v>
+        <v>46172.32291666666</v>
       </c>
       <c r="B129">
-        <v>899.0650000000001</v>
+        <v>920.982</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46171.33333333334</v>
+        <v>46172.33333333334</v>
       </c>
       <c r="B130">
-        <v>916.687</v>
+        <v>996.239</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46171.34375</v>
+        <v>46172.34375</v>
       </c>
       <c r="B131">
-        <v>943.788</v>
+        <v>1079.477</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46171.35416666666</v>
+        <v>46172.35416666666</v>
       </c>
       <c r="B132">
-        <v>971.8200000000001</v>
+        <v>1172.779</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46171.36458333334</v>
+        <v>46172.36458333334</v>
       </c>
       <c r="B133">
-        <v>1004.072</v>
+        <v>1255.584</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46171.375</v>
+        <v>46172.375</v>
       </c>
       <c r="B134">
-        <v>1125.688</v>
+        <v>1370.446</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46171.38541666666</v>
+        <v>46172.38541666666</v>
       </c>
       <c r="B135">
-        <v>1161.654</v>
+        <v>1438.15</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46171.39583333334</v>
+        <v>46172.39583333334</v>
       </c>
       <c r="B136">
-        <v>1197.062</v>
+        <v>1502.727</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46171.40625</v>
+        <v>46172.40625</v>
       </c>
       <c r="B137">
-        <v>1232.957</v>
+        <v>1566.007</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46171.41666666666</v>
+        <v>46172.41666666666</v>
       </c>
       <c r="B138">
-        <v>1352.951</v>
+        <v>1649.33</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46171.42708333334</v>
+        <v>46172.42708333334</v>
       </c>
       <c r="B139">
-        <v>1394.104</v>
+        <v>1677.929</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46171.4375</v>
+        <v>46172.4375</v>
       </c>
       <c r="B140">
-        <v>1436.909</v>
+        <v>1710.55</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46171.44791666666</v>
+        <v>46172.44791666666</v>
       </c>
       <c r="B141">
-        <v>1477.779</v>
+        <v>1725.045</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46171.45833333334</v>
+        <v>46172.45833333334</v>
       </c>
       <c r="B142">
-        <v>1528.587</v>
+        <v>1622.416</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46171.46875</v>
+        <v>46172.46875</v>
       </c>
       <c r="B143">
-        <v>1554.609</v>
+        <v>1533.62</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46171.47916666666</v>
+        <v>46172.47916666666</v>
       </c>
       <c r="B144">
-        <v>1577.678</v>
+        <v>1524.975</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46171.48958333334</v>
+        <v>46172.48958333334</v>
       </c>
       <c r="B145">
-        <v>1598.411</v>
+        <v>1515.487</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46171.5</v>
+        <v>46172.5</v>
       </c>
       <c r="B146">
-        <v>1580.333</v>
+        <v>1569.382</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46171.51041666666</v>
+        <v>46172.51041666666</v>
       </c>
       <c r="B147">
-        <v>1599.826</v>
+        <v>1543.926</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46171.52083333334</v>
+        <v>46172.52083333334</v>
       </c>
       <c r="B148">
-        <v>1619.63</v>
+        <v>1518.459</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46171.53125</v>
+        <v>46172.53125</v>
       </c>
       <c r="B149">
-        <v>1638.402</v>
+        <v>1490.711</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46171.54166666666</v>
+        <v>46172.54166666666</v>
       </c>
       <c r="B150">
-        <v>1606.43</v>
+        <v>1382.069</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46171.55208333334</v>
+        <v>46172.55208333334</v>
       </c>
       <c r="B151">
-        <v>1597.345</v>
+        <v>1373.176</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46171.5625</v>
+        <v>46172.5625</v>
       </c>
       <c r="B152">
-        <v>1588.115</v>
+        <v>1365.625</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46171.57291666666</v>
+        <v>46172.57291666666</v>
       </c>
       <c r="B153">
-        <v>1577.401</v>
+        <v>1356.032</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46171.58333333334</v>
+        <v>46172.58333333334</v>
       </c>
       <c r="B154">
-        <v>1573.094</v>
+        <v>1190.541</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46171.59375</v>
+        <v>46172.59375</v>
       </c>
       <c r="B155">
-        <v>1544.475</v>
+        <v>1144.247</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46171.60416666666</v>
+        <v>46172.60416666666</v>
       </c>
       <c r="B156">
-        <v>1515.642</v>
+        <v>1098.249</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46171.61458333334</v>
+        <v>46172.61458333334</v>
       </c>
       <c r="B157">
-        <v>1486.99</v>
+        <v>1050.673</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46171.625</v>
+        <v>46172.625</v>
       </c>
       <c r="B158">
-        <v>1473.462</v>
+        <v>974.6420000000001</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46171.63541666666</v>
+        <v>46172.63541666666</v>
       </c>
       <c r="B159">
-        <v>1437.031</v>
+        <v>916.854</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46171.64583333334</v>
+        <v>46172.64583333334</v>
       </c>
       <c r="B160">
-        <v>1401.151</v>
+        <v>860.986</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46171.65625</v>
+        <v>46172.65625</v>
       </c>
       <c r="B161">
-        <v>1361.086</v>
+        <v>798.122</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46171.66666666666</v>
+        <v>46172.66666666666</v>
       </c>
       <c r="B162">
-        <v>1230.863</v>
+        <v>777.851</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46171.67708333334</v>
+        <v>46172.67708333334</v>
       </c>
       <c r="B163">
-        <v>1202.179</v>
+        <v>785.264</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46171.6875</v>
+        <v>46172.6875</v>
       </c>
       <c r="B164">
-        <v>1174.575</v>
+        <v>726.9299999999999</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46171.69791666666</v>
+        <v>46172.69791666666</v>
       </c>
       <c r="B165">
-        <v>1149.54</v>
+        <v>668.698</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46171.70833333334</v>
+        <v>46172.70833333334</v>
       </c>
       <c r="B166">
-        <v>1094.509</v>
+        <v>585.206</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46171.71875</v>
+        <v>46172.71875</v>
       </c>
       <c r="B167">
-        <v>1043.154</v>
+        <v>535.2190000000001</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46171.72916666666</v>
+        <v>46172.72916666666</v>
       </c>
       <c r="B168">
-        <v>994.076</v>
+        <v>486.245</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46171.73958333334</v>
+        <v>46172.73958333334</v>
       </c>
       <c r="B169">
-        <v>947.4880000000001</v>
+        <v>439.021</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46171.75</v>
+        <v>46172.75</v>
       </c>
       <c r="B170">
-        <v>887.542</v>
+        <v>372.795</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46171.76041666666</v>
+        <v>46172.76041666666</v>
       </c>
       <c r="B171">
-        <v>864.98</v>
+        <v>344.618</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46171.77083333334</v>
+        <v>46172.77083333334</v>
       </c>
       <c r="B172">
-        <v>844.538</v>
+        <v>318.067</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46171.78125</v>
+        <v>46172.78125</v>
       </c>
       <c r="B173">
-        <v>825.651</v>
+        <v>291.761</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46171.79166666666</v>
+        <v>46172.79166666666</v>
       </c>
       <c r="B174">
-        <v>796.273</v>
+        <v>268.723</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46171.80208333334</v>
+        <v>46172.80208333334</v>
       </c>
       <c r="B175">
-        <v>793.112</v>
+        <v>265.295</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46171.8125</v>
+        <v>46172.8125</v>
       </c>
       <c r="B176">
-        <v>786.64</v>
+        <v>262.995</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46171.82291666666</v>
+        <v>46172.82291666666</v>
       </c>
       <c r="B177">
-        <v>780.309</v>
+        <v>261.1</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46171.83333333334</v>
+        <v>46172.83333333334</v>
       </c>
       <c r="B178">
-        <v>764.907</v>
+        <v>271.642</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46171.84375</v>
+        <v>46172.84375</v>
       </c>
       <c r="B179">
-        <v>747.316</v>
+        <v>281.93</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46171.85416666666</v>
+        <v>46172.85416666666</v>
       </c>
       <c r="B180">
-        <v>732.135</v>
+        <v>292.323</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46171.86458333334</v>
+        <v>46172.86458333334</v>
       </c>
       <c r="B181">
-        <v>712.827</v>
+        <v>304.509</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46171.875</v>
+        <v>46172.875</v>
       </c>
       <c r="B182">
-        <v>678.509</v>
+        <v>331.33</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46171.88541666666</v>
+        <v>46172.88541666666</v>
       </c>
       <c r="B183">
-        <v>660.641</v>
+        <v>343.128</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="2">
-        <v>46171.89583333334</v>
+        <v>46172.89583333334</v>
       </c>
       <c r="B184">
-        <v>645.8440000000001</v>
+        <v>341.174</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" s="2">
-        <v>46171.90625</v>
+        <v>46172.90625</v>
       </c>
       <c r="B185">
-        <v>627.514</v>
+        <v>353.159</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="2">
-        <v>46171.91666666666</v>
+        <v>46172.91666666666</v>
       </c>
       <c r="B186">
-        <v>608.4640000000001</v>
+        <v>365.107</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" s="2">
-        <v>46171.92708333334</v>
+        <v>46172.92708333334</v>
       </c>
       <c r="B187">
-        <v>585.35</v>
+        <v>367.455</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="2">
-        <v>46171.9375</v>
+        <v>46172.9375</v>
       </c>
       <c r="B188">
-        <v>563.232</v>
+        <v>369.926</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" s="2">
-        <v>46171.94791666666</v>
+        <v>46172.94791666666</v>
       </c>
       <c r="B189">
-        <v>542.976</v>
+        <v>372.556</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2">
-        <v>46171.95833333334</v>
+        <v>46172.95833333334</v>
       </c>
       <c r="B190">
-        <v>0</v>
+        <v>405.308</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2">
-        <v>46171.96875</v>
+        <v>46172.96875</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>410.738</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2">
-        <v>46171.97916666666</v>
+        <v>46172.97916666666</v>
       </c>
       <c r="B192">
-        <v>0</v>
+        <v>410.839</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2">
-        <v>46171.98958333334</v>
+        <v>46172.98958333334</v>
       </c>
       <c r="B193">
+        <v>412.845</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B194">
+        <v>458.914</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46173.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>494.367</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46173.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>547.603</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46173.03125</v>
+      </c>
+      <c r="B197">
+        <v>594.677</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46173.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>720.994</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46173.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>767.206</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46173.0625</v>
+      </c>
+      <c r="B200">
+        <v>814.225</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46173.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>872.2430000000001</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46173.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>897.3869999999999</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46173.09375</v>
+      </c>
+      <c r="B203">
+        <v>954.178</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46173.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1003.393</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46173.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>1056.482</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46173.125</v>
+      </c>
+      <c r="B206">
+        <v>1105.11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46173.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>1123.232</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46173.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>1118.488</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46173.15625</v>
+      </c>
+      <c r="B209">
+        <v>1143.33</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46173.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1177.744</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46173.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>1163.143</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46173.1875</v>
+      </c>
+      <c r="B212">
+        <v>1164.851</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46173.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1172.201</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46173.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>1094.498</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46173.21875</v>
+      </c>
+      <c r="B215">
+        <v>1041.961</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46173.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>981.479</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46173.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>923.692</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46173.25</v>
+      </c>
+      <c r="B218">
+        <v>838.8339999999999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46173.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>785.129</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46173.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>713.692</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46173.28125</v>
+      </c>
+      <c r="B221">
+        <v>659.157</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46173.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>600.941</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46173.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>562.9349999999999</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46173.3125</v>
+      </c>
+      <c r="B224">
+        <v>517.332</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46173.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>476.788</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46173.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>440.91</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46173.34375</v>
+      </c>
+      <c r="B227">
+        <v>425.918</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46173.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>416.036</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46173.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>404.753</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46173.375</v>
+      </c>
+      <c r="B230">
+        <v>419.255</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46173.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>426.522</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46173.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>433.514</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46173.40625</v>
+      </c>
+      <c r="B233">
+        <v>441.021</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46173.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>475.418</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46173.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>486.807</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46173.4375</v>
+      </c>
+      <c r="B236">
+        <v>496.765</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46173.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>505.838</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46173.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>505.428</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46173.46875</v>
+      </c>
+      <c r="B239">
+        <v>487.389</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46173.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>490.875</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46173.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>496.538</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46173.5</v>
+      </c>
+      <c r="B242">
+        <v>509.1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46173.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>517.145</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46173.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>525.395</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46173.53125</v>
+      </c>
+      <c r="B245">
+        <v>534.204</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46173.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>491.971</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46173.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>496.955</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46173.5625</v>
+      </c>
+      <c r="B248">
+        <v>501.824</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46173.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>506.052</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46173.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>497.174</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46173.59375</v>
+      </c>
+      <c r="B251">
+        <v>488.055</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46173.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>477.279</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46173.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>466.633</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46173.625</v>
+      </c>
+      <c r="B254">
+        <v>446.721</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46173.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>422.911</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46173.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>421.468</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46173.65625</v>
+      </c>
+      <c r="B257">
+        <v>415.228</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46173.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>384.896</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46173.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>363.26</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46173.6875</v>
+      </c>
+      <c r="B260">
+        <v>341.89</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46173.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>320.998</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46173.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>312.299</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46173.71875</v>
+      </c>
+      <c r="B263">
+        <v>292.727</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46173.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>273.02</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46173.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>254.507</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46173.75</v>
+      </c>
+      <c r="B266">
+        <v>239.957</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46173.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>232.584</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46173.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>226.305</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46173.78125</v>
+      </c>
+      <c r="B269">
+        <v>220.869</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46173.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>218.797</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46173.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>219.726</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46173.8125</v>
+      </c>
+      <c r="B272">
+        <v>220.27</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46173.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>221.28</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46173.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>223.261</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46173.84375</v>
+      </c>
+      <c r="B275">
+        <v>228.886</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46173.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>233.768</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46173.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>238.055</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46173.875</v>
+      </c>
+      <c r="B278">
+        <v>221.024</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46173.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>225.399</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46173.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>231.339</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46173.90625</v>
+      </c>
+      <c r="B281">
+        <v>236.881</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46173.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>242.259</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46173.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>248.559</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46173.9375</v>
+      </c>
+      <c r="B284">
+        <v>255.106</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46173.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>261.554</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46173.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>295.492</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46173.96875</v>
+      </c>
+      <c r="B287">
+        <v>300.52</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46173.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>306.226</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46173.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>310.461</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46174</v>
+      </c>
+      <c r="B290">
+        <v>174.034</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46174.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>169.715</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46174.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>164.633</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46174.03125</v>
+      </c>
+      <c r="B293">
+        <v>159.273</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46174.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>158.804</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46174.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>154.668</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46174.0625</v>
+      </c>
+      <c r="B296">
+        <v>150.469</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46174.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>146.507</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46174.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>148.718</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46174.09375</v>
+      </c>
+      <c r="B299">
+        <v>142.039</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46174.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>139.869</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46174.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>134.402</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46174.125</v>
+      </c>
+      <c r="B302">
+        <v>128.108</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46174.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>121.281</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46174.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>114.194</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46174.15625</v>
+      </c>
+      <c r="B305">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46174.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>96.95399999999999</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46174.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>93.449</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46174.1875</v>
+      </c>
+      <c r="B308">
+        <v>90.672</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46174.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>88.73999999999999</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46174.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>83.581</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46174.21875</v>
+      </c>
+      <c r="B311">
+        <v>82.718</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46174.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>82.107</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46174.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>81.626</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46174.25</v>
+      </c>
+      <c r="B314">
+        <v>92.79300000000001</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46174.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>92.652</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46174.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>92.527</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46174.28125</v>
+      </c>
+      <c r="B317">
+        <v>89.423</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46174.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>81.539</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46174.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>82.54300000000001</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46174.3125</v>
+      </c>
+      <c r="B320">
+        <v>82.825</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46174.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>82.55500000000001</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46174.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>88.974</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46174.34375</v>
+      </c>
+      <c r="B323">
+        <v>102.54</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46174.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>102.624</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46174.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>103.683</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46174.375</v>
+      </c>
+      <c r="B326">
+        <v>104.723</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46174.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>106.719</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46174.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>109.56</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46174.40625</v>
+      </c>
+      <c r="B329">
+        <v>111.115</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46174.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>106.249</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46174.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>111.842</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46174.4375</v>
+      </c>
+      <c r="B332">
+        <v>117.445</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46174.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>122.679</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46174.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>139.526</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46174.46875</v>
+      </c>
+      <c r="B335">
+        <v>151.691</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46174.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>163.626</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46174.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>175.648</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46174.5</v>
+      </c>
+      <c r="B338">
+        <v>193.297</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46174.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>208.689</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46174.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>224.398</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46174.53125</v>
+      </c>
+      <c r="B341">
+        <v>240.522</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46174.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>264.725</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46174.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>284.961</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46174.5625</v>
+      </c>
+      <c r="B344">
+        <v>305.74</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46174.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>326.656</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46174.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>304.475</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46174.59375</v>
+      </c>
+      <c r="B347">
+        <v>323.427</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46174.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>341.652</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46174.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>361.58</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46174.625</v>
+      </c>
+      <c r="B350">
+        <v>391.752</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46174.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>416.438</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46174.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>443.552</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46174.65625</v>
+      </c>
+      <c r="B353">
+        <v>470.336</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46174.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>508.579</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46174.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>533.276</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46174.6875</v>
+      </c>
+      <c r="B356">
+        <v>559.755</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46174.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>585.009</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46174.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>619.255</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46174.71875</v>
+      </c>
+      <c r="B359">
+        <v>639.134</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46174.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>658.397</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46174.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>678.662</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46174.75</v>
+      </c>
+      <c r="B362">
+        <v>711.8339999999999</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46174.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>730.283</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46174.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>751.24</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46174.78125</v>
+      </c>
+      <c r="B365">
+        <v>771.299</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46174.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>821.059</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46174.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>847.804</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46174.8125</v>
+      </c>
+      <c r="B368">
+        <v>875.215</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46174.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>898.808</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46174.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>878.652</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46174.84375</v>
+      </c>
+      <c r="B371">
+        <v>905.063</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46174.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>928.38</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46174.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>954.2809999999999</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46174.875</v>
+      </c>
+      <c r="B374">
+        <v>991.754</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46174.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>1016.141</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46174.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>1037.319</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46174.90625</v>
+      </c>
+      <c r="B377">
+        <v>1058.558</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46174.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>1082.242</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46174.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>1101.716</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46174.9375</v>
+      </c>
+      <c r="B380">
+        <v>1119.208</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46174.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>1136.937</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46174.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>1196.64</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46174.96875</v>
+      </c>
+      <c r="B383">
+        <v>1222.279</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46174.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>1246.632</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46174.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>1275.627</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46175</v>
+      </c>
+      <c r="B386">
+        <v>1259.457</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46175.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>1289.407</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46175.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>1327.644</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46175.03125</v>
+      </c>
+      <c r="B389">
+        <v>1353.208</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46175.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>1397.742</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46175.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>1416.372</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46175.0625</v>
+      </c>
+      <c r="B392">
+        <v>1441.258</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46175.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>1465.47</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46175.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>1485.816</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46175.09375</v>
+      </c>
+      <c r="B395">
+        <v>1508.359</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46175.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>1532.013</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46175.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>1553.699</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46175.125</v>
+      </c>
+      <c r="B398">
+        <v>1551.127</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46175.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>1569.935</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46175.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>1602.999</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46175.15625</v>
+      </c>
+      <c r="B401">
+        <v>1597.948</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46175.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>1658.025</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46175.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>1680.582</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46175.1875</v>
+      </c>
+      <c r="B404">
+        <v>1712.444</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46175.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>1753.097</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46175.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>1820.292</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46175.21875</v>
+      </c>
+      <c r="B407">
+        <v>1848.565</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46175.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>1873.186</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46175.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>1899.998</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46175.25</v>
+      </c>
+      <c r="B410">
+        <v>1956.989</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46175.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>1988.839</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46175.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>2005.433</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46175.28125</v>
+      </c>
+      <c r="B413">
+        <v>2011.419</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46175.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>2006.822</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46175.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>2014.171</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46175.3125</v>
+      </c>
+      <c r="B416">
+        <v>2036.924</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46175.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>2047.313</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46175.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>1979.124</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46175.34375</v>
+      </c>
+      <c r="B419">
+        <v>1990.703</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46175.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>2048.301</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46175.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>2051.048</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46175.375</v>
+      </c>
+      <c r="B422">
+        <v>2128.471</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46175.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>2130.665</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46175.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>2134.294</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46175.40625</v>
+      </c>
+      <c r="B425">
+        <v>2139.638</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46175.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>2183.989</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46175.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>2186.973</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46175.4375</v>
+      </c>
+      <c r="B428">
+        <v>2185.737</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46175.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>2187.888</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46175.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>2197.061</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46175.46875</v>
+      </c>
+      <c r="B431">
+        <v>2191.094</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46175.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>2183.561</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46175.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>2176.495</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46175.5</v>
+      </c>
+      <c r="B434">
+        <v>2166.939</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46175.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>2163.564</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46175.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>2159.186</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46175.53125</v>
+      </c>
+      <c r="B437">
+        <v>2158.244</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46175.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>2167.681</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46175.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>2172.899</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46175.5625</v>
+      </c>
+      <c r="B440">
+        <v>2175.207</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46175.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>2182.115</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46175.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>2212.273</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46175.59375</v>
+      </c>
+      <c r="B443">
+        <v>2211.518</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46175.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>2208.241</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46175.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>2204.857</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46175.625</v>
+      </c>
+      <c r="B446">
+        <v>2207.632</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46175.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>2188.928</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46175.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>2165.785</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46175.65625</v>
+      </c>
+      <c r="B449">
+        <v>2142.123</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46175.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>1975.303</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46175.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>1930.99</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46175.6875</v>
+      </c>
+      <c r="B452">
+        <v>1886.411</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46175.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>1841.635</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46175.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>1778.398</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46175.71875</v>
+      </c>
+      <c r="B455">
+        <v>1714.335</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46175.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>1645.022</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46175.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>1581.02</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46175.75</v>
+      </c>
+      <c r="B458">
+        <v>1514.531</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46175.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>1463.764</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46175.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>1415.436</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46175.78125</v>
+      </c>
+      <c r="B461">
+        <v>1367.634</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46175.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>1319.579</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46175.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>1302.378</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46175.8125</v>
+      </c>
+      <c r="B464">
+        <v>1282.662</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46175.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>1266.203</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46175.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>1240.776</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46175.84375</v>
+      </c>
+      <c r="B467">
+        <v>1220.532</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46175.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>1201.831</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46175.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>1181.765</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46175.875</v>
+      </c>
+      <c r="B470">
+        <v>1137.323</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46175.88541666666</v>
+      </c>
+      <c r="B471">
+        <v>1104.245</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472" s="2">
+        <v>46175.89583333334</v>
+      </c>
+      <c r="B472">
+        <v>1071.18</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473" s="2">
+        <v>46175.90625</v>
+      </c>
+      <c r="B473">
+        <v>1038.327</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474" s="2">
+        <v>46175.91666666666</v>
+      </c>
+      <c r="B474">
+        <v>975.751</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475" s="2">
+        <v>46175.92708333334</v>
+      </c>
+      <c r="B475">
+        <v>933.404</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476" s="2">
+        <v>46175.9375</v>
+      </c>
+      <c r="B476">
+        <v>892.415</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477" s="2">
+        <v>46175.94791666666</v>
+      </c>
+      <c r="B477">
+        <v>850.514</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478" s="2">
+        <v>46175.95833333334</v>
+      </c>
+      <c r="B478">
+        <v>640.117</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479" s="2">
+        <v>46175.96875</v>
+      </c>
+      <c r="B479">
+        <v>605.009</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480" s="2">
+        <v>46175.97916666666</v>
+      </c>
+      <c r="B480">
+        <v>577.645</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481" s="2">
+        <v>46175.98958333334</v>
+      </c>
+      <c r="B481">
+        <v>532.8339999999999</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B482">
+        <v>506.237</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483" s="2">
+        <v>46176.01041666666</v>
+      </c>
+      <c r="B483">
+        <v>482.218</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484" s="2">
+        <v>46176.02083333334</v>
+      </c>
+      <c r="B484">
+        <v>458.811</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485" s="2">
+        <v>46176.03125</v>
+      </c>
+      <c r="B485">
+        <v>433.199</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486" s="2">
+        <v>46176.04166666666</v>
+      </c>
+      <c r="B486">
+        <v>440.053</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487" s="2">
+        <v>46176.05208333334</v>
+      </c>
+      <c r="B487">
+        <v>397.051</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="2">
+        <v>46176.0625</v>
+      </c>
+      <c r="B488">
+        <v>359.298</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489" s="2">
+        <v>46176.07291666666</v>
+      </c>
+      <c r="B489">
+        <v>322.379</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490" s="2">
+        <v>46176.08333333334</v>
+      </c>
+      <c r="B490">
+        <v>315.47</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491" s="2">
+        <v>46176.09375</v>
+      </c>
+      <c r="B491">
+        <v>293.418</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492" s="2">
+        <v>46176.10416666666</v>
+      </c>
+      <c r="B492">
+        <v>275.588</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493" s="2">
+        <v>46176.11458333334</v>
+      </c>
+      <c r="B493">
+        <v>253.44</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494" s="2">
+        <v>46176.125</v>
+      </c>
+      <c r="B494">
+        <v>235.122</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495" s="2">
+        <v>46176.13541666666</v>
+      </c>
+      <c r="B495">
+        <v>225.416</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496" s="2">
+        <v>46176.14583333334</v>
+      </c>
+      <c r="B496">
+        <v>213.319</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497" s="2">
+        <v>46176.15625</v>
+      </c>
+      <c r="B497">
+        <v>201.61</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498" s="2">
+        <v>46176.16666666666</v>
+      </c>
+      <c r="B498">
+        <v>185.821</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499" s="2">
+        <v>46176.17708333334</v>
+      </c>
+      <c r="B499">
+        <v>176.531</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500" s="2">
+        <v>46176.1875</v>
+      </c>
+      <c r="B500">
+        <v>166.472</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501" s="2">
+        <v>46176.19791666666</v>
+      </c>
+      <c r="B501">
+        <v>158.317</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502" s="2">
+        <v>46176.20833333334</v>
+      </c>
+      <c r="B502">
+        <v>149.194</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503" s="2">
+        <v>46176.21875</v>
+      </c>
+      <c r="B503">
+        <v>143.187</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504" s="2">
+        <v>46176.22916666666</v>
+      </c>
+      <c r="B504">
+        <v>135.599</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505" s="2">
+        <v>46176.23958333334</v>
+      </c>
+      <c r="B505">
+        <v>128.961</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506" s="2">
+        <v>46176.25</v>
+      </c>
+      <c r="B506">
+        <v>114.24</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507" s="2">
+        <v>46176.26041666666</v>
+      </c>
+      <c r="B507">
+        <v>108.126</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508" s="2">
+        <v>46176.27083333334</v>
+      </c>
+      <c r="B508">
+        <v>104.276</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509" s="2">
+        <v>46176.28125</v>
+      </c>
+      <c r="B509">
+        <v>103.001</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510" s="2">
+        <v>46176.29166666666</v>
+      </c>
+      <c r="B510">
+        <v>105.169</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511" s="2">
+        <v>46176.30208333334</v>
+      </c>
+      <c r="B511">
+        <v>104.629</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512" s="2">
+        <v>46176.3125</v>
+      </c>
+      <c r="B512">
+        <v>106.448</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513" s="2">
+        <v>46176.32291666666</v>
+      </c>
+      <c r="B513">
+        <v>105.89</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514" s="2">
+        <v>46176.33333333334</v>
+      </c>
+      <c r="B514">
+        <v>104.555</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515" s="2">
+        <v>46176.34375</v>
+      </c>
+      <c r="B515">
+        <v>106.968</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516" s="2">
+        <v>46176.35416666666</v>
+      </c>
+      <c r="B516">
+        <v>105.514</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517" s="2">
+        <v>46176.36458333334</v>
+      </c>
+      <c r="B517">
+        <v>105.989</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518" s="2">
+        <v>46176.375</v>
+      </c>
+      <c r="B518">
+        <v>112.314</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519" s="2">
+        <v>46176.38541666666</v>
+      </c>
+      <c r="B519">
+        <v>114.048</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520" s="2">
+        <v>46176.39583333334</v>
+      </c>
+      <c r="B520">
+        <v>115.763</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521" s="2">
+        <v>46176.40625</v>
+      </c>
+      <c r="B521">
+        <v>117.868</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522" s="2">
+        <v>46176.41666666666</v>
+      </c>
+      <c r="B522">
+        <v>129.211</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523" s="2">
+        <v>46176.42708333334</v>
+      </c>
+      <c r="B523">
+        <v>133.885</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524" s="2">
+        <v>46176.4375</v>
+      </c>
+      <c r="B524">
+        <v>139.005</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525" s="2">
+        <v>46176.44791666666</v>
+      </c>
+      <c r="B525">
+        <v>144.313</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526" s="2">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="B526">
+        <v>160.708</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527" s="2">
+        <v>46176.46875</v>
+      </c>
+      <c r="B527">
+        <v>168.678</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528" s="2">
+        <v>46176.47916666666</v>
+      </c>
+      <c r="B528">
+        <v>177.214</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529" s="2">
+        <v>46176.48958333334</v>
+      </c>
+      <c r="B529">
+        <v>185.968</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530" s="2">
+        <v>46176.5</v>
+      </c>
+      <c r="B530">
+        <v>188.495</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531" s="2">
+        <v>46176.51041666666</v>
+      </c>
+      <c r="B531">
+        <v>196.124</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532" s="2">
+        <v>46176.52083333334</v>
+      </c>
+      <c r="B532">
+        <v>203.585</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533" s="2">
+        <v>46176.53125</v>
+      </c>
+      <c r="B533">
+        <v>210.698</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534" s="2">
+        <v>46176.54166666666</v>
+      </c>
+      <c r="B534">
+        <v>217.937</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535" s="2">
+        <v>46176.55208333334</v>
+      </c>
+      <c r="B535">
+        <v>226.669</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536" s="2">
+        <v>46176.5625</v>
+      </c>
+      <c r="B536">
+        <v>234.936</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537" s="2">
+        <v>46176.57291666666</v>
+      </c>
+      <c r="B537">
+        <v>243.295</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538" s="2">
+        <v>46176.58333333334</v>
+      </c>
+      <c r="B538">
+        <v>250.349</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539" s="2">
+        <v>46176.59375</v>
+      </c>
+      <c r="B539">
+        <v>255.498</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540" s="2">
+        <v>46176.60416666666</v>
+      </c>
+      <c r="B540">
+        <v>260.762</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541" s="2">
+        <v>46176.61458333334</v>
+      </c>
+      <c r="B541">
+        <v>265.785</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542" s="2">
+        <v>46176.625</v>
+      </c>
+      <c r="B542">
+        <v>273.192</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543" s="2">
+        <v>46176.63541666666</v>
+      </c>
+      <c r="B543">
+        <v>281.313</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544" s="2">
+        <v>46176.64583333334</v>
+      </c>
+      <c r="B544">
+        <v>289.76</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545" s="2">
+        <v>46176.65625</v>
+      </c>
+      <c r="B545">
+        <v>298.07</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546" s="2">
+        <v>46176.66666666666</v>
+      </c>
+      <c r="B546">
+        <v>322.211</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547" s="2">
+        <v>46176.67708333334</v>
+      </c>
+      <c r="B547">
+        <v>333.294</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548" s="2">
+        <v>46176.6875</v>
+      </c>
+      <c r="B548">
+        <v>344.542</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549" s="2">
+        <v>46176.69791666666</v>
+      </c>
+      <c r="B549">
+        <v>355.767</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550" s="2">
+        <v>46176.70833333334</v>
+      </c>
+      <c r="B550">
+        <v>381.306</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551" s="2">
+        <v>46176.71875</v>
+      </c>
+      <c r="B551">
+        <v>402.276</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552" s="2">
+        <v>46176.72916666666</v>
+      </c>
+      <c r="B552">
+        <v>420.686</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553" s="2">
+        <v>46176.73958333334</v>
+      </c>
+      <c r="B553">
+        <v>439.531</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554" s="2">
+        <v>46176.75</v>
+      </c>
+      <c r="B554">
+        <v>478.905</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555" s="2">
+        <v>46176.76041666666</v>
+      </c>
+      <c r="B555">
+        <v>497.362</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556" s="2">
+        <v>46176.77083333334</v>
+      </c>
+      <c r="B556">
+        <v>516.66</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557" s="2">
+        <v>46176.78125</v>
+      </c>
+      <c r="B557">
+        <v>538.093</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558" s="2">
+        <v>46176.79166666666</v>
+      </c>
+      <c r="B558">
+        <v>571.682</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559" s="2">
+        <v>46176.80208333334</v>
+      </c>
+      <c r="B559">
+        <v>602.39</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560" s="2">
+        <v>46176.8125</v>
+      </c>
+      <c r="B560">
+        <v>633.6079999999999</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561" s="2">
+        <v>46176.82291666666</v>
+      </c>
+      <c r="B561">
+        <v>664.222</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562" s="2">
+        <v>46176.83333333334</v>
+      </c>
+      <c r="B562">
+        <v>701.096</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563" s="2">
+        <v>46176.84375</v>
+      </c>
+      <c r="B563">
+        <v>719.1319999999999</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564" s="2">
+        <v>46176.85416666666</v>
+      </c>
+      <c r="B564">
+        <v>737.6420000000001</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565" s="2">
+        <v>46176.86458333334</v>
+      </c>
+      <c r="B565">
+        <v>755.994</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566" s="2">
+        <v>46176.875</v>
+      </c>
+      <c r="B566">
+        <v>777.736</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567" s="2">
+        <v>46176.88541666666</v>
+      </c>
+      <c r="B567">
+        <v>783.054</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568" s="2">
+        <v>46176.89583333334</v>
+      </c>
+      <c r="B568">
+        <v>787.794</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569" s="2">
+        <v>46176.90625</v>
+      </c>
+      <c r="B569">
+        <v>794.101</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570" s="2">
+        <v>46176.91666666666</v>
+      </c>
+      <c r="B570">
+        <v>759.388</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571" s="2">
+        <v>46176.92708333334</v>
+      </c>
+      <c r="B571">
+        <v>765.044</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572" s="2">
+        <v>46176.9375</v>
+      </c>
+      <c r="B572">
+        <v>771.395</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573" s="2">
+        <v>46176.94791666666</v>
+      </c>
+      <c r="B573">
+        <v>775.663</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574" s="2">
+        <v>46176.95833333334</v>
+      </c>
+      <c r="B574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575" s="2">
+        <v>46176.96875</v>
+      </c>
+      <c r="B575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576" s="2">
+        <v>46176.97916666666</v>
+      </c>
+      <c r="B576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577" s="2">
+        <v>46176.98958333334</v>
+      </c>
+      <c r="B577">
         <v>0</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_FA55453528F8D02304FF31D2F8375B064417D8EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EF7C0BF-4DD8-4287-BAC4-047388553EF2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B93"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,772 +425,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>46185.01041666666</v>
+        <v>46213</v>
       </c>
       <c r="B2">
-        <v>703.268</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>272.05599999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>46185.02083333334</v>
+        <v>46213.010416666657</v>
       </c>
       <c r="B3">
-        <v>691.595</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>267.387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>46185.03125</v>
+        <v>46213.020833333343</v>
       </c>
       <c r="B4">
-        <v>672.953</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>266.65199999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>46185.04166666666</v>
+        <v>46213.03125</v>
       </c>
       <c r="B5">
-        <v>667.522</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>264.54300000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>46185.05208333334</v>
+        <v>46213.041666666657</v>
       </c>
       <c r="B6">
-        <v>622.746</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>256.65100000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>46185.0625</v>
+        <v>46213.052083333343</v>
       </c>
       <c r="B7">
-        <v>603.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>263.541</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>46185.07291666666</v>
+        <v>46213.0625</v>
       </c>
       <c r="B8">
-        <v>584.78</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>274.44400000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>46185.08333333334</v>
+        <v>46213.072916666657</v>
       </c>
       <c r="B9">
-        <v>581.83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>284.791</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>46185.09375</v>
+        <v>46213.083333333343</v>
       </c>
       <c r="B10">
-        <v>556.008</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>298.49700000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>46185.10416666666</v>
+        <v>46213.09375</v>
       </c>
       <c r="B11">
-        <v>536.2859999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>296.73099999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>46185.11458333334</v>
+        <v>46213.104166666657</v>
       </c>
       <c r="B12">
-        <v>513.354</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>299.084</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>46185.125</v>
+        <v>46213.114583333343</v>
       </c>
       <c r="B13">
-        <v>495.133</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>305.43099999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>46185.13541666666</v>
+        <v>46213.125</v>
       </c>
       <c r="B14">
-        <v>463.779</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>306.75299999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>46185.14583333334</v>
+        <v>46213.135416666657</v>
       </c>
       <c r="B15">
-        <v>451.973</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>312.822</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>46185.15625</v>
+        <v>46213.145833333343</v>
       </c>
       <c r="B16">
-        <v>441.703</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>317.774</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>46185.16666666666</v>
+        <v>46213.15625</v>
       </c>
       <c r="B17">
-        <v>422.315</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>320.565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>46185.17708333334</v>
+        <v>46213.166666666657</v>
       </c>
       <c r="B18">
-        <v>388.295</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>321.16500000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>46185.1875</v>
+        <v>46213.177083333343</v>
       </c>
       <c r="B19">
-        <v>373.879</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>322.21499999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>46185.19791666666</v>
+        <v>46213.1875</v>
       </c>
       <c r="B20">
-        <v>376.052</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>313.38600000000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>46185.20833333334</v>
+        <v>46213.197916666657</v>
       </c>
       <c r="B21">
-        <v>363.785</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>308.98399999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>46185.21875</v>
+        <v>46213.208333333343</v>
       </c>
       <c r="B22">
-        <v>346.099</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>293.78800000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>46185.22916666666</v>
+        <v>46213.21875</v>
       </c>
       <c r="B23">
-        <v>334.848</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>284.81200000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>46185.23958333334</v>
+        <v>46213.229166666657</v>
       </c>
       <c r="B24">
-        <v>326.408</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>281.96100000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>46185.25</v>
+        <v>46213.239583333343</v>
       </c>
       <c r="B25">
-        <v>322.237</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>269.71100000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>46185.26041666666</v>
+        <v>46213.25</v>
       </c>
       <c r="B26">
-        <v>327.94</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>226.91300000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>46185.27083333334</v>
+        <v>46213.260416666657</v>
       </c>
       <c r="B27">
-        <v>311.471</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>208.566</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>46185.28125</v>
+        <v>46213.270833333343</v>
       </c>
       <c r="B28">
-        <v>301.59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>195.38200000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>46185.29166666666</v>
+        <v>46213.28125</v>
       </c>
       <c r="B29">
-        <v>292.085</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>183.11699999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>46185.30208333334</v>
+        <v>46213.291666666657</v>
       </c>
       <c r="B30">
-        <v>277.456</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>170.762</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>46185.3125</v>
+        <v>46213.302083333343</v>
       </c>
       <c r="B31">
-        <v>269.403</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>163.79599999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>46185.32291666666</v>
+        <v>46213.3125</v>
       </c>
       <c r="B32">
-        <v>263.254</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>151.83799999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>46185.33333333334</v>
+        <v>46213.322916666657</v>
       </c>
       <c r="B33">
-        <v>258.446</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>144.423</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>46185.34375</v>
+        <v>46213.333333333343</v>
       </c>
       <c r="B34">
-        <v>244.041</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>160.33699999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>46185.35416666666</v>
+        <v>46213.34375</v>
       </c>
       <c r="B35">
-        <v>250.211</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>168.083</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>46185.36458333334</v>
+        <v>46213.354166666657</v>
       </c>
       <c r="B36">
-        <v>269.267</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>159.20599999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>46185.375</v>
+        <v>46213.364583333343</v>
       </c>
       <c r="B37">
-        <v>274.716</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>158.066</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>46185.38541666666</v>
+        <v>46213.375</v>
       </c>
       <c r="B38">
-        <v>330.354</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>151.98699999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>46185.39583333334</v>
+        <v>46213.385416666657</v>
       </c>
       <c r="B39">
-        <v>340.926</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>154.16999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>46185.40625</v>
+        <v>46213.395833333343</v>
       </c>
       <c r="B40">
-        <v>350.881</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>156.40700000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>46185.41666666666</v>
+        <v>46213.40625</v>
       </c>
       <c r="B41">
-        <v>360.345</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>158.41900000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>46185.42708333334</v>
+        <v>46213.416666666657</v>
       </c>
       <c r="B42">
-        <v>332.263</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>137.62700000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>46185.4375</v>
+        <v>46213.427083333343</v>
       </c>
       <c r="B43">
-        <v>350.576</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>141.571</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>46185.44791666666</v>
+        <v>46213.4375</v>
       </c>
       <c r="B44">
-        <v>369.884</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>144.91900000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>46185.45833333334</v>
+        <v>46213.447916666657</v>
       </c>
       <c r="B45">
-        <v>390.023</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>148.71100000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>46185.46875</v>
+        <v>46213.458333333343</v>
       </c>
       <c r="B46">
-        <v>416.32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>154.80000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>46185.47916666666</v>
+        <v>46213.46875</v>
       </c>
       <c r="B47">
-        <v>442.182</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>160.119</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>46185.48958333334</v>
+        <v>46213.479166666657</v>
       </c>
       <c r="B48">
-        <v>467.256</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>166.03700000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>46185.5</v>
+        <v>46213.489583333343</v>
       </c>
       <c r="B49">
-        <v>492.503</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>172.01300000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>46185.51041666666</v>
+        <v>46213.5</v>
       </c>
       <c r="B50">
-        <v>583.2670000000001</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>180.79499999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
-        <v>46185.52083333334</v>
+        <v>46213.510416666657</v>
       </c>
       <c r="B51">
-        <v>620.328</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>187.69800000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>46185.53125</v>
+        <v>46213.520833333343</v>
       </c>
       <c r="B52">
-        <v>656.048</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>194.68799999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>46185.54166666666</v>
+        <v>46213.53125</v>
       </c>
       <c r="B53">
-        <v>695.883</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>201.16200000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
-        <v>46185.55208333334</v>
+        <v>46213.541666666657</v>
       </c>
       <c r="B54">
-        <v>756.11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>213.18799999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>46185.5625</v>
+        <v>46213.552083333343</v>
       </c>
       <c r="B55">
-        <v>802.866</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>218.78</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>46185.57291666666</v>
+        <v>46213.5625</v>
       </c>
       <c r="B56">
-        <v>849.521</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>225.298</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
-        <v>46185.58333333334</v>
+        <v>46213.572916666657</v>
       </c>
       <c r="B57">
-        <v>896.886</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>231.571</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
-        <v>46185.59375</v>
+        <v>46213.583333333343</v>
       </c>
       <c r="B58">
-        <v>991.41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>232.81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
-        <v>46185.60416666666</v>
+        <v>46213.59375</v>
       </c>
       <c r="B59">
-        <v>1025.834</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>238.26599999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
-        <v>46185.61458333334</v>
+        <v>46213.604166666657</v>
       </c>
       <c r="B60">
-        <v>1058.283</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>242.691</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
-        <v>46185.625</v>
+        <v>46213.614583333343</v>
       </c>
       <c r="B61">
-        <v>1092.029</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>247.779</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
-        <v>46185.63541666666</v>
+        <v>46213.625</v>
       </c>
       <c r="B62">
-        <v>1147.673</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>265.88299999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
-        <v>46185.64583333334</v>
+        <v>46213.635416666657</v>
       </c>
       <c r="B63">
-        <v>1188.13</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>272.48399999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
-        <v>46185.65625</v>
+        <v>46213.645833333343</v>
       </c>
       <c r="B64">
-        <v>1226.492</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>278.822</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
-        <v>46185.66666666666</v>
+        <v>46213.65625</v>
       </c>
       <c r="B65">
-        <v>1262.901</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>283.62299999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
-        <v>46185.67708333334</v>
+        <v>46213.666666666657</v>
       </c>
       <c r="B66">
-        <v>1230.626</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>282.18299999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
-        <v>46185.6875</v>
+        <v>46213.677083333343</v>
       </c>
       <c r="B67">
-        <v>1268.032</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>281.642</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
-        <v>46185.69791666666</v>
+        <v>46213.6875</v>
       </c>
       <c r="B68">
-        <v>1307.478</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>281.59699999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
-        <v>46185.70833333334</v>
+        <v>46213.697916666657</v>
       </c>
       <c r="B69">
-        <v>1345.105</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>281.39400000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
-        <v>46185.71875</v>
+        <v>46213.708333333343</v>
       </c>
       <c r="B70">
-        <v>1384.322</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>281.06200000000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
-        <v>46185.72916666666</v>
+        <v>46213.71875</v>
       </c>
       <c r="B71">
-        <v>1406.188</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>277.67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
-        <v>46185.73958333334</v>
+        <v>46213.729166666657</v>
       </c>
       <c r="B72">
-        <v>1428.982</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>274.173</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
-        <v>46185.75</v>
+        <v>46213.739583333343</v>
       </c>
       <c r="B73">
-        <v>1452.674</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>270.64699999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
-        <v>46185.76041666666</v>
+        <v>46213.75</v>
       </c>
       <c r="B74">
-        <v>1479.041</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>263.52999999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
-        <v>46185.77083333334</v>
+        <v>46213.760416666657</v>
       </c>
       <c r="B75">
-        <v>1494.595</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>261.142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
-        <v>46185.78125</v>
+        <v>46213.770833333343</v>
       </c>
       <c r="B76">
-        <v>1509.484</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>259.59699999999998</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
-        <v>46185.79166666666</v>
+        <v>46213.78125</v>
       </c>
       <c r="B77">
-        <v>1524.774</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>256.79500000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
-        <v>46185.80208333334</v>
+        <v>46213.791666666657</v>
       </c>
       <c r="B78">
-        <v>1566.269</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>223.89699999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
-        <v>46185.8125</v>
+        <v>46213.802083333343</v>
       </c>
       <c r="B79">
-        <v>1587.253</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>229.71899999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
-        <v>46185.82291666666</v>
+        <v>46213.8125</v>
       </c>
       <c r="B80">
-        <v>1606.463</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>235.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
-        <v>46185.83333333334</v>
+        <v>46213.822916666657</v>
       </c>
       <c r="B81">
-        <v>1626.694</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>243.33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
-        <v>46185.84375</v>
+        <v>46213.833333333343</v>
       </c>
       <c r="B82">
-        <v>1580.59</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>245.28399999999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
-        <v>46185.85416666666</v>
+        <v>46213.84375</v>
       </c>
       <c r="B83">
-        <v>1601.322</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>252.62200000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
-        <v>46185.86458333334</v>
+        <v>46213.854166666657</v>
       </c>
       <c r="B84">
-        <v>1618.817</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>261.22300000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
-        <v>46185.875</v>
+        <v>46213.864583333343</v>
       </c>
       <c r="B85">
-        <v>1636.85</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>270.25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
-        <v>46185.88541666666</v>
+        <v>46213.875</v>
       </c>
       <c r="B86">
-        <v>1659.634</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>279.84300000000002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
-        <v>46185.89583333334</v>
+        <v>46213.885416666657</v>
       </c>
       <c r="B87">
-        <v>1671.946</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>283.64999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
-        <v>46185.90625</v>
+        <v>46213.895833333343</v>
       </c>
       <c r="B88">
-        <v>1685.606</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>287.62099999999998</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
-        <v>46185.91666666666</v>
+        <v>46213.90625</v>
       </c>
       <c r="B89">
-        <v>1696.322</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>292.60399999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
-        <v>46185.92708333334</v>
+        <v>46213.916666666657</v>
       </c>
       <c r="B90">
-        <v>1701.162</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>295.14600000000002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
-        <v>46185.9375</v>
+        <v>46213.927083333343</v>
       </c>
       <c r="B91">
-        <v>1705.016</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>294.70800000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
-        <v>46185.94791666666</v>
+        <v>46213.9375</v>
       </c>
       <c r="B92">
-        <v>1707.337</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>295.61</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
-        <v>46185.95833333334</v>
+        <v>46213.947916666657</v>
       </c>
       <c r="B93">
-        <v>1710.318</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="2">
-        <v>46185.96875</v>
-      </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" s="2">
-        <v>46185.97916666666</v>
-      </c>
-      <c r="B95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="2">
-        <v>46185.98958333334</v>
-      </c>
-      <c r="B96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" s="2">
-        <v>46186</v>
-      </c>
-      <c r="B97">
-        <v>0</v>
+        <v>294.94</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_FA55453528F8D02304FF31D2F8375B064417D8EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EF7C0BF-4DD8-4287-BAC4-047388553EF2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,740 +392,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B2">
-        <v>272.05599999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>423.957</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46213.010416666657</v>
+        <v>46216.01041666666</v>
       </c>
       <c r="B3">
-        <v>267.387</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>416.548</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46213.020833333343</v>
+        <v>46216.02083333334</v>
       </c>
       <c r="B4">
-        <v>266.65199999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>407.141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46213.03125</v>
+        <v>46216.03125</v>
       </c>
       <c r="B5">
-        <v>264.54300000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>400.027</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46213.041666666657</v>
+        <v>46216.04166666666</v>
       </c>
       <c r="B6">
-        <v>256.65100000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>407.939</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46213.052083333343</v>
+        <v>46216.05208333334</v>
       </c>
       <c r="B7">
-        <v>263.541</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>405.446</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46213.0625</v>
+        <v>46216.0625</v>
       </c>
       <c r="B8">
-        <v>274.44400000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>405.455</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46213.072916666657</v>
+        <v>46216.07291666666</v>
       </c>
       <c r="B9">
-        <v>284.791</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>406.583</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46213.083333333343</v>
+        <v>46216.08333333334</v>
       </c>
       <c r="B10">
-        <v>298.49700000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>398.697</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46213.09375</v>
+        <v>46216.09375</v>
       </c>
       <c r="B11">
-        <v>296.73099999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>406.943</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46213.104166666657</v>
+        <v>46216.10416666666</v>
       </c>
       <c r="B12">
-        <v>299.084</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>403.355</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46213.114583333343</v>
+        <v>46216.11458333334</v>
       </c>
       <c r="B13">
-        <v>305.43099999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>399.372</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46213.125</v>
+        <v>46216.125</v>
       </c>
       <c r="B14">
-        <v>306.75299999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>389.303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46213.135416666657</v>
+        <v>46216.13541666666</v>
       </c>
       <c r="B15">
-        <v>312.822</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>393.037</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46213.145833333343</v>
+        <v>46216.14583333334</v>
       </c>
       <c r="B16">
-        <v>317.774</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>373.918</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46213.15625</v>
+        <v>46216.15625</v>
       </c>
       <c r="B17">
-        <v>320.565</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>360.961</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46213.166666666657</v>
+        <v>46216.16666666666</v>
       </c>
       <c r="B18">
-        <v>321.16500000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>345.899</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46213.177083333343</v>
+        <v>46216.17708333334</v>
       </c>
       <c r="B19">
-        <v>322.21499999999997</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>341.361</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46213.1875</v>
+        <v>46216.1875</v>
       </c>
       <c r="B20">
-        <v>313.38600000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>340.995</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46213.197916666657</v>
+        <v>46216.19791666666</v>
       </c>
       <c r="B21">
-        <v>308.98399999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>341.131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46213.208333333343</v>
+        <v>46216.20833333334</v>
       </c>
       <c r="B22">
-        <v>293.78800000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>353.375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46213.21875</v>
+        <v>46216.21875</v>
       </c>
       <c r="B23">
-        <v>284.81200000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>344.757</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46213.229166666657</v>
+        <v>46216.22916666666</v>
       </c>
       <c r="B24">
-        <v>281.96100000000001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>334.664</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46213.239583333343</v>
+        <v>46216.23958333334</v>
       </c>
       <c r="B25">
-        <v>269.71100000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>325.652</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46213.25</v>
+        <v>46216.25</v>
       </c>
       <c r="B26">
-        <v>226.91300000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>332.447</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46213.260416666657</v>
+        <v>46216.26041666666</v>
       </c>
       <c r="B27">
-        <v>208.566</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>329.939</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46213.270833333343</v>
+        <v>46216.27083333334</v>
       </c>
       <c r="B28">
-        <v>195.38200000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+        <v>321.56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46213.28125</v>
+        <v>46216.28125</v>
       </c>
       <c r="B29">
-        <v>183.11699999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+        <v>318.372</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46213.291666666657</v>
+        <v>46216.29166666666</v>
       </c>
       <c r="B30">
-        <v>170.762</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+        <v>327.894</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46213.302083333343</v>
+        <v>46216.30208333334</v>
       </c>
       <c r="B31">
-        <v>163.79599999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+        <v>333.59</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46213.3125</v>
+        <v>46216.3125</v>
       </c>
       <c r="B32">
-        <v>151.83799999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+        <v>339.881</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46213.322916666657</v>
+        <v>46216.32291666666</v>
       </c>
       <c r="B33">
-        <v>144.423</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>360.848</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46213.333333333343</v>
+        <v>46216.33333333334</v>
       </c>
       <c r="B34">
-        <v>160.33699999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>380.215</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46213.34375</v>
+        <v>46216.34375</v>
       </c>
       <c r="B35">
-        <v>168.083</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>392.637</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46213.354166666657</v>
+        <v>46216.35416666666</v>
       </c>
       <c r="B36">
-        <v>159.20599999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+        <v>412.904</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46213.364583333343</v>
+        <v>46216.36458333334</v>
       </c>
       <c r="B37">
-        <v>158.066</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>419.738</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46213.375</v>
+        <v>46216.375</v>
       </c>
       <c r="B38">
-        <v>151.98699999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+        <v>397.297</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46213.385416666657</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="B39">
-        <v>154.16999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+        <v>404.023</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46213.395833333343</v>
+        <v>46216.39583333334</v>
       </c>
       <c r="B40">
-        <v>156.40700000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+        <v>409.697</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46213.40625</v>
+        <v>46216.40625</v>
       </c>
       <c r="B41">
-        <v>158.41900000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>415.275</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46213.416666666657</v>
+        <v>46216.41666666666</v>
       </c>
       <c r="B42">
-        <v>137.62700000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+        <v>403.791</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46213.427083333343</v>
+        <v>46216.42708333334</v>
       </c>
       <c r="B43">
-        <v>141.571</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>406.629</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46213.4375</v>
+        <v>46216.4375</v>
       </c>
       <c r="B44">
-        <v>144.91900000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+        <v>408.349</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46213.447916666657</v>
+        <v>46216.44791666666</v>
       </c>
       <c r="B45">
-        <v>148.71100000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+        <v>409.673</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46213.458333333343</v>
+        <v>46216.45833333334</v>
       </c>
       <c r="B46">
-        <v>154.80000000000001</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+        <v>410.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46213.46875</v>
+        <v>46216.46875</v>
       </c>
       <c r="B47">
-        <v>160.119</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+        <v>409.149</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46213.479166666657</v>
+        <v>46216.47916666666</v>
       </c>
       <c r="B48">
-        <v>166.03700000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+        <v>407.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46213.489583333343</v>
+        <v>46216.48958333334</v>
       </c>
       <c r="B49">
-        <v>172.01300000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>404.075</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46213.5</v>
+        <v>46216.5</v>
       </c>
       <c r="B50">
-        <v>180.79499999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>406.623</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46213.510416666657</v>
+        <v>46216.51041666666</v>
       </c>
       <c r="B51">
-        <v>187.69800000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>405.428</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46213.520833333343</v>
+        <v>46216.52083333334</v>
       </c>
       <c r="B52">
-        <v>194.68799999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>403.987</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46213.53125</v>
+        <v>46216.53125</v>
       </c>
       <c r="B53">
-        <v>201.16200000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>403.899</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46213.541666666657</v>
+        <v>46216.54166666666</v>
       </c>
       <c r="B54">
-        <v>213.18799999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>404.761</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46213.552083333343</v>
+        <v>46216.55208333334</v>
       </c>
       <c r="B55">
-        <v>218.78</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+        <v>406.682</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46213.5625</v>
+        <v>46216.5625</v>
       </c>
       <c r="B56">
-        <v>225.298</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>409.076</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46213.572916666657</v>
+        <v>46216.57291666666</v>
       </c>
       <c r="B57">
-        <v>231.571</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+        <v>411.401</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46213.583333333343</v>
+        <v>46216.58333333334</v>
       </c>
       <c r="B58">
-        <v>232.81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+        <v>421.309</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46213.59375</v>
+        <v>46216.59375</v>
       </c>
       <c r="B59">
-        <v>238.26599999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+        <v>424.52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46213.604166666657</v>
+        <v>46216.60416666666</v>
       </c>
       <c r="B60">
-        <v>242.691</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+        <v>428.865</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46213.614583333343</v>
+        <v>46216.61458333334</v>
       </c>
       <c r="B61">
-        <v>247.779</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+        <v>430.604</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46213.625</v>
+        <v>46216.625</v>
       </c>
       <c r="B62">
-        <v>265.88299999999998</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+        <v>456.704</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46213.635416666657</v>
+        <v>46216.63541666666</v>
       </c>
       <c r="B63">
-        <v>272.48399999999998</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+        <v>459.863</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46213.645833333343</v>
+        <v>46216.64583333334</v>
       </c>
       <c r="B64">
-        <v>278.822</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+        <v>463.488</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46213.65625</v>
+        <v>46216.65625</v>
       </c>
       <c r="B65">
-        <v>283.62299999999999</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+        <v>466.337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46213.666666666657</v>
+        <v>46216.66666666666</v>
       </c>
       <c r="B66">
-        <v>282.18299999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>462.675</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46213.677083333343</v>
+        <v>46216.67708333334</v>
       </c>
       <c r="B67">
-        <v>281.642</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+        <v>460.284</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46213.6875</v>
+        <v>46216.6875</v>
       </c>
       <c r="B68">
-        <v>281.59699999999998</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+        <v>458.006</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46213.697916666657</v>
+        <v>46216.69791666666</v>
       </c>
       <c r="B69">
-        <v>281.39400000000001</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+        <v>455.679</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46213.708333333343</v>
+        <v>46216.70833333334</v>
       </c>
       <c r="B70">
-        <v>281.06200000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+        <v>460.176</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46213.71875</v>
+        <v>46216.71875</v>
       </c>
       <c r="B71">
-        <v>277.67</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+        <v>450.332</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46213.729166666657</v>
+        <v>46216.72916666666</v>
       </c>
       <c r="B72">
-        <v>274.173</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+        <v>440.992</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46213.739583333343</v>
+        <v>46216.73958333334</v>
       </c>
       <c r="B73">
-        <v>270.64699999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+        <v>431.643</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46213.75</v>
+        <v>46216.75</v>
       </c>
       <c r="B74">
-        <v>263.52999999999997</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+        <v>424.84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46213.760416666657</v>
+        <v>46216.76041666666</v>
       </c>
       <c r="B75">
-        <v>261.142</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+        <v>413.653</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46213.770833333343</v>
+        <v>46216.77083333334</v>
       </c>
       <c r="B76">
-        <v>259.59699999999998</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+        <v>402.696</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46213.78125</v>
+        <v>46216.78125</v>
       </c>
       <c r="B77">
-        <v>256.79500000000002</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+        <v>391.415</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46213.791666666657</v>
+        <v>46216.79166666666</v>
       </c>
       <c r="B78">
-        <v>223.89699999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+        <v>369.485</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46213.802083333343</v>
+        <v>46216.80208333334</v>
       </c>
       <c r="B79">
-        <v>229.71899999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+        <v>372.76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46213.8125</v>
+        <v>46216.8125</v>
       </c>
       <c r="B80">
-        <v>235.1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <v>375.197</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46213.822916666657</v>
+        <v>46216.82291666666</v>
       </c>
       <c r="B81">
-        <v>243.33</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>378.654</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46213.833333333343</v>
+        <v>46216.83333333334</v>
       </c>
       <c r="B82">
-        <v>245.28399999999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>392.976</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46213.84375</v>
+        <v>46216.84375</v>
       </c>
       <c r="B83">
-        <v>252.62200000000001</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>411.215</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46213.854166666657</v>
+        <v>46216.85416666666</v>
       </c>
       <c r="B84">
-        <v>261.22300000000001</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>428.155</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46213.864583333343</v>
+        <v>46216.86458333334</v>
       </c>
       <c r="B85">
-        <v>270.25</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>443.483</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46213.875</v>
+        <v>46216.875</v>
       </c>
       <c r="B86">
-        <v>279.84300000000002</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>467.508</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46213.885416666657</v>
+        <v>46216.88541666666</v>
       </c>
       <c r="B87">
-        <v>283.64999999999998</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <v>488.803</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46213.895833333343</v>
+        <v>46216.89583333334</v>
       </c>
       <c r="B88">
-        <v>287.62099999999998</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>510.856</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46213.90625</v>
+        <v>46216.90625</v>
       </c>
       <c r="B89">
-        <v>292.60399999999998</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>532.188</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46213.916666666657</v>
+        <v>46216.91666666666</v>
       </c>
       <c r="B90">
-        <v>295.14600000000002</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>558.942</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46213.927083333343</v>
+        <v>46216.92708333334</v>
       </c>
       <c r="B91">
-        <v>294.70800000000003</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>583.317</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46213.9375</v>
+        <v>46216.9375</v>
       </c>
       <c r="B92">
-        <v>295.61</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <v>608.278</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46213.947916666657</v>
+        <v>46216.94791666666</v>
       </c>
       <c r="B93">
-        <v>294.94</v>
+        <v>633.8339999999999</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_1B4445354128533B7EFE31D2F8375B061498E05B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E65628BA-0623-41EA-9FA8-42C23F7A4334}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B93"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,740 +425,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B2">
-        <v>423.957</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>733.73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46216.01041666666</v>
+        <v>46218.010416666657</v>
       </c>
       <c r="B3">
-        <v>416.548</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>748.15499999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46216.02083333334</v>
+        <v>46218.020833333343</v>
       </c>
       <c r="B4">
-        <v>407.141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>754.20399999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46216.03125</v>
+        <v>46218.03125</v>
       </c>
       <c r="B5">
-        <v>400.027</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>770.73599999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46216.04166666666</v>
+        <v>46218.041666666657</v>
       </c>
       <c r="B6">
-        <v>407.939</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>781.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46216.05208333334</v>
+        <v>46218.052083333343</v>
       </c>
       <c r="B7">
-        <v>405.446</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>789.17399999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46216.0625</v>
+        <v>46218.0625</v>
       </c>
       <c r="B8">
-        <v>405.455</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>805.84900000000005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46216.07291666666</v>
+        <v>46218.072916666657</v>
       </c>
       <c r="B9">
-        <v>406.583</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>816.42899999999997</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46216.08333333334</v>
+        <v>46218.083333333343</v>
       </c>
       <c r="B10">
-        <v>398.697</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>812.33100000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46216.09375</v>
+        <v>46218.09375</v>
       </c>
       <c r="B11">
-        <v>406.943</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>817.66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46216.10416666666</v>
+        <v>46218.104166666657</v>
       </c>
       <c r="B12">
-        <v>403.355</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>823.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46216.11458333334</v>
+        <v>46218.114583333343</v>
       </c>
       <c r="B13">
-        <v>399.372</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>830.39499999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46216.125</v>
+        <v>46218.125</v>
       </c>
       <c r="B14">
-        <v>389.303</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>818.91099999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46216.13541666666</v>
+        <v>46218.135416666657</v>
       </c>
       <c r="B15">
-        <v>393.037</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>826.92399999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46216.14583333334</v>
+        <v>46218.145833333343</v>
       </c>
       <c r="B16">
-        <v>373.918</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>832.42399999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46216.15625</v>
+        <v>46218.15625</v>
       </c>
       <c r="B17">
-        <v>360.961</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>833.12900000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46216.16666666666</v>
+        <v>46218.166666666657</v>
       </c>
       <c r="B18">
-        <v>345.899</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>782.40800000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46216.17708333334</v>
+        <v>46218.177083333343</v>
       </c>
       <c r="B19">
-        <v>341.361</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>773.63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46216.1875</v>
+        <v>46218.1875</v>
       </c>
       <c r="B20">
-        <v>340.995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>767.68399999999997</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46216.19791666666</v>
+        <v>46218.197916666657</v>
       </c>
       <c r="B21">
-        <v>341.131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>761.00199999999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46216.20833333334</v>
+        <v>46218.208333333343</v>
       </c>
       <c r="B22">
-        <v>353.375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>771.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46216.21875</v>
+        <v>46218.21875</v>
       </c>
       <c r="B23">
-        <v>344.757</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>749.45399999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46216.22916666666</v>
+        <v>46218.229166666657</v>
       </c>
       <c r="B24">
-        <v>334.664</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>727.00199999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46216.23958333334</v>
+        <v>46218.239583333343</v>
       </c>
       <c r="B25">
-        <v>325.652</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>710.14099999999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46216.25</v>
+        <v>46218.25</v>
       </c>
       <c r="B26">
-        <v>332.447</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>712.04100000000005</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46216.26041666666</v>
+        <v>46218.260416666657</v>
       </c>
       <c r="B27">
-        <v>329.939</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>668.73900000000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46216.27083333334</v>
+        <v>46218.270833333343</v>
       </c>
       <c r="B28">
-        <v>321.56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>626.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46216.28125</v>
+        <v>46218.28125</v>
       </c>
       <c r="B29">
-        <v>318.372</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>583.66399999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46216.29166666666</v>
+        <v>46218.291666666657</v>
       </c>
       <c r="B30">
-        <v>327.894</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>524.95000000000005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46216.30208333334</v>
+        <v>46218.302083333343</v>
       </c>
       <c r="B31">
-        <v>333.59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>510.34199999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46216.3125</v>
+        <v>46218.3125</v>
       </c>
       <c r="B32">
-        <v>339.881</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>496.17599999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46216.32291666666</v>
+        <v>46218.322916666657</v>
       </c>
       <c r="B33">
-        <v>360.848</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>479.935</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46216.33333333334</v>
+        <v>46218.333333333343</v>
       </c>
       <c r="B34">
-        <v>380.215</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>456.40800000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46216.34375</v>
+        <v>46218.34375</v>
       </c>
       <c r="B35">
-        <v>392.637</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>437.28800000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46216.35416666666</v>
+        <v>46218.354166666657</v>
       </c>
       <c r="B36">
-        <v>412.904</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>446.197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46216.36458333334</v>
+        <v>46218.364583333343</v>
       </c>
       <c r="B37">
-        <v>419.738</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>444.32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46216.375</v>
+        <v>46218.375</v>
       </c>
       <c r="B38">
-        <v>397.297</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>451.42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46216.38541666666</v>
+        <v>46218.385416666657</v>
       </c>
       <c r="B39">
-        <v>404.023</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>448.28699999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46216.39583333334</v>
+        <v>46218.395833333343</v>
       </c>
       <c r="B40">
-        <v>409.697</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>444.625</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46216.40625</v>
+        <v>46218.40625</v>
       </c>
       <c r="B41">
-        <v>415.275</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>441.74299999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46216.41666666666</v>
+        <v>46218.416666666657</v>
       </c>
       <c r="B42">
-        <v>403.791</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>456.15199999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46216.42708333334</v>
+        <v>46218.427083333343</v>
       </c>
       <c r="B43">
-        <v>406.629</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>451.69299999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46216.4375</v>
+        <v>46218.4375</v>
       </c>
       <c r="B44">
-        <v>408.349</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>447.16199999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46216.44791666666</v>
+        <v>46218.447916666657</v>
       </c>
       <c r="B45">
-        <v>409.673</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>442.64699999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46216.45833333334</v>
+        <v>46218.458333333343</v>
       </c>
       <c r="B46">
-        <v>410.6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>437.45499999999998</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46216.46875</v>
+        <v>46218.46875</v>
       </c>
       <c r="B47">
-        <v>409.149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>432.15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46216.47916666666</v>
+        <v>46218.479166666657</v>
       </c>
       <c r="B48">
-        <v>407.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>427.43400000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46216.48958333334</v>
+        <v>46218.489583333343</v>
       </c>
       <c r="B49">
-        <v>404.075</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>422.29300000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46216.5</v>
+        <v>46218.5</v>
       </c>
       <c r="B50">
-        <v>406.623</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>413.32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46216.51041666666</v>
+        <v>46218.510416666657</v>
       </c>
       <c r="B51">
-        <v>405.428</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>405.60500000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46216.52083333334</v>
+        <v>46218.520833333343</v>
       </c>
       <c r="B52">
-        <v>403.987</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>397.56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46216.53125</v>
+        <v>46218.53125</v>
       </c>
       <c r="B53">
-        <v>403.899</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>389.375</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46216.54166666666</v>
+        <v>46218.541666666657</v>
       </c>
       <c r="B54">
-        <v>404.761</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>375.01600000000002</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46216.55208333334</v>
+        <v>46218.552083333343</v>
       </c>
       <c r="B55">
-        <v>406.682</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>369.928</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46216.5625</v>
+        <v>46218.5625</v>
       </c>
       <c r="B56">
-        <v>409.076</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>364.678</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46216.57291666666</v>
+        <v>46218.572916666657</v>
       </c>
       <c r="B57">
-        <v>411.401</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>359.221</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46216.58333333334</v>
+        <v>46218.583333333343</v>
       </c>
       <c r="B58">
-        <v>421.309</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>332.17700000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46216.59375</v>
+        <v>46218.59375</v>
       </c>
       <c r="B59">
-        <v>424.52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>328.274</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46216.60416666666</v>
+        <v>46218.604166666657</v>
       </c>
       <c r="B60">
-        <v>428.865</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>324.43900000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46216.61458333334</v>
+        <v>46218.614583333343</v>
       </c>
       <c r="B61">
-        <v>430.604</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>320.79700000000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46216.625</v>
+        <v>46218.625</v>
       </c>
       <c r="B62">
-        <v>456.704</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>325.29199999999997</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46216.63541666666</v>
+        <v>46218.635416666657</v>
       </c>
       <c r="B63">
-        <v>459.863</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>320.197</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46216.64583333334</v>
+        <v>46218.645833333343</v>
       </c>
       <c r="B64">
-        <v>463.488</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>315.41300000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46216.65625</v>
+        <v>46218.65625</v>
       </c>
       <c r="B65">
-        <v>466.337</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>310.33</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46216.66666666666</v>
+        <v>46218.666666666657</v>
       </c>
       <c r="B66">
-        <v>462.675</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>297.96600000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46216.67708333334</v>
+        <v>46218.677083333343</v>
       </c>
       <c r="B67">
-        <v>460.284</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>293.90699999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46216.6875</v>
+        <v>46218.6875</v>
       </c>
       <c r="B68">
-        <v>458.006</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>290.53100000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46216.69791666666</v>
+        <v>46218.697916666657</v>
       </c>
       <c r="B69">
-        <v>455.679</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>286.774</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46216.70833333334</v>
+        <v>46218.708333333343</v>
       </c>
       <c r="B70">
-        <v>460.176</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>277.05099999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46216.71875</v>
+        <v>46218.71875</v>
       </c>
       <c r="B71">
-        <v>450.332</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>269.22300000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46216.72916666666</v>
+        <v>46218.729166666657</v>
       </c>
       <c r="B72">
-        <v>440.992</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>261.34399999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46216.73958333334</v>
+        <v>46218.739583333343</v>
       </c>
       <c r="B73">
-        <v>431.643</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>254.18100000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46216.75</v>
+        <v>46218.75</v>
       </c>
       <c r="B74">
-        <v>424.84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>248.547</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46216.76041666666</v>
+        <v>46218.760416666657</v>
       </c>
       <c r="B75">
-        <v>413.653</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>245.71199999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46216.77083333334</v>
+        <v>46218.770833333343</v>
       </c>
       <c r="B76">
-        <v>402.696</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>242.733</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46216.78125</v>
+        <v>46218.78125</v>
       </c>
       <c r="B77">
-        <v>391.415</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>239.66900000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46216.79166666666</v>
+        <v>46218.791666666657</v>
       </c>
       <c r="B78">
-        <v>369.485</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>237.96600000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46216.80208333334</v>
+        <v>46218.802083333343</v>
       </c>
       <c r="B79">
-        <v>372.76</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>240.19200000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46216.8125</v>
+        <v>46218.8125</v>
       </c>
       <c r="B80">
-        <v>375.197</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>243.21799999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46216.82291666666</v>
+        <v>46218.822916666657</v>
       </c>
       <c r="B81">
-        <v>378.654</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>246.34</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46216.83333333334</v>
+        <v>46218.833333333343</v>
       </c>
       <c r="B82">
-        <v>392.976</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>249.203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46216.84375</v>
+        <v>46218.84375</v>
       </c>
       <c r="B83">
-        <v>411.215</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>248.57499999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46216.85416666666</v>
+        <v>46218.854166666657</v>
       </c>
       <c r="B84">
-        <v>428.155</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>247.297</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46216.86458333334</v>
+        <v>46218.864583333343</v>
       </c>
       <c r="B85">
-        <v>443.483</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>247.19200000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46216.875</v>
+        <v>46218.875</v>
       </c>
       <c r="B86">
-        <v>467.508</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>249.011</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46216.88541666666</v>
+        <v>46218.885416666657</v>
       </c>
       <c r="B87">
-        <v>488.803</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>247.90899999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46216.89583333334</v>
+        <v>46218.895833333343</v>
       </c>
       <c r="B88">
-        <v>510.856</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>246.232</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46216.90625</v>
+        <v>46218.90625</v>
       </c>
       <c r="B89">
-        <v>532.188</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>245.35599999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>46216.91666666666</v>
+        <v>46218.916666666657</v>
       </c>
       <c r="B90">
-        <v>558.942</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>243.37100000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>46216.92708333334</v>
+        <v>46218.927083333343</v>
       </c>
       <c r="B91">
-        <v>583.317</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>242.46700000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>46216.9375</v>
+        <v>46218.9375</v>
       </c>
       <c r="B92">
-        <v>608.278</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>241.44200000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>46216.94791666666</v>
+        <v>46218.947916666657</v>
       </c>
       <c r="B93">
-        <v>633.8339999999999</v>
+        <v>240.495</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_1B4445354128533B7EFE31D2F8375B061498E05B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E65628BA-0623-41EA-9FA8-42C23F7A4334}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,740 +392,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B2">
-        <v>733.73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>280.286</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46218.010416666657</v>
+        <v>46219.01041666666</v>
       </c>
       <c r="B3">
-        <v>748.15499999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>286.179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46218.020833333343</v>
+        <v>46219.02083333334</v>
       </c>
       <c r="B4">
-        <v>754.20399999999995</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>301.466</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46218.03125</v>
+        <v>46219.03125</v>
       </c>
       <c r="B5">
-        <v>770.73599999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>303.633</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46218.041666666657</v>
+        <v>46219.04166666666</v>
       </c>
       <c r="B6">
-        <v>781.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>304.43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46218.052083333343</v>
+        <v>46219.05208333334</v>
       </c>
       <c r="B7">
-        <v>789.17399999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>321.524</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46218.0625</v>
+        <v>46219.0625</v>
       </c>
       <c r="B8">
-        <v>805.84900000000005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>335.091</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46218.072916666657</v>
+        <v>46219.07291666666</v>
       </c>
       <c r="B9">
-        <v>816.42899999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>347.145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46218.083333333343</v>
+        <v>46219.08333333334</v>
       </c>
       <c r="B10">
-        <v>812.33100000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>359.914</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46218.09375</v>
+        <v>46219.09375</v>
       </c>
       <c r="B11">
-        <v>817.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>373.36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46218.104166666657</v>
+        <v>46219.10416666666</v>
       </c>
       <c r="B12">
-        <v>823.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>382.526</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46218.114583333343</v>
+        <v>46219.11458333334</v>
       </c>
       <c r="B13">
-        <v>830.39499999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>381.501</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46218.125</v>
+        <v>46219.125</v>
       </c>
       <c r="B14">
-        <v>818.91099999999994</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>382.158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46218.135416666657</v>
+        <v>46219.13541666666</v>
       </c>
       <c r="B15">
-        <v>826.92399999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>387.892</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46218.145833333343</v>
+        <v>46219.14583333334</v>
       </c>
       <c r="B16">
-        <v>832.42399999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>397.298</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46218.15625</v>
+        <v>46219.15625</v>
       </c>
       <c r="B17">
-        <v>833.12900000000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>410.146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46218.166666666657</v>
+        <v>46219.16666666666</v>
       </c>
       <c r="B18">
-        <v>782.40800000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>408.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46218.177083333343</v>
+        <v>46219.17708333334</v>
       </c>
       <c r="B19">
-        <v>773.63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>411.516</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46218.1875</v>
+        <v>46219.1875</v>
       </c>
       <c r="B20">
-        <v>767.68399999999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>421.025</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46218.197916666657</v>
+        <v>46219.19791666666</v>
       </c>
       <c r="B21">
-        <v>761.00199999999995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>422.961</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46218.208333333343</v>
+        <v>46219.20833333334</v>
       </c>
       <c r="B22">
-        <v>771.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>408.233</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46218.21875</v>
+        <v>46219.21875</v>
       </c>
       <c r="B23">
-        <v>749.45399999999995</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>402.064</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46218.229166666657</v>
+        <v>46219.22916666666</v>
       </c>
       <c r="B24">
-        <v>727.00199999999995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>398.647</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46218.239583333343</v>
+        <v>46219.23958333334</v>
       </c>
       <c r="B25">
-        <v>710.14099999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>397.03</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46218.25</v>
+        <v>46219.25</v>
       </c>
       <c r="B26">
-        <v>712.04100000000005</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>384.665</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46218.260416666657</v>
+        <v>46219.26041666666</v>
       </c>
       <c r="B27">
-        <v>668.73900000000003</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>363.123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46218.270833333343</v>
+        <v>46219.27083333334</v>
       </c>
       <c r="B28">
-        <v>626.02</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>339.263</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46218.28125</v>
+        <v>46219.28125</v>
       </c>
       <c r="B29">
-        <v>583.66399999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>317.075</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46218.291666666657</v>
+        <v>46219.29166666666</v>
       </c>
       <c r="B30">
-        <v>524.95000000000005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>293.996</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46218.302083333343</v>
+        <v>46219.30208333334</v>
       </c>
       <c r="B31">
-        <v>510.34199999999998</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>267.461</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46218.3125</v>
+        <v>46219.3125</v>
       </c>
       <c r="B32">
-        <v>496.17599999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>244.517</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46218.322916666657</v>
+        <v>46219.32291666666</v>
       </c>
       <c r="B33">
-        <v>479.935</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>219.359</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46218.333333333343</v>
+        <v>46219.33333333334</v>
       </c>
       <c r="B34">
-        <v>456.40800000000002</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.459</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46218.34375</v>
+        <v>46219.34375</v>
       </c>
       <c r="B35">
-        <v>437.28800000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>197.968</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46218.354166666657</v>
+        <v>46219.35416666666</v>
       </c>
       <c r="B36">
-        <v>446.197</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>193.293</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46218.364583333343</v>
+        <v>46219.36458333334</v>
       </c>
       <c r="B37">
-        <v>444.32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>190.275</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46218.375</v>
+        <v>46219.375</v>
       </c>
       <c r="B38">
-        <v>451.42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>212.287</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46218.385416666657</v>
+        <v>46219.38541666666</v>
       </c>
       <c r="B39">
-        <v>448.28699999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.069</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46218.395833333343</v>
+        <v>46219.39583333334</v>
       </c>
       <c r="B40">
-        <v>444.625</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>215.124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46218.40625</v>
+        <v>46219.40625</v>
       </c>
       <c r="B41">
-        <v>441.74299999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>216.623</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46218.416666666657</v>
+        <v>46219.41666666666</v>
       </c>
       <c r="B42">
-        <v>456.15199999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>219.923</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46218.427083333343</v>
+        <v>46219.42708333334</v>
       </c>
       <c r="B43">
-        <v>451.69299999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>221.017</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46218.4375</v>
+        <v>46219.4375</v>
       </c>
       <c r="B44">
-        <v>447.16199999999998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>222.999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46218.447916666657</v>
+        <v>46219.44791666666</v>
       </c>
       <c r="B45">
-        <v>442.64699999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>224.531</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46218.458333333343</v>
+        <v>46219.45833333334</v>
       </c>
       <c r="B46">
-        <v>437.45499999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>230.399</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46218.46875</v>
+        <v>46219.46875</v>
       </c>
       <c r="B47">
-        <v>432.15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>230.558</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46218.479166666657</v>
+        <v>46219.47916666666</v>
       </c>
       <c r="B48">
-        <v>427.43400000000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>231.036</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46218.489583333343</v>
+        <v>46219.48958333334</v>
       </c>
       <c r="B49">
-        <v>422.29300000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>231.775</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46218.5</v>
+        <v>46219.5</v>
       </c>
       <c r="B50">
-        <v>413.32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>233.279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46218.510416666657</v>
+        <v>46219.51041666666</v>
       </c>
       <c r="B51">
-        <v>405.60500000000002</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+        <v>234.448</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46218.520833333343</v>
+        <v>46219.52083333334</v>
       </c>
       <c r="B52">
-        <v>397.56</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+        <v>235.806</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46218.53125</v>
+        <v>46219.53125</v>
       </c>
       <c r="B53">
-        <v>389.375</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+        <v>236.795</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46218.541666666657</v>
+        <v>46219.54166666666</v>
       </c>
       <c r="B54">
-        <v>375.01600000000002</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+        <v>236.896</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46218.552083333343</v>
+        <v>46219.55208333334</v>
       </c>
       <c r="B55">
-        <v>369.928</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+        <v>239.329</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46218.5625</v>
+        <v>46219.5625</v>
       </c>
       <c r="B56">
-        <v>364.678</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>242.879</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46218.572916666657</v>
+        <v>46219.57291666666</v>
       </c>
       <c r="B57">
-        <v>359.221</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>246.774</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46218.583333333343</v>
+        <v>46219.58333333334</v>
       </c>
       <c r="B58">
-        <v>332.17700000000002</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>257.043</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46218.59375</v>
+        <v>46219.59375</v>
       </c>
       <c r="B59">
-        <v>328.274</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>260.699</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46218.604166666657</v>
+        <v>46219.60416666666</v>
       </c>
       <c r="B60">
-        <v>324.43900000000002</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>263.558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46218.614583333343</v>
+        <v>46219.61458333334</v>
       </c>
       <c r="B61">
-        <v>320.79700000000003</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+        <v>266.189</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46218.625</v>
+        <v>46219.625</v>
       </c>
       <c r="B62">
-        <v>325.29199999999997</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+        <v>255.849</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46218.635416666657</v>
+        <v>46219.63541666666</v>
       </c>
       <c r="B63">
-        <v>320.197</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+        <v>259.793</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46218.645833333343</v>
+        <v>46219.64583333334</v>
       </c>
       <c r="B64">
-        <v>315.41300000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>264.154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46218.65625</v>
+        <v>46219.65625</v>
       </c>
       <c r="B65">
-        <v>310.33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+        <v>267.869</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46218.666666666657</v>
+        <v>46219.66666666666</v>
       </c>
       <c r="B66">
-        <v>297.96600000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+        <v>269.709</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46218.677083333343</v>
+        <v>46219.67708333334</v>
       </c>
       <c r="B67">
-        <v>293.90699999999998</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+        <v>269.769</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46218.6875</v>
+        <v>46219.6875</v>
       </c>
       <c r="B68">
-        <v>290.53100000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+        <v>269.081</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46218.697916666657</v>
+        <v>46219.69791666666</v>
       </c>
       <c r="B69">
-        <v>286.774</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+        <v>267.766</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46218.708333333343</v>
+        <v>46219.70833333334</v>
       </c>
       <c r="B70">
-        <v>277.05099999999999</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+        <v>258.798</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46218.71875</v>
+        <v>46219.71875</v>
       </c>
       <c r="B71">
-        <v>269.22300000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>255.237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46218.729166666657</v>
+        <v>46219.72916666666</v>
       </c>
       <c r="B72">
-        <v>261.34399999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+        <v>251.847</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46218.739583333343</v>
+        <v>46219.73958333334</v>
       </c>
       <c r="B73">
-        <v>254.18100000000001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+        <v>248.921</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46218.75</v>
+        <v>46219.75</v>
       </c>
       <c r="B74">
-        <v>248.547</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+        <v>232.197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46218.760416666657</v>
+        <v>46219.76041666666</v>
       </c>
       <c r="B75">
-        <v>245.71199999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+        <v>231.868</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46218.770833333343</v>
+        <v>46219.77083333334</v>
       </c>
       <c r="B76">
-        <v>242.733</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+        <v>231.598</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46218.78125</v>
+        <v>46219.78125</v>
       </c>
       <c r="B77">
-        <v>239.66900000000001</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+        <v>232.261</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46218.791666666657</v>
+        <v>46219.79166666666</v>
       </c>
       <c r="B78">
-        <v>237.96600000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>234.855</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46218.802083333343</v>
+        <v>46219.80208333334</v>
       </c>
       <c r="B79">
-        <v>240.19200000000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+        <v>235.506</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46218.8125</v>
+        <v>46219.8125</v>
       </c>
       <c r="B80">
-        <v>243.21799999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+        <v>238.229</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46218.822916666657</v>
+        <v>46219.82291666666</v>
       </c>
       <c r="B81">
-        <v>246.34</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+        <v>240.084</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46218.833333333343</v>
+        <v>46219.83333333334</v>
       </c>
       <c r="B82">
-        <v>249.203</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+        <v>248.451</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46218.84375</v>
+        <v>46219.84375</v>
       </c>
       <c r="B83">
-        <v>248.57499999999999</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+        <v>256.585</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46218.854166666657</v>
+        <v>46219.85416666666</v>
       </c>
       <c r="B84">
-        <v>247.297</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+        <v>265.827</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46218.864583333343</v>
+        <v>46219.86458333334</v>
       </c>
       <c r="B85">
-        <v>247.19200000000001</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+        <v>273.39</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46218.875</v>
+        <v>46219.875</v>
       </c>
       <c r="B86">
-        <v>249.011</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+        <v>304.998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46218.885416666657</v>
+        <v>46219.88541666666</v>
       </c>
       <c r="B87">
-        <v>247.90899999999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+        <v>316.129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46218.895833333343</v>
+        <v>46219.89583333334</v>
       </c>
       <c r="B88">
-        <v>246.232</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+        <v>325.108</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46218.90625</v>
+        <v>46219.90625</v>
       </c>
       <c r="B89">
-        <v>245.35599999999999</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+        <v>335.176</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46218.916666666657</v>
+        <v>46219.91666666666</v>
       </c>
       <c r="B90">
-        <v>243.37100000000001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+        <v>350.367</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46218.927083333343</v>
+        <v>46219.92708333334</v>
       </c>
       <c r="B91">
-        <v>242.46700000000001</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+        <v>360.474</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46218.9375</v>
+        <v>46219.9375</v>
       </c>
       <c r="B92">
-        <v>241.44200000000001</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+        <v>368.423</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46218.947916666657</v>
+        <v>46219.94791666666</v>
       </c>
       <c r="B93">
-        <v>240.495</v>
+        <v>377.94</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B2">
-        <v>280.286</v>
+        <v>938.553</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46219.01041666666</v>
+        <v>46223.01041666666</v>
       </c>
       <c r="B3">
-        <v>286.179</v>
+        <v>920.554</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46219.02083333334</v>
+        <v>46223.02083333334</v>
       </c>
       <c r="B4">
-        <v>301.466</v>
+        <v>904.029</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46219.03125</v>
+        <v>46223.03125</v>
       </c>
       <c r="B5">
-        <v>303.633</v>
+        <v>893.747</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46219.04166666666</v>
+        <v>46223.04166666666</v>
       </c>
       <c r="B6">
-        <v>304.43</v>
+        <v>861.2910000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46219.05208333334</v>
+        <v>46223.05208333334</v>
       </c>
       <c r="B7">
-        <v>321.524</v>
+        <v>847.641</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46219.0625</v>
+        <v>46223.0625</v>
       </c>
       <c r="B8">
-        <v>335.091</v>
+        <v>828.013</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46219.07291666666</v>
+        <v>46223.07291666666</v>
       </c>
       <c r="B9">
-        <v>347.145</v>
+        <v>816.129</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46219.08333333334</v>
+        <v>46223.08333333334</v>
       </c>
       <c r="B10">
-        <v>359.914</v>
+        <v>813.974</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46219.09375</v>
+        <v>46223.09375</v>
       </c>
       <c r="B11">
-        <v>373.36</v>
+        <v>796.501</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46219.10416666666</v>
+        <v>46223.10416666666</v>
       </c>
       <c r="B12">
-        <v>382.526</v>
+        <v>779.55</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46219.11458333334</v>
+        <v>46223.11458333334</v>
       </c>
       <c r="B13">
-        <v>381.501</v>
+        <v>755.379</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46219.125</v>
+        <v>46223.125</v>
       </c>
       <c r="B14">
-        <v>382.158</v>
+        <v>734.694</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46219.13541666666</v>
+        <v>46223.13541666666</v>
       </c>
       <c r="B15">
-        <v>387.892</v>
+        <v>697.351</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46219.14583333334</v>
+        <v>46223.14583333334</v>
       </c>
       <c r="B16">
-        <v>397.298</v>
+        <v>678.553</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46219.15625</v>
+        <v>46223.15625</v>
       </c>
       <c r="B17">
-        <v>410.146</v>
+        <v>660.923</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46219.16666666666</v>
+        <v>46223.16666666666</v>
       </c>
       <c r="B18">
-        <v>408.6</v>
+        <v>660.432</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46219.17708333334</v>
+        <v>46223.17708333334</v>
       </c>
       <c r="B19">
-        <v>411.516</v>
+        <v>648.326</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46219.1875</v>
+        <v>46223.1875</v>
       </c>
       <c r="B20">
-        <v>421.025</v>
+        <v>630.076</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46219.19791666666</v>
+        <v>46223.19791666666</v>
       </c>
       <c r="B21">
-        <v>422.961</v>
+        <v>617.187</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46219.20833333334</v>
+        <v>46223.20833333334</v>
       </c>
       <c r="B22">
-        <v>408.233</v>
+        <v>575.8440000000001</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46219.21875</v>
+        <v>46223.21875</v>
       </c>
       <c r="B23">
-        <v>402.064</v>
+        <v>560.886</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46219.22916666666</v>
+        <v>46223.22916666666</v>
       </c>
       <c r="B24">
-        <v>398.647</v>
+        <v>549.2619999999999</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46219.23958333334</v>
+        <v>46223.23958333334</v>
       </c>
       <c r="B25">
-        <v>397.03</v>
+        <v>538.705</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46219.25</v>
+        <v>46223.25</v>
       </c>
       <c r="B26">
-        <v>384.665</v>
+        <v>526.856</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46219.26041666666</v>
+        <v>46223.26041666666</v>
       </c>
       <c r="B27">
-        <v>363.123</v>
+        <v>507.083</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46219.27083333334</v>
+        <v>46223.27083333334</v>
       </c>
       <c r="B28">
-        <v>339.263</v>
+        <v>487.018</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46219.28125</v>
+        <v>46223.28125</v>
       </c>
       <c r="B29">
-        <v>317.075</v>
+        <v>471.341</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46219.29166666666</v>
+        <v>46223.29166666666</v>
       </c>
       <c r="B30">
-        <v>293.996</v>
+        <v>461.151</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46219.30208333334</v>
+        <v>46223.30208333334</v>
       </c>
       <c r="B31">
-        <v>267.461</v>
+        <v>460.63</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46219.3125</v>
+        <v>46223.3125</v>
       </c>
       <c r="B32">
-        <v>244.517</v>
+        <v>453.984</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46219.32291666666</v>
+        <v>46223.32291666666</v>
       </c>
       <c r="B33">
-        <v>219.359</v>
+        <v>452.607</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46219.33333333334</v>
+        <v>46223.33333333334</v>
       </c>
       <c r="B34">
-        <v>214.459</v>
+        <v>431.444</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46219.34375</v>
+        <v>46223.34375</v>
       </c>
       <c r="B35">
-        <v>197.968</v>
+        <v>437.933</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46219.35416666666</v>
+        <v>46223.35416666666</v>
       </c>
       <c r="B36">
-        <v>193.293</v>
+        <v>453.243</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46219.36458333334</v>
+        <v>46223.36458333334</v>
       </c>
       <c r="B37">
-        <v>190.275</v>
+        <v>461.506</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46219.375</v>
+        <v>46223.375</v>
       </c>
       <c r="B38">
-        <v>212.287</v>
+        <v>488.923</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46219.38541666666</v>
+        <v>46223.38541666666</v>
       </c>
       <c r="B39">
-        <v>214.069</v>
+        <v>501.785</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46219.39583333334</v>
+        <v>46223.39583333334</v>
       </c>
       <c r="B40">
-        <v>215.124</v>
+        <v>510.693</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46219.40625</v>
+        <v>46223.40625</v>
       </c>
       <c r="B41">
-        <v>216.623</v>
+        <v>519.486</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46219.41666666666</v>
+        <v>46223.41666666666</v>
       </c>
       <c r="B42">
-        <v>219.923</v>
+        <v>593.5359999999999</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46219.42708333334</v>
+        <v>46223.42708333334</v>
       </c>
       <c r="B43">
-        <v>221.017</v>
+        <v>606.47</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46219.4375</v>
+        <v>46223.4375</v>
       </c>
       <c r="B44">
-        <v>222.999</v>
+        <v>620.311</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46219.44791666666</v>
+        <v>46223.44791666666</v>
       </c>
       <c r="B45">
-        <v>224.531</v>
+        <v>632.775</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46219.45833333334</v>
+        <v>46223.45833333334</v>
       </c>
       <c r="B46">
-        <v>230.399</v>
+        <v>633.8</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46219.46875</v>
+        <v>46223.46875</v>
       </c>
       <c r="B47">
-        <v>230.558</v>
+        <v>648.787</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46219.47916666666</v>
+        <v>46223.47916666666</v>
       </c>
       <c r="B48">
-        <v>231.036</v>
+        <v>664.124</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46219.48958333334</v>
+        <v>46223.48958333334</v>
       </c>
       <c r="B49">
-        <v>231.775</v>
+        <v>678.731</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46219.5</v>
+        <v>46223.5</v>
       </c>
       <c r="B50">
-        <v>233.279</v>
+        <v>693.4589999999999</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46219.51041666666</v>
+        <v>46223.51041666666</v>
       </c>
       <c r="B51">
-        <v>234.448</v>
+        <v>709.093</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46219.52083333334</v>
+        <v>46223.52083333334</v>
       </c>
       <c r="B52">
-        <v>235.806</v>
+        <v>721.7809999999999</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46219.53125</v>
+        <v>46223.53125</v>
       </c>
       <c r="B53">
-        <v>236.795</v>
+        <v>734.276</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46219.54166666666</v>
+        <v>46223.54166666666</v>
       </c>
       <c r="B54">
-        <v>236.896</v>
+        <v>748.628</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46219.55208333334</v>
+        <v>46223.55208333334</v>
       </c>
       <c r="B55">
-        <v>239.329</v>
+        <v>762.576</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46219.5625</v>
+        <v>46223.5625</v>
       </c>
       <c r="B56">
-        <v>242.879</v>
+        <v>775.723</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46219.57291666666</v>
+        <v>46223.57291666666</v>
       </c>
       <c r="B57">
-        <v>246.774</v>
+        <v>785.694</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46219.58333333334</v>
+        <v>46223.58333333334</v>
       </c>
       <c r="B58">
-        <v>257.043</v>
+        <v>776.782</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46219.59375</v>
+        <v>46223.59375</v>
       </c>
       <c r="B59">
-        <v>260.699</v>
+        <v>781.97</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46219.60416666666</v>
+        <v>46223.60416666666</v>
       </c>
       <c r="B60">
-        <v>263.558</v>
+        <v>787.731</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46219.61458333334</v>
+        <v>46223.61458333334</v>
       </c>
       <c r="B61">
-        <v>266.189</v>
+        <v>794.71</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46219.625</v>
+        <v>46223.625</v>
       </c>
       <c r="B62">
-        <v>255.849</v>
+        <v>804.864</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46219.63541666666</v>
+        <v>46223.63541666666</v>
       </c>
       <c r="B63">
-        <v>259.793</v>
+        <v>803.404</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46219.64583333334</v>
+        <v>46223.64583333334</v>
       </c>
       <c r="B64">
-        <v>264.154</v>
+        <v>802.14</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46219.65625</v>
+        <v>46223.65625</v>
       </c>
       <c r="B65">
-        <v>267.869</v>
+        <v>799.121</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46219.66666666666</v>
+        <v>46223.66666666666</v>
       </c>
       <c r="B66">
-        <v>269.709</v>
+        <v>774.3390000000001</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46219.67708333334</v>
+        <v>46223.67708333334</v>
       </c>
       <c r="B67">
-        <v>269.769</v>
+        <v>752.812</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46219.6875</v>
+        <v>46223.6875</v>
       </c>
       <c r="B68">
-        <v>269.081</v>
+        <v>731.249</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46219.69791666666</v>
+        <v>46223.69791666666</v>
       </c>
       <c r="B69">
-        <v>267.766</v>
+        <v>709.8339999999999</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46219.70833333334</v>
+        <v>46223.70833333334</v>
       </c>
       <c r="B70">
-        <v>258.798</v>
+        <v>687.207</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46219.71875</v>
+        <v>46223.71875</v>
       </c>
       <c r="B71">
-        <v>255.237</v>
+        <v>665.2809999999999</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46219.72916666666</v>
+        <v>46223.72916666666</v>
       </c>
       <c r="B72">
-        <v>251.847</v>
+        <v>644.289</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46219.73958333334</v>
+        <v>46223.73958333334</v>
       </c>
       <c r="B73">
-        <v>248.921</v>
+        <v>625.122</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46219.75</v>
+        <v>46223.75</v>
       </c>
       <c r="B74">
-        <v>232.197</v>
+        <v>507.658</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46219.76041666666</v>
+        <v>46223.76041666666</v>
       </c>
       <c r="B75">
-        <v>231.868</v>
+        <v>483.976</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46219.77083333334</v>
+        <v>46223.77083333334</v>
       </c>
       <c r="B76">
-        <v>231.598</v>
+        <v>459.82</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46219.78125</v>
+        <v>46223.78125</v>
       </c>
       <c r="B77">
-        <v>232.261</v>
+        <v>434.93</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46219.79166666666</v>
+        <v>46223.79166666666</v>
       </c>
       <c r="B78">
-        <v>234.855</v>
+        <v>414.592</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46219.80208333334</v>
+        <v>46223.80208333334</v>
       </c>
       <c r="B79">
-        <v>235.506</v>
+        <v>397.789</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46219.8125</v>
+        <v>46223.8125</v>
       </c>
       <c r="B80">
-        <v>238.229</v>
+        <v>385.413</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46219.82291666666</v>
+        <v>46223.82291666666</v>
       </c>
       <c r="B81">
-        <v>240.084</v>
+        <v>371.53</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46219.83333333334</v>
+        <v>46223.83333333334</v>
       </c>
       <c r="B82">
-        <v>248.451</v>
+        <v>357.557</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46219.84375</v>
+        <v>46223.84375</v>
       </c>
       <c r="B83">
-        <v>256.585</v>
+        <v>349.363</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46219.85416666666</v>
+        <v>46223.85416666666</v>
       </c>
       <c r="B84">
-        <v>265.827</v>
+        <v>342.34</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46219.86458333334</v>
+        <v>46223.86458333334</v>
       </c>
       <c r="B85">
-        <v>273.39</v>
+        <v>334.816</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46219.875</v>
+        <v>46223.875</v>
       </c>
       <c r="B86">
-        <v>304.998</v>
+        <v>316.605</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46219.88541666666</v>
+        <v>46223.88541666666</v>
       </c>
       <c r="B87">
-        <v>316.129</v>
+        <v>312.312</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46219.89583333334</v>
+        <v>46223.89583333334</v>
       </c>
       <c r="B88">
-        <v>325.108</v>
+        <v>309.031</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46219.90625</v>
+        <v>46223.90625</v>
       </c>
       <c r="B89">
-        <v>335.176</v>
+        <v>305.255</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46219.91666666666</v>
+        <v>46223.91666666666</v>
       </c>
       <c r="B90">
-        <v>350.367</v>
+        <v>351.023</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46219.92708333334</v>
+        <v>46223.92708333334</v>
       </c>
       <c r="B91">
-        <v>360.474</v>
+        <v>352.214</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46219.9375</v>
+        <v>46223.9375</v>
       </c>
       <c r="B92">
-        <v>368.423</v>
+        <v>353.928</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46219.94791666666</v>
+        <v>46223.94791666666</v>
       </c>
       <c r="B93">
-        <v>377.94</v>
+        <v>354.85</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_FA5745354700970902FF31D2F8375B0674908F23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{263ED5FA-E1B5-40F9-AD09-088EB7E5EEC2}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -25,11 +44,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,13 +112,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -137,7 +164,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -171,6 +198,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -205,9 +233,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -380,11 +409,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B93"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,740 +425,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B2">
-        <v>938.553</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>1429.085</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>46223.01041666666</v>
+        <v>46226.010416666657</v>
       </c>
       <c r="B3">
-        <v>920.554</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>1453.2449999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46223.02083333334</v>
+        <v>46226.020833333343</v>
       </c>
       <c r="B4">
-        <v>904.029</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>1481.038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>46223.03125</v>
+        <v>46226.03125</v>
       </c>
       <c r="B5">
-        <v>893.747</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>1492.365</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
-        <v>46223.04166666666</v>
+        <v>46226.041666666657</v>
       </c>
       <c r="B6">
-        <v>861.2910000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>1512.2919999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>46223.05208333334</v>
+        <v>46226.052083333343</v>
       </c>
       <c r="B7">
-        <v>847.641</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>1543.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>46223.0625</v>
+        <v>46226.0625</v>
       </c>
       <c r="B8">
-        <v>828.013</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>1575.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>46223.07291666666</v>
+        <v>46226.072916666657</v>
       </c>
       <c r="B9">
-        <v>816.129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>1601.2270000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>46223.08333333334</v>
+        <v>46226.083333333343</v>
       </c>
       <c r="B10">
-        <v>813.974</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>1576.567</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>46223.09375</v>
+        <v>46226.09375</v>
       </c>
       <c r="B11">
-        <v>796.501</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>1574.7090000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>46223.10416666666</v>
+        <v>46226.104166666657</v>
       </c>
       <c r="B12">
-        <v>779.55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>1581.079</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>46223.11458333334</v>
+        <v>46226.114583333343</v>
       </c>
       <c r="B13">
-        <v>755.379</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>1585.806</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>46223.125</v>
+        <v>46226.125</v>
       </c>
       <c r="B14">
-        <v>734.694</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>1607.6220000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>46223.13541666666</v>
+        <v>46226.135416666657</v>
       </c>
       <c r="B15">
-        <v>697.351</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>1592.0640000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>46223.14583333334</v>
+        <v>46226.145833333343</v>
       </c>
       <c r="B16">
-        <v>678.553</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>1566.7639999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>46223.15625</v>
+        <v>46226.15625</v>
       </c>
       <c r="B17">
-        <v>660.923</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>1552.7460000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>46223.16666666666</v>
+        <v>46226.166666666657</v>
       </c>
       <c r="B18">
-        <v>660.432</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>1562.6780000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>46223.17708333334</v>
+        <v>46226.177083333343</v>
       </c>
       <c r="B19">
-        <v>648.326</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>1550.2159999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>46223.1875</v>
+        <v>46226.1875</v>
       </c>
       <c r="B20">
-        <v>630.076</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>1533.7360000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>46223.19791666666</v>
+        <v>46226.197916666657</v>
       </c>
       <c r="B21">
-        <v>617.187</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>1534.269</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>46223.20833333334</v>
+        <v>46226.208333333343</v>
       </c>
       <c r="B22">
-        <v>575.8440000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>1504.3040000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>46223.21875</v>
+        <v>46226.21875</v>
       </c>
       <c r="B23">
-        <v>560.886</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>1519.5229999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>46223.22916666666</v>
+        <v>46226.229166666657</v>
       </c>
       <c r="B24">
-        <v>549.2619999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+        <v>1524.193</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>46223.23958333334</v>
+        <v>46226.239583333343</v>
       </c>
       <c r="B25">
-        <v>538.705</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>1538.922</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>46223.25</v>
+        <v>46226.25</v>
       </c>
       <c r="B26">
-        <v>526.856</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>1520.4459999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>46223.26041666666</v>
+        <v>46226.260416666657</v>
       </c>
       <c r="B27">
-        <v>507.083</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>1505.9670000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>46223.27083333334</v>
+        <v>46226.270833333343</v>
       </c>
       <c r="B28">
-        <v>487.018</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>1498.193</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>46223.28125</v>
+        <v>46226.28125</v>
       </c>
       <c r="B29">
-        <v>471.341</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>1484.337</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>46223.29166666666</v>
+        <v>46226.291666666657</v>
       </c>
       <c r="B30">
-        <v>461.151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>1405.9380000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>46223.30208333334</v>
+        <v>46226.302083333343</v>
       </c>
       <c r="B31">
-        <v>460.63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>1405.4670000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>46223.3125</v>
+        <v>46226.3125</v>
       </c>
       <c r="B32">
-        <v>453.984</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>1391.5640000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>46223.32291666666</v>
+        <v>46226.322916666657</v>
       </c>
       <c r="B33">
-        <v>452.607</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>1402.33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>46223.33333333334</v>
+        <v>46226.333333333343</v>
       </c>
       <c r="B34">
-        <v>431.444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>1340.33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>46223.34375</v>
+        <v>46226.34375</v>
       </c>
       <c r="B35">
-        <v>437.933</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>1357.133</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>46223.35416666666</v>
+        <v>46226.354166666657</v>
       </c>
       <c r="B36">
-        <v>453.243</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>1342.0730000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>46223.36458333334</v>
+        <v>46226.364583333343</v>
       </c>
       <c r="B37">
-        <v>461.506</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>1336.377</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>46223.375</v>
+        <v>46226.375</v>
       </c>
       <c r="B38">
-        <v>488.923</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>1342.1010000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>46223.38541666666</v>
+        <v>46226.385416666657</v>
       </c>
       <c r="B39">
-        <v>501.785</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
+        <v>1336.067</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>46223.39583333334</v>
+        <v>46226.395833333343</v>
       </c>
       <c r="B40">
-        <v>510.693</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
+        <v>1328.307</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>46223.40625</v>
+        <v>46226.40625</v>
       </c>
       <c r="B41">
-        <v>519.486</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
+        <v>1319.604</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>46223.41666666666</v>
+        <v>46226.416666666657</v>
       </c>
       <c r="B42">
-        <v>593.5359999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>1280.029</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>46223.42708333334</v>
+        <v>46226.427083333343</v>
       </c>
       <c r="B43">
-        <v>606.47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>1263.5429999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>46223.4375</v>
+        <v>46226.4375</v>
       </c>
       <c r="B44">
-        <v>620.311</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
+        <v>1244.537</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>46223.44791666666</v>
+        <v>46226.447916666657</v>
       </c>
       <c r="B45">
-        <v>632.775</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
+        <v>1226.2560000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46223.45833333334</v>
+        <v>46226.458333333343</v>
       </c>
       <c r="B46">
-        <v>633.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
+        <v>1225.558</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>46223.46875</v>
+        <v>46226.46875</v>
       </c>
       <c r="B47">
-        <v>648.787</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>1205.721</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>46223.47916666666</v>
+        <v>46226.479166666657</v>
       </c>
       <c r="B48">
-        <v>664.124</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>1185.546</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>46223.48958333334</v>
+        <v>46226.489583333343</v>
       </c>
       <c r="B49">
-        <v>678.731</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>1165.242</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>46223.5</v>
+        <v>46226.5</v>
       </c>
       <c r="B50">
-        <v>693.4589999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>1131.0989999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>46223.51041666666</v>
+        <v>46226.510416666657</v>
       </c>
       <c r="B51">
-        <v>709.093</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>1097.029</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>46223.52083333334</v>
+        <v>46226.520833333343</v>
       </c>
       <c r="B52">
-        <v>721.7809999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>1063.47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>46223.53125</v>
+        <v>46226.53125</v>
       </c>
       <c r="B53">
-        <v>734.276</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>1029.0419999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>46223.54166666666</v>
+        <v>46226.541666666657</v>
       </c>
       <c r="B54">
-        <v>748.628</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
+        <v>951.28499999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>46223.55208333334</v>
+        <v>46226.552083333343</v>
       </c>
       <c r="B55">
-        <v>762.576</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
+        <v>922.68899999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>46223.5625</v>
+        <v>46226.5625</v>
       </c>
       <c r="B56">
-        <v>775.723</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+        <v>891.423</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>46223.57291666666</v>
+        <v>46226.572916666657</v>
       </c>
       <c r="B57">
-        <v>785.694</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>862.37699999999995</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>46223.58333333334</v>
+        <v>46226.583333333343</v>
       </c>
       <c r="B58">
-        <v>776.782</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
+        <v>820.024</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>46223.59375</v>
+        <v>46226.59375</v>
       </c>
       <c r="B59">
-        <v>781.97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>793.476</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>46223.60416666666</v>
+        <v>46226.604166666657</v>
       </c>
       <c r="B60">
-        <v>787.731</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>766.46199999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>46223.61458333334</v>
+        <v>46226.614583333343</v>
       </c>
       <c r="B61">
-        <v>794.71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
+        <v>739.58600000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>46223.625</v>
+        <v>46226.625</v>
       </c>
       <c r="B62">
-        <v>804.864</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
+        <v>646.76599999999996</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>46223.63541666666</v>
+        <v>46226.635416666657</v>
       </c>
       <c r="B63">
-        <v>803.404</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
+        <v>622.12400000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>46223.64583333334</v>
+        <v>46226.645833333343</v>
       </c>
       <c r="B64">
-        <v>802.14</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
+        <v>597.58799999999997</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>46223.65625</v>
+        <v>46226.65625</v>
       </c>
       <c r="B65">
-        <v>799.121</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
+        <v>571.70000000000005</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>46223.66666666666</v>
+        <v>46226.666666666657</v>
       </c>
       <c r="B66">
-        <v>774.3390000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
+        <v>523.33000000000004</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>46223.67708333334</v>
+        <v>46226.677083333343</v>
       </c>
       <c r="B67">
-        <v>752.812</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
+        <v>492.45499999999998</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>46223.6875</v>
+        <v>46226.6875</v>
       </c>
       <c r="B68">
-        <v>731.249</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
+        <v>463.14400000000001</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>46223.69791666666</v>
+        <v>46226.697916666657</v>
       </c>
       <c r="B69">
-        <v>709.8339999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
+        <v>433.63799999999998</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>46223.70833333334</v>
+        <v>46226.708333333343</v>
       </c>
       <c r="B70">
-        <v>687.207</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
+        <v>397.12099999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>46223.71875</v>
+        <v>46226.71875</v>
       </c>
       <c r="B71">
-        <v>665.2809999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
+        <v>366.54</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>46223.72916666666</v>
+        <v>46226.729166666657</v>
       </c>
       <c r="B72">
-        <v>644.289</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
+        <v>337.17599999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>46223.73958333334</v>
+        <v>46226.739583333343</v>
       </c>
       <c r="B73">
-        <v>625.122</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
+        <v>308.322</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>46223.75</v>
+        <v>46226.75</v>
       </c>
       <c r="B74">
-        <v>507.658</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
+        <v>261.83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>46223.76041666666</v>
+        <v>46226.760416666657</v>
       </c>
       <c r="B75">
-        <v>483.976</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
+        <v>246.89500000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>46223.77083333334</v>
+        <v>46226.770833333343</v>
       </c>
       <c r="B76">
-        <v>459.82</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
+        <v>231.809</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>46223.78125</v>
+        <v>46226.78125</v>
       </c>
       <c r="B77">
-        <v>434.93</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
+        <v>218.095</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>46223.79166666666</v>
+        <v>46226.791666666657</v>
       </c>
       <c r="B78">
-        <v>414.592</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
+        <v>209.00299999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>46223.80208333334</v>
+        <v>46226.802083333343</v>
       </c>
       <c r="B79">
-        <v>397.789</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
+        <v>205.54900000000001</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>46223.8125</v>
+        <v>46226.8125</v>
       </c>
       <c r="B80">
-        <v>385.413</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
+        <v>203.41900000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>46223.82291666666</v>
+        <v>46226.822916666657</v>
       </c>
       <c r="B81">
-        <v>371.53</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
+        <v>200.93</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>46223.83333333334</v>
+        <v>46226.833333333343</v>
       </c>
       <c r="B82">
-        <v>357.557</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
+        <v>173.10400000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>46223.84375</v>
+        <v>46226.84375</v>
       </c>
       <c r="B83">
-        <v>349.363</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
+        <v>173.655</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>46223.85416666666</v>
+        <v>46226.854166666657</v>
       </c>
       <c r="B84">
-        <v>342.34</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
+        <v>173.874</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>46223.86458333334</v>
+        <v>46226.864583333343</v>
       </c>
       <c r="B85">
-        <v>334.816</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
+        <v>174.16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>46223.875</v>
+        <v>46226.875</v>
       </c>
       <c r="B86">
-        <v>316.605</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
+        <v>189.53200000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>46223.88541666666</v>
+        <v>46226.885416666657</v>
       </c>
       <c r="B87">
-        <v>312.312</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
+        <v>187.876</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>46223.89583333334</v>
+        <v>46226.895833333343</v>
       </c>
       <c r="B88">
-        <v>309.031</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
+        <v>186.178</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>46223.90625</v>
+        <v>46226.90625</v>
       </c>
       <c r="B89">
-        <v>305.255</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
+        <v>184.495</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>46223.91666666666</v>
+        <v>46226.916666666657</v>
       </c>
       <c r="B90">
-        <v>351.023</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
+        <v>182.99100000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>46223.92708333334</v>
+        <v>46226.927083333343</v>
       </c>
       <c r="B91">
-        <v>352.214</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
+        <v>181.869</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>46223.9375</v>
+        <v>46226.9375</v>
       </c>
       <c r="B92">
-        <v>353.928</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
+        <v>180.446</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>46223.94791666666</v>
+        <v>46226.947916666657</v>
       </c>
       <c r="B93">
-        <v>354.85</v>
+        <v>179.27500000000001</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -1,34 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adremgrup-my.sharepoint.com/personal/andrei_ionita_adrem_ro/Documents/Desktop/ML/AdremTrading/data_fetching/Entsoe/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_FA5745354700970902FF31D2F8375B0674908F23" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{263ED5FA-E1B5-40F9-AD09-088EB7E5EEC2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -44,11 +25,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,21 +93,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -164,7 +137,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -198,7 +171,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,10 +205,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,15 +380,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -425,740 +392,740 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B2">
-        <v>1429.085</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>205.374</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46226.010416666657</v>
+        <v>46227.01041666666</v>
       </c>
       <c r="B3">
-        <v>1453.2449999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>209.537</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46226.020833333343</v>
+        <v>46227.02083333334</v>
       </c>
       <c r="B4">
-        <v>1481.038</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46226.03125</v>
+        <v>46227.03125</v>
       </c>
       <c r="B5">
-        <v>1492.365</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.144</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46226.041666666657</v>
+        <v>46227.04166666666</v>
       </c>
       <c r="B6">
-        <v>1512.2919999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.208</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46226.052083333343</v>
+        <v>46227.05208333334</v>
       </c>
       <c r="B7">
-        <v>1543.3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>203.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46226.0625</v>
+        <v>46227.0625</v>
       </c>
       <c r="B8">
-        <v>1575.95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>201.059</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46226.072916666657</v>
+        <v>46227.07291666666</v>
       </c>
       <c r="B9">
-        <v>1601.2270000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>199.477</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46226.083333333343</v>
+        <v>46227.08333333334</v>
       </c>
       <c r="B10">
-        <v>1576.567</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>206.461</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46226.09375</v>
+        <v>46227.09375</v>
       </c>
       <c r="B11">
-        <v>1574.7090000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.462</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46226.104166666657</v>
+        <v>46227.10416666666</v>
       </c>
       <c r="B12">
-        <v>1581.079</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>222.354</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46226.114583333343</v>
+        <v>46227.11458333334</v>
       </c>
       <c r="B13">
-        <v>1585.806</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>224.418</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46226.125</v>
+        <v>46227.125</v>
       </c>
       <c r="B14">
-        <v>1607.6220000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.753</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46226.135416666657</v>
+        <v>46227.13541666666</v>
       </c>
       <c r="B15">
-        <v>1592.0640000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>216.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46226.145833333343</v>
+        <v>46227.14583333334</v>
       </c>
       <c r="B16">
-        <v>1566.7639999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>216.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46226.15625</v>
+        <v>46227.15625</v>
       </c>
       <c r="B17">
-        <v>1552.7460000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>217.559</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46226.166666666657</v>
+        <v>46227.16666666666</v>
       </c>
       <c r="B18">
-        <v>1562.6780000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>232.58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46226.177083333343</v>
+        <v>46227.17708333334</v>
       </c>
       <c r="B19">
-        <v>1550.2159999999999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>231.041</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46226.1875</v>
+        <v>46227.1875</v>
       </c>
       <c r="B20">
-        <v>1533.7360000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>229.339</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46226.197916666657</v>
+        <v>46227.19791666666</v>
       </c>
       <c r="B21">
-        <v>1534.269</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>225.193</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46226.208333333343</v>
+        <v>46227.20833333334</v>
       </c>
       <c r="B22">
-        <v>1504.3040000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>226.782</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46226.21875</v>
+        <v>46227.21875</v>
       </c>
       <c r="B23">
-        <v>1519.5229999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46226.229166666657</v>
+        <v>46227.22916666666</v>
       </c>
       <c r="B24">
-        <v>1524.193</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>217.25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46226.239583333343</v>
+        <v>46227.23958333334</v>
       </c>
       <c r="B25">
-        <v>1538.922</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>214.955</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46226.25</v>
+        <v>46227.25</v>
       </c>
       <c r="B26">
-        <v>1520.4459999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>205.832</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46226.260416666657</v>
+        <v>46227.26041666666</v>
       </c>
       <c r="B27">
-        <v>1505.9670000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>202.914</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46226.270833333343</v>
+        <v>46227.27083333334</v>
       </c>
       <c r="B28">
-        <v>1498.193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+        <v>205.469</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46226.28125</v>
+        <v>46227.28125</v>
       </c>
       <c r="B29">
-        <v>1484.337</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+        <v>206.775</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46226.291666666657</v>
+        <v>46227.29166666666</v>
       </c>
       <c r="B30">
-        <v>1405.9380000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+        <v>195.215</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46226.302083333343</v>
+        <v>46227.30208333334</v>
       </c>
       <c r="B31">
-        <v>1405.4670000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+        <v>189.075</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46226.3125</v>
+        <v>46227.3125</v>
       </c>
       <c r="B32">
-        <v>1391.5640000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+        <v>188.332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46226.322916666657</v>
+        <v>46227.32291666666</v>
       </c>
       <c r="B33">
-        <v>1402.33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+        <v>182.229</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46226.333333333343</v>
+        <v>46227.33333333334</v>
       </c>
       <c r="B34">
-        <v>1340.33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+        <v>184.059</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46226.34375</v>
+        <v>46227.34375</v>
       </c>
       <c r="B35">
-        <v>1357.133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+        <v>184.155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46226.354166666657</v>
+        <v>46227.35416666666</v>
       </c>
       <c r="B36">
-        <v>1342.0730000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+        <v>181.13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46226.364583333343</v>
+        <v>46227.36458333334</v>
       </c>
       <c r="B37">
-        <v>1336.377</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+        <v>178.563</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46226.375</v>
+        <v>46227.375</v>
       </c>
       <c r="B38">
-        <v>1342.1010000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+        <v>177.223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46226.385416666657</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="B39">
-        <v>1336.067</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+        <v>182.218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46226.395833333343</v>
+        <v>46227.39583333334</v>
       </c>
       <c r="B40">
-        <v>1328.307</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+        <v>180.149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46226.40625</v>
+        <v>46227.40625</v>
       </c>
       <c r="B41">
-        <v>1319.604</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+        <v>179.071</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46226.416666666657</v>
+        <v>46227.41666666666</v>
       </c>
       <c r="B42">
-        <v>1280.029</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+        <v>178.047</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46226.427083333343</v>
+        <v>46227.42708333334</v>
       </c>
       <c r="B43">
-        <v>1263.5429999999999</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+        <v>173.194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46226.4375</v>
+        <v>46227.4375</v>
       </c>
       <c r="B44">
-        <v>1244.537</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+        <v>173.994</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46226.447916666657</v>
+        <v>46227.44791666666</v>
       </c>
       <c r="B45">
-        <v>1226.2560000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+        <v>169.891</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46226.458333333343</v>
+        <v>46227.45833333334</v>
       </c>
       <c r="B46">
-        <v>1225.558</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+        <v>165.676</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46226.46875</v>
+        <v>46227.46875</v>
       </c>
       <c r="B47">
-        <v>1205.721</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+        <v>164.629</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46226.479166666657</v>
+        <v>46227.47916666666</v>
       </c>
       <c r="B48">
-        <v>1185.546</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+        <v>163.481</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46226.489583333343</v>
+        <v>46227.48958333334</v>
       </c>
       <c r="B49">
-        <v>1165.242</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+        <v>161.107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46226.5</v>
+        <v>46227.5</v>
       </c>
       <c r="B50">
-        <v>1131.0989999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+        <v>162.804</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46226.510416666657</v>
+        <v>46227.51041666666</v>
       </c>
       <c r="B51">
-        <v>1097.029</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+        <v>162.965</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46226.520833333343</v>
+        <v>46227.52083333334</v>
       </c>
       <c r="B52">
-        <v>1063.47</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+        <v>163.816</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46226.53125</v>
+        <v>46227.53125</v>
       </c>
       <c r="B53">
-        <v>1029.0419999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+        <v>164.014</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46226.541666666657</v>
+        <v>46227.54166666666</v>
       </c>
       <c r="B54">
-        <v>951.28499999999997</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+        <v>163.406</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46226.552083333343</v>
+        <v>46227.55208333334</v>
       </c>
       <c r="B55">
-        <v>922.68899999999996</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+        <v>167.273</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46226.5625</v>
+        <v>46227.5625</v>
       </c>
       <c r="B56">
-        <v>891.423</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+        <v>170.858</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46226.572916666657</v>
+        <v>46227.57291666666</v>
       </c>
       <c r="B57">
-        <v>862.37699999999995</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+        <v>174.744</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46226.583333333343</v>
+        <v>46227.58333333334</v>
       </c>
       <c r="B58">
-        <v>820.024</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+        <v>178.062</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46226.59375</v>
+        <v>46227.59375</v>
       </c>
       <c r="B59">
-        <v>793.476</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+        <v>183.146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46226.604166666657</v>
+        <v>46227.60416666666</v>
       </c>
       <c r="B60">
-        <v>766.46199999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+        <v>188.403</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46226.614583333343</v>
+        <v>46227.61458333334</v>
       </c>
       <c r="B61">
-        <v>739.58600000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+        <v>193.249</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46226.625</v>
+        <v>46227.625</v>
       </c>
       <c r="B62">
-        <v>646.76599999999996</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+        <v>205.867</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46226.635416666657</v>
+        <v>46227.63541666666</v>
       </c>
       <c r="B63">
-        <v>622.12400000000002</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+        <v>211.819</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46226.645833333343</v>
+        <v>46227.64583333334</v>
       </c>
       <c r="B64">
-        <v>597.58799999999997</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+        <v>217.29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46226.65625</v>
+        <v>46227.65625</v>
       </c>
       <c r="B65">
-        <v>571.70000000000005</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+        <v>223.19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46226.666666666657</v>
+        <v>46227.66666666666</v>
       </c>
       <c r="B66">
-        <v>523.33000000000004</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+        <v>220.501</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46226.677083333343</v>
+        <v>46227.67708333334</v>
       </c>
       <c r="B67">
-        <v>492.45499999999998</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+        <v>224.96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46226.6875</v>
+        <v>46227.6875</v>
       </c>
       <c r="B68">
-        <v>463.14400000000001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+        <v>229.674</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46226.697916666657</v>
+        <v>46227.69791666666</v>
       </c>
       <c r="B69">
-        <v>433.63799999999998</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+        <v>235.382</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46226.708333333343</v>
+        <v>46227.70833333334</v>
       </c>
       <c r="B70">
-        <v>397.12099999999998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+        <v>220.601</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46226.71875</v>
+        <v>46227.71875</v>
       </c>
       <c r="B71">
-        <v>366.54</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+        <v>224.632</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46226.729166666657</v>
+        <v>46227.72916666666</v>
       </c>
       <c r="B72">
-        <v>337.17599999999999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+        <v>227.409</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46226.739583333343</v>
+        <v>46227.73958333334</v>
       </c>
       <c r="B73">
-        <v>308.322</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+        <v>232.251</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46226.75</v>
+        <v>46227.75</v>
       </c>
       <c r="B74">
-        <v>261.83</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+        <v>235.729</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46226.760416666657</v>
+        <v>46227.76041666666</v>
       </c>
       <c r="B75">
-        <v>246.89500000000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+        <v>242.198</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46226.770833333343</v>
+        <v>46227.77083333334</v>
       </c>
       <c r="B76">
-        <v>231.809</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+        <v>247.999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46226.78125</v>
+        <v>46227.78125</v>
       </c>
       <c r="B77">
-        <v>218.095</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+        <v>254.002</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46226.791666666657</v>
+        <v>46227.79166666666</v>
       </c>
       <c r="B78">
-        <v>209.00299999999999</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+        <v>239.939</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46226.802083333343</v>
+        <v>46227.80208333334</v>
       </c>
       <c r="B79">
-        <v>205.54900000000001</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+        <v>253.671</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46226.8125</v>
+        <v>46227.8125</v>
       </c>
       <c r="B80">
-        <v>203.41900000000001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+        <v>269.292</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46226.822916666657</v>
+        <v>46227.82291666666</v>
       </c>
       <c r="B81">
-        <v>200.93</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+        <v>283.221</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46226.833333333343</v>
+        <v>46227.83333333334</v>
       </c>
       <c r="B82">
-        <v>173.10400000000001</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+        <v>313.979</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46226.84375</v>
+        <v>46227.84375</v>
       </c>
       <c r="B83">
-        <v>173.655</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+        <v>336.687</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46226.854166666657</v>
+        <v>46227.85416666666</v>
       </c>
       <c r="B84">
-        <v>173.874</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+        <v>360.726</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46226.864583333343</v>
+        <v>46227.86458333334</v>
       </c>
       <c r="B85">
-        <v>174.16</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+        <v>383.302</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46226.875</v>
+        <v>46227.875</v>
       </c>
       <c r="B86">
-        <v>189.53200000000001</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+        <v>441.509</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46226.885416666657</v>
+        <v>46227.88541666666</v>
       </c>
       <c r="B87">
-        <v>187.876</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+        <v>475.547</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46226.895833333343</v>
+        <v>46227.89583333334</v>
       </c>
       <c r="B88">
-        <v>186.178</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+        <v>508.987</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46226.90625</v>
+        <v>46227.90625</v>
       </c>
       <c r="B89">
-        <v>184.495</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+        <v>543.332</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46226.916666666657</v>
+        <v>46227.91666666666</v>
       </c>
       <c r="B90">
-        <v>182.99100000000001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+        <v>579.116</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46226.927083333343</v>
+        <v>46227.92708333334</v>
       </c>
       <c r="B91">
-        <v>181.869</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+        <v>613.0549999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46226.9375</v>
+        <v>46227.9375</v>
       </c>
       <c r="B92">
-        <v>180.446</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+        <v>648.0119999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46226.947916666657</v>
+        <v>46227.94791666666</v>
       </c>
       <c r="B93">
-        <v>179.27500000000001</v>
+        <v>681.373</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46227</v>
+        <v>46229</v>
       </c>
       <c r="B2">
-        <v>205.374</v>
+        <v>727.514</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46227.01041666666</v>
+        <v>46229.01041666666</v>
       </c>
       <c r="B3">
-        <v>209.537</v>
+        <v>721.0940000000001</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46227.02083333334</v>
+        <v>46229.02083333334</v>
       </c>
       <c r="B4">
-        <v>214.481</v>
+        <v>722.076</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46227.03125</v>
+        <v>46229.03125</v>
       </c>
       <c r="B5">
-        <v>214.144</v>
+        <v>713.2809999999999</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46227.04166666666</v>
+        <v>46229.04166666666</v>
       </c>
       <c r="B6">
-        <v>214.208</v>
+        <v>683.9589999999999</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46227.05208333334</v>
+        <v>46229.05208333334</v>
       </c>
       <c r="B7">
-        <v>203.24</v>
+        <v>680.676</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46227.0625</v>
+        <v>46229.0625</v>
       </c>
       <c r="B8">
-        <v>201.059</v>
+        <v>672.953</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46227.07291666666</v>
+        <v>46229.07291666666</v>
       </c>
       <c r="B9">
-        <v>199.477</v>
+        <v>666.4829999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46227.08333333334</v>
+        <v>46229.08333333334</v>
       </c>
       <c r="B10">
-        <v>206.461</v>
+        <v>645.871</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46227.09375</v>
+        <v>46229.09375</v>
       </c>
       <c r="B11">
-        <v>214.462</v>
+        <v>646.336</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46227.10416666666</v>
+        <v>46229.10416666666</v>
       </c>
       <c r="B12">
-        <v>222.354</v>
+        <v>625.751</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46227.11458333334</v>
+        <v>46229.11458333334</v>
       </c>
       <c r="B13">
-        <v>224.418</v>
+        <v>625.52</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46227.125</v>
+        <v>46229.125</v>
       </c>
       <c r="B14">
-        <v>214.753</v>
+        <v>613.372</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46227.13541666666</v>
+        <v>46229.13541666666</v>
       </c>
       <c r="B15">
-        <v>216.56</v>
+        <v>596.343</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46227.14583333334</v>
+        <v>46229.14583333334</v>
       </c>
       <c r="B16">
-        <v>216.9</v>
+        <v>581.766</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46227.15625</v>
+        <v>46229.15625</v>
       </c>
       <c r="B17">
-        <v>217.559</v>
+        <v>563.773</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46227.16666666666</v>
+        <v>46229.16666666666</v>
       </c>
       <c r="B18">
-        <v>232.58</v>
+        <v>535.292</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46227.17708333334</v>
+        <v>46229.17708333334</v>
       </c>
       <c r="B19">
-        <v>231.041</v>
+        <v>517.775</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46227.1875</v>
+        <v>46229.1875</v>
       </c>
       <c r="B20">
-        <v>229.339</v>
+        <v>499.631</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46227.19791666666</v>
+        <v>46229.19791666666</v>
       </c>
       <c r="B21">
-        <v>225.193</v>
+        <v>480.847</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46227.20833333334</v>
+        <v>46229.20833333334</v>
       </c>
       <c r="B22">
-        <v>226.782</v>
+        <v>436.793</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46227.21875</v>
+        <v>46229.21875</v>
       </c>
       <c r="B23">
-        <v>214.202</v>
+        <v>415.868</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46227.22916666666</v>
+        <v>46229.22916666666</v>
       </c>
       <c r="B24">
-        <v>217.25</v>
+        <v>393.966</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46227.23958333334</v>
+        <v>46229.23958333334</v>
       </c>
       <c r="B25">
-        <v>214.955</v>
+        <v>374.449</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46227.25</v>
+        <v>46229.25</v>
       </c>
       <c r="B26">
-        <v>205.832</v>
+        <v>338.968</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46227.26041666666</v>
+        <v>46229.26041666666</v>
       </c>
       <c r="B27">
-        <v>202.914</v>
+        <v>310.063</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46227.27083333334</v>
+        <v>46229.27083333334</v>
       </c>
       <c r="B28">
-        <v>205.469</v>
+        <v>288.577</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46227.28125</v>
+        <v>46229.28125</v>
       </c>
       <c r="B29">
-        <v>206.775</v>
+        <v>266.266</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46227.29166666666</v>
+        <v>46229.29166666666</v>
       </c>
       <c r="B30">
-        <v>195.215</v>
+        <v>261.839</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46227.30208333334</v>
+        <v>46229.30208333334</v>
       </c>
       <c r="B31">
-        <v>189.075</v>
+        <v>238.593</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46227.3125</v>
+        <v>46229.3125</v>
       </c>
       <c r="B32">
-        <v>188.332</v>
+        <v>211.106</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46227.32291666666</v>
+        <v>46229.32291666666</v>
       </c>
       <c r="B33">
-        <v>182.229</v>
+        <v>187.007</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46227.33333333334</v>
+        <v>46229.33333333334</v>
       </c>
       <c r="B34">
-        <v>184.059</v>
+        <v>175.595</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46227.34375</v>
+        <v>46229.34375</v>
       </c>
       <c r="B35">
-        <v>184.155</v>
+        <v>173.842</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46227.35416666666</v>
+        <v>46229.35416666666</v>
       </c>
       <c r="B36">
-        <v>181.13</v>
+        <v>174.065</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46227.36458333334</v>
+        <v>46229.36458333334</v>
       </c>
       <c r="B37">
-        <v>178.563</v>
+        <v>168.398</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46227.375</v>
+        <v>46229.375</v>
       </c>
       <c r="B38">
-        <v>177.223</v>
+        <v>181.339</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46227.38541666666</v>
+        <v>46229.38541666666</v>
       </c>
       <c r="B39">
-        <v>182.218</v>
+        <v>185.505</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46227.39583333334</v>
+        <v>46229.39583333334</v>
       </c>
       <c r="B40">
-        <v>180.149</v>
+        <v>189.108</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46227.40625</v>
+        <v>46229.40625</v>
       </c>
       <c r="B41">
-        <v>179.071</v>
+        <v>193.191</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46227.41666666666</v>
+        <v>46229.41666666666</v>
       </c>
       <c r="B42">
-        <v>178.047</v>
+        <v>193.982</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46227.42708333334</v>
+        <v>46229.42708333334</v>
       </c>
       <c r="B43">
-        <v>173.194</v>
+        <v>184.762</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46227.4375</v>
+        <v>46229.4375</v>
       </c>
       <c r="B44">
-        <v>173.994</v>
+        <v>204.248</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46227.44791666666</v>
+        <v>46229.44791666666</v>
       </c>
       <c r="B45">
-        <v>169.891</v>
+        <v>193.039</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46227.45833333334</v>
+        <v>46229.45833333334</v>
       </c>
       <c r="B46">
-        <v>165.676</v>
+        <v>217.605</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46227.46875</v>
+        <v>46229.46875</v>
       </c>
       <c r="B47">
-        <v>164.629</v>
+        <v>224.036</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46227.47916666666</v>
+        <v>46229.47916666666</v>
       </c>
       <c r="B48">
-        <v>163.481</v>
+        <v>230.332</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46227.48958333334</v>
+        <v>46229.48958333334</v>
       </c>
       <c r="B49">
-        <v>161.107</v>
+        <v>218.148</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46227.5</v>
+        <v>46229.5</v>
       </c>
       <c r="B50">
-        <v>162.804</v>
+        <v>232.596</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46227.51041666666</v>
+        <v>46229.51041666666</v>
       </c>
       <c r="B51">
-        <v>162.965</v>
+        <v>222.473</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46227.52083333334</v>
+        <v>46229.52083333334</v>
       </c>
       <c r="B52">
-        <v>163.816</v>
+        <v>222.991</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46227.53125</v>
+        <v>46229.53125</v>
       </c>
       <c r="B53">
-        <v>164.014</v>
+        <v>223.505</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46227.54166666666</v>
+        <v>46229.54166666666</v>
       </c>
       <c r="B54">
-        <v>163.406</v>
+        <v>219.873</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46227.55208333334</v>
+        <v>46229.55208333334</v>
       </c>
       <c r="B55">
-        <v>167.273</v>
+        <v>216.762</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46227.5625</v>
+        <v>46229.5625</v>
       </c>
       <c r="B56">
-        <v>170.858</v>
+        <v>212.554</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46227.57291666666</v>
+        <v>46229.57291666666</v>
       </c>
       <c r="B57">
-        <v>174.744</v>
+        <v>209.198</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46227.58333333334</v>
+        <v>46229.58333333334</v>
       </c>
       <c r="B58">
-        <v>178.062</v>
+        <v>186.697</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46227.59375</v>
+        <v>46229.59375</v>
       </c>
       <c r="B59">
-        <v>183.146</v>
+        <v>186.289</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46227.60416666666</v>
+        <v>46229.60416666666</v>
       </c>
       <c r="B60">
-        <v>188.403</v>
+        <v>186.259</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46227.61458333334</v>
+        <v>46229.61458333334</v>
       </c>
       <c r="B61">
-        <v>193.249</v>
+        <v>184.996</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46227.625</v>
+        <v>46229.625</v>
       </c>
       <c r="B62">
-        <v>205.867</v>
+        <v>187.393</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46227.63541666666</v>
+        <v>46229.63541666666</v>
       </c>
       <c r="B63">
-        <v>211.819</v>
+        <v>191.897</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46227.64583333334</v>
+        <v>46229.64583333334</v>
       </c>
       <c r="B64">
-        <v>217.29</v>
+        <v>206.712</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46227.65625</v>
+        <v>46229.65625</v>
       </c>
       <c r="B65">
-        <v>223.19</v>
+        <v>209.543</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46227.66666666666</v>
+        <v>46229.66666666666</v>
       </c>
       <c r="B66">
-        <v>220.501</v>
+        <v>215.76</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46227.67708333334</v>
+        <v>46229.67708333334</v>
       </c>
       <c r="B67">
-        <v>224.96</v>
+        <v>224.073</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46227.6875</v>
+        <v>46229.6875</v>
       </c>
       <c r="B68">
-        <v>229.674</v>
+        <v>231.876</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46227.69791666666</v>
+        <v>46229.69791666666</v>
       </c>
       <c r="B69">
-        <v>235.382</v>
+        <v>240.747</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46227.70833333334</v>
+        <v>46229.70833333334</v>
       </c>
       <c r="B70">
-        <v>220.601</v>
+        <v>259.731</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46227.71875</v>
+        <v>46229.71875</v>
       </c>
       <c r="B71">
-        <v>224.632</v>
+        <v>275.817</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46227.72916666666</v>
+        <v>46229.72916666666</v>
       </c>
       <c r="B72">
-        <v>227.409</v>
+        <v>293.664</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46227.73958333334</v>
+        <v>46229.73958333334</v>
       </c>
       <c r="B73">
-        <v>232.251</v>
+        <v>309.811</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46227.75</v>
+        <v>46229.75</v>
       </c>
       <c r="B74">
-        <v>235.729</v>
+        <v>309.707</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46227.76041666666</v>
+        <v>46229.76041666666</v>
       </c>
       <c r="B75">
-        <v>242.198</v>
+        <v>340.096</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46227.77083333334</v>
+        <v>46229.77083333334</v>
       </c>
       <c r="B76">
-        <v>247.999</v>
+        <v>373.099</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46227.78125</v>
+        <v>46229.78125</v>
       </c>
       <c r="B77">
-        <v>254.002</v>
+        <v>406.499</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46227.79166666666</v>
+        <v>46229.79166666666</v>
       </c>
       <c r="B78">
-        <v>239.939</v>
+        <v>457.04</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46227.80208333334</v>
+        <v>46229.80208333334</v>
       </c>
       <c r="B79">
-        <v>253.671</v>
+        <v>509.455</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46227.8125</v>
+        <v>46229.8125</v>
       </c>
       <c r="B80">
-        <v>269.292</v>
+        <v>563.39</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46227.82291666666</v>
+        <v>46229.82291666666</v>
       </c>
       <c r="B81">
-        <v>283.221</v>
+        <v>616.158</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46227.83333333334</v>
+        <v>46229.83333333334</v>
       </c>
       <c r="B82">
-        <v>313.979</v>
+        <v>690.362</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46227.84375</v>
+        <v>46229.84375</v>
       </c>
       <c r="B83">
-        <v>336.687</v>
+        <v>748.17</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46227.85416666666</v>
+        <v>46229.85416666666</v>
       </c>
       <c r="B84">
-        <v>360.726</v>
+        <v>806.211</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46227.86458333334</v>
+        <v>46229.86458333334</v>
       </c>
       <c r="B85">
-        <v>383.302</v>
+        <v>866.7089999999999</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46227.875</v>
+        <v>46229.875</v>
       </c>
       <c r="B86">
-        <v>441.509</v>
+        <v>927.6180000000001</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46227.88541666666</v>
+        <v>46229.88541666666</v>
       </c>
       <c r="B87">
-        <v>475.547</v>
+        <v>965.694</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46227.89583333334</v>
+        <v>46229.89583333334</v>
       </c>
       <c r="B88">
-        <v>508.987</v>
+        <v>1003.223</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46227.90625</v>
+        <v>46229.90625</v>
       </c>
       <c r="B89">
-        <v>543.332</v>
+        <v>1039.017</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46227.91666666666</v>
+        <v>46229.91666666666</v>
       </c>
       <c r="B90">
-        <v>579.116</v>
+        <v>1085.561</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46227.92708333334</v>
+        <v>46229.92708333334</v>
       </c>
       <c r="B91">
-        <v>613.0549999999999</v>
+        <v>1111.69</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46227.9375</v>
+        <v>46229.9375</v>
       </c>
       <c r="B92">
-        <v>648.0119999999999</v>
+        <v>1136.115</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46227.94791666666</v>
+        <v>46229.94791666666</v>
       </c>
       <c r="B93">
-        <v>681.373</v>
+        <v>1158.221</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46229</v>
+        <v>46246</v>
       </c>
       <c r="B2">
-        <v>727.514</v>
+        <v>197.186</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46229.01041666666</v>
+        <v>46246.01041666666</v>
       </c>
       <c r="B3">
-        <v>721.0940000000001</v>
+        <v>213.956</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46229.02083333334</v>
+        <v>46246.02083333334</v>
       </c>
       <c r="B4">
-        <v>722.076</v>
+        <v>229.824</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46229.03125</v>
+        <v>46246.03125</v>
       </c>
       <c r="B5">
-        <v>713.2809999999999</v>
+        <v>246.049</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46229.04166666666</v>
+        <v>46246.04166666666</v>
       </c>
       <c r="B6">
-        <v>683.9589999999999</v>
+        <v>289.544</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46229.05208333334</v>
+        <v>46246.05208333334</v>
       </c>
       <c r="B7">
-        <v>680.676</v>
+        <v>325.288</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46229.0625</v>
+        <v>46246.0625</v>
       </c>
       <c r="B8">
-        <v>672.953</v>
+        <v>361.138</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46229.07291666666</v>
+        <v>46246.07291666666</v>
       </c>
       <c r="B9">
-        <v>666.4829999999999</v>
+        <v>395.071</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46229.08333333334</v>
+        <v>46246.08333333334</v>
       </c>
       <c r="B10">
-        <v>645.871</v>
+        <v>470.211</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46229.09375</v>
+        <v>46246.09375</v>
       </c>
       <c r="B11">
-        <v>646.336</v>
+        <v>516.203</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46229.10416666666</v>
+        <v>46246.10416666666</v>
       </c>
       <c r="B12">
-        <v>625.751</v>
+        <v>567.402</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46229.11458333334</v>
+        <v>46246.11458333334</v>
       </c>
       <c r="B13">
-        <v>625.52</v>
+        <v>611.177</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46229.125</v>
+        <v>46246.125</v>
       </c>
       <c r="B14">
-        <v>613.372</v>
+        <v>705.867</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46229.13541666666</v>
+        <v>46246.13541666666</v>
       </c>
       <c r="B15">
-        <v>596.343</v>
+        <v>752.492</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46229.14583333334</v>
+        <v>46246.14583333334</v>
       </c>
       <c r="B16">
-        <v>581.766</v>
+        <v>808.777</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46229.15625</v>
+        <v>46246.15625</v>
       </c>
       <c r="B17">
-        <v>563.773</v>
+        <v>895.694</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46229.16666666666</v>
+        <v>46246.16666666666</v>
       </c>
       <c r="B18">
-        <v>535.292</v>
+        <v>1009.387</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46229.17708333334</v>
+        <v>46246.17708333334</v>
       </c>
       <c r="B19">
-        <v>517.775</v>
+        <v>1077.265</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46229.1875</v>
+        <v>46246.1875</v>
       </c>
       <c r="B20">
-        <v>499.631</v>
+        <v>1132.164</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46229.19791666666</v>
+        <v>46246.19791666666</v>
       </c>
       <c r="B21">
-        <v>480.847</v>
+        <v>1203.584</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46229.20833333334</v>
+        <v>46246.20833333334</v>
       </c>
       <c r="B22">
-        <v>436.793</v>
+        <v>1259.799</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46229.21875</v>
+        <v>46246.21875</v>
       </c>
       <c r="B23">
-        <v>415.868</v>
+        <v>1330.724</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46229.22916666666</v>
+        <v>46246.22916666666</v>
       </c>
       <c r="B24">
-        <v>393.966</v>
+        <v>1385.392</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46229.23958333334</v>
+        <v>46246.23958333334</v>
       </c>
       <c r="B25">
-        <v>374.449</v>
+        <v>1444.67</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46229.25</v>
+        <v>46246.25</v>
       </c>
       <c r="B26">
-        <v>338.968</v>
+        <v>1527.896</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46229.26041666666</v>
+        <v>46246.26041666666</v>
       </c>
       <c r="B27">
-        <v>310.063</v>
+        <v>1578.667</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46229.27083333334</v>
+        <v>46246.27083333334</v>
       </c>
       <c r="B28">
-        <v>288.577</v>
+        <v>1631.225</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46229.28125</v>
+        <v>46246.28125</v>
       </c>
       <c r="B29">
-        <v>266.266</v>
+        <v>1680.859</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46229.29166666666</v>
+        <v>46246.29166666666</v>
       </c>
       <c r="B30">
-        <v>261.839</v>
+        <v>1714.836</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46229.30208333334</v>
+        <v>46246.30208333334</v>
       </c>
       <c r="B31">
-        <v>238.593</v>
+        <v>1739.285</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46229.3125</v>
+        <v>46246.3125</v>
       </c>
       <c r="B32">
-        <v>211.106</v>
+        <v>1750.255</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46229.32291666666</v>
+        <v>46246.32291666666</v>
       </c>
       <c r="B33">
-        <v>187.007</v>
+        <v>1765.513</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46229.33333333334</v>
+        <v>46246.33333333334</v>
       </c>
       <c r="B34">
-        <v>175.595</v>
+        <v>1703.943</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46229.34375</v>
+        <v>46246.34375</v>
       </c>
       <c r="B35">
-        <v>173.842</v>
+        <v>1722.716</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46229.35416666666</v>
+        <v>46246.35416666666</v>
       </c>
       <c r="B36">
-        <v>174.065</v>
+        <v>1879.172</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46229.36458333334</v>
+        <v>46246.36458333334</v>
       </c>
       <c r="B37">
-        <v>168.398</v>
+        <v>1862.56</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46229.375</v>
+        <v>46246.375</v>
       </c>
       <c r="B38">
-        <v>181.339</v>
+        <v>1828.041</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46229.38541666666</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="B39">
-        <v>185.505</v>
+        <v>1823.414</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46229.39583333334</v>
+        <v>46246.39583333334</v>
       </c>
       <c r="B40">
-        <v>189.108</v>
+        <v>1817.008</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46229.40625</v>
+        <v>46246.40625</v>
       </c>
       <c r="B41">
-        <v>193.191</v>
+        <v>1811.272</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46229.41666666666</v>
+        <v>46246.41666666666</v>
       </c>
       <c r="B42">
-        <v>193.982</v>
+        <v>1730.225</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46229.42708333334</v>
+        <v>46246.42708333334</v>
       </c>
       <c r="B43">
-        <v>184.762</v>
+        <v>1709.468</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46229.4375</v>
+        <v>46246.4375</v>
       </c>
       <c r="B44">
-        <v>204.248</v>
+        <v>1689.832</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46229.44791666666</v>
+        <v>46246.44791666666</v>
       </c>
       <c r="B45">
-        <v>193.039</v>
+        <v>1670.48</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46229.45833333334</v>
+        <v>46246.45833333334</v>
       </c>
       <c r="B46">
-        <v>217.605</v>
+        <v>1682.603</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46229.46875</v>
+        <v>46246.46875</v>
       </c>
       <c r="B47">
-        <v>224.036</v>
+        <v>1652.686</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46229.47916666666</v>
+        <v>46246.47916666666</v>
       </c>
       <c r="B48">
-        <v>230.332</v>
+        <v>1621.397</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46229.48958333334</v>
+        <v>46246.48958333334</v>
       </c>
       <c r="B49">
-        <v>218.148</v>
+        <v>1591.093</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46229.5</v>
+        <v>46246.5</v>
       </c>
       <c r="B50">
-        <v>232.596</v>
+        <v>1538.718</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46229.51041666666</v>
+        <v>46246.51041666666</v>
       </c>
       <c r="B51">
-        <v>222.473</v>
+        <v>1500.508</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46229.52083333334</v>
+        <v>46246.52083333334</v>
       </c>
       <c r="B52">
-        <v>222.991</v>
+        <v>1464.494</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46229.53125</v>
+        <v>46246.53125</v>
       </c>
       <c r="B53">
-        <v>223.505</v>
+        <v>1425.158</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46229.54166666666</v>
+        <v>46246.54166666666</v>
       </c>
       <c r="B54">
-        <v>219.873</v>
+        <v>1390.415</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46229.55208333334</v>
+        <v>46246.55208333334</v>
       </c>
       <c r="B55">
-        <v>216.762</v>
+        <v>1356.325</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46229.5625</v>
+        <v>46246.5625</v>
       </c>
       <c r="B56">
-        <v>212.554</v>
+        <v>1322.714</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46229.57291666666</v>
+        <v>46246.57291666666</v>
       </c>
       <c r="B57">
-        <v>209.198</v>
+        <v>1289.151</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46229.58333333334</v>
+        <v>46246.58333333334</v>
       </c>
       <c r="B58">
-        <v>186.697</v>
+        <v>1237.555</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46229.59375</v>
+        <v>46246.59375</v>
       </c>
       <c r="B59">
-        <v>186.289</v>
+        <v>1215.356</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46229.60416666666</v>
+        <v>46246.60416666666</v>
       </c>
       <c r="B60">
-        <v>186.259</v>
+        <v>1193.194</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46229.61458333334</v>
+        <v>46246.61458333334</v>
       </c>
       <c r="B61">
-        <v>184.996</v>
+        <v>1172.885</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46229.625</v>
+        <v>46246.625</v>
       </c>
       <c r="B62">
-        <v>187.393</v>
+        <v>1160.822</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46229.63541666666</v>
+        <v>46246.63541666666</v>
       </c>
       <c r="B63">
-        <v>191.897</v>
+        <v>1140.4</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46229.64583333334</v>
+        <v>46246.64583333334</v>
       </c>
       <c r="B64">
-        <v>206.712</v>
+        <v>1120.439</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46229.65625</v>
+        <v>46246.65625</v>
       </c>
       <c r="B65">
-        <v>209.543</v>
+        <v>1101.254</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46229.66666666666</v>
+        <v>46246.66666666666</v>
       </c>
       <c r="B66">
-        <v>215.76</v>
+        <v>1079.98</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46229.67708333334</v>
+        <v>46246.67708333334</v>
       </c>
       <c r="B67">
-        <v>224.073</v>
+        <v>1062.643</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46229.6875</v>
+        <v>46246.6875</v>
       </c>
       <c r="B68">
-        <v>231.876</v>
+        <v>1045.639</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46229.69791666666</v>
+        <v>46246.69791666666</v>
       </c>
       <c r="B69">
-        <v>240.747</v>
+        <v>1026.307</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46229.70833333334</v>
+        <v>46246.70833333334</v>
       </c>
       <c r="B70">
-        <v>259.731</v>
+        <v>928.352</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46229.71875</v>
+        <v>46246.71875</v>
       </c>
       <c r="B71">
-        <v>275.817</v>
+        <v>914.675</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46229.72916666666</v>
+        <v>46246.72916666666</v>
       </c>
       <c r="B72">
-        <v>293.664</v>
+        <v>902.021</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46229.73958333334</v>
+        <v>46246.73958333334</v>
       </c>
       <c r="B73">
-        <v>309.811</v>
+        <v>888.158</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46229.75</v>
+        <v>46246.75</v>
       </c>
       <c r="B74">
-        <v>309.707</v>
+        <v>865.557</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46229.76041666666</v>
+        <v>46246.76041666666</v>
       </c>
       <c r="B75">
-        <v>340.096</v>
+        <v>855.207</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46229.77083333334</v>
+        <v>46246.77083333334</v>
       </c>
       <c r="B76">
-        <v>373.099</v>
+        <v>845.723</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46229.78125</v>
+        <v>46246.78125</v>
       </c>
       <c r="B77">
-        <v>406.499</v>
+        <v>837.295</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46229.79166666666</v>
+        <v>46246.79166666666</v>
       </c>
       <c r="B78">
-        <v>457.04</v>
+        <v>838.372</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46229.80208333334</v>
+        <v>46246.80208333334</v>
       </c>
       <c r="B79">
-        <v>509.455</v>
+        <v>846.937</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46229.8125</v>
+        <v>46246.8125</v>
       </c>
       <c r="B80">
-        <v>563.39</v>
+        <v>855.37</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46229.82291666666</v>
+        <v>46246.82291666666</v>
       </c>
       <c r="B81">
-        <v>616.158</v>
+        <v>865.309</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46229.83333333334</v>
+        <v>46246.83333333334</v>
       </c>
       <c r="B82">
-        <v>690.362</v>
+        <v>883.449</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46229.84375</v>
+        <v>46246.84375</v>
       </c>
       <c r="B83">
-        <v>748.17</v>
+        <v>898.177</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46229.85416666666</v>
+        <v>46246.85416666666</v>
       </c>
       <c r="B84">
-        <v>806.211</v>
+        <v>913.028</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46229.86458333334</v>
+        <v>46246.86458333334</v>
       </c>
       <c r="B85">
-        <v>866.7089999999999</v>
+        <v>929.1319999999999</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46229.875</v>
+        <v>46246.875</v>
       </c>
       <c r="B86">
-        <v>927.6180000000001</v>
+        <v>949.826</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46229.88541666666</v>
+        <v>46246.88541666666</v>
       </c>
       <c r="B87">
-        <v>965.694</v>
+        <v>970.248</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46229.89583333334</v>
+        <v>46246.89583333334</v>
       </c>
       <c r="B88">
-        <v>1003.223</v>
+        <v>989.924</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46229.90625</v>
+        <v>46246.90625</v>
       </c>
       <c r="B89">
-        <v>1039.017</v>
+        <v>1012.414</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46229.91666666666</v>
+        <v>46246.91666666666</v>
       </c>
       <c r="B90">
-        <v>1085.561</v>
+        <v>1046.897</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46229.92708333334</v>
+        <v>46246.92708333334</v>
       </c>
       <c r="B91">
-        <v>1111.69</v>
+        <v>1074.813</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46229.9375</v>
+        <v>46246.9375</v>
       </c>
       <c r="B92">
-        <v>1136.115</v>
+        <v>1102.574</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46229.94791666666</v>
+        <v>46246.94791666666</v>
       </c>
       <c r="B93">
-        <v>1158.221</v>
+        <v>1129.677</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B2">
-        <v>197.186</v>
+        <v>463.704</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46246.01041666666</v>
+        <v>46251.01041666666</v>
       </c>
       <c r="B3">
-        <v>213.956</v>
+        <v>453.313</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46246.02083333334</v>
+        <v>46251.02083333334</v>
       </c>
       <c r="B4">
-        <v>229.824</v>
+        <v>445.574</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46246.03125</v>
+        <v>46251.03125</v>
       </c>
       <c r="B5">
-        <v>246.049</v>
+        <v>420.452</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46246.04166666666</v>
+        <v>46251.04166666666</v>
       </c>
       <c r="B6">
-        <v>289.544</v>
+        <v>424.898</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46246.05208333334</v>
+        <v>46251.05208333334</v>
       </c>
       <c r="B7">
-        <v>325.288</v>
+        <v>414.694</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46246.0625</v>
+        <v>46251.0625</v>
       </c>
       <c r="B8">
-        <v>361.138</v>
+        <v>390.793</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46246.07291666666</v>
+        <v>46251.07291666666</v>
       </c>
       <c r="B9">
-        <v>395.071</v>
+        <v>379.057</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46246.08333333334</v>
+        <v>46251.08333333334</v>
       </c>
       <c r="B10">
-        <v>470.211</v>
+        <v>362.136</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46246.09375</v>
+        <v>46251.09375</v>
       </c>
       <c r="B11">
-        <v>516.203</v>
+        <v>350.967</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46246.10416666666</v>
+        <v>46251.10416666666</v>
       </c>
       <c r="B12">
-        <v>567.402</v>
+        <v>341.162</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46246.11458333334</v>
+        <v>46251.11458333334</v>
       </c>
       <c r="B13">
-        <v>611.177</v>
+        <v>332.759</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46246.125</v>
+        <v>46251.125</v>
       </c>
       <c r="B14">
-        <v>705.867</v>
+        <v>322.289</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46246.13541666666</v>
+        <v>46251.13541666666</v>
       </c>
       <c r="B15">
-        <v>752.492</v>
+        <v>314.554</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46246.14583333334</v>
+        <v>46251.14583333334</v>
       </c>
       <c r="B16">
-        <v>808.777</v>
+        <v>305.284</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46246.15625</v>
+        <v>46251.15625</v>
       </c>
       <c r="B17">
-        <v>895.694</v>
+        <v>292.172</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46246.16666666666</v>
+        <v>46251.16666666666</v>
       </c>
       <c r="B18">
-        <v>1009.387</v>
+        <v>281.316</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46246.17708333334</v>
+        <v>46251.17708333334</v>
       </c>
       <c r="B19">
-        <v>1077.265</v>
+        <v>268.468</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46246.1875</v>
+        <v>46251.1875</v>
       </c>
       <c r="B20">
-        <v>1132.164</v>
+        <v>249.051</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46246.19791666666</v>
+        <v>46251.19791666666</v>
       </c>
       <c r="B21">
-        <v>1203.584</v>
+        <v>237.781</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46246.20833333334</v>
+        <v>46251.20833333334</v>
       </c>
       <c r="B22">
-        <v>1259.799</v>
+        <v>216.833</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46246.21875</v>
+        <v>46251.21875</v>
       </c>
       <c r="B23">
-        <v>1330.724</v>
+        <v>208.228</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46246.22916666666</v>
+        <v>46251.22916666666</v>
       </c>
       <c r="B24">
-        <v>1385.392</v>
+        <v>196.428</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46246.23958333334</v>
+        <v>46251.23958333334</v>
       </c>
       <c r="B25">
-        <v>1444.67</v>
+        <v>219.669</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46246.25</v>
+        <v>46251.25</v>
       </c>
       <c r="B26">
-        <v>1527.896</v>
+        <v>178.895</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46246.26041666666</v>
+        <v>46251.26041666666</v>
       </c>
       <c r="B27">
-        <v>1578.667</v>
+        <v>173.518</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46246.27083333334</v>
+        <v>46251.27083333334</v>
       </c>
       <c r="B28">
-        <v>1631.225</v>
+        <v>179.15</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46246.28125</v>
+        <v>46251.28125</v>
       </c>
       <c r="B29">
-        <v>1680.859</v>
+        <v>174.638</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46246.29166666666</v>
+        <v>46251.29166666666</v>
       </c>
       <c r="B30">
-        <v>1714.836</v>
+        <v>178.005</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46246.30208333334</v>
+        <v>46251.30208333334</v>
       </c>
       <c r="B31">
-        <v>1739.285</v>
+        <v>173.637</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46246.3125</v>
+        <v>46251.3125</v>
       </c>
       <c r="B32">
-        <v>1750.255</v>
+        <v>166.789</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46246.32291666666</v>
+        <v>46251.32291666666</v>
       </c>
       <c r="B33">
-        <v>1765.513</v>
+        <v>161.457</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46246.33333333334</v>
+        <v>46251.33333333334</v>
       </c>
       <c r="B34">
-        <v>1703.943</v>
+        <v>158.19</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46246.34375</v>
+        <v>46251.34375</v>
       </c>
       <c r="B35">
-        <v>1722.716</v>
+        <v>161.653</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46246.35416666666</v>
+        <v>46251.35416666666</v>
       </c>
       <c r="B36">
-        <v>1879.172</v>
+        <v>144.57</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46246.36458333334</v>
+        <v>46251.36458333334</v>
       </c>
       <c r="B37">
-        <v>1862.56</v>
+        <v>144.887</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46246.375</v>
+        <v>46251.375</v>
       </c>
       <c r="B38">
-        <v>1828.041</v>
+        <v>155.584</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46246.38541666666</v>
+        <v>46251.38541666666</v>
       </c>
       <c r="B39">
-        <v>1823.414</v>
+        <v>162.074</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46246.39583333334</v>
+        <v>46251.39583333334</v>
       </c>
       <c r="B40">
-        <v>1817.008</v>
+        <v>166.93</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46246.40625</v>
+        <v>46251.40625</v>
       </c>
       <c r="B41">
-        <v>1811.272</v>
+        <v>172.727</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46246.41666666666</v>
+        <v>46251.41666666666</v>
       </c>
       <c r="B42">
-        <v>1730.225</v>
+        <v>170.296</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46246.42708333334</v>
+        <v>46251.42708333334</v>
       </c>
       <c r="B43">
-        <v>1709.468</v>
+        <v>177.297</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46246.4375</v>
+        <v>46251.4375</v>
       </c>
       <c r="B44">
-        <v>1689.832</v>
+        <v>184.761</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46246.44791666666</v>
+        <v>46251.44791666666</v>
       </c>
       <c r="B45">
-        <v>1670.48</v>
+        <v>191.387</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46246.45833333334</v>
+        <v>46251.45833333334</v>
       </c>
       <c r="B46">
-        <v>1682.603</v>
+        <v>199.437</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46246.46875</v>
+        <v>46251.46875</v>
       </c>
       <c r="B47">
-        <v>1652.686</v>
+        <v>208.416</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46246.47916666666</v>
+        <v>46251.47916666666</v>
       </c>
       <c r="B48">
-        <v>1621.397</v>
+        <v>216.524</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46246.48958333334</v>
+        <v>46251.48958333334</v>
       </c>
       <c r="B49">
-        <v>1591.093</v>
+        <v>225.025</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46246.5</v>
+        <v>46251.5</v>
       </c>
       <c r="B50">
-        <v>1538.718</v>
+        <v>236.832</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46246.51041666666</v>
+        <v>46251.51041666666</v>
       </c>
       <c r="B51">
-        <v>1500.508</v>
+        <v>247.432</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46246.52083333334</v>
+        <v>46251.52083333334</v>
       </c>
       <c r="B52">
-        <v>1464.494</v>
+        <v>258.927</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46246.53125</v>
+        <v>46251.53125</v>
       </c>
       <c r="B53">
-        <v>1425.158</v>
+        <v>270.568</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46246.54166666666</v>
+        <v>46251.54166666666</v>
       </c>
       <c r="B54">
-        <v>1390.415</v>
+        <v>289.749</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46246.55208333334</v>
+        <v>46251.55208333334</v>
       </c>
       <c r="B55">
-        <v>1356.325</v>
+        <v>307.091</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46246.5625</v>
+        <v>46251.5625</v>
       </c>
       <c r="B56">
-        <v>1322.714</v>
+        <v>324.777</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46246.57291666666</v>
+        <v>46251.57291666666</v>
       </c>
       <c r="B57">
-        <v>1289.151</v>
+        <v>342.686</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46246.58333333334</v>
+        <v>46251.58333333334</v>
       </c>
       <c r="B58">
-        <v>1237.555</v>
+        <v>380.907</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46246.59375</v>
+        <v>46251.59375</v>
       </c>
       <c r="B59">
-        <v>1215.356</v>
+        <v>400.757</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46246.60416666666</v>
+        <v>46251.60416666666</v>
       </c>
       <c r="B60">
-        <v>1193.194</v>
+        <v>420.084</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46246.61458333334</v>
+        <v>46251.61458333334</v>
       </c>
       <c r="B61">
-        <v>1172.885</v>
+        <v>439.019</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46246.625</v>
+        <v>46251.625</v>
       </c>
       <c r="B62">
-        <v>1160.822</v>
+        <v>467.191</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46246.63541666666</v>
+        <v>46251.63541666666</v>
       </c>
       <c r="B63">
-        <v>1140.4</v>
+        <v>489.304</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46246.64583333334</v>
+        <v>46251.64583333334</v>
       </c>
       <c r="B64">
-        <v>1120.439</v>
+        <v>510.689</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46246.65625</v>
+        <v>46251.65625</v>
       </c>
       <c r="B65">
-        <v>1101.254</v>
+        <v>531.907</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46246.66666666666</v>
+        <v>46251.66666666666</v>
       </c>
       <c r="B66">
-        <v>1079.98</v>
+        <v>555.821</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46246.67708333334</v>
+        <v>46251.67708333334</v>
       </c>
       <c r="B67">
-        <v>1062.643</v>
+        <v>578.954</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46246.6875</v>
+        <v>46251.6875</v>
       </c>
       <c r="B68">
-        <v>1045.639</v>
+        <v>602.323</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46246.69791666666</v>
+        <v>46251.69791666666</v>
       </c>
       <c r="B69">
-        <v>1026.307</v>
+        <v>624.869</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46246.70833333334</v>
+        <v>46251.70833333334</v>
       </c>
       <c r="B70">
-        <v>928.352</v>
+        <v>576.5359999999999</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46246.71875</v>
+        <v>46251.71875</v>
       </c>
       <c r="B71">
-        <v>914.675</v>
+        <v>595.336</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46246.72916666666</v>
+        <v>46251.72916666666</v>
       </c>
       <c r="B72">
-        <v>902.021</v>
+        <v>614.861</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46246.73958333334</v>
+        <v>46251.73958333334</v>
       </c>
       <c r="B73">
-        <v>888.158</v>
+        <v>635.681</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46246.75</v>
+        <v>46251.75</v>
       </c>
       <c r="B74">
-        <v>865.557</v>
+        <v>682.905</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46246.76041666666</v>
+        <v>46251.76041666666</v>
       </c>
       <c r="B75">
-        <v>855.207</v>
+        <v>725.941</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46246.77083333334</v>
+        <v>46251.77083333334</v>
       </c>
       <c r="B76">
-        <v>845.723</v>
+        <v>769.203</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46246.78125</v>
+        <v>46251.78125</v>
       </c>
       <c r="B77">
-        <v>837.295</v>
+        <v>815.124</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46246.79166666666</v>
+        <v>46251.79166666666</v>
       </c>
       <c r="B78">
-        <v>838.372</v>
+        <v>901.727</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46246.80208333334</v>
+        <v>46251.80208333334</v>
       </c>
       <c r="B79">
-        <v>846.937</v>
+        <v>952.554</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46246.8125</v>
+        <v>46251.8125</v>
       </c>
       <c r="B80">
-        <v>855.37</v>
+        <v>1002.492</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46246.82291666666</v>
+        <v>46251.82291666666</v>
       </c>
       <c r="B81">
-        <v>865.309</v>
+        <v>1053.082</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46246.83333333334</v>
+        <v>46251.83333333334</v>
       </c>
       <c r="B82">
-        <v>883.449</v>
+        <v>1135.355</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46246.84375</v>
+        <v>46251.84375</v>
       </c>
       <c r="B83">
-        <v>898.177</v>
+        <v>1153.282</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46246.85416666666</v>
+        <v>46251.85416666666</v>
       </c>
       <c r="B84">
-        <v>913.028</v>
+        <v>1170.008</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46246.86458333334</v>
+        <v>46251.86458333334</v>
       </c>
       <c r="B85">
-        <v>929.1319999999999</v>
+        <v>1185.842</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46246.875</v>
+        <v>46251.875</v>
       </c>
       <c r="B86">
-        <v>949.826</v>
+        <v>1195.462</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46246.88541666666</v>
+        <v>46251.88541666666</v>
       </c>
       <c r="B87">
-        <v>970.248</v>
+        <v>1199.911</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46246.89583333334</v>
+        <v>46251.89583333334</v>
       </c>
       <c r="B88">
-        <v>989.924</v>
+        <v>1204.549</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46246.90625</v>
+        <v>46251.90625</v>
       </c>
       <c r="B89">
-        <v>1012.414</v>
+        <v>1209.19</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46246.91666666666</v>
+        <v>46251.91666666666</v>
       </c>
       <c r="B90">
-        <v>1046.897</v>
+        <v>1213.141</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46246.92708333334</v>
+        <v>46251.92708333334</v>
       </c>
       <c r="B91">
-        <v>1074.813</v>
+        <v>1213.841</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46246.9375</v>
+        <v>46251.9375</v>
       </c>
       <c r="B92">
-        <v>1102.574</v>
+        <v>1215.035</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46246.94791666666</v>
+        <v>46251.94791666666</v>
       </c>
       <c r="B93">
-        <v>1129.677</v>
+        <v>1216.91</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B2">
-        <v>463.704</v>
+        <v>1175.964</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46251.01041666666</v>
+        <v>46252.01041666666</v>
       </c>
       <c r="B3">
-        <v>453.313</v>
+        <v>1168.757</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46251.02083333334</v>
+        <v>46252.02083333334</v>
       </c>
       <c r="B4">
-        <v>445.574</v>
+        <v>1172.745</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46251.03125</v>
+        <v>46252.03125</v>
       </c>
       <c r="B5">
-        <v>420.452</v>
+        <v>1163.486</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46251.04166666666</v>
+        <v>46252.04166666666</v>
       </c>
       <c r="B6">
-        <v>424.898</v>
+        <v>1141.859</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46251.05208333334</v>
+        <v>46252.05208333334</v>
       </c>
       <c r="B7">
-        <v>414.694</v>
+        <v>1129.075</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46251.0625</v>
+        <v>46252.0625</v>
       </c>
       <c r="B8">
-        <v>390.793</v>
+        <v>1103.162</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46251.07291666666</v>
+        <v>46252.07291666666</v>
       </c>
       <c r="B9">
-        <v>379.057</v>
+        <v>1094.345</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46251.08333333334</v>
+        <v>46252.08333333334</v>
       </c>
       <c r="B10">
-        <v>362.136</v>
+        <v>1080.845</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46251.09375</v>
+        <v>46252.09375</v>
       </c>
       <c r="B11">
-        <v>350.967</v>
+        <v>1066.591</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46251.10416666666</v>
+        <v>46252.10416666666</v>
       </c>
       <c r="B12">
-        <v>341.162</v>
+        <v>1059.409</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46251.11458333334</v>
+        <v>46252.11458333334</v>
       </c>
       <c r="B13">
-        <v>332.759</v>
+        <v>1050.111</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46251.125</v>
+        <v>46252.125</v>
       </c>
       <c r="B14">
-        <v>322.289</v>
+        <v>1059.622</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46251.13541666666</v>
+        <v>46252.13541666666</v>
       </c>
       <c r="B15">
-        <v>314.554</v>
+        <v>1048.092</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46251.14583333334</v>
+        <v>46252.14583333334</v>
       </c>
       <c r="B16">
-        <v>305.284</v>
+        <v>1035.006</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46251.15625</v>
+        <v>46252.15625</v>
       </c>
       <c r="B17">
-        <v>292.172</v>
+        <v>1021.403</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46251.16666666666</v>
+        <v>46252.16666666666</v>
       </c>
       <c r="B18">
-        <v>281.316</v>
+        <v>1018.864</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46251.17708333334</v>
+        <v>46252.17708333334</v>
       </c>
       <c r="B19">
-        <v>268.468</v>
+        <v>1006.036</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46251.1875</v>
+        <v>46252.1875</v>
       </c>
       <c r="B20">
-        <v>249.051</v>
+        <v>998.326</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46251.19791666666</v>
+        <v>46252.19791666666</v>
       </c>
       <c r="B21">
-        <v>237.781</v>
+        <v>985.023</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46251.20833333334</v>
+        <v>46252.20833333334</v>
       </c>
       <c r="B22">
-        <v>216.833</v>
+        <v>981.824</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46251.21875</v>
+        <v>46252.21875</v>
       </c>
       <c r="B23">
-        <v>208.228</v>
+        <v>975.299</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46251.22916666666</v>
+        <v>46252.22916666666</v>
       </c>
       <c r="B24">
-        <v>196.428</v>
+        <v>971.307</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46251.23958333334</v>
+        <v>46252.23958333334</v>
       </c>
       <c r="B25">
-        <v>219.669</v>
+        <v>966.6559999999999</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46251.25</v>
+        <v>46252.25</v>
       </c>
       <c r="B26">
-        <v>178.895</v>
+        <v>863.165</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46251.26041666666</v>
+        <v>46252.26041666666</v>
       </c>
       <c r="B27">
-        <v>173.518</v>
+        <v>851.412</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46251.27083333334</v>
+        <v>46252.27083333334</v>
       </c>
       <c r="B28">
-        <v>179.15</v>
+        <v>838.171</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46251.28125</v>
+        <v>46252.28125</v>
       </c>
       <c r="B29">
-        <v>174.638</v>
+        <v>827.503</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46251.29166666666</v>
+        <v>46252.29166666666</v>
       </c>
       <c r="B30">
-        <v>178.005</v>
+        <v>850.266</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46251.30208333334</v>
+        <v>46252.30208333334</v>
       </c>
       <c r="B31">
-        <v>173.637</v>
+        <v>816.904</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46251.3125</v>
+        <v>46252.3125</v>
       </c>
       <c r="B32">
-        <v>166.789</v>
+        <v>771.533</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46251.32291666666</v>
+        <v>46252.32291666666</v>
       </c>
       <c r="B33">
-        <v>161.457</v>
+        <v>735.962</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46251.33333333334</v>
+        <v>46252.33333333334</v>
       </c>
       <c r="B34">
-        <v>158.19</v>
+        <v>707.327</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46251.34375</v>
+        <v>46252.34375</v>
       </c>
       <c r="B35">
-        <v>161.653</v>
+        <v>692.755</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46251.35416666666</v>
+        <v>46252.35416666666</v>
       </c>
       <c r="B36">
-        <v>144.57</v>
+        <v>681.3049999999999</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46251.36458333334</v>
+        <v>46252.36458333334</v>
       </c>
       <c r="B37">
-        <v>144.887</v>
+        <v>670.603</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46251.375</v>
+        <v>46252.375</v>
       </c>
       <c r="B38">
-        <v>155.584</v>
+        <v>668.66</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46251.38541666666</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="B39">
-        <v>162.074</v>
+        <v>682.103</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46251.39583333334</v>
+        <v>46252.39583333334</v>
       </c>
       <c r="B40">
-        <v>166.93</v>
+        <v>695.1559999999999</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46251.40625</v>
+        <v>46252.40625</v>
       </c>
       <c r="B41">
-        <v>172.727</v>
+        <v>709.277</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46251.41666666666</v>
+        <v>46252.41666666666</v>
       </c>
       <c r="B42">
-        <v>170.296</v>
+        <v>783.889</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46251.42708333334</v>
+        <v>46252.42708333334</v>
       </c>
       <c r="B43">
-        <v>177.297</v>
+        <v>806.467</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46251.4375</v>
+        <v>46252.4375</v>
       </c>
       <c r="B44">
-        <v>184.761</v>
+        <v>829.981</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46251.44791666666</v>
+        <v>46252.44791666666</v>
       </c>
       <c r="B45">
-        <v>191.387</v>
+        <v>853.947</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46251.45833333334</v>
+        <v>46252.45833333334</v>
       </c>
       <c r="B46">
-        <v>199.437</v>
+        <v>875.476</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46251.46875</v>
+        <v>46252.46875</v>
       </c>
       <c r="B47">
-        <v>208.416</v>
+        <v>890.152</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46251.47916666666</v>
+        <v>46252.47916666666</v>
       </c>
       <c r="B48">
-        <v>216.524</v>
+        <v>906.537</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46251.48958333334</v>
+        <v>46252.48958333334</v>
       </c>
       <c r="B49">
-        <v>225.025</v>
+        <v>922.316</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46251.5</v>
+        <v>46252.5</v>
       </c>
       <c r="B50">
-        <v>236.832</v>
+        <v>932.119</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46251.51041666666</v>
+        <v>46252.51041666666</v>
       </c>
       <c r="B51">
-        <v>247.432</v>
+        <v>939.527</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46251.52083333334</v>
+        <v>46252.52083333334</v>
       </c>
       <c r="B52">
-        <v>258.927</v>
+        <v>945.864</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46251.53125</v>
+        <v>46252.53125</v>
       </c>
       <c r="B53">
-        <v>270.568</v>
+        <v>952.317</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46251.54166666666</v>
+        <v>46252.54166666666</v>
       </c>
       <c r="B54">
-        <v>289.749</v>
+        <v>966.114</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46251.55208333334</v>
+        <v>46252.55208333334</v>
       </c>
       <c r="B55">
-        <v>307.091</v>
+        <v>975.074</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46251.5625</v>
+        <v>46252.5625</v>
       </c>
       <c r="B56">
-        <v>324.777</v>
+        <v>982.896</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46251.57291666666</v>
+        <v>46252.57291666666</v>
       </c>
       <c r="B57">
-        <v>342.686</v>
+        <v>991.417</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46251.58333333334</v>
+        <v>46252.58333333334</v>
       </c>
       <c r="B58">
-        <v>380.907</v>
+        <v>1035.641</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46251.59375</v>
+        <v>46252.59375</v>
       </c>
       <c r="B59">
-        <v>400.757</v>
+        <v>1045.629</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46251.60416666666</v>
+        <v>46252.60416666666</v>
       </c>
       <c r="B60">
-        <v>420.084</v>
+        <v>1054.814</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46251.61458333334</v>
+        <v>46252.61458333334</v>
       </c>
       <c r="B61">
-        <v>439.019</v>
+        <v>1063.681</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46251.625</v>
+        <v>46252.625</v>
       </c>
       <c r="B62">
-        <v>467.191</v>
+        <v>1010.984</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46251.63541666666</v>
+        <v>46252.63541666666</v>
       </c>
       <c r="B63">
-        <v>489.304</v>
+        <v>1019.439</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46251.64583333334</v>
+        <v>46252.64583333334</v>
       </c>
       <c r="B64">
-        <v>510.689</v>
+        <v>1029.364</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46251.65625</v>
+        <v>46252.65625</v>
       </c>
       <c r="B65">
-        <v>531.907</v>
+        <v>1039.548</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46251.66666666666</v>
+        <v>46252.66666666666</v>
       </c>
       <c r="B66">
-        <v>555.821</v>
+        <v>1042.402</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46251.67708333334</v>
+        <v>46252.67708333334</v>
       </c>
       <c r="B67">
-        <v>578.954</v>
+        <v>1043.268</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46251.6875</v>
+        <v>46252.6875</v>
       </c>
       <c r="B68">
-        <v>602.323</v>
+        <v>1042.591</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46251.69791666666</v>
+        <v>46252.69791666666</v>
       </c>
       <c r="B69">
-        <v>624.869</v>
+        <v>1043.505</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46251.70833333334</v>
+        <v>46252.70833333334</v>
       </c>
       <c r="B70">
-        <v>576.5359999999999</v>
+        <v>1056.059</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46251.71875</v>
+        <v>46252.71875</v>
       </c>
       <c r="B71">
-        <v>595.336</v>
+        <v>1055.94</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46251.72916666666</v>
+        <v>46252.72916666666</v>
       </c>
       <c r="B72">
-        <v>614.861</v>
+        <v>1055.318</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46251.73958333334</v>
+        <v>46252.73958333334</v>
       </c>
       <c r="B73">
-        <v>635.681</v>
+        <v>1053.817</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46251.75</v>
+        <v>46252.75</v>
       </c>
       <c r="B74">
-        <v>682.905</v>
+        <v>1007.952</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46251.76041666666</v>
+        <v>46252.76041666666</v>
       </c>
       <c r="B75">
-        <v>725.941</v>
+        <v>1006.5</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46251.77083333334</v>
+        <v>46252.77083333334</v>
       </c>
       <c r="B76">
-        <v>769.203</v>
+        <v>1004.146</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46251.78125</v>
+        <v>46252.78125</v>
       </c>
       <c r="B77">
-        <v>815.124</v>
+        <v>1001.035</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46251.79166666666</v>
+        <v>46252.79166666666</v>
       </c>
       <c r="B78">
-        <v>901.727</v>
+        <v>985.693</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46251.80208333334</v>
+        <v>46252.80208333334</v>
       </c>
       <c r="B79">
-        <v>952.554</v>
+        <v>974.893</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46251.8125</v>
+        <v>46252.8125</v>
       </c>
       <c r="B80">
-        <v>1002.492</v>
+        <v>965.635</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46251.82291666666</v>
+        <v>46252.82291666666</v>
       </c>
       <c r="B81">
-        <v>1053.082</v>
+        <v>959.753</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46251.83333333334</v>
+        <v>46252.83333333334</v>
       </c>
       <c r="B82">
-        <v>1135.355</v>
+        <v>944.0940000000001</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46251.84375</v>
+        <v>46252.84375</v>
       </c>
       <c r="B83">
-        <v>1153.282</v>
+        <v>935.718</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46251.85416666666</v>
+        <v>46252.85416666666</v>
       </c>
       <c r="B84">
-        <v>1170.008</v>
+        <v>931.732</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46251.86458333334</v>
+        <v>46252.86458333334</v>
       </c>
       <c r="B85">
-        <v>1185.842</v>
+        <v>948.181</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46251.875</v>
+        <v>46252.875</v>
       </c>
       <c r="B86">
-        <v>1195.462</v>
+        <v>962.288</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46251.88541666666</v>
+        <v>46252.88541666666</v>
       </c>
       <c r="B87">
-        <v>1199.911</v>
+        <v>968.285</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46251.89583333334</v>
+        <v>46252.89583333334</v>
       </c>
       <c r="B88">
-        <v>1204.549</v>
+        <v>973.995</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46251.90625</v>
+        <v>46252.90625</v>
       </c>
       <c r="B89">
-        <v>1209.19</v>
+        <v>979.014</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46251.91666666666</v>
+        <v>46252.91666666666</v>
       </c>
       <c r="B90">
-        <v>1213.141</v>
+        <v>998.9109999999999</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46251.92708333334</v>
+        <v>46252.92708333334</v>
       </c>
       <c r="B91">
-        <v>1213.841</v>
+        <v>996.407</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46251.9375</v>
+        <v>46252.9375</v>
       </c>
       <c r="B92">
-        <v>1215.035</v>
+        <v>1014.686</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46251.94791666666</v>
+        <v>46252.94791666666</v>
       </c>
       <c r="B93">
-        <v>1216.91</v>
+        <v>1031.047</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B189"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,738 +394,1506 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B2">
-        <v>1175.964</v>
+        <v>1344.495</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46252.01041666666</v>
+        <v>46253.01041666666</v>
       </c>
       <c r="B3">
-        <v>1168.757</v>
+        <v>1306.978</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46252.02083333334</v>
+        <v>46253.02083333334</v>
       </c>
       <c r="B4">
-        <v>1172.745</v>
+        <v>1288.924</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46252.03125</v>
+        <v>46253.03125</v>
       </c>
       <c r="B5">
-        <v>1163.486</v>
+        <v>1252.444</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46252.04166666666</v>
+        <v>46253.04166666666</v>
       </c>
       <c r="B6">
-        <v>1141.859</v>
+        <v>1206.737</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46252.05208333334</v>
+        <v>46253.05208333334</v>
       </c>
       <c r="B7">
-        <v>1129.075</v>
+        <v>1183.74</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46252.0625</v>
+        <v>46253.0625</v>
       </c>
       <c r="B8">
-        <v>1103.162</v>
+        <v>1139.272</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46252.07291666666</v>
+        <v>46253.07291666666</v>
       </c>
       <c r="B9">
-        <v>1094.345</v>
+        <v>1087.922</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46252.08333333334</v>
+        <v>46253.08333333334</v>
       </c>
       <c r="B10">
-        <v>1080.845</v>
+        <v>999.347</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46252.09375</v>
+        <v>46253.09375</v>
       </c>
       <c r="B11">
-        <v>1066.591</v>
+        <v>948.38</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46252.10416666666</v>
+        <v>46253.10416666666</v>
       </c>
       <c r="B12">
-        <v>1059.409</v>
+        <v>906.348</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46252.11458333334</v>
+        <v>46253.11458333334</v>
       </c>
       <c r="B13">
-        <v>1050.111</v>
+        <v>863.183</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46252.125</v>
+        <v>46253.125</v>
       </c>
       <c r="B14">
-        <v>1059.622</v>
+        <v>746.581</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46252.13541666666</v>
+        <v>46253.13541666666</v>
       </c>
       <c r="B15">
-        <v>1048.092</v>
+        <v>706.611</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46252.14583333334</v>
+        <v>46253.14583333334</v>
       </c>
       <c r="B16">
-        <v>1035.006</v>
+        <v>666.3680000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46252.15625</v>
+        <v>46253.15625</v>
       </c>
       <c r="B17">
-        <v>1021.403</v>
+        <v>626.728</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46252.16666666666</v>
+        <v>46253.16666666666</v>
       </c>
       <c r="B18">
-        <v>1018.864</v>
+        <v>506.221</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46252.17708333334</v>
+        <v>46253.17708333334</v>
       </c>
       <c r="B19">
-        <v>1006.036</v>
+        <v>476.495</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46252.1875</v>
+        <v>46253.1875</v>
       </c>
       <c r="B20">
-        <v>998.326</v>
+        <v>447.486</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46252.19791666666</v>
+        <v>46253.19791666666</v>
       </c>
       <c r="B21">
-        <v>985.023</v>
+        <v>414.017</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46252.20833333334</v>
+        <v>46253.20833333334</v>
       </c>
       <c r="B22">
-        <v>981.824</v>
+        <v>339.243</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46252.21875</v>
+        <v>46253.21875</v>
       </c>
       <c r="B23">
-        <v>975.299</v>
+        <v>312.691</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46252.22916666666</v>
+        <v>46253.22916666666</v>
       </c>
       <c r="B24">
-        <v>971.307</v>
+        <v>285.964</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46252.23958333334</v>
+        <v>46253.23958333334</v>
       </c>
       <c r="B25">
-        <v>966.6559999999999</v>
+        <v>258.963</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46252.25</v>
+        <v>46253.25</v>
       </c>
       <c r="B26">
-        <v>863.165</v>
+        <v>213.184</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46252.26041666666</v>
+        <v>46253.26041666666</v>
       </c>
       <c r="B27">
-        <v>851.412</v>
+        <v>194.176</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46252.27083333334</v>
+        <v>46253.27083333334</v>
       </c>
       <c r="B28">
-        <v>838.171</v>
+        <v>179.111</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46252.28125</v>
+        <v>46253.28125</v>
       </c>
       <c r="B29">
-        <v>827.503</v>
+        <v>162.545</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46252.29166666666</v>
+        <v>46253.29166666666</v>
       </c>
       <c r="B30">
-        <v>850.266</v>
+        <v>146.196</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46252.30208333334</v>
+        <v>46253.30208333334</v>
       </c>
       <c r="B31">
-        <v>816.904</v>
+        <v>136.418</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46252.3125</v>
+        <v>46253.3125</v>
       </c>
       <c r="B32">
-        <v>771.533</v>
+        <v>126.034</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46252.32291666666</v>
+        <v>46253.32291666666</v>
       </c>
       <c r="B33">
-        <v>735.962</v>
+        <v>116.049</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46252.33333333334</v>
+        <v>46253.33333333334</v>
       </c>
       <c r="B34">
-        <v>707.327</v>
+        <v>116.477</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46252.34375</v>
+        <v>46253.34375</v>
       </c>
       <c r="B35">
-        <v>692.755</v>
+        <v>111.35</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46252.35416666666</v>
+        <v>46253.35416666666</v>
       </c>
       <c r="B36">
-        <v>681.3049999999999</v>
+        <v>110.647</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46252.36458333334</v>
+        <v>46253.36458333334</v>
       </c>
       <c r="B37">
-        <v>670.603</v>
+        <v>111.582</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46252.375</v>
+        <v>46253.375</v>
       </c>
       <c r="B38">
-        <v>668.66</v>
+        <v>120.039</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46252.38541666666</v>
+        <v>46253.38541666666</v>
       </c>
       <c r="B39">
-        <v>682.103</v>
+        <v>126.135</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46252.39583333334</v>
+        <v>46253.39583333334</v>
       </c>
       <c r="B40">
-        <v>695.1559999999999</v>
+        <v>132.083</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46252.40625</v>
+        <v>46253.40625</v>
       </c>
       <c r="B41">
-        <v>709.277</v>
+        <v>138.51</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46252.41666666666</v>
+        <v>46253.41666666666</v>
       </c>
       <c r="B42">
-        <v>783.889</v>
+        <v>154.227</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46252.42708333334</v>
+        <v>46253.42708333334</v>
       </c>
       <c r="B43">
-        <v>806.467</v>
+        <v>165.556</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46252.4375</v>
+        <v>46253.4375</v>
       </c>
       <c r="B44">
-        <v>829.981</v>
+        <v>174.627</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46252.44791666666</v>
+        <v>46253.44791666666</v>
       </c>
       <c r="B45">
-        <v>853.947</v>
+        <v>182.133</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46252.45833333334</v>
+        <v>46253.45833333334</v>
       </c>
       <c r="B46">
-        <v>875.476</v>
+        <v>185.785</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46252.46875</v>
+        <v>46253.46875</v>
       </c>
       <c r="B47">
-        <v>890.152</v>
+        <v>193.849</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46252.47916666666</v>
+        <v>46253.47916666666</v>
       </c>
       <c r="B48">
-        <v>906.537</v>
+        <v>201.075</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46252.48958333334</v>
+        <v>46253.48958333334</v>
       </c>
       <c r="B49">
-        <v>922.316</v>
+        <v>207.893</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46252.5</v>
+        <v>46253.5</v>
       </c>
       <c r="B50">
-        <v>932.119</v>
+        <v>212.777</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46252.51041666666</v>
+        <v>46253.51041666666</v>
       </c>
       <c r="B51">
-        <v>939.527</v>
+        <v>221.339</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46252.52083333334</v>
+        <v>46253.52083333334</v>
       </c>
       <c r="B52">
-        <v>945.864</v>
+        <v>230.911</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46252.53125</v>
+        <v>46253.53125</v>
       </c>
       <c r="B53">
-        <v>952.317</v>
+        <v>240.521</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46252.54166666666</v>
+        <v>46253.54166666666</v>
       </c>
       <c r="B54">
-        <v>966.114</v>
+        <v>254.697</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46252.55208333334</v>
+        <v>46253.55208333334</v>
       </c>
       <c r="B55">
-        <v>975.074</v>
+        <v>261.207</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46252.5625</v>
+        <v>46253.5625</v>
       </c>
       <c r="B56">
-        <v>982.896</v>
+        <v>267.189</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46252.57291666666</v>
+        <v>46253.57291666666</v>
       </c>
       <c r="B57">
-        <v>991.417</v>
+        <v>273.766</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46252.58333333334</v>
+        <v>46253.58333333334</v>
       </c>
       <c r="B58">
-        <v>1035.641</v>
+        <v>276.797</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46252.59375</v>
+        <v>46253.59375</v>
       </c>
       <c r="B59">
-        <v>1045.629</v>
+        <v>282.918</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46252.60416666666</v>
+        <v>46253.60416666666</v>
       </c>
       <c r="B60">
-        <v>1054.814</v>
+        <v>290.553</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46252.61458333334</v>
+        <v>46253.61458333334</v>
       </c>
       <c r="B61">
-        <v>1063.681</v>
+        <v>297.66</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46252.625</v>
+        <v>46253.625</v>
       </c>
       <c r="B62">
-        <v>1010.984</v>
+        <v>317.308</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46252.63541666666</v>
+        <v>46253.63541666666</v>
       </c>
       <c r="B63">
-        <v>1019.439</v>
+        <v>321.27</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46252.64583333334</v>
+        <v>46253.64583333334</v>
       </c>
       <c r="B64">
-        <v>1029.364</v>
+        <v>321.083</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46252.65625</v>
+        <v>46253.65625</v>
       </c>
       <c r="B65">
-        <v>1039.548</v>
+        <v>317.445</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46252.66666666666</v>
+        <v>46253.66666666666</v>
       </c>
       <c r="B66">
-        <v>1042.402</v>
+        <v>300.095</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46252.67708333334</v>
+        <v>46253.67708333334</v>
       </c>
       <c r="B67">
-        <v>1043.268</v>
+        <v>296.553</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46252.6875</v>
+        <v>46253.6875</v>
       </c>
       <c r="B68">
-        <v>1042.591</v>
+        <v>293.413</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46252.69791666666</v>
+        <v>46253.69791666666</v>
       </c>
       <c r="B69">
-        <v>1043.505</v>
+        <v>292.534</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46252.70833333334</v>
+        <v>46253.70833333334</v>
       </c>
       <c r="B70">
-        <v>1056.059</v>
+        <v>280.72</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46252.71875</v>
+        <v>46253.71875</v>
       </c>
       <c r="B71">
-        <v>1055.94</v>
+        <v>280.664</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46252.72916666666</v>
+        <v>46253.72916666666</v>
       </c>
       <c r="B72">
-        <v>1055.318</v>
+        <v>280.932</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46252.73958333334</v>
+        <v>46253.73958333334</v>
       </c>
       <c r="B73">
-        <v>1053.817</v>
+        <v>281.371</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46252.75</v>
+        <v>46253.75</v>
       </c>
       <c r="B74">
-        <v>1007.952</v>
+        <v>298.553</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46252.76041666666</v>
+        <v>46253.76041666666</v>
       </c>
       <c r="B75">
-        <v>1006.5</v>
+        <v>304.286</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46252.77083333334</v>
+        <v>46253.77083333334</v>
       </c>
       <c r="B76">
-        <v>1004.146</v>
+        <v>311.952</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46252.78125</v>
+        <v>46253.78125</v>
       </c>
       <c r="B77">
-        <v>1001.035</v>
+        <v>320.037</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46252.79166666666</v>
+        <v>46253.79166666666</v>
       </c>
       <c r="B78">
-        <v>985.693</v>
+        <v>328.129</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46252.80208333334</v>
+        <v>46253.80208333334</v>
       </c>
       <c r="B79">
-        <v>974.893</v>
+        <v>345.134</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46252.8125</v>
+        <v>46253.8125</v>
       </c>
       <c r="B80">
-        <v>965.635</v>
+        <v>362.783</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46252.82291666666</v>
+        <v>46253.82291666666</v>
       </c>
       <c r="B81">
-        <v>959.753</v>
+        <v>382.063</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46252.83333333334</v>
+        <v>46253.83333333334</v>
       </c>
       <c r="B82">
-        <v>944.0940000000001</v>
+        <v>399.227</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46252.84375</v>
+        <v>46253.84375</v>
       </c>
       <c r="B83">
-        <v>935.718</v>
+        <v>420.886</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46252.85416666666</v>
+        <v>46253.85416666666</v>
       </c>
       <c r="B84">
-        <v>931.732</v>
+        <v>443.122</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46252.86458333334</v>
+        <v>46253.86458333334</v>
       </c>
       <c r="B85">
-        <v>948.181</v>
+        <v>466.085</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46252.875</v>
+        <v>46253.875</v>
       </c>
       <c r="B86">
-        <v>962.288</v>
+        <v>481.731</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46252.88541666666</v>
+        <v>46253.88541666666</v>
       </c>
       <c r="B87">
-        <v>968.285</v>
+        <v>496.96</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46252.89583333334</v>
+        <v>46253.89583333334</v>
       </c>
       <c r="B88">
-        <v>973.995</v>
+        <v>512.047</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46252.90625</v>
+        <v>46253.90625</v>
       </c>
       <c r="B89">
-        <v>979.014</v>
+        <v>527.039</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46252.91666666666</v>
+        <v>46253.91666666666</v>
       </c>
       <c r="B90">
-        <v>998.9109999999999</v>
+        <v>535.75</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46252.92708333334</v>
+        <v>46253.92708333334</v>
       </c>
       <c r="B91">
-        <v>996.407</v>
+        <v>539.009</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46252.9375</v>
+        <v>46253.9375</v>
       </c>
       <c r="B92">
-        <v>1014.686</v>
+        <v>543.229</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46252.94791666666</v>
+        <v>46253.94791666666</v>
       </c>
       <c r="B93">
-        <v>1031.047</v>
+        <v>545.997</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46253.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>525.172</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46253.96875</v>
+      </c>
+      <c r="B95">
+        <v>525.4400000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46253.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>518.587</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46253.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>515.659</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46254</v>
+      </c>
+      <c r="B98">
+        <v>550.463</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46254.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>548.9589999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46254.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>550.672</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46254.03125</v>
+      </c>
+      <c r="B101">
+        <v>551.011</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46254.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>549.106</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46254.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>541.265</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46254.0625</v>
+      </c>
+      <c r="B104">
+        <v>544.361</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46254.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>537.6130000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46254.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>529.347</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46254.09375</v>
+      </c>
+      <c r="B107">
+        <v>519.711</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46254.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>517.672</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46254.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>509.718</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46254.125</v>
+      </c>
+      <c r="B110">
+        <v>502.887</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46254.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>498.069</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46254.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>493.125</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46254.15625</v>
+      </c>
+      <c r="B113">
+        <v>488.122</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46254.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>473.168</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46254.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>463.592</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46254.1875</v>
+      </c>
+      <c r="B116">
+        <v>457.005</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46254.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>451.187</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46254.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>455.172</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46254.21875</v>
+      </c>
+      <c r="B119">
+        <v>452.468</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46254.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>447.223</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46254.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>443.526</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46254.25</v>
+      </c>
+      <c r="B122">
+        <v>437.275</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46254.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>431.081</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46254.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>441.806</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46254.28125</v>
+      </c>
+      <c r="B125">
+        <v>438.604</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46254.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>438.575</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46254.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>419.094</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46254.3125</v>
+      </c>
+      <c r="B128">
+        <v>397.058</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46254.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>379.613</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46254.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>375.374</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46254.34375</v>
+      </c>
+      <c r="B131">
+        <v>367.27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46254.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>334.501</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46254.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>328.61</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46254.375</v>
+      </c>
+      <c r="B134">
+        <v>375.239</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46254.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>394.398</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46254.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>416.255</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46254.40625</v>
+      </c>
+      <c r="B137">
+        <v>437.889</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46254.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>448.979</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46254.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>478.24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46254.4375</v>
+      </c>
+      <c r="B140">
+        <v>508.959</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46254.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>540.206</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46254.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>612.9450000000001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46254.46875</v>
+      </c>
+      <c r="B143">
+        <v>643.718</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46254.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>674.528</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46254.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>706.057</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46254.5</v>
+      </c>
+      <c r="B146">
+        <v>756.484</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46254.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>787.818</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46254.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>818.88</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46254.53125</v>
+      </c>
+      <c r="B149">
+        <v>849.534</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46254.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>894.221</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46254.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>934.7380000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46254.5625</v>
+      </c>
+      <c r="B152">
+        <v>973.827</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46254.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>1013.471</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46254.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>1075.093</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46254.59375</v>
+      </c>
+      <c r="B155">
+        <v>1114.85</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46254.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>1152.648</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46254.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>1190.7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46254.625</v>
+      </c>
+      <c r="B158">
+        <v>1251.611</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46254.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>1286.403</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46254.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>1319.902</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46254.65625</v>
+      </c>
+      <c r="B161">
+        <v>1351.993</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46254.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>1307.655</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46254.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>1330.836</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46254.6875</v>
+      </c>
+      <c r="B164">
+        <v>1353.465</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46254.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>1376.235</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46254.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>1409.788</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46254.71875</v>
+      </c>
+      <c r="B167">
+        <v>1440.649</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46254.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>1474.092</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46254.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>1506.642</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46254.75</v>
+      </c>
+      <c r="B170">
+        <v>1614.463</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46254.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>1649.719</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46254.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>1685.103</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46254.78125</v>
+      </c>
+      <c r="B173">
+        <v>1720.972</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46254.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>1758.839</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46254.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>1785.963</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46254.8125</v>
+      </c>
+      <c r="B176">
+        <v>1815.863</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46254.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>1848.81</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46254.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>1878.86</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46254.84375</v>
+      </c>
+      <c r="B179">
+        <v>1881.052</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46254.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>1882.958</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46254.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>1883.735</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46254.875</v>
+      </c>
+      <c r="B182">
+        <v>1875.06</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46254.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>1865.733</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46254.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>1863.364</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46254.90625</v>
+      </c>
+      <c r="B185">
+        <v>1868.548</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46254.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>1890.85</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46254.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>1884.78</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
+        <v>46254.9375</v>
+      </c>
+      <c r="B188">
+        <v>1873.843</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46254.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>1855.898</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="B2">
-        <v>518.453</v>
+        <v>1076.771</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46259.01041666666</v>
+        <v>46262.01041666666</v>
       </c>
       <c r="B3">
-        <v>496.937</v>
+        <v>1127.41</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46259.02083333334</v>
+        <v>46262.02083333334</v>
       </c>
       <c r="B4">
-        <v>461.068</v>
+        <v>1171.979</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46259.03125</v>
+        <v>46262.03125</v>
       </c>
       <c r="B5">
-        <v>421.968</v>
+        <v>1219.721</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46259.04166666666</v>
+        <v>46262.04166666666</v>
       </c>
       <c r="B6">
-        <v>390.384</v>
+        <v>1243.039</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46259.05208333334</v>
+        <v>46262.05208333334</v>
       </c>
       <c r="B7">
-        <v>352</v>
+        <v>1277.882</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46259.0625</v>
+        <v>46262.0625</v>
       </c>
       <c r="B8">
-        <v>336.737</v>
+        <v>1309.763</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46259.07291666666</v>
+        <v>46262.07291666666</v>
       </c>
       <c r="B9">
-        <v>312.698</v>
+        <v>1343.579</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46259.08333333334</v>
+        <v>46262.08333333334</v>
       </c>
       <c r="B10">
-        <v>288.588</v>
+        <v>1369.167</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46259.09375</v>
+        <v>46262.09375</v>
       </c>
       <c r="B11">
-        <v>296.027</v>
+        <v>1375.355</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46259.10416666666</v>
+        <v>46262.10416666666</v>
       </c>
       <c r="B12">
-        <v>267.413</v>
+        <v>1383.592</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46259.11458333334</v>
+        <v>46262.11458333334</v>
       </c>
       <c r="B13">
-        <v>248.925</v>
+        <v>1393.941</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46259.125</v>
+        <v>46262.125</v>
       </c>
       <c r="B14">
-        <v>245.679</v>
+        <v>1404.575</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46259.13541666666</v>
+        <v>46262.13541666666</v>
       </c>
       <c r="B15">
-        <v>228.875</v>
+        <v>1418.894</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46259.14583333334</v>
+        <v>46262.14583333334</v>
       </c>
       <c r="B16">
-        <v>226.572</v>
+        <v>1443.205</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46259.15625</v>
+        <v>46262.15625</v>
       </c>
       <c r="B17">
-        <v>221.914</v>
+        <v>1462.642</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46259.16666666666</v>
+        <v>46262.16666666666</v>
       </c>
       <c r="B18">
-        <v>227.417</v>
+        <v>1558.514</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46259.17708333334</v>
+        <v>46262.17708333334</v>
       </c>
       <c r="B19">
-        <v>228</v>
+        <v>1547.731</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46259.1875</v>
+        <v>46262.1875</v>
       </c>
       <c r="B20">
-        <v>220.316</v>
+        <v>1554.165</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46259.19791666666</v>
+        <v>46262.19791666666</v>
       </c>
       <c r="B21">
-        <v>237.094</v>
+        <v>1567.359</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46259.20833333334</v>
+        <v>46262.20833333334</v>
       </c>
       <c r="B22">
-        <v>240.412</v>
+        <v>1588.332</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46259.21875</v>
+        <v>46262.21875</v>
       </c>
       <c r="B23">
-        <v>247.56</v>
+        <v>1577.331</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46259.22916666666</v>
+        <v>46262.22916666666</v>
       </c>
       <c r="B24">
-        <v>252.991</v>
+        <v>1576.617</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46259.23958333334</v>
+        <v>46262.23958333334</v>
       </c>
       <c r="B25">
-        <v>273.352</v>
+        <v>1554.963</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46259.25</v>
+        <v>46262.25</v>
       </c>
       <c r="B26">
-        <v>295.028</v>
+        <v>1522.136</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46259.26041666666</v>
+        <v>46262.26041666666</v>
       </c>
       <c r="B27">
-        <v>305.662</v>
+        <v>1510.874</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46259.27083333334</v>
+        <v>46262.27083333334</v>
       </c>
       <c r="B28">
-        <v>317.138</v>
+        <v>1490.558</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46259.28125</v>
+        <v>46262.28125</v>
       </c>
       <c r="B29">
-        <v>327.829</v>
+        <v>1471.053</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46259.29166666666</v>
+        <v>46262.29166666666</v>
       </c>
       <c r="B30">
-        <v>376.792</v>
+        <v>1411.365</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46259.30208333334</v>
+        <v>46262.30208333334</v>
       </c>
       <c r="B31">
-        <v>389.317</v>
+        <v>1424.498</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46259.3125</v>
+        <v>46262.3125</v>
       </c>
       <c r="B32">
-        <v>399.891</v>
+        <v>1434.088</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46259.32291666666</v>
+        <v>46262.32291666666</v>
       </c>
       <c r="B33">
-        <v>418.854</v>
+        <v>1443.177</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46259.33333333334</v>
+        <v>46262.33333333334</v>
       </c>
       <c r="B34">
-        <v>482.94</v>
+        <v>1465.467</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46259.34375</v>
+        <v>46262.34375</v>
       </c>
       <c r="B35">
-        <v>510.731</v>
+        <v>1504.687</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46259.35416666666</v>
+        <v>46262.35416666666</v>
       </c>
       <c r="B36">
-        <v>519.5359999999999</v>
+        <v>1517.822</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46259.36458333334</v>
+        <v>46262.36458333334</v>
       </c>
       <c r="B37">
-        <v>532.721</v>
+        <v>1593.914</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46259.375</v>
+        <v>46262.375</v>
       </c>
       <c r="B38">
-        <v>540.9109999999999</v>
+        <v>1824.375</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46259.38541666666</v>
+        <v>46262.38541666666</v>
       </c>
       <c r="B39">
-        <v>555.451</v>
+        <v>1889.771</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46259.39583333334</v>
+        <v>46262.39583333334</v>
       </c>
       <c r="B40">
-        <v>568.96</v>
+        <v>1952.405</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46259.40625</v>
+        <v>46262.40625</v>
       </c>
       <c r="B41">
-        <v>582.553</v>
+        <v>2009.305</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46259.41666666666</v>
+        <v>46262.41666666666</v>
       </c>
       <c r="B42">
-        <v>531.562</v>
+        <v>2225.301</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46259.42708333334</v>
+        <v>46262.42708333334</v>
       </c>
       <c r="B43">
-        <v>541.782</v>
+        <v>2276.44</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46259.4375</v>
+        <v>46262.4375</v>
       </c>
       <c r="B44">
-        <v>552.624</v>
+        <v>2327.317</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46259.44791666666</v>
+        <v>46262.44791666666</v>
       </c>
       <c r="B45">
-        <v>563.01</v>
+        <v>2377.195</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46259.45833333334</v>
+        <v>46262.45833333334</v>
       </c>
       <c r="B46">
-        <v>534.679</v>
+        <v>2392.438</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46259.46875</v>
+        <v>46262.46875</v>
       </c>
       <c r="B47">
-        <v>554.987</v>
+        <v>2421.499</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46259.47916666666</v>
+        <v>46262.47916666666</v>
       </c>
       <c r="B48">
-        <v>575.704</v>
+        <v>2446.772</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46259.48958333334</v>
+        <v>46262.48958333334</v>
       </c>
       <c r="B49">
-        <v>595.7190000000001</v>
+        <v>2471.516</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46259.5</v>
+        <v>46262.5</v>
       </c>
       <c r="B50">
-        <v>621.111</v>
+        <v>2485.562</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46259.51041666666</v>
+        <v>46262.51041666666</v>
       </c>
       <c r="B51">
-        <v>645.601</v>
+        <v>2492.083</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46259.52083333334</v>
+        <v>46262.52083333334</v>
       </c>
       <c r="B52">
-        <v>668.586</v>
+        <v>2497.74</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46259.53125</v>
+        <v>46262.53125</v>
       </c>
       <c r="B53">
-        <v>693.7569999999999</v>
+        <v>2504.273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46259.54166666666</v>
+        <v>46262.54166666666</v>
       </c>
       <c r="B54">
-        <v>726.623</v>
+        <v>2516.016</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46259.55208333334</v>
+        <v>46262.55208333334</v>
       </c>
       <c r="B55">
-        <v>753.112</v>
+        <v>2511.679</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46259.5625</v>
+        <v>46262.5625</v>
       </c>
       <c r="B56">
-        <v>777.658</v>
+        <v>2504.439</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46259.57291666666</v>
+        <v>46262.57291666666</v>
       </c>
       <c r="B57">
-        <v>801.64</v>
+        <v>2496.61</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46259.58333333334</v>
+        <v>46262.58333333334</v>
       </c>
       <c r="B58">
-        <v>846.376</v>
+        <v>2585.335</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46259.59375</v>
+        <v>46262.59375</v>
       </c>
       <c r="B59">
-        <v>874.082</v>
+        <v>2569.5</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46259.60416666666</v>
+        <v>46262.60416666666</v>
       </c>
       <c r="B60">
-        <v>900.294</v>
+        <v>2552.792</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46259.61458333334</v>
+        <v>46262.61458333334</v>
       </c>
       <c r="B61">
-        <v>926.388</v>
+        <v>2536.096</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46259.625</v>
+        <v>46262.625</v>
       </c>
       <c r="B62">
-        <v>960.115</v>
+        <v>2502.511</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46259.63541666666</v>
+        <v>46262.63541666666</v>
       </c>
       <c r="B63">
-        <v>984.4109999999999</v>
+        <v>2472.172</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46259.64583333334</v>
+        <v>46262.64583333334</v>
       </c>
       <c r="B64">
-        <v>1010.169</v>
+        <v>2443.576</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46259.65625</v>
+        <v>46262.65625</v>
       </c>
       <c r="B65">
-        <v>1034.807</v>
+        <v>2415.378</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46259.66666666666</v>
+        <v>46262.66666666666</v>
       </c>
       <c r="B66">
-        <v>1060.146</v>
+        <v>2311.691</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46259.67708333334</v>
+        <v>46262.67708333334</v>
       </c>
       <c r="B67">
-        <v>1074.686</v>
+        <v>2274.883</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46259.6875</v>
+        <v>46262.6875</v>
       </c>
       <c r="B68">
-        <v>1088.455</v>
+        <v>2235.776</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46259.69791666666</v>
+        <v>46262.69791666666</v>
       </c>
       <c r="B69">
-        <v>1102.188</v>
+        <v>2196.28</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46259.70833333334</v>
+        <v>46262.70833333334</v>
       </c>
       <c r="B70">
-        <v>1120.69</v>
+        <v>2121.071</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46259.71875</v>
+        <v>46262.71875</v>
       </c>
       <c r="B71">
-        <v>1121.166</v>
+        <v>2040.969</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46259.72916666666</v>
+        <v>46262.72916666666</v>
       </c>
       <c r="B72">
-        <v>1120.937</v>
+        <v>1957.849</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46259.73958333334</v>
+        <v>46262.73958333334</v>
       </c>
       <c r="B73">
-        <v>1122.994</v>
+        <v>1874.196</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46259.75</v>
+        <v>46262.75</v>
       </c>
       <c r="B74">
-        <v>1027.947</v>
+        <v>1772.885</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46259.76041666666</v>
+        <v>46262.76041666666</v>
       </c>
       <c r="B75">
-        <v>1038.551</v>
+        <v>1698.273</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46259.77083333334</v>
+        <v>46262.77083333334</v>
       </c>
       <c r="B76">
-        <v>1055.748</v>
+        <v>1625.255</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46259.78125</v>
+        <v>46262.78125</v>
       </c>
       <c r="B77">
-        <v>1079.649</v>
+        <v>1553.008</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46259.79166666666</v>
+        <v>46262.79166666666</v>
       </c>
       <c r="B78">
-        <v>1133.737</v>
+        <v>1478.008</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46259.80208333334</v>
+        <v>46262.80208333334</v>
       </c>
       <c r="B79">
-        <v>1160.946</v>
+        <v>1439.24</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46259.8125</v>
+        <v>46262.8125</v>
       </c>
       <c r="B80">
-        <v>1182.61</v>
+        <v>1403.196</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46259.82291666666</v>
+        <v>46262.82291666666</v>
       </c>
       <c r="B81">
-        <v>1199.182</v>
+        <v>1369.622</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46259.83333333334</v>
+        <v>46262.83333333334</v>
       </c>
       <c r="B82">
-        <v>1211.308</v>
+        <v>1354.858</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46259.84375</v>
+        <v>46262.84375</v>
       </c>
       <c r="B83">
-        <v>1213.089</v>
+        <v>1353.929</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46259.85416666666</v>
+        <v>46262.85416666666</v>
       </c>
       <c r="B84">
-        <v>1212.544</v>
+        <v>1352.827</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46259.86458333334</v>
+        <v>46262.86458333334</v>
       </c>
       <c r="B85">
-        <v>1209.508</v>
+        <v>1354.014</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46259.875</v>
+        <v>46262.875</v>
       </c>
       <c r="B86">
-        <v>1190.522</v>
+        <v>1355.778</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46259.88541666666</v>
+        <v>46262.88541666666</v>
       </c>
       <c r="B87">
-        <v>1176.602</v>
+        <v>1364.601</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46259.89583333334</v>
+        <v>46262.89583333334</v>
       </c>
       <c r="B88">
-        <v>1163.484</v>
+        <v>1373.596</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46259.90625</v>
+        <v>46262.90625</v>
       </c>
       <c r="B89">
-        <v>1151.402</v>
+        <v>1381.877</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46259.91666666666</v>
+        <v>46262.91666666666</v>
       </c>
       <c r="B90">
-        <v>1137.583</v>
+        <v>1379.203</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46259.92708333334</v>
+        <v>46262.92708333334</v>
       </c>
       <c r="B91">
-        <v>1122.732</v>
+        <v>1376.77</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46259.9375</v>
+        <v>46262.9375</v>
       </c>
       <c r="B92">
-        <v>1109.212</v>
+        <v>1375.357</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46259.94791666666</v>
+        <v>46262.94791666666</v>
       </c>
       <c r="B93">
-        <v>1098.433</v>
+        <v>1375.219</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Wind.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Wind.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="B2">
-        <v>1076.771</v>
+        <v>177.573</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46262.01041666666</v>
+        <v>46269.01041666666</v>
       </c>
       <c r="B3">
-        <v>1127.41</v>
+        <v>172.29</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46262.02083333334</v>
+        <v>46269.02083333334</v>
       </c>
       <c r="B4">
-        <v>1171.979</v>
+        <v>162.283</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46262.03125</v>
+        <v>46269.03125</v>
       </c>
       <c r="B5">
-        <v>1219.721</v>
+        <v>156.43</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46262.04166666666</v>
+        <v>46269.04166666666</v>
       </c>
       <c r="B6">
-        <v>1243.039</v>
+        <v>144.313</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46262.05208333334</v>
+        <v>46269.05208333334</v>
       </c>
       <c r="B7">
-        <v>1277.882</v>
+        <v>135.558</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46262.0625</v>
+        <v>46269.0625</v>
       </c>
       <c r="B8">
-        <v>1309.763</v>
+        <v>131.185</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46262.07291666666</v>
+        <v>46269.07291666666</v>
       </c>
       <c r="B9">
-        <v>1343.579</v>
+        <v>126.733</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46262.08333333334</v>
+        <v>46269.08333333334</v>
       </c>
       <c r="B10">
-        <v>1369.167</v>
+        <v>131.235</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46262.09375</v>
+        <v>46269.09375</v>
       </c>
       <c r="B11">
-        <v>1375.355</v>
+        <v>128.687</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46262.10416666666</v>
+        <v>46269.10416666666</v>
       </c>
       <c r="B12">
-        <v>1383.592</v>
+        <v>126.361</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46262.11458333334</v>
+        <v>46269.11458333334</v>
       </c>
       <c r="B13">
-        <v>1393.941</v>
+        <v>125.147</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46262.125</v>
+        <v>46269.125</v>
       </c>
       <c r="B14">
-        <v>1404.575</v>
+        <v>129.272</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46262.13541666666</v>
+        <v>46269.13541666666</v>
       </c>
       <c r="B15">
-        <v>1418.894</v>
+        <v>129.064</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46262.14583333334</v>
+        <v>46269.14583333334</v>
       </c>
       <c r="B16">
-        <v>1443.205</v>
+        <v>118.502</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46262.15625</v>
+        <v>46269.15625</v>
       </c>
       <c r="B17">
-        <v>1462.642</v>
+        <v>119.618</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46262.16666666666</v>
+        <v>46269.16666666666</v>
       </c>
       <c r="B18">
-        <v>1558.514</v>
+        <v>112.846</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46262.17708333334</v>
+        <v>46269.17708333334</v>
       </c>
       <c r="B19">
-        <v>1547.731</v>
+        <v>120.1</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46262.1875</v>
+        <v>46269.1875</v>
       </c>
       <c r="B20">
-        <v>1554.165</v>
+        <v>118.942</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46262.19791666666</v>
+        <v>46269.19791666666</v>
       </c>
       <c r="B21">
-        <v>1567.359</v>
+        <v>116.596</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46262.20833333334</v>
+        <v>46269.20833333334</v>
       </c>
       <c r="B22">
-        <v>1588.332</v>
+        <v>117.78</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46262.21875</v>
+        <v>46269.21875</v>
       </c>
       <c r="B23">
-        <v>1577.331</v>
+        <v>113.379</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46262.22916666666</v>
+        <v>46269.22916666666</v>
       </c>
       <c r="B24">
-        <v>1576.617</v>
+        <v>108.661</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46262.23958333334</v>
+        <v>46269.23958333334</v>
       </c>
       <c r="B25">
-        <v>1554.963</v>
+        <v>104.269</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46262.25</v>
+        <v>46269.25</v>
       </c>
       <c r="B26">
-        <v>1522.136</v>
+        <v>94.523</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46262.26041666666</v>
+        <v>46269.26041666666</v>
       </c>
       <c r="B27">
-        <v>1510.874</v>
+        <v>92.51600000000001</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46262.27083333334</v>
+        <v>46269.27083333334</v>
       </c>
       <c r="B28">
-        <v>1490.558</v>
+        <v>91.985</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46262.28125</v>
+        <v>46269.28125</v>
       </c>
       <c r="B29">
-        <v>1471.053</v>
+        <v>90.164</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46262.29166666666</v>
+        <v>46269.29166666666</v>
       </c>
       <c r="B30">
-        <v>1411.365</v>
+        <v>96.399</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46262.30208333334</v>
+        <v>46269.30208333334</v>
       </c>
       <c r="B31">
-        <v>1424.498</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46262.3125</v>
+        <v>46269.3125</v>
       </c>
       <c r="B32">
-        <v>1434.088</v>
+        <v>91.349</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46262.32291666666</v>
+        <v>46269.32291666666</v>
       </c>
       <c r="B33">
-        <v>1443.177</v>
+        <v>91.312</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46262.33333333334</v>
+        <v>46269.33333333334</v>
       </c>
       <c r="B34">
-        <v>1465.467</v>
+        <v>104.049</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46262.34375</v>
+        <v>46269.34375</v>
       </c>
       <c r="B35">
-        <v>1504.687</v>
+        <v>103.108</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46262.35416666666</v>
+        <v>46269.35416666666</v>
       </c>
       <c r="B36">
-        <v>1517.822</v>
+        <v>102.311</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46262.36458333334</v>
+        <v>46269.36458333334</v>
       </c>
       <c r="B37">
-        <v>1593.914</v>
+        <v>100.549</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46262.375</v>
+        <v>46269.375</v>
       </c>
       <c r="B38">
-        <v>1824.375</v>
+        <v>100.752</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46262.38541666666</v>
+        <v>46269.38541666666</v>
       </c>
       <c r="B39">
-        <v>1889.771</v>
+        <v>101.581</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46262.39583333334</v>
+        <v>46269.39583333334</v>
       </c>
       <c r="B40">
-        <v>1952.405</v>
+        <v>102.282</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46262.40625</v>
+        <v>46269.40625</v>
       </c>
       <c r="B41">
-        <v>2009.305</v>
+        <v>102.813</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46262.41666666666</v>
+        <v>46269.41666666666</v>
       </c>
       <c r="B42">
-        <v>2225.301</v>
+        <v>101.048</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46262.42708333334</v>
+        <v>46269.42708333334</v>
       </c>
       <c r="B43">
-        <v>2276.44</v>
+        <v>103.606</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46262.4375</v>
+        <v>46269.4375</v>
       </c>
       <c r="B44">
-        <v>2327.317</v>
+        <v>106.81</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46262.44791666666</v>
+        <v>46269.44791666666</v>
       </c>
       <c r="B45">
-        <v>2377.195</v>
+        <v>109.875</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46262.45833333334</v>
+        <v>46269.45833333334</v>
       </c>
       <c r="B46">
-        <v>2392.438</v>
+        <v>113.642</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46262.46875</v>
+        <v>46269.46875</v>
       </c>
       <c r="B47">
-        <v>2421.499</v>
+        <v>119.571</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46262.47916666666</v>
+        <v>46269.47916666666</v>
       </c>
       <c r="B48">
-        <v>2446.772</v>
+        <v>125.654</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46262.48958333334</v>
+        <v>46269.48958333334</v>
       </c>
       <c r="B49">
-        <v>2471.516</v>
+        <v>131.345</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46262.5</v>
+        <v>46269.5</v>
       </c>
       <c r="B50">
-        <v>2485.562</v>
+        <v>139.944</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46262.51041666666</v>
+        <v>46269.51041666666</v>
       </c>
       <c r="B51">
-        <v>2492.083</v>
+        <v>147.358</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46262.52083333334</v>
+        <v>46269.52083333334</v>
       </c>
       <c r="B52">
-        <v>2497.74</v>
+        <v>155.268</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46262.53125</v>
+        <v>46269.53125</v>
       </c>
       <c r="B53">
-        <v>2504.273</v>
+        <v>163.676</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46262.54166666666</v>
+        <v>46269.54166666666</v>
       </c>
       <c r="B54">
-        <v>2516.016</v>
+        <v>173.134</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46262.55208333334</v>
+        <v>46269.55208333334</v>
       </c>
       <c r="B55">
-        <v>2511.679</v>
+        <v>180.053</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46262.5625</v>
+        <v>46269.5625</v>
       </c>
       <c r="B56">
-        <v>2504.439</v>
+        <v>187.611</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46262.57291666666</v>
+        <v>46269.57291666666</v>
       </c>
       <c r="B57">
-        <v>2496.61</v>
+        <v>195.344</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46262.58333333334</v>
+        <v>46269.58333333334</v>
       </c>
       <c r="B58">
-        <v>2585.335</v>
+        <v>209.702</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46262.59375</v>
+        <v>46269.59375</v>
       </c>
       <c r="B59">
-        <v>2569.5</v>
+        <v>216.826</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46262.60416666666</v>
+        <v>46269.60416666666</v>
       </c>
       <c r="B60">
-        <v>2552.792</v>
+        <v>225.029</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46262.61458333334</v>
+        <v>46269.61458333334</v>
       </c>
       <c r="B61">
-        <v>2536.096</v>
+        <v>233.312</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46262.625</v>
+        <v>46269.625</v>
       </c>
       <c r="B62">
-        <v>2502.511</v>
+        <v>221.3</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46262.63541666666</v>
+        <v>46269.63541666666</v>
       </c>
       <c r="B63">
-        <v>2472.172</v>
+        <v>226.323</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46262.64583333334</v>
+        <v>46269.64583333334</v>
       </c>
       <c r="B64">
-        <v>2443.576</v>
+        <v>232.152</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46262.65625</v>
+        <v>46269.65625</v>
       </c>
       <c r="B65">
-        <v>2415.378</v>
+        <v>238.068</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46262.66666666666</v>
+        <v>46269.66666666666</v>
       </c>
       <c r="B66">
-        <v>2311.691</v>
+        <v>245.109</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46262.67708333334</v>
+        <v>46269.67708333334</v>
       </c>
       <c r="B67">
-        <v>2274.883</v>
+        <v>247.26</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46262.6875</v>
+        <v>46269.6875</v>
       </c>
       <c r="B68">
-        <v>2235.776</v>
+        <v>248.325</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46262.69791666666</v>
+        <v>46269.69791666666</v>
       </c>
       <c r="B69">
-        <v>2196.28</v>
+        <v>248.465</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46262.70833333334</v>
+        <v>46269.70833333334</v>
       </c>
       <c r="B70">
-        <v>2121.071</v>
+        <v>229.332</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46262.71875</v>
+        <v>46269.71875</v>
       </c>
       <c r="B71">
-        <v>2040.969</v>
+        <v>229.944</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46262.72916666666</v>
+        <v>46269.72916666666</v>
       </c>
       <c r="B72">
-        <v>1957.849</v>
+        <v>232.055</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46262.73958333334</v>
+        <v>46269.73958333334</v>
       </c>
       <c r="B73">
-        <v>1874.196</v>
+        <v>233.663</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46262.75</v>
+        <v>46269.75</v>
       </c>
       <c r="B74">
-        <v>1772.885</v>
+        <v>217.665</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46262.76041666666</v>
+        <v>46269.76041666666</v>
       </c>
       <c r="B75">
-        <v>1698.273</v>
+        <v>222.889</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46262.77083333334</v>
+        <v>46269.77083333334</v>
       </c>
       <c r="B76">
-        <v>1625.255</v>
+        <v>230.394</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46262.78125</v>
+        <v>46269.78125</v>
       </c>
       <c r="B77">
-        <v>1553.008</v>
+        <v>241.271</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46262.79166666666</v>
+        <v>46269.79166666666</v>
       </c>
       <c r="B78">
-        <v>1478.008</v>
+        <v>265.716</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46262.80208333334</v>
+        <v>46269.80208333334</v>
       </c>
       <c r="B79">
-        <v>1439.24</v>
+        <v>281.786</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46262.8125</v>
+        <v>46269.8125</v>
       </c>
       <c r="B80">
-        <v>1403.196</v>
+        <v>299.201</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46262.82291666666</v>
+        <v>46269.82291666666</v>
       </c>
       <c r="B81">
-        <v>1369.622</v>
+        <v>317.365</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46262.83333333334</v>
+        <v>46269.83333333334</v>
       </c>
       <c r="B82">
-        <v>1354.858</v>
+        <v>351.929</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46262.84375</v>
+        <v>46269.84375</v>
       </c>
       <c r="B83">
-        <v>1353.929</v>
+        <v>363.251</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46262.85416666666</v>
+        <v>46269.85416666666</v>
       </c>
       <c r="B84">
-        <v>1352.827</v>
+        <v>375.35</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46262.86458333334</v>
+        <v>46269.86458333334</v>
       </c>
       <c r="B85">
-        <v>1354.014</v>
+        <v>388.224</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46262.875</v>
+        <v>46269.875</v>
       </c>
       <c r="B86">
-        <v>1355.778</v>
+        <v>401.236</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46262.88541666666</v>
+        <v>46269.88541666666</v>
       </c>
       <c r="B87">
-        <v>1364.601</v>
+        <v>411.585</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46262.89583333334</v>
+        <v>46269.89583333334</v>
       </c>
       <c r="B88">
-        <v>1373.596</v>
+        <v>422.299</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46262.90625</v>
+        <v>46269.90625</v>
       </c>
       <c r="B89">
-        <v>1381.877</v>
+        <v>431.896</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46262.91666666666</v>
+        <v>46269.91666666666</v>
       </c>
       <c r="B90">
-        <v>1379.203</v>
+        <v>476.749</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46262.92708333334</v>
+        <v>46269.92708333334</v>
       </c>
       <c r="B91">
-        <v>1376.77</v>
+        <v>484.721</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46262.9375</v>
+        <v>46269.9375</v>
       </c>
       <c r="B92">
-        <v>1375.357</v>
+        <v>491.889</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46262.94791666666</v>
+        <v>46269.94791666666</v>
       </c>
       <c r="B93">
-        <v>1375.219</v>
+        <v>500.485</v>
       </c>
     </row>
   </sheetData>
